--- a/research/traditional_assets/database/data/japan/japan_tobacco.xlsx
+++ b/research/traditional_assets/database/data/japan/japan_tobacco.xlsx
@@ -647,10 +647,10 @@
         <v>0.1284052624357821</v>
       </c>
       <c r="X2">
-        <v>0.07863896617975742</v>
+        <v>0.0786244675205251</v>
       </c>
       <c r="Y2">
-        <v>0.0497662962560247</v>
+        <v>0.04978079491525703</v>
       </c>
       <c r="Z2">
         <v>2.366129849529643</v>
@@ -659,10 +659,10 @@
         <v>0.4044611001354652</v>
       </c>
       <c r="AB2">
-        <v>0.07333356271854374</v>
+        <v>0.0733211614351143</v>
       </c>
       <c r="AC2">
-        <v>0.3311275374169214</v>
+        <v>0.3311399387003509</v>
       </c>
       <c r="AD2">
         <v>7793.6</v>
@@ -781,10 +781,10 @@
         <v>0.1284052624357821</v>
       </c>
       <c r="X3">
-        <v>0.07863896617975742</v>
+        <v>0.0786244675205251</v>
       </c>
       <c r="Y3">
-        <v>0.0497662962560247</v>
+        <v>0.04978079491525703</v>
       </c>
       <c r="Z3">
         <v>2.366129849529643</v>
@@ -793,10 +793,10 @@
         <v>0.4044611001354652</v>
       </c>
       <c r="AB3">
-        <v>0.07333356271854374</v>
+        <v>0.0733211614351143</v>
       </c>
       <c r="AC3">
-        <v>0.3311275374169214</v>
+        <v>0.3311399387003509</v>
       </c>
       <c r="AD3">
         <v>7793.6</v>
@@ -1133,49 +1133,49 @@
         <v>5.98255093999775</v>
       </c>
       <c r="F2">
-        <v>3.040514225978</v>
+        <v>3.04561321906847</v>
       </c>
       <c r="G2">
         <v>1.35682451253482</v>
       </c>
       <c r="H2">
-        <v>4.68970229805014</v>
+        <v>4.87729038997214</v>
       </c>
       <c r="I2">
         <v>0.144659983331879</v>
       </c>
       <c r="J2">
-        <v>0.5</v>
+        <v>0.52</v>
       </c>
       <c r="K2">
         <v>46081.7</v>
       </c>
       <c r="L2">
-        <v>29186.4292716741</v>
+        <v>29002.526972522</v>
       </c>
       <c r="M2">
         <v>48327.2</v>
       </c>
       <c r="N2">
-        <v>50575.9792716741</v>
+        <v>51469.582972522</v>
       </c>
       <c r="O2">
         <v>7793.6</v>
       </c>
       <c r="P2">
-        <v>26937.65</v>
+        <v>28015.156</v>
       </c>
       <c r="Q2">
-        <v>0.0733335627185437</v>
+        <v>0.0733211614351143</v>
       </c>
       <c r="R2">
-        <v>0.0702990124951301</v>
+        <v>0.0691544325218116</v>
       </c>
       <c r="S2">
         <v>0.0419639760476072</v>
       </c>
       <c r="T2">
-        <v>0.0450166960476072</v>
+        <v>0.0432128160476072</v>
       </c>
       <c r="U2" t="inlineStr">
         <is>
@@ -1188,16 +1188,16 @@
         </is>
       </c>
       <c r="W2">
-        <v>0.07863896617975739</v>
+        <v>0.0786244675205251</v>
       </c>
       <c r="X2">
-        <v>0.095581328942653</v>
+        <v>0.09725785036886619</v>
       </c>
       <c r="Y2">
         <v>0.622668019473203</v>
       </c>
       <c r="Z2">
-        <v>0.943916484148429</v>
+        <v>0.976136406645289</v>
       </c>
       <c r="AA2">
         <v>7793.6</v>
@@ -1230,7 +1230,7 @@
         <v>46081.7</v>
       </c>
       <c r="AK2">
-        <v>0.05273912446561848</v>
+        <v>0.05271583973157258</v>
       </c>
       <c r="AL2" t="inlineStr">
         <is>
@@ -1418,13 +1418,13 @@
         <v>0</v>
       </c>
       <c r="B2">
-        <v>0.07519032290863917</v>
+        <v>0.07517734685226005</v>
       </c>
       <c r="C2">
-        <v>52595.33492599686</v>
+        <v>52595.70626413845</v>
       </c>
       <c r="D2">
-        <v>47047.23492599686</v>
+        <v>47047.60626413846</v>
       </c>
       <c r="E2">
         <v>-7793.6</v>
@@ -1469,19 +1469,19 @@
         <v>0</v>
       </c>
       <c r="S2">
-        <v>0.07519032290863917</v>
+        <v>0.07517734685226005</v>
       </c>
       <c r="T2">
         <v>0.5572774141861078</v>
       </c>
       <c r="U2">
-        <v>0.05868425489709894</v>
+        <v>0.05728425489709894</v>
       </c>
       <c r="V2">
         <v>0.3062</v>
       </c>
       <c r="W2">
-        <v>0.04071513604760724</v>
+        <v>0.03974381604760725</v>
       </c>
       <c r="X2" t="inlineStr">
         <is>
@@ -1500,13 +1500,13 @@
         <v>0.01</v>
       </c>
       <c r="B3">
-        <v>0.07504948110036898</v>
+        <v>0.07502683157667452</v>
       </c>
       <c r="C3">
-        <v>52151.2905977859</v>
+        <v>52158.18359924489</v>
       </c>
       <c r="D3">
-        <v>47141.9435977859</v>
+        <v>47148.83659924489</v>
       </c>
       <c r="E3">
         <v>-7254.847000000001</v>
@@ -1533,37 +1533,37 @@
         <v>5314.3</v>
       </c>
       <c r="M3">
-        <v>31.61631837857674</v>
+        <v>30.86206417857674</v>
       </c>
       <c r="N3">
-        <v>5282.683681621424</v>
+        <v>5283.437935821424</v>
       </c>
       <c r="O3">
-        <v>1617.55774331248</v>
+        <v>1617.78869594852</v>
       </c>
       <c r="P3">
-        <v>3665.125938308944</v>
+        <v>3665.649239872903</v>
       </c>
       <c r="Q3">
-        <v>4094.825938308943</v>
+        <v>4095.349239872903</v>
       </c>
       <c r="R3">
         <v>0.0101010101010101</v>
       </c>
       <c r="S3">
-        <v>0.07539629266655849</v>
+        <v>0.07538322567292771</v>
       </c>
       <c r="T3">
         <v>0.5611828593372423</v>
       </c>
       <c r="U3">
-        <v>0.05868425489709894</v>
+        <v>0.05728425489709894</v>
       </c>
       <c r="V3">
         <v>0.3062</v>
       </c>
       <c r="W3">
-        <v>0.04071513604760724</v>
+        <v>0.03974381604760725</v>
       </c>
       <c r="X3" t="inlineStr">
         <is>
@@ -1571,7 +1571,7 @@
         </is>
       </c>
       <c r="Y3">
-        <v>168.0872496400775</v>
+        <v>172.1952222395086</v>
       </c>
       <c r="Z3">
         <v>0</v>
@@ -1582,13 +1582,13 @@
         <v>0.02</v>
       </c>
       <c r="B4">
-        <v>0.0749086392920988</v>
+        <v>0.07487631630108894</v>
       </c>
       <c r="C4">
-        <v>51707.628346248</v>
+        <v>51721.09749971099</v>
       </c>
       <c r="D4">
-        <v>47237.034346248</v>
+        <v>47250.50349971099</v>
       </c>
       <c r="E4">
         <v>-6716.094000000001</v>
@@ -1615,37 +1615,37 @@
         <v>5314.3</v>
       </c>
       <c r="M4">
-        <v>63.23263675715349</v>
+        <v>61.72412835715349</v>
       </c>
       <c r="N4">
-        <v>5251.067363242847</v>
+        <v>5252.575871642846</v>
       </c>
       <c r="O4">
-        <v>1607.87682662496</v>
+        <v>1608.33873189704</v>
       </c>
       <c r="P4">
-        <v>3643.190536617887</v>
+        <v>3644.237139745806</v>
       </c>
       <c r="Q4">
-        <v>4072.890536617887</v>
+        <v>4073.937139745806</v>
       </c>
       <c r="R4">
         <v>0.02040816326530612</v>
       </c>
       <c r="S4">
-        <v>0.07560646588892515</v>
+        <v>0.07559330610218042</v>
       </c>
       <c r="T4">
         <v>0.5651680074506449</v>
       </c>
       <c r="U4">
-        <v>0.05868425489709894</v>
+        <v>0.05728425489709894</v>
       </c>
       <c r="V4">
         <v>0.3062</v>
       </c>
       <c r="W4">
-        <v>0.04071513604760724</v>
+        <v>0.03974381604760725</v>
       </c>
       <c r="X4" t="inlineStr">
         <is>
@@ -1653,7 +1653,7 @@
         </is>
       </c>
       <c r="Y4">
-        <v>84.04362482003877</v>
+        <v>86.09761111975429</v>
       </c>
       <c r="Z4">
         <v>0</v>
@@ -1664,13 +1664,13 @@
         <v>0.03</v>
       </c>
       <c r="B5">
-        <v>0.07476779748382863</v>
+        <v>0.0747258010255034</v>
       </c>
       <c r="C5">
-        <v>51264.35048813476</v>
+        <v>51284.45079573335</v>
       </c>
       <c r="D5">
-        <v>47332.50948813476</v>
+        <v>47352.60979573335</v>
       </c>
       <c r="E5">
         <v>-6177.341</v>
@@ -1697,37 +1697,37 @@
         <v>5314.3</v>
       </c>
       <c r="M5">
-        <v>94.84895513573022</v>
+        <v>92.58619253573023</v>
       </c>
       <c r="N5">
-        <v>5219.45104486427</v>
+        <v>5221.71380746427</v>
       </c>
       <c r="O5">
-        <v>1598.195909937439</v>
+        <v>1598.88876784556</v>
       </c>
       <c r="P5">
-        <v>3621.25513492683</v>
+        <v>3622.82503961871</v>
       </c>
       <c r="Q5">
-        <v>4050.95513492683</v>
+        <v>4052.52503961871</v>
       </c>
       <c r="R5">
         <v>0.03092783505154639</v>
       </c>
       <c r="S5">
-        <v>0.07582097257979423</v>
+        <v>0.07580771808667545</v>
       </c>
       <c r="T5">
         <v>0.5692353235663858</v>
       </c>
       <c r="U5">
-        <v>0.05868425489709894</v>
+        <v>0.05728425489709894</v>
       </c>
       <c r="V5">
         <v>0.3062</v>
       </c>
       <c r="W5">
-        <v>0.04071513604760724</v>
+        <v>0.03974381604760725</v>
       </c>
       <c r="X5" t="inlineStr">
         <is>
@@ -1735,7 +1735,7 @@
         </is>
       </c>
       <c r="Y5">
-        <v>56.02908321335918</v>
+        <v>57.39840741316954</v>
       </c>
       <c r="Z5">
         <v>0</v>
@@ -1746,13 +1746,13 @@
         <v>0.04</v>
       </c>
       <c r="B6">
-        <v>0.07462695567555844</v>
+        <v>0.07457528574991786</v>
       </c>
       <c r="C6">
-        <v>50821.45935896611</v>
+        <v>50848.2463420253</v>
       </c>
       <c r="D6">
-        <v>47428.37135896611</v>
+        <v>47455.15834202531</v>
       </c>
       <c r="E6">
         <v>-5638.588000000001</v>
@@ -1779,37 +1779,37 @@
         <v>5314.3</v>
       </c>
       <c r="M6">
-        <v>126.465273514307</v>
+        <v>123.448256714307</v>
       </c>
       <c r="N6">
-        <v>5187.834726485693</v>
+        <v>5190.851743285693</v>
       </c>
       <c r="O6">
-        <v>1588.514993249919</v>
+        <v>1589.438803794079</v>
       </c>
       <c r="P6">
-        <v>3599.319733235774</v>
+        <v>3601.412939491614</v>
       </c>
       <c r="Q6">
-        <v>4029.019733235773</v>
+        <v>4031.112939491614</v>
       </c>
       <c r="R6">
         <v>0.04166666666666667</v>
       </c>
       <c r="S6">
-        <v>0.07603994816005639</v>
+        <v>0.07602659698751413</v>
       </c>
       <c r="T6">
         <v>0.5733873754345378</v>
       </c>
       <c r="U6">
-        <v>0.05868425489709894</v>
+        <v>0.05728425489709894</v>
       </c>
       <c r="V6">
         <v>0.3062</v>
       </c>
       <c r="W6">
-        <v>0.04071513604760724</v>
+        <v>0.03974381604760725</v>
       </c>
       <c r="X6" t="inlineStr">
         <is>
@@ -1817,7 +1817,7 @@
         </is>
       </c>
       <c r="Y6">
-        <v>42.02181241001938</v>
+        <v>43.04880555987715</v>
       </c>
       <c r="Z6">
         <v>0</v>
@@ -1828,13 +1828,13 @@
         <v>0.05</v>
       </c>
       <c r="B7">
-        <v>0.07448611386728825</v>
+        <v>0.0744247704743323</v>
       </c>
       <c r="C7">
-        <v>50378.95731322072</v>
+        <v>50412.48701808297</v>
       </c>
       <c r="D7">
-        <v>47524.62231322072</v>
+        <v>47558.15201808298</v>
       </c>
       <c r="E7">
         <v>-5099.835000000001</v>
@@ -1861,37 +1861,37 @@
         <v>5314.3</v>
       </c>
       <c r="M7">
-        <v>158.0815918928837</v>
+        <v>154.3103208928837</v>
       </c>
       <c r="N7">
-        <v>5156.218408107116</v>
+        <v>5159.989679107117</v>
       </c>
       <c r="O7">
-        <v>1578.834076562399</v>
+        <v>1579.988839742599</v>
       </c>
       <c r="P7">
-        <v>3577.384331544717</v>
+        <v>3580.000839364518</v>
       </c>
       <c r="Q7">
-        <v>4007.084331544717</v>
+        <v>4009.700839364517</v>
       </c>
       <c r="R7">
         <v>0.05263157894736843</v>
       </c>
       <c r="S7">
-        <v>0.07626353375253463</v>
+        <v>0.07625008386521258</v>
       </c>
       <c r="T7">
         <v>0.5776268389209669</v>
       </c>
       <c r="U7">
-        <v>0.05868425489709894</v>
+        <v>0.05728425489709894</v>
       </c>
       <c r="V7">
         <v>0.3062</v>
       </c>
       <c r="W7">
-        <v>0.04071513604760724</v>
+        <v>0.03974381604760725</v>
       </c>
       <c r="X7" t="inlineStr">
         <is>
@@ -1899,7 +1899,7 @@
         </is>
       </c>
       <c r="Y7">
-        <v>33.6174499280155</v>
+        <v>34.43904444790172</v>
       </c>
       <c r="Z7">
         <v>0</v>
@@ -1910,13 +1910,13 @@
         <v>0.06</v>
       </c>
       <c r="B8">
-        <v>0.07434527205901807</v>
+        <v>0.07427425519874675</v>
       </c>
       <c r="C8">
-        <v>49936.84672452883</v>
+        <v>49977.17572845471</v>
       </c>
       <c r="D8">
-        <v>47621.26472452883</v>
+        <v>47661.5937284547</v>
       </c>
       <c r="E8">
         <v>-4561.082</v>
@@ -1943,37 +1943,37 @@
         <v>5314.3</v>
       </c>
       <c r="M8">
-        <v>189.6979102714604</v>
+        <v>185.1723850714605</v>
       </c>
       <c r="N8">
-        <v>5124.60208972854</v>
+        <v>5129.12761492854</v>
       </c>
       <c r="O8">
-        <v>1569.153159874879</v>
+        <v>1570.538875691119</v>
       </c>
       <c r="P8">
-        <v>3555.448929853661</v>
+        <v>3558.588739237421</v>
       </c>
       <c r="Q8">
-        <v>3985.148929853661</v>
+        <v>3988.28873923742</v>
       </c>
       <c r="R8">
         <v>0.06382978723404255</v>
       </c>
       <c r="S8">
-        <v>0.07649187648527835</v>
+        <v>0.07647832578286205</v>
       </c>
       <c r="T8">
         <v>0.5819565037581709</v>
       </c>
       <c r="U8">
-        <v>0.05868425489709894</v>
+        <v>0.05728425489709894</v>
       </c>
       <c r="V8">
         <v>0.3062</v>
       </c>
       <c r="W8">
-        <v>0.04071513604760724</v>
+        <v>0.03974381604760725</v>
       </c>
       <c r="X8" t="inlineStr">
         <is>
@@ -1981,7 +1981,7 @@
         </is>
       </c>
       <c r="Y8">
-        <v>28.01454160667959</v>
+        <v>28.69920370658477</v>
       </c>
       <c r="Z8">
         <v>0</v>
@@ -1992,13 +1992,13 @@
         <v>0.07000000000000001</v>
       </c>
       <c r="B9">
-        <v>0.07420443025074788</v>
+        <v>0.07412373992316121</v>
       </c>
       <c r="C9">
-        <v>49495.12998586737</v>
+        <v>49542.31540301419</v>
       </c>
       <c r="D9">
-        <v>47718.30098586737</v>
+        <v>47765.48640301419</v>
       </c>
       <c r="E9">
         <v>-4022.329</v>
@@ -2025,37 +2025,37 @@
         <v>5314.3</v>
       </c>
       <c r="M9">
-        <v>221.3142286500372</v>
+        <v>216.0344492500372</v>
       </c>
       <c r="N9">
-        <v>5092.985771349963</v>
+        <v>5098.265550749963</v>
       </c>
       <c r="O9">
-        <v>1559.472243187359</v>
+        <v>1561.088911639639</v>
       </c>
       <c r="P9">
-        <v>3533.513528162604</v>
+        <v>3537.176639110324</v>
       </c>
       <c r="Q9">
-        <v>3963.213528162604</v>
+        <v>3966.876639110324</v>
       </c>
       <c r="R9">
         <v>0.07526881720430109</v>
       </c>
       <c r="S9">
-        <v>0.07672512981442514</v>
+        <v>0.07671147612884807</v>
       </c>
       <c r="T9">
         <v>0.5863792796671428</v>
       </c>
       <c r="U9">
-        <v>0.05868425489709894</v>
+        <v>0.05728425489709894</v>
       </c>
       <c r="V9">
         <v>0.3062</v>
       </c>
       <c r="W9">
-        <v>0.04071513604760724</v>
+        <v>0.03974381604760725</v>
       </c>
       <c r="X9" t="inlineStr">
         <is>
@@ -2063,7 +2063,7 @@
         </is>
       </c>
       <c r="Y9">
-        <v>24.01246423429679</v>
+        <v>24.59931746278694</v>
       </c>
       <c r="Z9">
         <v>0</v>
@@ -2074,13 +2074,13 @@
         <v>0.08</v>
       </c>
       <c r="B10">
-        <v>0.07406358844247771</v>
+        <v>0.07397322464757566</v>
       </c>
       <c r="C10">
-        <v>49053.8095097574</v>
+        <v>49107.90899723707</v>
       </c>
       <c r="D10">
-        <v>47815.7335097574</v>
+        <v>47869.83299723707</v>
       </c>
       <c r="E10">
         <v>-3483.576000000001</v>
@@ -2107,37 +2107,37 @@
         <v>5314.3</v>
       </c>
       <c r="M10">
-        <v>252.9305470286139</v>
+        <v>246.896513428614</v>
       </c>
       <c r="N10">
-        <v>5061.369452971387</v>
+        <v>5067.403486571387</v>
       </c>
       <c r="O10">
-        <v>1549.791326499839</v>
+        <v>1551.638947588159</v>
       </c>
       <c r="P10">
-        <v>3511.578126471548</v>
+        <v>3515.764538983228</v>
       </c>
       <c r="Q10">
-        <v>3941.278126471548</v>
+        <v>3945.464538983228</v>
       </c>
       <c r="R10">
         <v>0.08695652173913043</v>
       </c>
       <c r="S10">
-        <v>0.07696345386811862</v>
+        <v>0.07694969496061639</v>
       </c>
       <c r="T10">
         <v>0.5908982028784835</v>
       </c>
       <c r="U10">
-        <v>0.05868425489709894</v>
+        <v>0.05728425489709894</v>
       </c>
       <c r="V10">
         <v>0.3062</v>
       </c>
       <c r="W10">
-        <v>0.04071513604760724</v>
+        <v>0.03974381604760725</v>
       </c>
       <c r="X10" t="inlineStr">
         <is>
@@ -2145,7 +2145,7 @@
         </is>
       </c>
       <c r="Y10">
-        <v>21.01090620500969</v>
+        <v>21.52440277993858</v>
       </c>
       <c r="Z10">
         <v>0</v>
@@ -2156,13 +2156,13 @@
         <v>0.09</v>
       </c>
       <c r="B11">
-        <v>0.07392274663420753</v>
+        <v>0.07382270937199012</v>
       </c>
       <c r="C11">
-        <v>48612.88772846414</v>
+        <v>48673.95949248118</v>
       </c>
       <c r="D11">
-        <v>47913.56472846415</v>
+        <v>47974.63649248119</v>
       </c>
       <c r="E11">
         <v>-2944.823000000001</v>
@@ -2189,37 +2189,37 @@
         <v>5314.3</v>
       </c>
       <c r="M11">
-        <v>284.5468654071907</v>
+        <v>277.7585776071907</v>
       </c>
       <c r="N11">
-        <v>5029.753134592809</v>
+        <v>5036.541422392809</v>
       </c>
       <c r="O11">
-        <v>1540.110409812318</v>
+        <v>1542.188983536678</v>
       </c>
       <c r="P11">
-        <v>3489.642724780491</v>
+        <v>3494.352438856131</v>
       </c>
       <c r="Q11">
-        <v>3919.342724780491</v>
+        <v>3924.052438856131</v>
       </c>
       <c r="R11">
         <v>0.0989010989010989</v>
       </c>
       <c r="S11">
-        <v>0.07720701581310206</v>
+        <v>0.07719314937110491</v>
       </c>
       <c r="T11">
         <v>0.5955164430834802</v>
       </c>
       <c r="U11">
-        <v>0.05868425489709894</v>
+        <v>0.05728425489709894</v>
       </c>
       <c r="V11">
         <v>0.3062</v>
       </c>
       <c r="W11">
-        <v>0.04071513604760724</v>
+        <v>0.03974381604760725</v>
       </c>
       <c r="X11" t="inlineStr">
         <is>
@@ -2227,7 +2227,7 @@
         </is>
       </c>
       <c r="Y11">
-        <v>18.67636107111973</v>
+        <v>19.13280247105651</v>
       </c>
       <c r="Z11">
         <v>0</v>
@@ -2238,13 +2238,13 @@
         <v>0.1</v>
       </c>
       <c r="B12">
-        <v>0.07378190482593736</v>
+        <v>0.07367219409640459</v>
       </c>
       <c r="C12">
-        <v>48172.36709419933</v>
+        <v>48240.46989627051</v>
       </c>
       <c r="D12">
-        <v>48011.79709419933</v>
+        <v>48079.89989627051</v>
       </c>
       <c r="E12">
         <v>-2406.070000000001</v>
@@ -2271,37 +2271,37 @@
         <v>5314.3</v>
       </c>
       <c r="M12">
-        <v>316.1631837857674</v>
+        <v>308.6206417857675</v>
       </c>
       <c r="N12">
-        <v>4998.136816214233</v>
+        <v>5005.679358214233</v>
       </c>
       <c r="O12">
-        <v>1530.429493124798</v>
+        <v>1532.739019485198</v>
       </c>
       <c r="P12">
-        <v>3467.707323089434</v>
+        <v>3472.940338729034</v>
       </c>
       <c r="Q12">
-        <v>3897.407323089434</v>
+        <v>3902.640338729034</v>
       </c>
       <c r="R12">
         <v>0.1111111111111111</v>
       </c>
       <c r="S12">
-        <v>0.07745599024575181</v>
+        <v>0.07744201387960428</v>
       </c>
       <c r="T12">
         <v>0.600237310848588</v>
       </c>
       <c r="U12">
-        <v>0.05868425489709894</v>
+        <v>0.05728425489709894</v>
       </c>
       <c r="V12">
         <v>0.3062</v>
       </c>
       <c r="W12">
-        <v>0.04071513604760724</v>
+        <v>0.03974381604760725</v>
       </c>
       <c r="X12" t="inlineStr">
         <is>
@@ -2309,7 +2309,7 @@
         </is>
       </c>
       <c r="Y12">
-        <v>16.80872496400775</v>
+        <v>17.21952222395086</v>
       </c>
       <c r="Z12">
         <v>0</v>
@@ -2320,13 +2320,13 @@
         <v>0.11</v>
       </c>
       <c r="B13">
-        <v>0.07364106301766718</v>
+        <v>0.07352167882081904</v>
       </c>
       <c r="C13">
-        <v>47732.25007932607</v>
+        <v>47807.4432425829</v>
       </c>
       <c r="D13">
-        <v>48110.43307932607</v>
+        <v>48185.6262425829</v>
       </c>
       <c r="E13">
         <v>-1867.317000000001</v>
@@ -2353,37 +2353,37 @@
         <v>5314.3</v>
       </c>
       <c r="M13">
-        <v>347.7795021643442</v>
+        <v>339.4827059643442</v>
       </c>
       <c r="N13">
-        <v>4966.520497835656</v>
+        <v>4974.817294035656</v>
       </c>
       <c r="O13">
-        <v>1520.748576437278</v>
+        <v>1523.289055433718</v>
       </c>
       <c r="P13">
-        <v>3445.771921398378</v>
+        <v>3451.528238601938</v>
       </c>
       <c r="Q13">
-        <v>3875.471921398378</v>
+        <v>3881.228238601938</v>
       </c>
       <c r="R13">
         <v>0.1235955056179775</v>
       </c>
       <c r="S13">
-        <v>0.07771055960947233</v>
+        <v>0.0776964708489688</v>
       </c>
       <c r="T13">
         <v>0.6050642655297654</v>
       </c>
       <c r="U13">
-        <v>0.05868425489709894</v>
+        <v>0.05728425489709894</v>
       </c>
       <c r="V13">
         <v>0.3062</v>
       </c>
       <c r="W13">
-        <v>0.04071513604760724</v>
+        <v>0.03974381604760725</v>
       </c>
       <c r="X13" t="inlineStr">
         <is>
@@ -2391,7 +2391,7 @@
         </is>
       </c>
       <c r="Y13">
-        <v>15.28065905818887</v>
+        <v>15.6541111126826</v>
       </c>
       <c r="Z13">
         <v>0</v>
@@ -2402,13 +2402,13 @@
         <v>0.12</v>
       </c>
       <c r="B14">
-        <v>0.073500221209397</v>
+        <v>0.07337116354523347</v>
       </c>
       <c r="C14">
-        <v>47292.53917656634</v>
+        <v>47374.88259214153</v>
       </c>
       <c r="D14">
-        <v>48209.47517656635</v>
+        <v>48291.81859214154</v>
       </c>
       <c r="E14">
         <v>-1328.564000000001</v>
@@ -2435,37 +2435,37 @@
         <v>5314.3</v>
       </c>
       <c r="M14">
-        <v>379.3958205429209</v>
+        <v>370.3447701429209</v>
       </c>
       <c r="N14">
-        <v>4934.904179457079</v>
+        <v>4943.955229857079</v>
       </c>
       <c r="O14">
-        <v>1511.067659749758</v>
+        <v>1513.839091382238</v>
       </c>
       <c r="P14">
-        <v>3423.836519707322</v>
+        <v>3430.116138474841</v>
       </c>
       <c r="Q14">
-        <v>3853.536519707322</v>
+        <v>3859.816138474841</v>
       </c>
       <c r="R14">
         <v>0.1363636363636364</v>
       </c>
       <c r="S14">
-        <v>0.07797091464055014</v>
+        <v>0.07795671093127342</v>
       </c>
       <c r="T14">
         <v>0.6100009237264243</v>
       </c>
       <c r="U14">
-        <v>0.05868425489709894</v>
+        <v>0.05728425489709894</v>
       </c>
       <c r="V14">
         <v>0.3062</v>
       </c>
       <c r="W14">
-        <v>0.04071513604760724</v>
+        <v>0.03974381604760725</v>
       </c>
       <c r="X14" t="inlineStr">
         <is>
@@ -2473,7 +2473,7 @@
         </is>
       </c>
       <c r="Y14">
-        <v>14.00727080333979</v>
+        <v>14.34960185329238</v>
       </c>
       <c r="Z14">
         <v>0</v>
@@ -2484,13 +2484,13 @@
         <v>0.13</v>
       </c>
       <c r="B15">
-        <v>0.0733593794011268</v>
+        <v>0.07322064826964793</v>
       </c>
       <c r="C15">
-        <v>46853.23689921096</v>
+        <v>46942.79103271024</v>
       </c>
       <c r="D15">
-        <v>48308.92589921095</v>
+        <v>48398.48003271024</v>
       </c>
       <c r="E15">
         <v>-789.8110000000006</v>
@@ -2517,37 +2517,37 @@
         <v>5314.3</v>
       </c>
       <c r="M15">
-        <v>411.0121389214977</v>
+        <v>401.2068343214977</v>
       </c>
       <c r="N15">
-        <v>4903.287861078503</v>
+        <v>4913.093165678502</v>
       </c>
       <c r="O15">
-        <v>1501.386743062238</v>
+        <v>1504.389127330758</v>
       </c>
       <c r="P15">
-        <v>3401.901118016265</v>
+        <v>3408.704038347745</v>
       </c>
       <c r="Q15">
-        <v>3831.601118016265</v>
+        <v>3838.404038347745</v>
       </c>
       <c r="R15">
         <v>0.1494252873563219</v>
       </c>
       <c r="S15">
-        <v>0.07823725484475617</v>
+        <v>0.07822293354420573</v>
       </c>
       <c r="T15">
         <v>0.6150510683184087</v>
       </c>
       <c r="U15">
-        <v>0.05868425489709894</v>
+        <v>0.05728425489709894</v>
       </c>
       <c r="V15">
         <v>0.3062</v>
       </c>
       <c r="W15">
-        <v>0.04071513604760724</v>
+        <v>0.03974381604760725</v>
       </c>
       <c r="X15" t="inlineStr">
         <is>
@@ -2555,7 +2555,7 @@
         </is>
       </c>
       <c r="Y15">
-        <v>12.92978843385212</v>
+        <v>13.24578632611605</v>
       </c>
       <c r="Z15">
         <v>0</v>
@@ -2566,13 +2566,13 @@
         <v>0.14</v>
       </c>
       <c r="B16">
-        <v>0.07321853759285661</v>
+        <v>0.07307013299406238</v>
       </c>
       <c r="C16">
-        <v>46414.34578133205</v>
+        <v>46511.17167939289</v>
       </c>
       <c r="D16">
-        <v>48408.78778133205</v>
+        <v>48505.61367939289</v>
       </c>
       <c r="E16">
         <v>-251.058</v>
@@ -2599,37 +2599,37 @@
         <v>5314.3</v>
       </c>
       <c r="M16">
-        <v>442.6284573000744</v>
+        <v>432.0688985000745</v>
       </c>
       <c r="N16">
-        <v>4871.671542699925</v>
+        <v>4882.231101499926</v>
       </c>
       <c r="O16">
-        <v>1491.705826374717</v>
+        <v>1494.939163279277</v>
       </c>
       <c r="P16">
-        <v>3379.965716325208</v>
+        <v>3387.291938220648</v>
       </c>
       <c r="Q16">
-        <v>3809.665716325208</v>
+        <v>3816.991938220648</v>
       </c>
       <c r="R16">
         <v>0.1627906976744186</v>
       </c>
       <c r="S16">
-        <v>0.07850978900719954</v>
+        <v>0.07849534738069461</v>
       </c>
       <c r="T16">
         <v>0.6202186581334624</v>
       </c>
       <c r="U16">
-        <v>0.05868425489709894</v>
+        <v>0.05728425489709894</v>
       </c>
       <c r="V16">
         <v>0.3062</v>
       </c>
       <c r="W16">
-        <v>0.04071513604760724</v>
+        <v>0.03974381604760725</v>
       </c>
       <c r="X16" t="inlineStr">
         <is>
@@ -2637,7 +2637,7 @@
         </is>
       </c>
       <c r="Y16">
-        <v>12.00623211714839</v>
+        <v>12.29965873139347</v>
       </c>
       <c r="Z16">
         <v>0</v>
@@ -2648,13 +2648,13 @@
         <v>0.15</v>
       </c>
       <c r="B17">
-        <v>0.07307769578458645</v>
+        <v>0.07291961771847683</v>
       </c>
       <c r="C17">
-        <v>45975.86837799849</v>
+        <v>46080.0276749366</v>
       </c>
       <c r="D17">
-        <v>48509.06337799849</v>
+        <v>48613.2226749366</v>
       </c>
       <c r="E17">
         <v>287.6949999999988</v>
@@ -2681,37 +2681,37 @@
         <v>5314.3</v>
       </c>
       <c r="M17">
-        <v>474.2447756786511</v>
+        <v>462.9309626786512</v>
       </c>
       <c r="N17">
-        <v>4840.055224321349</v>
+        <v>4851.369037321349</v>
       </c>
       <c r="O17">
-        <v>1482.024909687197</v>
+        <v>1485.489199227797</v>
       </c>
       <c r="P17">
-        <v>3358.030314634152</v>
+        <v>3365.879838093552</v>
       </c>
       <c r="Q17">
-        <v>3787.730314634151</v>
+        <v>3795.579838093552</v>
       </c>
       <c r="R17">
         <v>0.1764705882352941</v>
       </c>
       <c r="S17">
-        <v>0.07878873573817102</v>
+        <v>0.07877417095451264</v>
       </c>
       <c r="T17">
         <v>0.6255078382971057</v>
       </c>
       <c r="U17">
-        <v>0.05868425489709894</v>
+        <v>0.05728425489709894</v>
       </c>
       <c r="V17">
         <v>0.3062</v>
       </c>
       <c r="W17">
-        <v>0.04071513604760724</v>
+        <v>0.03974381604760725</v>
       </c>
       <c r="X17" t="inlineStr">
         <is>
@@ -2719,7 +2719,7 @@
         </is>
       </c>
       <c r="Y17">
-        <v>11.20581664267183</v>
+        <v>11.47968148263391</v>
       </c>
       <c r="Z17">
         <v>0</v>
@@ -2730,13 +2730,13 @@
         <v>0.16</v>
       </c>
       <c r="B18">
-        <v>0.07293685397631626</v>
+        <v>0.07276910244289128</v>
       </c>
       <c r="C18">
-        <v>45537.8072654937</v>
+        <v>45649.36219003901</v>
       </c>
       <c r="D18">
-        <v>48609.7552654937</v>
+        <v>48721.31019003901</v>
       </c>
       <c r="E18">
         <v>826.4479999999985</v>
@@ -2763,37 +2763,37 @@
         <v>5314.3</v>
       </c>
       <c r="M18">
-        <v>505.8610940572279</v>
+        <v>493.7930268572279</v>
       </c>
       <c r="N18">
-        <v>4808.438905942772</v>
+        <v>4820.506973142772</v>
       </c>
       <c r="O18">
-        <v>1472.343992999677</v>
+        <v>1476.039235176317</v>
       </c>
       <c r="P18">
-        <v>3336.094912943095</v>
+        <v>3344.467737966455</v>
       </c>
       <c r="Q18">
-        <v>3765.794912943095</v>
+        <v>3774.167737966455</v>
       </c>
       <c r="R18">
         <v>0.1904761904761905</v>
       </c>
       <c r="S18">
-        <v>0.07907432405797513</v>
+        <v>0.07905963318485015</v>
       </c>
       <c r="T18">
         <v>0.6309229513217881</v>
       </c>
       <c r="U18">
-        <v>0.05868425489709894</v>
+        <v>0.05728425489709894</v>
       </c>
       <c r="V18">
         <v>0.3062</v>
       </c>
       <c r="W18">
-        <v>0.04071513604760724</v>
+        <v>0.03974381604760725</v>
       </c>
       <c r="X18" t="inlineStr">
         <is>
@@ -2801,7 +2801,7 @@
         </is>
       </c>
       <c r="Y18">
-        <v>10.50545310250484</v>
+        <v>10.76220138996929</v>
       </c>
       <c r="Z18">
         <v>0</v>
@@ -2812,13 +2812,13 @@
         <v>0.17</v>
       </c>
       <c r="B19">
-        <v>0.07279601216804608</v>
+        <v>0.07261858716730574</v>
       </c>
       <c r="C19">
-        <v>45100.16504153627</v>
+        <v>45219.17842365977</v>
       </c>
       <c r="D19">
-        <v>48710.86604153627</v>
+        <v>48829.87942365978</v>
       </c>
       <c r="E19">
         <v>1365.200999999999</v>
@@ -2845,37 +2845,37 @@
         <v>5314.3</v>
       </c>
       <c r="M19">
-        <v>537.4774124358047</v>
+        <v>524.6550910358046</v>
       </c>
       <c r="N19">
-        <v>4776.822587564196</v>
+        <v>4789.644908964196</v>
       </c>
       <c r="O19">
-        <v>1462.663076312157</v>
+        <v>1466.589271124837</v>
       </c>
       <c r="P19">
-        <v>3314.159511252039</v>
+        <v>3323.055637839358</v>
       </c>
       <c r="Q19">
-        <v>3743.859511252039</v>
+        <v>3752.755637839358</v>
       </c>
       <c r="R19">
         <v>0.2048192771084338</v>
       </c>
       <c r="S19">
-        <v>0.07936679402403959</v>
+        <v>0.07935197402314759</v>
       </c>
       <c r="T19">
         <v>0.6364685489976676</v>
       </c>
       <c r="U19">
-        <v>0.05868425489709894</v>
+        <v>0.05728425489709894</v>
       </c>
       <c r="V19">
         <v>0.3062</v>
       </c>
       <c r="W19">
-        <v>0.04071513604760724</v>
+        <v>0.03974381604760725</v>
       </c>
       <c r="X19" t="inlineStr">
         <is>
@@ -2883,7 +2883,7 @@
         </is>
       </c>
       <c r="Y19">
-        <v>9.887485272945735</v>
+        <v>10.1291307199711</v>
       </c>
       <c r="Z19">
         <v>0</v>
@@ -2894,13 +2894,13 @@
         <v>0.18</v>
       </c>
       <c r="B20">
-        <v>0.07265517035977591</v>
+        <v>0.07246807189172018</v>
       </c>
       <c r="C20">
-        <v>44662.94432550346</v>
+        <v>44789.47960333614</v>
       </c>
       <c r="D20">
-        <v>48812.39832550345</v>
+        <v>48938.93360333614</v>
       </c>
       <c r="E20">
         <v>1903.953999999998</v>
@@ -2927,37 +2927,37 @@
         <v>5314.3</v>
       </c>
       <c r="M20">
-        <v>569.0937308143814</v>
+        <v>555.5171552143813</v>
       </c>
       <c r="N20">
-        <v>4745.206269185619</v>
+        <v>4758.782844785619</v>
       </c>
       <c r="O20">
-        <v>1452.982159624637</v>
+        <v>1457.139307073357</v>
       </c>
       <c r="P20">
-        <v>3292.224109560982</v>
+        <v>3301.643537712263</v>
       </c>
       <c r="Q20">
-        <v>3721.924109560982</v>
+        <v>3731.343537712262</v>
       </c>
       <c r="R20">
         <v>0.2195121951219512</v>
       </c>
       <c r="S20">
-        <v>0.07966639740391049</v>
+        <v>0.07965144512579375</v>
       </c>
       <c r="T20">
         <v>0.6421494051534465</v>
       </c>
       <c r="U20">
-        <v>0.05868425489709894</v>
+        <v>0.05728425489709894</v>
       </c>
       <c r="V20">
         <v>0.3062</v>
       </c>
       <c r="W20">
-        <v>0.04071513604760724</v>
+        <v>0.03974381604760725</v>
       </c>
       <c r="X20" t="inlineStr">
         <is>
@@ -2965,7 +2965,7 @@
         </is>
       </c>
       <c r="Y20">
-        <v>9.338180535559863</v>
+        <v>9.566401235528257</v>
       </c>
       <c r="Z20">
         <v>0</v>
@@ -2976,13 +2976,13 @@
         <v>0.19</v>
       </c>
       <c r="B21">
-        <v>0.07251432855150573</v>
+        <v>0.07231755661613465</v>
       </c>
       <c r="C21">
-        <v>44226.14775865725</v>
+        <v>44360.26898550271</v>
       </c>
       <c r="D21">
-        <v>48914.35475865725</v>
+        <v>49048.47598550272</v>
       </c>
       <c r="E21">
         <v>2442.706999999999</v>
@@ -3009,37 +3009,37 @@
         <v>5314.3</v>
       </c>
       <c r="M21">
-        <v>600.7100491929581</v>
+        <v>586.3792193929581</v>
       </c>
       <c r="N21">
-        <v>4713.589950807042</v>
+        <v>4727.920780607042</v>
       </c>
       <c r="O21">
-        <v>1443.301242937117</v>
+        <v>1447.689343021876</v>
       </c>
       <c r="P21">
-        <v>3270.288707869926</v>
+        <v>3280.231437585166</v>
       </c>
       <c r="Q21">
-        <v>3699.988707869926</v>
+        <v>3709.931437585165</v>
       </c>
       <c r="R21">
         <v>0.2345679012345679</v>
       </c>
       <c r="S21">
-        <v>0.07997339839809919</v>
+        <v>0.07995831057665341</v>
       </c>
       <c r="T21">
         <v>0.6479705293624547</v>
       </c>
       <c r="U21">
-        <v>0.05868425489709894</v>
+        <v>0.05728425489709894</v>
       </c>
       <c r="V21">
         <v>0.3062</v>
       </c>
       <c r="W21">
-        <v>0.04071513604760724</v>
+        <v>0.03974381604760725</v>
       </c>
       <c r="X21" t="inlineStr">
         <is>
@@ -3047,7 +3047,7 @@
         </is>
       </c>
       <c r="Y21">
-        <v>8.846697349477765</v>
+        <v>9.062906433658346</v>
       </c>
       <c r="Z21">
         <v>0</v>
@@ -3058,13 +3058,13 @@
         <v>0.2</v>
       </c>
       <c r="B22">
-        <v>0.07252612274323554</v>
+        <v>0.0723751813405491</v>
       </c>
       <c r="C22">
-        <v>43678.84051827174</v>
+        <v>43779.51983622946</v>
       </c>
       <c r="D22">
-        <v>48905.80051827174</v>
+        <v>49006.47983622946</v>
       </c>
       <c r="E22">
         <v>2981.459999999999</v>
@@ -3091,37 +3091,37 @@
         <v>5314.3</v>
       </c>
       <c r="M22">
-        <v>644.1789335715349</v>
+        <v>633.4038735715349</v>
       </c>
       <c r="N22">
-        <v>4670.121066428465</v>
+        <v>4680.896126428465</v>
       </c>
       <c r="O22">
-        <v>1429.991070540396</v>
+        <v>1433.290393912396</v>
       </c>
       <c r="P22">
-        <v>3240.129995888069</v>
+        <v>3247.605732516069</v>
       </c>
       <c r="Q22">
-        <v>3669.829995888069</v>
+        <v>3677.305732516069</v>
       </c>
       <c r="R22">
         <v>0.25</v>
       </c>
       <c r="S22">
-        <v>0.08028807441714261</v>
+        <v>0.08027284766378456</v>
       </c>
       <c r="T22">
         <v>0.6539371816766881</v>
       </c>
       <c r="U22">
-        <v>0.05978425489709894</v>
+        <v>0.05878425489709894</v>
       </c>
       <c r="V22">
         <v>0.3062</v>
       </c>
       <c r="W22">
-        <v>0.04147831604760724</v>
+        <v>0.04078451604760724</v>
       </c>
       <c r="X22" t="inlineStr">
         <is>
@@ -3129,7 +3129,7 @@
         </is>
       </c>
       <c r="Y22">
-        <v>8.249726470463438</v>
+        <v>8.390065520178442</v>
       </c>
       <c r="Z22">
         <v>0</v>
@@ -3140,13 +3140,13 @@
         <v>0.21</v>
       </c>
       <c r="B23">
-        <v>0.07239291273496537</v>
+        <v>0.07223507306496355</v>
       </c>
       <c r="C23">
-        <v>43236.87804143976</v>
+        <v>43343.0013283704</v>
       </c>
       <c r="D23">
-        <v>49002.59104143977</v>
+        <v>49108.7143283704</v>
       </c>
       <c r="E23">
         <v>3520.212999999998</v>
@@ -3173,37 +3173,37 @@
         <v>5314.3</v>
       </c>
       <c r="M23">
-        <v>676.3878802501115</v>
+        <v>665.0740672501115</v>
       </c>
       <c r="N23">
-        <v>4637.912119749889</v>
+        <v>4649.225932749889</v>
       </c>
       <c r="O23">
-        <v>1420.128691067416</v>
+        <v>1423.592980608016</v>
       </c>
       <c r="P23">
-        <v>3217.783428682473</v>
+        <v>3225.632952141873</v>
       </c>
       <c r="Q23">
-        <v>3647.483428682473</v>
+        <v>3655.332952141873</v>
       </c>
       <c r="R23">
         <v>0.2658227848101266</v>
       </c>
       <c r="S23">
-        <v>0.08061071691768082</v>
+        <v>0.08059534771514687</v>
       </c>
       <c r="T23">
         <v>0.6600548884798895</v>
       </c>
       <c r="U23">
-        <v>0.05978425489709894</v>
+        <v>0.05878425489709894</v>
       </c>
       <c r="V23">
         <v>0.3062</v>
       </c>
       <c r="W23">
-        <v>0.04147831604760724</v>
+        <v>0.04078451604760724</v>
       </c>
       <c r="X23" t="inlineStr">
         <is>
@@ -3211,7 +3211,7 @@
         </is>
       </c>
       <c r="Y23">
-        <v>7.856882352822324</v>
+        <v>7.990538590646137</v>
       </c>
       <c r="Z23">
         <v>0</v>
@@ -3222,13 +3222,13 @@
         <v>0.22</v>
       </c>
       <c r="B24">
-        <v>0.0722597027266952</v>
+        <v>0.072094964789378</v>
       </c>
       <c r="C24">
-        <v>42795.29944477157</v>
+        <v>42906.91026362224</v>
       </c>
       <c r="D24">
-        <v>49099.76544477157</v>
+        <v>49211.37626362224</v>
       </c>
       <c r="E24">
         <v>4058.965999999999</v>
@@ -3255,37 +3255,37 @@
         <v>5314.3</v>
       </c>
       <c r="M24">
-        <v>708.5968269286883</v>
+        <v>696.7442609286883</v>
       </c>
       <c r="N24">
-        <v>4605.703173071312</v>
+        <v>4617.555739071312</v>
       </c>
       <c r="O24">
-        <v>1410.266311594436</v>
+        <v>1413.895567303636</v>
       </c>
       <c r="P24">
-        <v>3195.436861476875</v>
+        <v>3203.660171767676</v>
       </c>
       <c r="Q24">
-        <v>3625.136861476875</v>
+        <v>3633.360171767676</v>
       </c>
       <c r="R24">
         <v>0.282051282051282</v>
       </c>
       <c r="S24">
-        <v>0.0809416323028482</v>
+        <v>0.08092611699859539</v>
       </c>
       <c r="T24">
         <v>0.6663294595600959</v>
       </c>
       <c r="U24">
-        <v>0.05978425489709894</v>
+        <v>0.05878425489709894</v>
       </c>
       <c r="V24">
         <v>0.3062</v>
       </c>
       <c r="W24">
-        <v>0.04147831604760724</v>
+        <v>0.04078451604760724</v>
       </c>
       <c r="X24" t="inlineStr">
         <is>
@@ -3293,7 +3293,7 @@
         </is>
       </c>
       <c r="Y24">
-        <v>7.499751336784944</v>
+        <v>7.627332291071313</v>
       </c>
       <c r="Z24">
         <v>0</v>
@@ -3304,13 +3304,13 @@
         <v>0.23</v>
       </c>
       <c r="B25">
-        <v>0.072126492718425</v>
+        <v>0.07195485651379245</v>
       </c>
       <c r="C25">
-        <v>42354.10701656128</v>
+        <v>42471.24932831462</v>
       </c>
       <c r="D25">
-        <v>49197.32601656128</v>
+        <v>49314.46832831462</v>
       </c>
       <c r="E25">
         <v>4597.718999999999</v>
@@ -3337,37 +3337,37 @@
         <v>5314.3</v>
       </c>
       <c r="M25">
-        <v>740.8057736072651</v>
+        <v>728.414454607265</v>
       </c>
       <c r="N25">
-        <v>4573.494226392735</v>
+        <v>4585.885545392735</v>
       </c>
       <c r="O25">
-        <v>1400.403932121456</v>
+        <v>1404.198153999256</v>
       </c>
       <c r="P25">
-        <v>3173.090294271279</v>
+        <v>3181.68739139348</v>
       </c>
       <c r="Q25">
-        <v>3602.790294271279</v>
+        <v>3611.387391393479</v>
       </c>
       <c r="R25">
         <v>0.2987012987012987</v>
       </c>
       <c r="S25">
-        <v>0.08128114289282512</v>
+        <v>0.08126547769200362</v>
       </c>
       <c r="T25">
         <v>0.6727670065125155</v>
       </c>
       <c r="U25">
-        <v>0.05978425489709894</v>
+        <v>0.05878425489709894</v>
       </c>
       <c r="V25">
         <v>0.3062</v>
       </c>
       <c r="W25">
-        <v>0.04147831604760724</v>
+        <v>0.04078451604760724</v>
       </c>
       <c r="X25" t="inlineStr">
         <is>
@@ -3375,7 +3375,7 @@
         </is>
       </c>
       <c r="Y25">
-        <v>7.173675191707337</v>
+        <v>7.295709147981255</v>
       </c>
       <c r="Z25">
         <v>0</v>
@@ -3386,13 +3386,13 @@
         <v>0.24</v>
       </c>
       <c r="B26">
-        <v>0.07199328271015482</v>
+        <v>0.0718147482382069</v>
       </c>
       <c r="C26">
-        <v>41913.30306332646</v>
+        <v>42036.02123133464</v>
       </c>
       <c r="D26">
-        <v>49295.27506332646</v>
+        <v>49417.99323133464</v>
       </c>
       <c r="E26">
         <v>5136.471999999998</v>
@@ -3419,37 +3419,37 @@
         <v>5314.3</v>
       </c>
       <c r="M26">
-        <v>773.0147202858418</v>
+        <v>760.0846482858418</v>
       </c>
       <c r="N26">
-        <v>4541.285279714159</v>
+        <v>4554.215351714159</v>
       </c>
       <c r="O26">
-        <v>1390.541552648476</v>
+        <v>1394.500740694876</v>
       </c>
       <c r="P26">
-        <v>3150.743727065683</v>
+        <v>3159.714611019283</v>
       </c>
       <c r="Q26">
-        <v>3580.443727065683</v>
+        <v>3589.414611019283</v>
       </c>
       <c r="R26">
         <v>0.3157894736842105</v>
       </c>
       <c r="S26">
-        <v>0.08162958797201195</v>
+        <v>0.08161376892997521</v>
       </c>
       <c r="T26">
         <v>0.6793739625952619</v>
       </c>
       <c r="U26">
-        <v>0.05978425489709894</v>
+        <v>0.05878425489709894</v>
       </c>
       <c r="V26">
         <v>0.3062</v>
       </c>
       <c r="W26">
-        <v>0.04147831604760724</v>
+        <v>0.04078451604760724</v>
       </c>
       <c r="X26" t="inlineStr">
         <is>
@@ -3457,7 +3457,7 @@
         </is>
       </c>
       <c r="Y26">
-        <v>6.874772058719532</v>
+        <v>6.99172126681537</v>
       </c>
       <c r="Z26">
         <v>0</v>
@@ -3468,13 +3468,13 @@
         <v>0.25</v>
       </c>
       <c r="B27">
-        <v>0.07224166270188465</v>
+        <v>0.07167463996262136</v>
       </c>
       <c r="C27">
-        <v>41192.22997047981</v>
+        <v>41601.22870436406</v>
       </c>
       <c r="D27">
-        <v>49112.95497047981</v>
+        <v>49521.95370436406</v>
       </c>
       <c r="E27">
         <v>5675.224999999999</v>
@@ -3501,45 +3501,45 @@
         <v>5314.3</v>
       </c>
       <c r="M27">
-        <v>834.8550819644186</v>
+        <v>791.7548419644186</v>
       </c>
       <c r="N27">
-        <v>4479.444918035581</v>
+        <v>4522.545158035582</v>
       </c>
       <c r="O27">
-        <v>1371.606033902495</v>
+        <v>1384.803327390495</v>
       </c>
       <c r="P27">
-        <v>3107.838884133086</v>
+        <v>3137.741830645087</v>
       </c>
       <c r="Q27">
-        <v>3537.538884133086</v>
+        <v>3567.441830645087</v>
       </c>
       <c r="R27">
         <v>0.3333333333333333</v>
       </c>
       <c r="S27">
-        <v>0.08198732491997712</v>
+        <v>0.08197134793429273</v>
       </c>
       <c r="T27">
         <v>0.6861571041735484</v>
       </c>
       <c r="U27">
-        <v>0.06198425489709894</v>
+        <v>0.05878425489709894</v>
       </c>
       <c r="V27">
         <v>0.3062</v>
       </c>
       <c r="W27">
-        <v>0.04300467604760724</v>
+        <v>0.04078451604760724</v>
       </c>
       <c r="X27" t="inlineStr">
         <is>
-          <t>A1/A+</t>
+          <t>Aa2/AA</t>
         </is>
       </c>
       <c r="Y27">
-        <v>6.36553590533991</v>
+        <v>6.712052416142755</v>
       </c>
       <c r="Z27">
         <v>0</v>
@@ -3550,13 +3550,13 @@
         <v>0.26</v>
       </c>
       <c r="B28">
-        <v>0.07212371629361447</v>
+        <v>0.0718411912870358</v>
       </c>
       <c r="C28">
-        <v>40739.88554399832</v>
+        <v>40938.94340800585</v>
       </c>
       <c r="D28">
-        <v>49199.36354399833</v>
+        <v>49398.42140800585</v>
       </c>
       <c r="E28">
         <v>6213.977999999999</v>
@@ -3583,37 +3583,37 @@
         <v>5314.3</v>
       </c>
       <c r="M28">
-        <v>868.2492852429954</v>
+        <v>847.2379182429953</v>
       </c>
       <c r="N28">
-        <v>4446.050714757005</v>
+        <v>4467.062081757005</v>
       </c>
       <c r="O28">
-        <v>1361.380728858595</v>
+        <v>1367.814409433995</v>
       </c>
       <c r="P28">
-        <v>3084.66998589841</v>
+        <v>3099.24767232301</v>
       </c>
       <c r="Q28">
-        <v>3514.36998589841</v>
+        <v>3528.94767232301</v>
       </c>
       <c r="R28">
         <v>0.3513513513513514</v>
       </c>
       <c r="S28">
-        <v>0.08235473043410349</v>
+        <v>0.08233859123602422</v>
       </c>
       <c r="T28">
         <v>0.6931235739025992</v>
       </c>
       <c r="U28">
-        <v>0.06198425489709894</v>
+        <v>0.06048425489709894</v>
       </c>
       <c r="V28">
         <v>0.3062</v>
       </c>
       <c r="W28">
-        <v>0.04300467604760724</v>
+        <v>0.04196397604760724</v>
       </c>
       <c r="X28" t="inlineStr">
         <is>
@@ -3621,7 +3621,7 @@
         </is>
       </c>
       <c r="Y28">
-        <v>6.120707601288375</v>
+        <v>6.272500186276853</v>
       </c>
       <c r="Z28">
         <v>0</v>
@@ -3632,13 +3632,13 @@
         <v>0.27</v>
       </c>
       <c r="B29">
-        <v>0.07200576988534428</v>
+        <v>0.07171287761145026</v>
       </c>
       <c r="C29">
-        <v>40287.84570521988</v>
+        <v>40495.30696023503</v>
       </c>
       <c r="D29">
-        <v>49286.07670521988</v>
+        <v>49493.53796023503</v>
       </c>
       <c r="E29">
         <v>6752.731</v>
@@ -3665,37 +3665,37 @@
         <v>5314.3</v>
       </c>
       <c r="M29">
-        <v>901.6434885215721</v>
+        <v>879.8239920215721</v>
       </c>
       <c r="N29">
-        <v>4412.656511478428</v>
+        <v>4434.476007978428</v>
       </c>
       <c r="O29">
-        <v>1351.155423814695</v>
+        <v>1357.836553642995</v>
       </c>
       <c r="P29">
-        <v>3061.501087663733</v>
+        <v>3076.639454335434</v>
       </c>
       <c r="Q29">
-        <v>3491.201087663733</v>
+        <v>3506.339454335433</v>
       </c>
       <c r="R29">
         <v>0.3698630136986302</v>
       </c>
       <c r="S29">
-        <v>0.08273220185272648</v>
+        <v>0.08271589599807713</v>
       </c>
       <c r="T29">
         <v>0.7002809058160075</v>
       </c>
       <c r="U29">
-        <v>0.06198425489709894</v>
+        <v>0.06048425489709894</v>
       </c>
       <c r="V29">
         <v>0.3062</v>
       </c>
       <c r="W29">
-        <v>0.04300467604760724</v>
+        <v>0.04196397604760724</v>
       </c>
       <c r="X29" t="inlineStr">
         <is>
@@ -3703,7 +3703,7 @@
         </is>
       </c>
       <c r="Y29">
-        <v>5.894014727166583</v>
+        <v>6.040185364562895</v>
       </c>
       <c r="Z29">
         <v>0</v>
@@ -3714,13 +3714,13 @@
         <v>0.28</v>
       </c>
       <c r="B30">
-        <v>0.07188782347707411</v>
+        <v>0.07158456393586472</v>
       </c>
       <c r="C30">
-        <v>39836.11206748211</v>
+        <v>40052.03751254803</v>
       </c>
       <c r="D30">
-        <v>49373.09606748212</v>
+        <v>49589.02151254803</v>
       </c>
       <c r="E30">
         <v>7291.484</v>
@@ -3747,37 +3747,37 @@
         <v>5314.3</v>
       </c>
       <c r="M30">
-        <v>935.0376918001489</v>
+        <v>912.4100658001489</v>
       </c>
       <c r="N30">
-        <v>4379.262308199852</v>
+        <v>4401.889934199851</v>
       </c>
       <c r="O30">
-        <v>1340.930118770795</v>
+        <v>1347.858697851995</v>
       </c>
       <c r="P30">
-        <v>3038.332189429057</v>
+        <v>3054.031236347857</v>
       </c>
       <c r="Q30">
-        <v>3468.032189429057</v>
+        <v>3483.731236347857</v>
       </c>
       <c r="R30">
         <v>0.388888888888889</v>
       </c>
       <c r="S30">
-        <v>0.08312015858853344</v>
+        <v>0.08310368144796484</v>
       </c>
       <c r="T30">
         <v>0.7076370525047885</v>
       </c>
       <c r="U30">
-        <v>0.06198425489709894</v>
+        <v>0.06048425489709894</v>
       </c>
       <c r="V30">
         <v>0.3062</v>
       </c>
       <c r="W30">
-        <v>0.04300467604760724</v>
+        <v>0.04196397604760724</v>
       </c>
       <c r="X30" t="inlineStr">
         <is>
@@ -3785,7 +3785,7 @@
         </is>
       </c>
       <c r="Y30">
-        <v>5.683514201196348</v>
+        <v>5.824464458685648</v>
       </c>
       <c r="Z30">
         <v>0</v>
@@ -3796,13 +3796,13 @@
         <v>0.29</v>
       </c>
       <c r="B31">
-        <v>0.07207168006880391</v>
+        <v>0.07145625026027916</v>
       </c>
       <c r="C31">
-        <v>39161.84547653705</v>
+        <v>39609.13719311406</v>
       </c>
       <c r="D31">
-        <v>49237.58247653705</v>
+        <v>49684.87419311406</v>
       </c>
       <c r="E31">
         <v>7830.236999999997</v>
@@ -3829,45 +3829,45 @@
         <v>5314.3</v>
       </c>
       <c r="M31">
-        <v>991.8676505787255</v>
+        <v>944.9961395787254</v>
       </c>
       <c r="N31">
-        <v>4322.432349421275</v>
+        <v>4369.303860421274</v>
       </c>
       <c r="O31">
-        <v>1323.528785392795</v>
+        <v>1337.880842060994</v>
       </c>
       <c r="P31">
-        <v>2998.90356402848</v>
+        <v>3031.42301836028</v>
       </c>
       <c r="Q31">
-        <v>3428.60356402848</v>
+        <v>3461.12301836028</v>
       </c>
       <c r="R31">
         <v>0.4084507042253521</v>
       </c>
       <c r="S31">
-        <v>0.08351904368309551</v>
+        <v>0.0835023904316522</v>
       </c>
       <c r="T31">
         <v>0.7152004145932532</v>
       </c>
       <c r="U31">
-        <v>0.06348425489709894</v>
+        <v>0.06048425489709894</v>
       </c>
       <c r="V31">
         <v>0.3062</v>
       </c>
       <c r="W31">
-        <v>0.04404537604760724</v>
+        <v>0.04196397604760724</v>
       </c>
       <c r="X31" t="inlineStr">
         <is>
-          <t>A2/A</t>
+          <t>A1/A+</t>
         </is>
       </c>
       <c r="Y31">
-        <v>5.357872087973898</v>
+        <v>5.623620856662005</v>
       </c>
       <c r="Z31">
         <v>0</v>
@@ -3878,13 +3878,13 @@
         <v>0.3</v>
       </c>
       <c r="B32">
-        <v>0.07196414066053373</v>
+        <v>0.0714944485846936</v>
       </c>
       <c r="C32">
-        <v>38702.26517067833</v>
+        <v>39041.81062655097</v>
       </c>
       <c r="D32">
-        <v>49316.75517067833</v>
+        <v>49656.30062655097</v>
       </c>
       <c r="E32">
         <v>8368.989999999998</v>
@@ -3911,37 +3911,37 @@
         <v>5314.3</v>
       </c>
       <c r="M32">
-        <v>1026.069983357302</v>
+        <v>990.5122853573023</v>
       </c>
       <c r="N32">
-        <v>4288.230016642698</v>
+        <v>4323.787714642698</v>
       </c>
       <c r="O32">
-        <v>1313.056031095994</v>
+        <v>1323.943798223594</v>
       </c>
       <c r="P32">
-        <v>2975.173985546704</v>
+        <v>2999.843916419104</v>
       </c>
       <c r="Q32">
-        <v>3404.873985546703</v>
+        <v>3429.543916419104</v>
       </c>
       <c r="R32">
         <v>0.4285714285714286</v>
       </c>
       <c r="S32">
-        <v>0.0839293254946451</v>
+        <v>0.08391249110058777</v>
       </c>
       <c r="T32">
         <v>0.7229798727413884</v>
       </c>
       <c r="U32">
-        <v>0.06348425489709894</v>
+        <v>0.06128425489709894</v>
       </c>
       <c r="V32">
         <v>0.3062</v>
       </c>
       <c r="W32">
-        <v>0.04404537604760724</v>
+        <v>0.04251901604760724</v>
       </c>
       <c r="X32" t="inlineStr">
         <is>
@@ -3949,7 +3949,7 @@
         </is>
       </c>
       <c r="Y32">
-        <v>5.1792763517081</v>
+        <v>5.365203519997737</v>
       </c>
       <c r="Z32">
         <v>0</v>
@@ -3960,13 +3960,13 @@
         <v>0.31</v>
       </c>
       <c r="B33">
-        <v>0.07185660125226355</v>
+        <v>0.07137168530910806</v>
       </c>
       <c r="C33">
-        <v>38242.93988997301</v>
+        <v>38595.00561001849</v>
       </c>
       <c r="D33">
-        <v>49396.18288997301</v>
+        <v>49748.24861001848</v>
       </c>
       <c r="E33">
         <v>8907.742999999997</v>
@@ -3993,37 +3993,37 @@
         <v>5314.3</v>
       </c>
       <c r="M33">
-        <v>1060.272316135879</v>
+        <v>1023.529361535879</v>
       </c>
       <c r="N33">
-        <v>4254.027683864121</v>
+        <v>4290.770638464121</v>
       </c>
       <c r="O33">
-        <v>1302.583276799194</v>
+        <v>1313.833969497714</v>
       </c>
       <c r="P33">
-        <v>2951.444407064927</v>
+        <v>2976.936668966408</v>
       </c>
       <c r="Q33">
-        <v>3381.144407064927</v>
+        <v>3406.636668966407</v>
       </c>
       <c r="R33">
         <v>0.4492753623188406</v>
       </c>
       <c r="S33">
-        <v>0.08435149953261639</v>
+        <v>0.08433447874543452</v>
       </c>
       <c r="T33">
         <v>0.7309848224300494</v>
       </c>
       <c r="U33">
-        <v>0.06348425489709894</v>
+        <v>0.06128425489709894</v>
       </c>
       <c r="V33">
         <v>0.3062</v>
       </c>
       <c r="W33">
-        <v>0.04404537604760724</v>
+        <v>0.04251901604760724</v>
       </c>
       <c r="X33" t="inlineStr">
         <is>
@@ -4031,7 +4031,7 @@
         </is>
       </c>
       <c r="Y33">
-        <v>5.012202921007839</v>
+        <v>5.192132438707487</v>
       </c>
       <c r="Z33">
         <v>0</v>
@@ -4042,13 +4042,13 @@
         <v>0.32</v>
       </c>
       <c r="B34">
-        <v>0.07174906184399336</v>
+        <v>0.07124892203352251</v>
       </c>
       <c r="C34">
-        <v>37783.87086861071</v>
+        <v>38148.54174317174</v>
       </c>
       <c r="D34">
-        <v>49475.86686861071</v>
+        <v>49840.53774317174</v>
       </c>
       <c r="E34">
         <v>9446.495999999997</v>
@@ -4075,37 +4075,37 @@
         <v>5314.3</v>
       </c>
       <c r="M34">
-        <v>1094.474648914456</v>
+        <v>1056.546437714456</v>
       </c>
       <c r="N34">
-        <v>4219.825351085545</v>
+        <v>4257.753562285545</v>
       </c>
       <c r="O34">
-        <v>1292.110522502394</v>
+        <v>1303.724140771834</v>
       </c>
       <c r="P34">
-        <v>2927.714828583151</v>
+        <v>2954.029421513711</v>
       </c>
       <c r="Q34">
-        <v>3357.414828583151</v>
+        <v>3383.729421513711</v>
       </c>
       <c r="R34">
         <v>0.4705882352941177</v>
       </c>
       <c r="S34">
-        <v>0.08478609045405744</v>
+        <v>0.08476887779160029</v>
       </c>
       <c r="T34">
         <v>0.7392252118154355</v>
       </c>
       <c r="U34">
-        <v>0.06348425489709894</v>
+        <v>0.06128425489709894</v>
       </c>
       <c r="V34">
         <v>0.3062</v>
       </c>
       <c r="W34">
-        <v>0.04404537604760724</v>
+        <v>0.04251901604760724</v>
       </c>
       <c r="X34" t="inlineStr">
         <is>
@@ -4113,7 +4113,7 @@
         </is>
       </c>
       <c r="Y34">
-        <v>4.855571579726345</v>
+        <v>5.029878299997878</v>
       </c>
       <c r="Z34">
         <v>0</v>
@@ -4124,13 +4124,13 @@
         <v>0.33</v>
       </c>
       <c r="B35">
-        <v>0.07164152243572319</v>
+        <v>0.07112615875793697</v>
       </c>
       <c r="C35">
-        <v>37325.0593487577</v>
+        <v>37702.4209281636</v>
       </c>
       <c r="D35">
-        <v>49555.8083487577</v>
+        <v>49933.1699281636</v>
       </c>
       <c r="E35">
         <v>9985.248999999998</v>
@@ -4157,37 +4157,37 @@
         <v>5314.3</v>
       </c>
       <c r="M35">
-        <v>1128.676981693033</v>
+        <v>1089.563513893032</v>
       </c>
       <c r="N35">
-        <v>4185.623018306967</v>
+        <v>4224.736486106967</v>
       </c>
       <c r="O35">
-        <v>1281.637768205594</v>
+        <v>1293.614312045954</v>
       </c>
       <c r="P35">
-        <v>2903.985250101374</v>
+        <v>2931.122174061014</v>
       </c>
       <c r="Q35">
-        <v>3333.685250101374</v>
+        <v>3360.822174061013</v>
       </c>
       <c r="R35">
         <v>0.4925373134328359</v>
       </c>
       <c r="S35">
-        <v>0.08523365423882509</v>
+        <v>0.08521624397347251</v>
       </c>
       <c r="T35">
         <v>0.7477115829735199</v>
       </c>
       <c r="U35">
-        <v>0.06348425489709894</v>
+        <v>0.06128425489709894</v>
       </c>
       <c r="V35">
         <v>0.3062</v>
       </c>
       <c r="W35">
-        <v>0.04404537604760724</v>
+        <v>0.04251901604760724</v>
       </c>
       <c r="X35" t="inlineStr">
         <is>
@@ -4195,7 +4195,7 @@
         </is>
       </c>
       <c r="Y35">
-        <v>4.708433047007365</v>
+        <v>4.877457745452487</v>
       </c>
       <c r="Z35">
         <v>0</v>
@@ -4206,13 +4206,13 @@
         <v>0.34</v>
       </c>
       <c r="B36">
-        <v>0.07153398302745301</v>
+        <v>0.07100339548235142</v>
       </c>
       <c r="C36">
-        <v>36866.50658062148</v>
+        <v>37256.64508131442</v>
       </c>
       <c r="D36">
-        <v>49636.00858062148</v>
+        <v>50026.14708131442</v>
       </c>
       <c r="E36">
         <v>10524.002</v>
@@ -4239,37 +4239,37 @@
         <v>5314.3</v>
       </c>
       <c r="M36">
-        <v>1162.879314471609</v>
+        <v>1122.580590071609</v>
       </c>
       <c r="N36">
-        <v>4151.420685528391</v>
+        <v>4191.719409928391</v>
       </c>
       <c r="O36">
-        <v>1271.165013908794</v>
+        <v>1283.504483320073</v>
       </c>
       <c r="P36">
-        <v>2880.255671619598</v>
+        <v>2908.214926608317</v>
       </c>
       <c r="Q36">
-        <v>3309.955671619598</v>
+        <v>3337.914926608317</v>
       </c>
       <c r="R36">
         <v>0.5151515151515152</v>
       </c>
       <c r="S36">
-        <v>0.08569478056252508</v>
+        <v>0.08567716670631055</v>
       </c>
       <c r="T36">
         <v>0.7564551168939705</v>
       </c>
       <c r="U36">
-        <v>0.06348425489709894</v>
+        <v>0.06128425489709894</v>
       </c>
       <c r="V36">
         <v>0.3062</v>
       </c>
       <c r="W36">
-        <v>0.04404537604760724</v>
+        <v>0.04251901604760724</v>
       </c>
       <c r="X36" t="inlineStr">
         <is>
@@ -4277,7 +4277,7 @@
         </is>
       </c>
       <c r="Y36">
-        <v>4.569949722095384</v>
+        <v>4.734003105880355</v>
       </c>
       <c r="Z36">
         <v>0</v>
@@ -4288,13 +4288,13 @@
         <v>0.35</v>
       </c>
       <c r="B37">
-        <v>0.07142644361918282</v>
+        <v>0.07088063220676587</v>
       </c>
       <c r="C37">
-        <v>36408.21382251589</v>
+        <v>36811.21613324419</v>
       </c>
       <c r="D37">
-        <v>49716.46882251588</v>
+        <v>50119.47113324419</v>
       </c>
       <c r="E37">
         <v>11062.755</v>
@@ -4321,37 +4321,37 @@
         <v>5314.3</v>
       </c>
       <c r="M37">
-        <v>1197.081647250186</v>
+        <v>1155.597666250186</v>
       </c>
       <c r="N37">
-        <v>4117.218352749815</v>
+        <v>4158.702333749814</v>
       </c>
       <c r="O37">
-        <v>1260.692259611993</v>
+        <v>1273.394654594193</v>
       </c>
       <c r="P37">
-        <v>2856.526093137821</v>
+        <v>2885.307679155621</v>
       </c>
       <c r="Q37">
-        <v>3286.226093137821</v>
+        <v>3315.007679155621</v>
       </c>
       <c r="R37">
         <v>0.5384615384615385</v>
       </c>
       <c r="S37">
-        <v>0.08617009538849277</v>
+        <v>0.08615227167708206</v>
       </c>
       <c r="T37">
         <v>0.7654676826273579</v>
       </c>
       <c r="U37">
-        <v>0.06348425489709894</v>
+        <v>0.06128425489709894</v>
       </c>
       <c r="V37">
         <v>0.3062</v>
       </c>
       <c r="W37">
-        <v>0.04404537604760724</v>
+        <v>0.04251901604760724</v>
       </c>
       <c r="X37" t="inlineStr">
         <is>
@@ -4359,7 +4359,7 @@
         </is>
       </c>
       <c r="Y37">
-        <v>4.439379730035515</v>
+        <v>4.598745874283773</v>
       </c>
       <c r="Z37">
         <v>0</v>
@@ -4370,13 +4370,13 @@
         <v>0.36</v>
       </c>
       <c r="B38">
-        <v>0.07131890421091265</v>
+        <v>0.07075786893118033</v>
       </c>
       <c r="C38">
-        <v>35950.18234092696</v>
+        <v>36366.13602900614</v>
       </c>
       <c r="D38">
-        <v>49797.19034092695</v>
+        <v>50213.14402900614</v>
       </c>
       <c r="E38">
         <v>11601.508</v>
@@ -4403,37 +4403,37 @@
         <v>5314.3</v>
       </c>
       <c r="M38">
-        <v>1231.283980028763</v>
+        <v>1188.614742428763</v>
       </c>
       <c r="N38">
-        <v>4083.016019971237</v>
+        <v>4125.685257571237</v>
       </c>
       <c r="O38">
-        <v>1250.219505315193</v>
+        <v>1263.284825868313</v>
       </c>
       <c r="P38">
-        <v>2832.796514656045</v>
+        <v>2862.400431702924</v>
       </c>
       <c r="Q38">
-        <v>3262.496514656044</v>
+        <v>3292.100431702924</v>
       </c>
       <c r="R38">
         <v>0.5625</v>
       </c>
       <c r="S38">
-        <v>0.08666026380277195</v>
+        <v>0.08664222367819019</v>
       </c>
       <c r="T38">
         <v>0.7747618910399137</v>
       </c>
       <c r="U38">
-        <v>0.06348425489709894</v>
+        <v>0.06128425489709894</v>
       </c>
       <c r="V38">
         <v>0.3062</v>
       </c>
       <c r="W38">
-        <v>0.04404537604760724</v>
+        <v>0.04251901604760724</v>
       </c>
       <c r="X38" t="inlineStr">
         <is>
@@ -4441,7 +4441,7 @@
         </is>
       </c>
       <c r="Y38">
-        <v>4.316063626423418</v>
+        <v>4.471002933331447</v>
       </c>
       <c r="Z38">
         <v>0</v>
@@ -4452,13 +4452,13 @@
         <v>0.37</v>
       </c>
       <c r="B39">
-        <v>0.07157075320264247</v>
+        <v>0.07063510565559478</v>
       </c>
       <c r="C39">
-        <v>35222.79610393565</v>
+        <v>35921.4067282219</v>
       </c>
       <c r="D39">
-        <v>49608.55710393565</v>
+        <v>50307.1677282219</v>
       </c>
       <c r="E39">
         <v>12140.261</v>
@@ -4485,45 +4485,45 @@
         <v>5314.3</v>
       </c>
       <c r="M39">
-        <v>1293.393718207339</v>
+        <v>1221.631818607339</v>
       </c>
       <c r="N39">
-        <v>4020.906281792661</v>
+        <v>4092.668181392661</v>
       </c>
       <c r="O39">
-        <v>1231.201503484913</v>
+        <v>1253.174997142433</v>
       </c>
       <c r="P39">
-        <v>2789.704778307748</v>
+        <v>2839.493184250228</v>
       </c>
       <c r="Q39">
-        <v>3219.404778307748</v>
+        <v>3269.193184250228</v>
       </c>
       <c r="R39">
         <v>0.5873015873015873</v>
       </c>
       <c r="S39">
-        <v>0.08716599311909173</v>
+        <v>0.08714772971107952</v>
       </c>
       <c r="T39">
         <v>0.7843511536877886</v>
       </c>
       <c r="U39">
-        <v>0.06488425489709894</v>
+        <v>0.06128425489709894</v>
       </c>
       <c r="V39">
         <v>0.3062</v>
       </c>
       <c r="W39">
-        <v>0.04501669604760724</v>
+        <v>0.04251901604760724</v>
       </c>
       <c r="X39" t="inlineStr">
         <is>
-          <t>A3/A-</t>
+          <t>A2/A</t>
         </is>
       </c>
       <c r="Y39">
-        <v>4.108803008078382</v>
+        <v>4.350165016214381</v>
       </c>
       <c r="Z39">
         <v>0</v>
@@ -4534,13 +4534,13 @@
         <v>0.38</v>
       </c>
       <c r="B40">
-        <v>0.0714729269943723</v>
+        <v>0.07077598638000923</v>
       </c>
       <c r="C40">
-        <v>34757.14429706012</v>
+        <v>35274.78373071074</v>
       </c>
       <c r="D40">
-        <v>49681.65829706012</v>
+        <v>50199.29773071074</v>
       </c>
       <c r="E40">
         <v>12679.014</v>
@@ -4567,37 +4567,37 @@
         <v>5314.3</v>
       </c>
       <c r="M40">
-        <v>1328.350305185916</v>
+        <v>1275.121508785916</v>
       </c>
       <c r="N40">
-        <v>3985.949694814084</v>
+        <v>4039.178491214084</v>
       </c>
       <c r="O40">
-        <v>1220.497796552073</v>
+        <v>1236.796454009753</v>
       </c>
       <c r="P40">
-        <v>2765.451898262011</v>
+        <v>2802.382037204331</v>
       </c>
       <c r="Q40">
-        <v>3195.151898262011</v>
+        <v>3232.082037204331</v>
       </c>
       <c r="R40">
         <v>0.6129032258064516</v>
       </c>
       <c r="S40">
-        <v>0.08768803628432506</v>
+        <v>0.08766954239019109</v>
       </c>
       <c r="T40">
         <v>0.794249747388821</v>
       </c>
       <c r="U40">
-        <v>0.06488425489709894</v>
+        <v>0.06228425489709894</v>
       </c>
       <c r="V40">
         <v>0.3062</v>
       </c>
       <c r="W40">
-        <v>0.04501669604760724</v>
+        <v>0.04321281604760725</v>
       </c>
       <c r="X40" t="inlineStr">
         <is>
@@ -4605,7 +4605,7 @@
         </is>
       </c>
       <c r="Y40">
-        <v>4.000676613128952</v>
+        <v>4.167681247146332</v>
       </c>
       <c r="Z40">
         <v>0</v>
@@ -4616,13 +4616,13 @@
         <v>0.39</v>
       </c>
       <c r="B41">
-        <v>0.07137510078610212</v>
+        <v>0.07066016110442369</v>
       </c>
       <c r="C41">
-        <v>34291.70824612499</v>
+        <v>34824.68231337438</v>
       </c>
       <c r="D41">
-        <v>49754.97524612499</v>
+        <v>50287.94931337438</v>
       </c>
       <c r="E41">
         <v>13217.767</v>
@@ -4649,37 +4649,37 @@
         <v>5314.3</v>
       </c>
       <c r="M41">
-        <v>1363.306892164493</v>
+        <v>1308.677337964493</v>
       </c>
       <c r="N41">
-        <v>3950.993107835508</v>
+        <v>4005.622662035507</v>
       </c>
       <c r="O41">
-        <v>1209.794089619232</v>
+        <v>1226.521659115273</v>
       </c>
       <c r="P41">
-        <v>2741.199018216275</v>
+        <v>2779.101002920235</v>
       </c>
       <c r="Q41">
-        <v>3170.899018216275</v>
+        <v>3208.801002920235</v>
       </c>
       <c r="R41">
         <v>0.639344262295082</v>
       </c>
       <c r="S41">
-        <v>0.08822719561891032</v>
+        <v>0.08820846368173256</v>
       </c>
       <c r="T41">
         <v>0.8044728851456249</v>
       </c>
       <c r="U41">
-        <v>0.06488425489709894</v>
+        <v>0.06228425489709894</v>
       </c>
       <c r="V41">
         <v>0.3062</v>
       </c>
       <c r="W41">
-        <v>0.04501669604760724</v>
+        <v>0.04321281604760725</v>
       </c>
       <c r="X41" t="inlineStr">
         <is>
@@ -4687,7 +4687,7 @@
         </is>
       </c>
       <c r="Y41">
-        <v>3.898095161510261</v>
+        <v>4.060817625424631</v>
       </c>
       <c r="Z41">
         <v>0</v>
@@ -4698,13 +4698,13 @@
         <v>0.4</v>
       </c>
       <c r="B42">
-        <v>0.07127727457783192</v>
+        <v>0.07054433582883814</v>
       </c>
       <c r="C42">
-        <v>33826.48890773757</v>
+        <v>34374.89456603485</v>
       </c>
       <c r="D42">
-        <v>49828.50890773757</v>
+        <v>50376.91456603485</v>
       </c>
       <c r="E42">
         <v>13756.52</v>
@@ -4731,37 +4731,37 @@
         <v>5314.3</v>
       </c>
       <c r="M42">
-        <v>1398.26347914307</v>
+        <v>1342.23316714307</v>
       </c>
       <c r="N42">
-        <v>3916.036520856931</v>
+        <v>3972.06683285693</v>
       </c>
       <c r="O42">
-        <v>1199.090382686392</v>
+        <v>1216.246864220792</v>
       </c>
       <c r="P42">
-        <v>2716.946138170538</v>
+        <v>2755.819968636138</v>
       </c>
       <c r="Q42">
-        <v>3146.646138170538</v>
+        <v>3185.519968636138</v>
       </c>
       <c r="R42">
         <v>0.6666666666666667</v>
       </c>
       <c r="S42">
-        <v>0.08878432693131505</v>
+        <v>0.08876534901632541</v>
       </c>
       <c r="T42">
         <v>0.8150367941609888</v>
       </c>
       <c r="U42">
-        <v>0.06488425489709894</v>
+        <v>0.06228425489709894</v>
       </c>
       <c r="V42">
         <v>0.3062</v>
       </c>
       <c r="W42">
-        <v>0.04501669604760724</v>
+        <v>0.04321281604760725</v>
       </c>
       <c r="X42" t="inlineStr">
         <is>
@@ -4769,7 +4769,7 @@
         </is>
       </c>
       <c r="Y42">
-        <v>3.800642782472504</v>
+        <v>3.959297184789015</v>
       </c>
       <c r="Z42">
         <v>0</v>
@@ -4780,13 +4780,13 @@
         <v>0.41</v>
       </c>
       <c r="B43">
-        <v>0.07117944836956175</v>
+        <v>0.0704285105532526</v>
       </c>
       <c r="C43">
-        <v>33361.48724416863</v>
+        <v>33925.422156399</v>
       </c>
       <c r="D43">
-        <v>49902.26024416863</v>
+        <v>50466.195156399</v>
       </c>
       <c r="E43">
         <v>14295.273</v>
@@ -4813,37 +4813,37 @@
         <v>5314.3</v>
       </c>
       <c r="M43">
-        <v>1433.220066121647</v>
+        <v>1375.788996321646</v>
       </c>
       <c r="N43">
-        <v>3881.079933878354</v>
+        <v>3938.511003678354</v>
       </c>
       <c r="O43">
-        <v>1188.386675753552</v>
+        <v>1205.972069326312</v>
       </c>
       <c r="P43">
-        <v>2692.693258124802</v>
+        <v>2732.538934352041</v>
       </c>
       <c r="Q43">
-        <v>3122.393258124801</v>
+        <v>3162.238934352041</v>
       </c>
       <c r="R43">
         <v>0.6949152542372882</v>
       </c>
       <c r="S43">
-        <v>0.08936034405091997</v>
+        <v>0.08934111181988749</v>
       </c>
       <c r="T43">
         <v>0.8259588017870431</v>
       </c>
       <c r="U43">
-        <v>0.06488425489709894</v>
+        <v>0.06228425489709894</v>
       </c>
       <c r="V43">
         <v>0.3062</v>
       </c>
       <c r="W43">
-        <v>0.04501669604760724</v>
+        <v>0.04321281604760725</v>
       </c>
       <c r="X43" t="inlineStr">
         <is>
@@ -4851,7 +4851,7 @@
         </is>
       </c>
       <c r="Y43">
-        <v>3.707944178021954</v>
+        <v>3.862728960769771</v>
       </c>
       <c r="Z43">
         <v>0</v>
@@ -4862,13 +4862,13 @@
         <v>0.42</v>
       </c>
       <c r="B44">
-        <v>0.07108162216129157</v>
+        <v>0.07031268527766704</v>
       </c>
       <c r="C44">
-        <v>32896.70422339452</v>
+        <v>33476.26676401715</v>
       </c>
       <c r="D44">
-        <v>49976.23022339452</v>
+        <v>50555.79276401715</v>
       </c>
       <c r="E44">
         <v>14834.026</v>
@@ -4895,37 +4895,37 @@
         <v>5314.3</v>
       </c>
       <c r="M44">
-        <v>1468.176653100223</v>
+        <v>1409.344825500223</v>
       </c>
       <c r="N44">
-        <v>3846.123346899777</v>
+        <v>3904.955174499777</v>
       </c>
       <c r="O44">
-        <v>1177.682968820712</v>
+        <v>1195.697274431832</v>
       </c>
       <c r="P44">
-        <v>2668.440378079065</v>
+        <v>2709.257900067945</v>
       </c>
       <c r="Q44">
-        <v>3098.140378079065</v>
+        <v>3138.957900067945</v>
       </c>
       <c r="R44">
         <v>0.7241379310344827</v>
       </c>
       <c r="S44">
-        <v>0.0899562238298216</v>
+        <v>0.08993672851322758</v>
       </c>
       <c r="T44">
         <v>0.8372574303657199</v>
       </c>
       <c r="U44">
-        <v>0.06488425489709894</v>
+        <v>0.06228425489709894</v>
       </c>
       <c r="V44">
         <v>0.3062</v>
       </c>
       <c r="W44">
-        <v>0.04501669604760724</v>
+        <v>0.04321281604760725</v>
       </c>
       <c r="X44" t="inlineStr">
         <is>
@@ -4933,7 +4933,7 @@
         </is>
       </c>
       <c r="Y44">
-        <v>3.619659792830956</v>
+        <v>3.770759223608587</v>
       </c>
       <c r="Z44">
         <v>0</v>
@@ -4944,13 +4944,13 @@
         <v>0.43</v>
       </c>
       <c r="B45">
-        <v>0.07098379595302139</v>
+        <v>0.0701968600020815</v>
       </c>
       <c r="C45">
-        <v>32432.14081913937</v>
+        <v>33027.43008038821</v>
       </c>
       <c r="D45">
-        <v>50050.41981913937</v>
+        <v>50645.70908038821</v>
       </c>
       <c r="E45">
         <v>15372.779</v>
@@ -4977,37 +4977,37 @@
         <v>5314.3</v>
       </c>
       <c r="M45">
-        <v>1503.1332400788</v>
+        <v>1442.9006546788</v>
       </c>
       <c r="N45">
-        <v>3811.166759921201</v>
+        <v>3871.399345321201</v>
       </c>
       <c r="O45">
-        <v>1166.979261887872</v>
+        <v>1185.422479537352</v>
       </c>
       <c r="P45">
-        <v>2644.187498033329</v>
+        <v>2685.976865783849</v>
       </c>
       <c r="Q45">
-        <v>3073.887498033328</v>
+        <v>3115.676865783848</v>
       </c>
       <c r="R45">
         <v>0.7543859649122806</v>
       </c>
       <c r="S45">
-        <v>0.09057301167114083</v>
+        <v>0.09055324403791294</v>
       </c>
       <c r="T45">
         <v>0.8489525020524205</v>
       </c>
       <c r="U45">
-        <v>0.06488425489709894</v>
+        <v>0.06228425489709894</v>
       </c>
       <c r="V45">
         <v>0.3062</v>
       </c>
       <c r="W45">
-        <v>0.04501669604760724</v>
+        <v>0.04321281604760725</v>
       </c>
       <c r="X45" t="inlineStr">
         <is>
@@ -5015,7 +5015,7 @@
         </is>
       </c>
       <c r="Y45">
-        <v>3.535481658113957</v>
+        <v>3.683067148640945</v>
       </c>
       <c r="Z45">
         <v>0</v>
@@ -5026,13 +5026,13 @@
         <v>0.44</v>
       </c>
       <c r="B46">
-        <v>0.07088596974475121</v>
+        <v>0.07008103472649595</v>
       </c>
       <c r="C46">
-        <v>31967.79801091786</v>
+        <v>32578.91380906632</v>
       </c>
       <c r="D46">
-        <v>50124.83001091786</v>
+        <v>50735.94580906632</v>
       </c>
       <c r="E46">
         <v>15911.532</v>
@@ -5059,37 +5059,37 @@
         <v>5314.3</v>
       </c>
       <c r="M46">
-        <v>1538.089827057377</v>
+        <v>1476.456483857377</v>
       </c>
       <c r="N46">
-        <v>3776.210172942624</v>
+        <v>3837.843516142623</v>
       </c>
       <c r="O46">
-        <v>1156.275554955031</v>
+        <v>1175.147684642871</v>
       </c>
       <c r="P46">
-        <v>2619.934617987592</v>
+        <v>2662.695831499752</v>
       </c>
       <c r="Q46">
-        <v>3049.634617987592</v>
+        <v>3092.395831499752</v>
       </c>
       <c r="R46">
         <v>0.7857142857142857</v>
       </c>
       <c r="S46">
-        <v>0.09121182764965004</v>
+        <v>0.09119177797419421</v>
       </c>
       <c r="T46">
         <v>0.861065254870789</v>
       </c>
       <c r="U46">
-        <v>0.06488425489709894</v>
+        <v>0.06228425489709894</v>
       </c>
       <c r="V46">
         <v>0.3062</v>
       </c>
       <c r="W46">
-        <v>0.04501669604760724</v>
+        <v>0.04321281604760725</v>
       </c>
       <c r="X46" t="inlineStr">
         <is>
@@ -5097,7 +5097,7 @@
         </is>
       </c>
       <c r="Y46">
-        <v>3.455129802247731</v>
+        <v>3.599361077080923</v>
       </c>
       <c r="Z46">
         <v>0</v>
@@ -5108,13 +5108,13 @@
         <v>0.45</v>
       </c>
       <c r="B47">
-        <v>0.07078814353648102</v>
+        <v>0.06996520945091041</v>
       </c>
       <c r="C47">
-        <v>31503.67678407838</v>
+        <v>32130.71966576831</v>
       </c>
       <c r="D47">
-        <v>50199.46178407838</v>
+        <v>50826.50466576831</v>
       </c>
       <c r="E47">
         <v>16450.285</v>
@@ -5141,37 +5141,37 @@
         <v>5314.3</v>
       </c>
       <c r="M47">
-        <v>1573.046414035953</v>
+        <v>1510.012313035953</v>
       </c>
       <c r="N47">
-        <v>3741.253585964047</v>
+        <v>3804.287686964047</v>
       </c>
       <c r="O47">
-        <v>1145.571848022191</v>
+        <v>1164.872889748391</v>
       </c>
       <c r="P47">
-        <v>2595.681737941855</v>
+        <v>2639.414797215656</v>
       </c>
       <c r="Q47">
-        <v>3025.381737941855</v>
+        <v>3069.114797215655</v>
       </c>
       <c r="R47">
         <v>0.8181818181818181</v>
       </c>
       <c r="S47">
-        <v>0.09187387330010503</v>
+        <v>0.09185353132634025</v>
       </c>
       <c r="T47">
         <v>0.8736184714280072</v>
       </c>
       <c r="U47">
-        <v>0.06488425489709894</v>
+        <v>0.06228425489709894</v>
       </c>
       <c r="V47">
         <v>0.3062</v>
       </c>
       <c r="W47">
-        <v>0.04501669604760724</v>
+        <v>0.04321281604760725</v>
       </c>
       <c r="X47" t="inlineStr">
         <is>
@@ -5179,7 +5179,7 @@
         </is>
       </c>
       <c r="Y47">
-        <v>3.378349139975559</v>
+        <v>3.519375275368014</v>
       </c>
       <c r="Z47">
         <v>0</v>
@@ -5190,13 +5190,13 @@
         <v>0.46</v>
       </c>
       <c r="B48">
-        <v>0.07069031732821085</v>
+        <v>0.06984938417532485</v>
       </c>
       <c r="C48">
-        <v>31039.77812984643</v>
+        <v>31682.84937848249</v>
       </c>
       <c r="D48">
-        <v>50274.31612984643</v>
+        <v>50917.38737848249</v>
       </c>
       <c r="E48">
         <v>16989.038</v>
@@ -5223,37 +5223,37 @@
         <v>5314.3</v>
       </c>
       <c r="M48">
-        <v>1608.00300101453</v>
+        <v>1543.56814221453</v>
       </c>
       <c r="N48">
-        <v>3706.29699898547</v>
+        <v>3770.73185778547</v>
       </c>
       <c r="O48">
-        <v>1134.868141089351</v>
+        <v>1154.598094853911</v>
       </c>
       <c r="P48">
-        <v>2571.428857896119</v>
+        <v>2616.133762931559</v>
       </c>
       <c r="Q48">
-        <v>3001.128857896119</v>
+        <v>3045.833762931559</v>
       </c>
       <c r="R48">
         <v>0.8518518518518519</v>
       </c>
       <c r="S48">
-        <v>0.09256043915983614</v>
+        <v>0.09253979406189911</v>
       </c>
       <c r="T48">
         <v>0.886636621931789</v>
       </c>
       <c r="U48">
-        <v>0.06488425489709894</v>
+        <v>0.06228425489709894</v>
       </c>
       <c r="V48">
         <v>0.3062</v>
       </c>
       <c r="W48">
-        <v>0.04501669604760724</v>
+        <v>0.04321281604760725</v>
       </c>
       <c r="X48" t="inlineStr">
         <is>
@@ -5261,7 +5261,7 @@
         </is>
       </c>
       <c r="Y48">
-        <v>3.304906767367395</v>
+        <v>3.442867117207839</v>
       </c>
       <c r="Z48">
         <v>0</v>
@@ -5272,13 +5272,13 @@
         <v>0.47</v>
       </c>
       <c r="B49">
-        <v>0.07059249111994068</v>
+        <v>0.06973355889973931</v>
       </c>
       <c r="C49">
-        <v>30576.10304536861</v>
+        <v>31235.30468757856</v>
       </c>
       <c r="D49">
-        <v>50349.39404536862</v>
+        <v>51008.59568757856</v>
       </c>
       <c r="E49">
         <v>17527.791</v>
@@ -5305,37 +5305,37 @@
         <v>5314.3</v>
       </c>
       <c r="M49">
-        <v>1642.959587993107</v>
+        <v>1577.123971393107</v>
       </c>
       <c r="N49">
-        <v>3671.340412006894</v>
+        <v>3737.176028606893</v>
       </c>
       <c r="O49">
-        <v>1124.164434156511</v>
+        <v>1144.323299959431</v>
       </c>
       <c r="P49">
-        <v>2547.175977850383</v>
+        <v>2592.852728647462</v>
       </c>
       <c r="Q49">
-        <v>2976.875977850383</v>
+        <v>3022.552728647462</v>
       </c>
       <c r="R49">
         <v>0.8867924528301887</v>
       </c>
       <c r="S49">
-        <v>0.09327291316521748</v>
+        <v>0.09325195350446019</v>
       </c>
       <c r="T49">
         <v>0.9001460233979779</v>
       </c>
       <c r="U49">
-        <v>0.06488425489709894</v>
+        <v>0.06228425489709894</v>
       </c>
       <c r="V49">
         <v>0.3062</v>
       </c>
       <c r="W49">
-        <v>0.04501669604760724</v>
+        <v>0.04321281604760725</v>
       </c>
       <c r="X49" t="inlineStr">
         <is>
@@ -5343,7 +5343,7 @@
         </is>
       </c>
       <c r="Y49">
-        <v>3.234589602104259</v>
+        <v>3.369614625352353</v>
       </c>
       <c r="Z49">
         <v>0</v>
@@ -5354,13 +5354,13 @@
         <v>0.48</v>
       </c>
       <c r="B50">
-        <v>0.07049466491167049</v>
+        <v>0.06961773362415376</v>
       </c>
       <c r="C50">
-        <v>30112.65253375685</v>
+        <v>30788.08734591868</v>
       </c>
       <c r="D50">
-        <v>50424.69653375685</v>
+        <v>51100.13134591868</v>
       </c>
       <c r="E50">
         <v>18066.54399999999</v>
@@ -5387,37 +5387,37 @@
         <v>5314.3</v>
       </c>
       <c r="M50">
-        <v>1677.916174971684</v>
+        <v>1610.679800571683</v>
       </c>
       <c r="N50">
-        <v>3636.383825028317</v>
+        <v>3703.620199428316</v>
       </c>
       <c r="O50">
-        <v>1113.460727223671</v>
+        <v>1134.048505064951</v>
       </c>
       <c r="P50">
-        <v>2522.923097804646</v>
+        <v>2569.571694363366</v>
       </c>
       <c r="Q50">
-        <v>2952.623097804646</v>
+        <v>2999.271694363366</v>
       </c>
       <c r="R50">
         <v>0.923076923076923</v>
       </c>
       <c r="S50">
-        <v>0.09401279001695964</v>
+        <v>0.09399150369481207</v>
       </c>
       <c r="T50">
         <v>0.9141750172282507</v>
       </c>
       <c r="U50">
-        <v>0.06488425489709894</v>
+        <v>0.06228425489709894</v>
       </c>
       <c r="V50">
         <v>0.3062</v>
       </c>
       <c r="W50">
-        <v>0.04501669604760724</v>
+        <v>0.04321281604760725</v>
       </c>
       <c r="X50" t="inlineStr">
         <is>
@@ -5425,7 +5425,7 @@
         </is>
       </c>
       <c r="Y50">
-        <v>3.167202318727087</v>
+        <v>3.299414320657513</v>
       </c>
       <c r="Z50">
         <v>0</v>
@@ -5436,13 +5436,13 @@
         <v>0.49</v>
       </c>
       <c r="B51">
-        <v>0.07039683870340031</v>
+        <v>0.0695019083485682</v>
       </c>
       <c r="C51">
-        <v>29649.42760413299</v>
+        <v>30341.19911896979</v>
       </c>
       <c r="D51">
-        <v>50500.22460413299</v>
+        <v>51191.99611896979</v>
       </c>
       <c r="E51">
         <v>18605.297</v>
@@ -5469,37 +5469,37 @@
         <v>5314.3</v>
       </c>
       <c r="M51">
-        <v>1712.87276195026</v>
+        <v>1644.23562975026</v>
       </c>
       <c r="N51">
-        <v>3601.42723804974</v>
+        <v>3670.06437024974</v>
       </c>
       <c r="O51">
-        <v>1102.75702029083</v>
+        <v>1123.77371017047</v>
       </c>
       <c r="P51">
-        <v>2498.67021775891</v>
+        <v>2546.290660079269</v>
       </c>
       <c r="Q51">
-        <v>2928.370217758909</v>
+        <v>2975.990660079269</v>
       </c>
       <c r="R51">
         <v>0.9607843137254901</v>
       </c>
       <c r="S51">
-        <v>0.09478168164720149</v>
+        <v>0.09476005585341304</v>
       </c>
       <c r="T51">
         <v>0.9287541676793187</v>
       </c>
       <c r="U51">
-        <v>0.06488425489709894</v>
+        <v>0.06228425489709894</v>
       </c>
       <c r="V51">
         <v>0.3062</v>
       </c>
       <c r="W51">
-        <v>0.04501669604760724</v>
+        <v>0.04321281604760725</v>
       </c>
       <c r="X51" t="inlineStr">
         <is>
@@ -5507,7 +5507,7 @@
         </is>
       </c>
       <c r="Y51">
-        <v>3.102565536712248</v>
+        <v>3.232079334521646</v>
       </c>
       <c r="Z51">
         <v>0</v>
@@ -5518,13 +5518,13 @@
         <v>0.5</v>
       </c>
       <c r="B52">
-        <v>0.07029901249513013</v>
+        <v>0.06938608307298266</v>
       </c>
       <c r="C52">
-        <v>29186.42927167406</v>
+        <v>29894.64178491706</v>
       </c>
       <c r="D52">
-        <v>50575.97927167406</v>
+        <v>51284.19178491706</v>
       </c>
       <c r="E52">
         <v>19144.05</v>
@@ -5551,37 +5551,37 @@
         <v>5314.3</v>
       </c>
       <c r="M52">
-        <v>1747.829348928837</v>
+        <v>1677.791458928837</v>
       </c>
       <c r="N52">
-        <v>3566.470651071163</v>
+        <v>3636.508541071163</v>
       </c>
       <c r="O52">
-        <v>1092.05331335799</v>
+        <v>1113.49891527599</v>
       </c>
       <c r="P52">
-        <v>2474.417337713173</v>
+        <v>2523.009625795173</v>
       </c>
       <c r="Q52">
-        <v>2904.117337713173</v>
+        <v>2952.709625795173</v>
       </c>
       <c r="R52">
         <v>1</v>
       </c>
       <c r="S52">
-        <v>0.095581328942653</v>
+        <v>0.09555935009835807</v>
       </c>
       <c r="T52">
         <v>0.9439164841484293</v>
       </c>
       <c r="U52">
-        <v>0.06488425489709894</v>
+        <v>0.06228425489709894</v>
       </c>
       <c r="V52">
         <v>0.3062</v>
       </c>
       <c r="W52">
-        <v>0.04501669604760724</v>
+        <v>0.04321281604760725</v>
       </c>
       <c r="X52" t="inlineStr">
         <is>
@@ -5589,7 +5589,7 @@
         </is>
       </c>
       <c r="Y52">
-        <v>3.040514225978003</v>
+        <v>3.167437747831213</v>
       </c>
       <c r="Z52">
         <v>0</v>
@@ -5600,13 +5600,13 @@
         <v>0.51</v>
       </c>
       <c r="B53">
-        <v>0.07112116508685995</v>
+        <v>0.06927025779739711</v>
       </c>
       <c r="C53">
-        <v>28018.00097939264</v>
+        <v>29448.41713477872</v>
       </c>
       <c r="D53">
-        <v>49946.30397939264</v>
+        <v>51376.72013477872</v>
       </c>
       <c r="E53">
         <v>19682.803</v>
@@ -5633,45 +5633,45 @@
         <v>5314.3</v>
       </c>
       <c r="M53">
-        <v>1854.224583707414</v>
+        <v>1711.347288107414</v>
       </c>
       <c r="N53">
-        <v>3460.075416292586</v>
+        <v>3602.952711892586</v>
       </c>
       <c r="O53">
-        <v>1059.47509246879</v>
+        <v>1103.22412038151</v>
       </c>
       <c r="P53">
-        <v>2400.600323823796</v>
+        <v>2499.728591511076</v>
       </c>
       <c r="Q53">
-        <v>2830.300323823796</v>
+        <v>2929.428591511076</v>
       </c>
       <c r="R53">
         <v>1.040816326530612</v>
       </c>
       <c r="S53">
-        <v>0.096413614903225</v>
+        <v>0.0963912685981988</v>
       </c>
       <c r="T53">
         <v>0.9596976706775037</v>
       </c>
       <c r="U53">
-        <v>0.06748425489709894</v>
+        <v>0.06228425489709894</v>
       </c>
       <c r="V53">
         <v>0.3062</v>
       </c>
       <c r="W53">
-        <v>0.04682057604760725</v>
+        <v>0.04321281604760725</v>
       </c>
       <c r="X53" t="inlineStr">
         <is>
-          <t>Baa2/BBB</t>
+          <t>A3/A-</t>
         </is>
       </c>
       <c r="Y53">
-        <v>2.86604980146168</v>
+        <v>3.105331125324718</v>
       </c>
       <c r="Z53">
         <v>0</v>
@@ -5682,13 +5682,13 @@
         <v>0.52</v>
       </c>
       <c r="B54">
-        <v>0.07104137767858976</v>
+        <v>0.06915443252181155</v>
       </c>
       <c r="C54">
-        <v>27539.6682528339</v>
+        <v>29002.52697252197</v>
       </c>
       <c r="D54">
-        <v>50006.7242528339</v>
+        <v>51469.58297252197</v>
       </c>
       <c r="E54">
         <v>20221.556</v>
@@ -5715,45 +5715,45 @@
         <v>5314.3</v>
       </c>
       <c r="M54">
-        <v>1890.581928485991</v>
+        <v>1744.903117285991</v>
       </c>
       <c r="N54">
-        <v>3423.718071514009</v>
+        <v>3569.39688271401</v>
       </c>
       <c r="O54">
-        <v>1048.34247349759</v>
+        <v>1092.94932548703</v>
       </c>
       <c r="P54">
-        <v>2375.37559801642</v>
+        <v>2476.44755722698</v>
       </c>
       <c r="Q54">
-        <v>2805.075598016419</v>
+        <v>2906.14755722698</v>
       </c>
       <c r="R54">
         <v>1.083333333333333</v>
       </c>
       <c r="S54">
-        <v>0.09728057944548749</v>
+        <v>0.09725785036886624</v>
       </c>
       <c r="T54">
         <v>0.9761364066452894</v>
       </c>
       <c r="U54">
-        <v>0.06748425489709894</v>
+        <v>0.06228425489709894</v>
       </c>
       <c r="V54">
         <v>0.3062</v>
       </c>
       <c r="W54">
-        <v>0.04682057604760725</v>
+        <v>0.04321281604760725</v>
       </c>
       <c r="X54" t="inlineStr">
         <is>
-          <t>Baa2/BBB</t>
+          <t>A3/A-</t>
         </is>
       </c>
       <c r="Y54">
-        <v>2.810933459125878</v>
+        <v>3.045613219068473</v>
       </c>
       <c r="Z54">
         <v>0</v>
@@ -5764,13 +5764,13 @@
         <v>0.53</v>
       </c>
       <c r="B55">
-        <v>0.07096159027031959</v>
+        <v>0.06995789224622601</v>
       </c>
       <c r="C55">
-        <v>27061.48188469047</v>
+        <v>27826.42753468717</v>
       </c>
       <c r="D55">
-        <v>50067.29088469047</v>
+        <v>50832.23653468717</v>
       </c>
       <c r="E55">
         <v>20760.309</v>
@@ -5797,37 +5797,37 @@
         <v>5314.3</v>
       </c>
       <c r="M55">
-        <v>1926.939273264568</v>
+        <v>1849.843718964567</v>
       </c>
       <c r="N55">
-        <v>3387.360726735433</v>
+        <v>3464.456281035433</v>
       </c>
       <c r="O55">
-        <v>1037.20985452639</v>
+        <v>1060.81651325305</v>
       </c>
       <c r="P55">
-        <v>2350.150872209043</v>
+        <v>2403.639767782383</v>
       </c>
       <c r="Q55">
-        <v>2779.850872209043</v>
+        <v>2833.339767782383</v>
       </c>
       <c r="R55">
         <v>1.127659574468085</v>
       </c>
       <c r="S55">
-        <v>0.09818443609593137</v>
+        <v>0.09816130795956207</v>
       </c>
       <c r="T55">
         <v>0.9932746632925555</v>
       </c>
       <c r="U55">
-        <v>0.06748425489709894</v>
+        <v>0.06478425489709894</v>
       </c>
       <c r="V55">
         <v>0.3062</v>
       </c>
       <c r="W55">
-        <v>0.04682057604760725</v>
+        <v>0.04494731604760724</v>
       </c>
       <c r="X55" t="inlineStr">
         <is>
@@ -5835,7 +5835,7 @@
         </is>
       </c>
       <c r="Y55">
-        <v>2.757896978765013</v>
+        <v>2.872837281072927</v>
       </c>
       <c r="Z55">
         <v>0</v>
@@ -5846,13 +5846,13 @@
         <v>0.54</v>
       </c>
       <c r="B56">
-        <v>0.0708818028620494</v>
+        <v>0.06985941197064047</v>
       </c>
       <c r="C56">
-        <v>26583.44240740189</v>
+        <v>27364.94418408018</v>
       </c>
       <c r="D56">
-        <v>50128.00440740189</v>
+        <v>50909.50618408018</v>
       </c>
       <c r="E56">
         <v>21299.062</v>
@@ -5879,37 +5879,37 @@
         <v>5314.3</v>
       </c>
       <c r="M56">
-        <v>1963.296618043144</v>
+        <v>1884.746430643144</v>
       </c>
       <c r="N56">
-        <v>3351.003381956856</v>
+        <v>3429.553569356856</v>
       </c>
       <c r="O56">
-        <v>1026.077235555189</v>
+        <v>1050.129302937069</v>
       </c>
       <c r="P56">
-        <v>2324.926146401666</v>
+        <v>2379.424266419787</v>
       </c>
       <c r="Q56">
-        <v>2754.626146401666</v>
+        <v>2809.124266419787</v>
       </c>
       <c r="R56">
         <v>1.173913043478261</v>
       </c>
       <c r="S56">
-        <v>0.09912759086161194</v>
+        <v>0.09910404631507078</v>
       </c>
       <c r="T56">
         <v>1.011158061533181</v>
       </c>
       <c r="U56">
-        <v>0.06748425489709894</v>
+        <v>0.06478425489709894</v>
       </c>
       <c r="V56">
         <v>0.3062</v>
       </c>
       <c r="W56">
-        <v>0.04682057604760725</v>
+        <v>0.04494731604760724</v>
       </c>
       <c r="X56" t="inlineStr">
         <is>
@@ -5917,7 +5917,7 @@
         </is>
       </c>
       <c r="Y56">
-        <v>2.706824812491586</v>
+        <v>2.819636590682688</v>
       </c>
       <c r="Z56">
         <v>0</v>
@@ -5928,13 +5928,13 @@
         <v>0.55</v>
       </c>
       <c r="B57">
-        <v>0.07080201545377923</v>
+        <v>0.06976093169505493</v>
       </c>
       <c r="C57">
-        <v>26105.55035599342</v>
+        <v>26903.69610497797</v>
       </c>
       <c r="D57">
-        <v>50188.86535599342</v>
+        <v>50987.01110497797</v>
       </c>
       <c r="E57">
         <v>21837.815</v>
@@ -5961,37 +5961,37 @@
         <v>5314.3</v>
       </c>
       <c r="M57">
-        <v>1999.653962821721</v>
+        <v>1919.649142321721</v>
       </c>
       <c r="N57">
-        <v>3314.646037178279</v>
+        <v>3394.650857678279</v>
       </c>
       <c r="O57">
-        <v>1014.944616583989</v>
+        <v>1039.442092621089</v>
       </c>
       <c r="P57">
-        <v>2299.70142059429</v>
+        <v>2355.20876505719</v>
       </c>
       <c r="Q57">
-        <v>2729.401420594289</v>
+        <v>2784.90876505719</v>
       </c>
       <c r="R57">
         <v>1.222222222222223</v>
       </c>
       <c r="S57">
-        <v>0.1001126636168783</v>
+        <v>0.1000886841530465</v>
       </c>
       <c r="T57">
         <v>1.02983627747339</v>
       </c>
       <c r="U57">
-        <v>0.06748425489709894</v>
+        <v>0.06478425489709894</v>
       </c>
       <c r="V57">
         <v>0.3062</v>
       </c>
       <c r="W57">
-        <v>0.04682057604760725</v>
+        <v>0.04494731604760724</v>
       </c>
       <c r="X57" t="inlineStr">
         <is>
@@ -5999,7 +5999,7 @@
         </is>
       </c>
       <c r="Y57">
-        <v>2.65760981590083</v>
+        <v>2.768370470852093</v>
       </c>
       <c r="Z57">
         <v>0</v>
@@ -6010,13 +6010,13 @@
         <v>0.5600000000000001</v>
       </c>
       <c r="B58">
-        <v>0.07072222804550904</v>
+        <v>0.06966245141946936</v>
       </c>
       <c r="C58">
-        <v>25627.80626809188</v>
+        <v>26442.68437355496</v>
       </c>
       <c r="D58">
-        <v>50249.87426809188</v>
+        <v>51064.75237355496</v>
       </c>
       <c r="E58">
         <v>22376.568</v>
@@ -6043,37 +6043,37 @@
         <v>5314.3</v>
       </c>
       <c r="M58">
-        <v>2036.011307600298</v>
+        <v>1954.551854000298</v>
       </c>
       <c r="N58">
-        <v>3278.288692399702</v>
+        <v>3359.748145999703</v>
       </c>
       <c r="O58">
-        <v>1003.811997612789</v>
+        <v>1028.754882305109</v>
       </c>
       <c r="P58">
-        <v>2274.476694786913</v>
+        <v>2330.993263694593</v>
       </c>
       <c r="Q58">
-        <v>2704.176694786913</v>
+        <v>2760.693263694593</v>
       </c>
       <c r="R58">
         <v>1.272727272727273</v>
       </c>
       <c r="S58">
-        <v>0.101142512406475</v>
+        <v>0.1011180782563848</v>
       </c>
       <c r="T58">
         <v>1.049363503229062</v>
       </c>
       <c r="U58">
-        <v>0.06748425489709894</v>
+        <v>0.06478425489709894</v>
       </c>
       <c r="V58">
         <v>0.3062</v>
       </c>
       <c r="W58">
-        <v>0.04682057604760725</v>
+        <v>0.04494731604760724</v>
       </c>
       <c r="X58" t="inlineStr">
         <is>
@@ -6081,7 +6081,7 @@
         </is>
       </c>
       <c r="Y58">
-        <v>2.610152497759744</v>
+        <v>2.718935283872592</v>
       </c>
       <c r="Z58">
         <v>0</v>
@@ -6092,13 +6092,13 @@
         <v>0.5700000000000001</v>
       </c>
       <c r="B59">
-        <v>0.07064244063723886</v>
+        <v>0.06956397114388382</v>
       </c>
       <c r="C59">
-        <v>25150.21068394131</v>
+        <v>25981.91007255903</v>
       </c>
       <c r="D59">
-        <v>50311.03168394131</v>
+        <v>51142.73107255904</v>
       </c>
       <c r="E59">
         <v>22915.321</v>
@@ -6125,37 +6125,37 @@
         <v>5314.3</v>
       </c>
       <c r="M59">
-        <v>2072.368652378875</v>
+        <v>1989.454565678875</v>
       </c>
       <c r="N59">
-        <v>3241.931347621125</v>
+        <v>3324.845434321126</v>
       </c>
       <c r="O59">
-        <v>992.6793786415888</v>
+        <v>1018.067671989129</v>
       </c>
       <c r="P59">
-        <v>2249.251968979537</v>
+        <v>2306.777762331997</v>
       </c>
       <c r="Q59">
-        <v>2678.951968979537</v>
+        <v>2736.477762331997</v>
       </c>
       <c r="R59">
         <v>1.325581395348838</v>
       </c>
       <c r="S59">
-        <v>0.1022202611397738</v>
+        <v>0.1021953511552272</v>
       </c>
       <c r="T59">
         <v>1.069798972043139</v>
       </c>
       <c r="U59">
-        <v>0.06748425489709894</v>
+        <v>0.06478425489709894</v>
       </c>
       <c r="V59">
         <v>0.3062</v>
       </c>
       <c r="W59">
-        <v>0.04682057604760725</v>
+        <v>0.04494731604760724</v>
       </c>
       <c r="X59" t="inlineStr">
         <is>
@@ -6163,7 +6163,7 @@
         </is>
       </c>
       <c r="Y59">
-        <v>2.56436034867624</v>
+        <v>2.671234664857283</v>
       </c>
       <c r="Z59">
         <v>0</v>
@@ -6174,13 +6174,13 @@
         <v>0.58</v>
       </c>
       <c r="B60">
-        <v>0.07056265322896868</v>
+        <v>0.06946549086829829</v>
       </c>
       <c r="C60">
-        <v>24672.76414641909</v>
+        <v>25521.37429136187</v>
       </c>
       <c r="D60">
-        <v>50372.33814641908</v>
+        <v>51220.94829136187</v>
       </c>
       <c r="E60">
         <v>23454.07399999999</v>
@@ -6207,37 +6207,37 @@
         <v>5314.3</v>
       </c>
       <c r="M60">
-        <v>2108.725997157451</v>
+        <v>2024.357277357451</v>
       </c>
       <c r="N60">
-        <v>3205.574002842549</v>
+        <v>3289.94272264255</v>
       </c>
       <c r="O60">
-        <v>981.5467596703887</v>
+        <v>1007.380461673149</v>
       </c>
       <c r="P60">
-        <v>2224.027243172161</v>
+        <v>2282.562260969401</v>
       </c>
       <c r="Q60">
-        <v>2653.72724317216</v>
+        <v>2712.262260969401</v>
       </c>
       <c r="R60">
         <v>1.380952380952381</v>
       </c>
       <c r="S60">
-        <v>0.1033493312413249</v>
+        <v>0.1033239227635383</v>
       </c>
       <c r="T60">
         <v>1.09120755841979</v>
       </c>
       <c r="U60">
-        <v>0.06748425489709894</v>
+        <v>0.06478425489709894</v>
       </c>
       <c r="V60">
         <v>0.3062</v>
       </c>
       <c r="W60">
-        <v>0.04682057604760725</v>
+        <v>0.04494731604760724</v>
       </c>
       <c r="X60" t="inlineStr">
         <is>
@@ -6245,7 +6245,7 @@
         </is>
       </c>
       <c r="Y60">
-        <v>2.520147239216305</v>
+        <v>2.625178894773537</v>
       </c>
       <c r="Z60">
         <v>0</v>
@@ -6256,13 +6256,13 @@
         <v>0.59</v>
       </c>
       <c r="B61">
-        <v>0.07158808922069849</v>
+        <v>0.06936701059271272</v>
       </c>
       <c r="C61">
-        <v>23357.2980984458</v>
+        <v>25061.07812600968</v>
       </c>
       <c r="D61">
-        <v>49595.62509844579</v>
+        <v>51299.40512600967</v>
       </c>
       <c r="E61">
         <v>23992.827</v>
@@ -6289,45 +6289,45 @@
         <v>5314.3</v>
       </c>
       <c r="M61">
-        <v>2230.906694836028</v>
+        <v>2059.259989036027</v>
       </c>
       <c r="N61">
-        <v>3083.393305163972</v>
+        <v>3255.040010963973</v>
       </c>
       <c r="O61">
-        <v>944.1350300412084</v>
+        <v>996.6932513571685</v>
       </c>
       <c r="P61">
-        <v>2139.258275122764</v>
+        <v>2258.346759606804</v>
       </c>
       <c r="Q61">
-        <v>2568.958275122764</v>
+        <v>2688.046759606804</v>
       </c>
       <c r="R61">
         <v>1.439024390243902</v>
       </c>
       <c r="S61">
-        <v>0.1045334779331957</v>
+        <v>0.1045075466454255</v>
       </c>
       <c r="T61">
         <v>1.113660466083107</v>
       </c>
       <c r="U61">
-        <v>0.07018425489709894</v>
+        <v>0.06478425489709894</v>
       </c>
       <c r="V61">
         <v>0.3062</v>
       </c>
       <c r="W61">
-        <v>0.04869383604760724</v>
+        <v>0.04494731604760724</v>
       </c>
       <c r="X61" t="inlineStr">
         <is>
-          <t>Ba1/BB+</t>
+          <t>Baa2/BBB</t>
         </is>
       </c>
       <c r="Y61">
-        <v>2.382125622869496</v>
+        <v>2.580684337235003</v>
       </c>
       <c r="Z61">
         <v>0</v>
@@ -6338,13 +6338,13 @@
         <v>0.6</v>
       </c>
       <c r="B62">
-        <v>0.07152703441242832</v>
+        <v>0.06926853031712718</v>
       </c>
       <c r="C62">
-        <v>22864.11961536656</v>
+        <v>24601.02267927432</v>
       </c>
       <c r="D62">
-        <v>49641.19961536655</v>
+        <v>51378.10267927432</v>
       </c>
       <c r="E62">
         <v>24531.57999999999</v>
@@ -6371,45 +6371,45 @@
         <v>5314.3</v>
       </c>
       <c r="M62">
-        <v>2268.718672714605</v>
+        <v>2094.162700714604</v>
       </c>
       <c r="N62">
-        <v>3045.581327285396</v>
+        <v>3220.137299285396</v>
       </c>
       <c r="O62">
-        <v>932.5570024147883</v>
+        <v>986.0060410411883</v>
       </c>
       <c r="P62">
-        <v>2113.024324870607</v>
+        <v>2234.131258244207</v>
       </c>
       <c r="Q62">
-        <v>2542.724324870607</v>
+        <v>2663.831258244207</v>
       </c>
       <c r="R62">
         <v>1.5</v>
       </c>
       <c r="S62">
-        <v>0.1057768319596599</v>
+        <v>0.1057503517214071</v>
       </c>
       <c r="T62">
         <v>1.13723601912959</v>
       </c>
       <c r="U62">
-        <v>0.07018425489709894</v>
+        <v>0.06478425489709894</v>
       </c>
       <c r="V62">
         <v>0.3062</v>
       </c>
       <c r="W62">
-        <v>0.04869383604760724</v>
+        <v>0.04494731604760724</v>
       </c>
       <c r="X62" t="inlineStr">
         <is>
-          <t>Ba1/BB+</t>
+          <t>Baa2/BBB</t>
         </is>
       </c>
       <c r="Y62">
-        <v>2.342423529155004</v>
+        <v>2.53767293161442</v>
       </c>
       <c r="Z62">
         <v>0</v>
@@ -6420,13 +6420,13 @@
         <v>0.61</v>
       </c>
       <c r="B63">
-        <v>0.07146597960415814</v>
+        <v>0.07065131304154162</v>
       </c>
       <c r="C63">
-        <v>22371.02496818933</v>
+        <v>22978.9014130053</v>
       </c>
       <c r="D63">
-        <v>49686.85796818932</v>
+        <v>50294.7344130053</v>
       </c>
       <c r="E63">
         <v>25070.333</v>
@@ -6453,37 +6453,37 @@
         <v>5314.3</v>
       </c>
       <c r="M63">
-        <v>2306.530650593181</v>
+        <v>2244.089177893181</v>
       </c>
       <c r="N63">
-        <v>3007.769349406819</v>
+        <v>3070.210822106819</v>
       </c>
       <c r="O63">
-        <v>920.9789747883681</v>
+        <v>940.0985537291079</v>
       </c>
       <c r="P63">
-        <v>2086.790374618451</v>
+        <v>2130.112268377711</v>
       </c>
       <c r="Q63">
-        <v>2516.490374618451</v>
+        <v>2559.812268377711</v>
       </c>
       <c r="R63">
         <v>1.564102564102564</v>
       </c>
       <c r="S63">
-        <v>0.1070839477310711</v>
+        <v>0.1070568903910288</v>
       </c>
       <c r="T63">
         <v>1.162020574896406</v>
       </c>
       <c r="U63">
-        <v>0.07018425489709894</v>
+        <v>0.06828425489709894</v>
       </c>
       <c r="V63">
         <v>0.3062</v>
       </c>
       <c r="W63">
-        <v>0.04869383604760724</v>
+        <v>0.04737561604760724</v>
       </c>
       <c r="X63" t="inlineStr">
         <is>
@@ -6491,7 +6491,7 @@
         </is>
       </c>
       <c r="Y63">
-        <v>2.304023143431151</v>
+        <v>2.368132270478317</v>
       </c>
       <c r="Z63">
         <v>0</v>
@@ -6502,13 +6502,13 @@
         <v>0.62</v>
       </c>
       <c r="B64">
-        <v>0.07140492479588795</v>
+        <v>0.07057711576595607</v>
       </c>
       <c r="C64">
-        <v>21878.01438845565</v>
+        <v>22497.11841540599</v>
       </c>
       <c r="D64">
-        <v>49732.60038845564</v>
+        <v>50351.70441540598</v>
       </c>
       <c r="E64">
         <v>25609.086</v>
@@ -6535,37 +6535,37 @@
         <v>5314.3</v>
       </c>
       <c r="M64">
-        <v>2344.342628471758</v>
+        <v>2280.877525071758</v>
       </c>
       <c r="N64">
-        <v>2969.957371528242</v>
+        <v>3033.422474928243</v>
       </c>
       <c r="O64">
-        <v>909.4009471619479</v>
+        <v>928.8339618230279</v>
       </c>
       <c r="P64">
-        <v>2060.556424366294</v>
+        <v>2104.588513105215</v>
       </c>
       <c r="Q64">
-        <v>2490.256424366294</v>
+        <v>2534.288513105214</v>
       </c>
       <c r="R64">
         <v>1.631578947368421</v>
       </c>
       <c r="S64">
-        <v>0.1084598590693986</v>
+        <v>0.1084321942537884</v>
       </c>
       <c r="T64">
         <v>1.188109580966738</v>
       </c>
       <c r="U64">
-        <v>0.07018425489709894</v>
+        <v>0.06828425489709894</v>
       </c>
       <c r="V64">
         <v>0.3062</v>
       </c>
       <c r="W64">
-        <v>0.04869383604760724</v>
+        <v>0.04737561604760724</v>
       </c>
       <c r="X64" t="inlineStr">
         <is>
@@ -6573,7 +6573,7 @@
         </is>
       </c>
       <c r="Y64">
-        <v>2.266861479827423</v>
+        <v>2.329936588696409</v>
       </c>
       <c r="Z64">
         <v>0</v>
@@ -6584,13 +6584,13 @@
         <v>0.63</v>
       </c>
       <c r="B65">
-        <v>0.07339821178761777</v>
+        <v>0.07050291849037053</v>
       </c>
       <c r="C65">
-        <v>19888.12576529919</v>
+        <v>22015.46462662842</v>
       </c>
       <c r="D65">
-        <v>48281.46476529919</v>
+        <v>50408.80362662842</v>
       </c>
       <c r="E65">
         <v>26147.839</v>
@@ -6617,45 +6617,45 @@
         <v>5314.3</v>
       </c>
       <c r="M65">
-        <v>2541.679369650335</v>
+        <v>2317.665872250335</v>
       </c>
       <c r="N65">
-        <v>2772.620630349666</v>
+        <v>2996.634127749665</v>
       </c>
       <c r="O65">
-        <v>848.9764370130677</v>
+        <v>917.5693699169476</v>
       </c>
       <c r="P65">
-        <v>1923.644193336598</v>
+        <v>2079.064757832718</v>
       </c>
       <c r="Q65">
-        <v>2353.344193336598</v>
+        <v>2508.764757832718</v>
       </c>
       <c r="R65">
         <v>1.702702702702703</v>
       </c>
       <c r="S65">
-        <v>0.1099101439935816</v>
+        <v>0.1098818388658864</v>
       </c>
       <c r="T65">
         <v>1.215608803581412</v>
       </c>
       <c r="U65">
-        <v>0.07488425489709893</v>
+        <v>0.06828425489709894</v>
       </c>
       <c r="V65">
         <v>0.3062</v>
       </c>
       <c r="W65">
-        <v>0.05195469604760724</v>
+        <v>0.04737561604760724</v>
       </c>
       <c r="X65" t="inlineStr">
         <is>
-          <t>Ba2/BB</t>
+          <t>Ba1/BB+</t>
         </is>
       </c>
       <c r="Y65">
-        <v>2.090861681239952</v>
+        <v>2.292953468240911</v>
       </c>
       <c r="Z65">
         <v>0</v>
@@ -6666,13 +6666,13 @@
         <v>0.64</v>
       </c>
       <c r="B66">
-        <v>0.0733697655793476</v>
+        <v>0.070428721214785</v>
       </c>
       <c r="C66">
-        <v>19369.4860364302</v>
+        <v>21533.94048674298</v>
       </c>
       <c r="D66">
-        <v>48301.5780364302</v>
+        <v>50466.03248674297</v>
       </c>
       <c r="E66">
         <v>26686.592</v>
@@ -6699,45 +6699,45 @@
         <v>5314.3</v>
       </c>
       <c r="M66">
-        <v>2582.023486628911</v>
+        <v>2354.454219428912</v>
       </c>
       <c r="N66">
-        <v>2732.276513371089</v>
+        <v>2959.845780571089</v>
       </c>
       <c r="O66">
-        <v>836.6230683942275</v>
+        <v>906.3047780108674</v>
       </c>
       <c r="P66">
-        <v>1895.653444976861</v>
+        <v>2053.541002560221</v>
       </c>
       <c r="Q66">
-        <v>2325.353444976861</v>
+        <v>2483.241002560221</v>
       </c>
       <c r="R66">
         <v>1.777777777777778</v>
       </c>
       <c r="S66">
-        <v>0.1114410003024416</v>
+        <v>0.1114120192897677</v>
       </c>
       <c r="T66">
         <v>1.244635760785791</v>
       </c>
       <c r="U66">
-        <v>0.07488425489709893</v>
+        <v>0.06828425489709894</v>
       </c>
       <c r="V66">
         <v>0.3062</v>
       </c>
       <c r="W66">
-        <v>0.05195469604760724</v>
+        <v>0.04737561604760724</v>
       </c>
       <c r="X66" t="inlineStr">
         <is>
-          <t>Ba2/BB</t>
+          <t>Ba1/BB+</t>
         </is>
       </c>
       <c r="Y66">
-        <v>2.058191967470578</v>
+        <v>2.257126070299647</v>
       </c>
       <c r="Z66">
         <v>0</v>
@@ -6748,13 +6748,13 @@
         <v>0.65</v>
       </c>
       <c r="B67">
-        <v>0.07334131937107742</v>
+        <v>0.07161723993919944</v>
       </c>
       <c r="C67">
-        <v>18850.86307226684</v>
+        <v>20093.8259901945</v>
       </c>
       <c r="D67">
-        <v>48321.70807226684</v>
+        <v>49564.6709901945</v>
       </c>
       <c r="E67">
         <v>27225.345</v>
@@ -6781,37 +6781,37 @@
         <v>5314.3</v>
       </c>
       <c r="M67">
-        <v>2622.367603607488</v>
+        <v>2489.295612607488</v>
       </c>
       <c r="N67">
-        <v>2691.932396392512</v>
+        <v>2825.004387392512</v>
       </c>
       <c r="O67">
-        <v>824.2696997753873</v>
+        <v>865.0163434195872</v>
       </c>
       <c r="P67">
-        <v>1867.662696617125</v>
+        <v>1959.988043972925</v>
       </c>
       <c r="Q67">
-        <v>2297.362696617125</v>
+        <v>2389.688043972925</v>
       </c>
       <c r="R67">
         <v>1.857142857142857</v>
       </c>
       <c r="S67">
-        <v>0.1130593341146649</v>
+        <v>0.1130296385950135</v>
       </c>
       <c r="T67">
         <v>1.275321401258991</v>
       </c>
       <c r="U67">
-        <v>0.07488425489709893</v>
+        <v>0.07108425489709894</v>
       </c>
       <c r="V67">
         <v>0.3062</v>
       </c>
       <c r="W67">
-        <v>0.05195469604760724</v>
+        <v>0.04931825604760724</v>
       </c>
       <c r="X67" t="inlineStr">
         <is>
@@ -6819,7 +6819,7 @@
         </is>
       </c>
       <c r="Y67">
-        <v>2.026527475663338</v>
+        <v>2.134860951461436</v>
       </c>
       <c r="Z67">
         <v>0</v>
@@ -6830,13 +6830,13 @@
         <v>0.66</v>
       </c>
       <c r="B68">
-        <v>0.07757141756280723</v>
+        <v>0.07156246906361388</v>
       </c>
       <c r="C68">
-        <v>15492.18415827204</v>
+        <v>19595.90242143654</v>
       </c>
       <c r="D68">
-        <v>45501.78215827204</v>
+        <v>49605.50042143654</v>
       </c>
       <c r="E68">
         <v>27764.098</v>
@@ -6863,45 +6863,45 @@
         <v>5314.3</v>
       </c>
       <c r="M68">
-        <v>2993.398311986065</v>
+        <v>2527.592468186065</v>
       </c>
       <c r="N68">
-        <v>2320.901688013935</v>
+        <v>2786.707531813935</v>
       </c>
       <c r="O68">
-        <v>710.6600968698671</v>
+        <v>853.2898462414271</v>
       </c>
       <c r="P68">
-        <v>1610.241591144068</v>
+        <v>1933.417685572508</v>
       </c>
       <c r="Q68">
-        <v>2039.941591144068</v>
+        <v>2363.117685572508</v>
       </c>
       <c r="R68">
         <v>1.941176470588236</v>
       </c>
       <c r="S68">
-        <v>0.1147728640334896</v>
+        <v>0.1147424119770385</v>
       </c>
       <c r="T68">
         <v>1.307812079407085</v>
       </c>
       <c r="U68">
-        <v>0.08418425489709894</v>
+        <v>0.07108425489709894</v>
       </c>
       <c r="V68">
         <v>0.3062</v>
       </c>
       <c r="W68">
-        <v>0.05840703604760724</v>
+        <v>0.04931825604760724</v>
       </c>
       <c r="X68" t="inlineStr">
         <is>
-          <t>B1/B+</t>
+          <t>Ba2/BB</t>
         </is>
       </c>
       <c r="Y68">
-        <v>1.77534008044324</v>
+        <v>2.10251457340899</v>
       </c>
       <c r="Z68">
         <v>0</v>
@@ -6912,13 +6912,13 @@
         <v>0.67</v>
       </c>
       <c r="B69">
-        <v>0.07979227095453706</v>
+        <v>0.07150769818802835</v>
       </c>
       <c r="C69">
-        <v>13600.77633320085</v>
+        <v>19098.04617550341</v>
       </c>
       <c r="D69">
-        <v>44149.12733320086</v>
+        <v>49646.39717550341</v>
       </c>
       <c r="E69">
         <v>28302.851</v>
@@ -6945,45 +6945,45 @@
         <v>5314.3</v>
       </c>
       <c r="M69">
-        <v>3208.406151564642</v>
+        <v>2565.889323764642</v>
       </c>
       <c r="N69">
-        <v>2105.893848435358</v>
+        <v>2748.410676235358</v>
       </c>
       <c r="O69">
-        <v>644.8246963909066</v>
+        <v>841.5633490632667</v>
       </c>
       <c r="P69">
-        <v>1461.069152044451</v>
+        <v>1906.847327172091</v>
       </c>
       <c r="Q69">
-        <v>1890.769152044451</v>
+        <v>2336.547327172091</v>
       </c>
       <c r="R69">
         <v>2.030303030303031</v>
       </c>
       <c r="S69">
-        <v>0.1165902442504249</v>
+        <v>0.1165589898064591</v>
       </c>
       <c r="T69">
         <v>1.342271889564155</v>
       </c>
       <c r="U69">
-        <v>0.08888425489709895</v>
+        <v>0.07108425489709894</v>
       </c>
       <c r="V69">
         <v>0.3062</v>
       </c>
       <c r="W69">
-        <v>0.06166789604760724</v>
+        <v>0.04931825604760724</v>
       </c>
       <c r="X69" t="inlineStr">
         <is>
-          <t>B2/B</t>
+          <t>Ba2/BB</t>
         </is>
       </c>
       <c r="Y69">
-        <v>1.656367600906256</v>
+        <v>2.071133758880497</v>
       </c>
       <c r="Z69">
         <v>0</v>
@@ -6994,13 +6994,13 @@
         <v>0.68</v>
       </c>
       <c r="B70">
-        <v>0.07986095674626686</v>
+        <v>0.07145292731244279</v>
       </c>
       <c r="C70">
-        <v>13021.46980786123</v>
+        <v>18600.25741904341</v>
       </c>
       <c r="D70">
-        <v>44108.57380786123</v>
+        <v>49687.36141904341</v>
       </c>
       <c r="E70">
         <v>28841.604</v>
@@ -7027,45 +7027,45 @@
         <v>5314.3</v>
       </c>
       <c r="M70">
-        <v>3256.292810543219</v>
+        <v>2604.186179343219</v>
       </c>
       <c r="N70">
-        <v>2058.007189456781</v>
+        <v>2710.113820656782</v>
       </c>
       <c r="O70">
-        <v>630.1618014116665</v>
+        <v>829.8368518851066</v>
       </c>
       <c r="P70">
-        <v>1427.845388045115</v>
+        <v>1880.276968771675</v>
       </c>
       <c r="Q70">
-        <v>1857.545388045115</v>
+        <v>2309.976968771675</v>
       </c>
       <c r="R70">
         <v>2.125</v>
       </c>
       <c r="S70">
-        <v>0.1185212107309186</v>
+        <v>0.1184891037502184</v>
       </c>
       <c r="T70">
         <v>1.378885437856041</v>
       </c>
       <c r="U70">
-        <v>0.08888425489709895</v>
+        <v>0.07108425489709894</v>
       </c>
       <c r="V70">
         <v>0.3062</v>
       </c>
       <c r="W70">
-        <v>0.06166789604760724</v>
+        <v>0.04931825604760724</v>
       </c>
       <c r="X70" t="inlineStr">
         <is>
-          <t>B2/B</t>
+          <t>Ba2/BB</t>
         </is>
       </c>
       <c r="Y70">
-        <v>1.632009253834105</v>
+        <v>2.040675909485196</v>
       </c>
       <c r="Z70">
         <v>0</v>
@@ -7076,13 +7076,13 @@
         <v>0.6900000000000001</v>
       </c>
       <c r="B71">
-        <v>0.0799296425379967</v>
+        <v>0.07139815643685725</v>
       </c>
       <c r="C71">
-        <v>12442.2377156646</v>
+        <v>18102.53631925525</v>
       </c>
       <c r="D71">
-        <v>44068.09471566461</v>
+        <v>49728.39331925525</v>
       </c>
       <c r="E71">
         <v>29380.357</v>
@@ -7109,45 +7109,45 @@
         <v>5314.3</v>
       </c>
       <c r="M71">
-        <v>3304.179469521796</v>
+        <v>2642.483034921795</v>
       </c>
       <c r="N71">
-        <v>2010.120530478204</v>
+        <v>2671.816965078205</v>
       </c>
       <c r="O71">
-        <v>615.4989064324262</v>
+        <v>818.1103547069464</v>
       </c>
       <c r="P71">
-        <v>1394.621624045778</v>
+        <v>1853.706610371258</v>
       </c>
       <c r="Q71">
-        <v>1824.321624045778</v>
+        <v>2283.406610371258</v>
       </c>
       <c r="R71">
         <v>2.225806451612904</v>
       </c>
       <c r="S71">
-        <v>0.1205767556940248</v>
+        <v>0.1205437411742202</v>
       </c>
       <c r="T71">
         <v>1.417861150553856</v>
       </c>
       <c r="U71">
-        <v>0.08888425489709895</v>
+        <v>0.07108425489709894</v>
       </c>
       <c r="V71">
         <v>0.3062</v>
       </c>
       <c r="W71">
-        <v>0.06166789604760724</v>
+        <v>0.04931825604760724</v>
       </c>
       <c r="X71" t="inlineStr">
         <is>
-          <t>B2/B</t>
+          <t>Ba2/BB</t>
         </is>
       </c>
       <c r="Y71">
-        <v>1.608356945807524</v>
+        <v>2.011100896304251</v>
       </c>
       <c r="Z71">
         <v>0</v>
@@ -7158,13 +7158,13 @@
         <v>0.7000000000000001</v>
       </c>
       <c r="B72">
-        <v>0.0799983283297265</v>
+        <v>0.0751315335612717</v>
       </c>
       <c r="C72">
-        <v>11863.07985187371</v>
+        <v>14913.76233564843</v>
       </c>
       <c r="D72">
-        <v>44027.68985187371</v>
+        <v>47078.37233564843</v>
       </c>
       <c r="E72">
         <v>29919.11</v>
@@ -7191,45 +7191,45 @@
         <v>5314.3</v>
       </c>
       <c r="M72">
-        <v>3352.066128500373</v>
+        <v>2974.939028500372</v>
       </c>
       <c r="N72">
-        <v>1962.233871499628</v>
+        <v>2339.360971499628</v>
       </c>
       <c r="O72">
-        <v>600.8360114531861</v>
+        <v>716.3123294731862</v>
       </c>
       <c r="P72">
-        <v>1361.397860046442</v>
+        <v>1623.048642026442</v>
       </c>
       <c r="Q72">
-        <v>1791.097860046442</v>
+        <v>2052.748642026442</v>
       </c>
       <c r="R72">
         <v>2.333333333333334</v>
       </c>
       <c r="S72">
-        <v>0.1227693369880048</v>
+        <v>0.1227353544264888</v>
       </c>
       <c r="T72">
         <v>1.459435244098192</v>
       </c>
       <c r="U72">
-        <v>0.08888425489709895</v>
+        <v>0.07888425489709894</v>
       </c>
       <c r="V72">
         <v>0.3062</v>
       </c>
       <c r="W72">
-        <v>0.06166789604760724</v>
+        <v>0.05472989604760724</v>
       </c>
       <c r="X72" t="inlineStr">
         <is>
-          <t>B2/B</t>
+          <t>B1/B+</t>
         </is>
       </c>
       <c r="Y72">
-        <v>1.585380418010274</v>
+        <v>1.786355938420314</v>
       </c>
       <c r="Z72">
         <v>0</v>
@@ -7240,13 +7240,13 @@
         <v>0.71</v>
       </c>
       <c r="B73">
-        <v>0.08006701412145634</v>
+        <v>0.07513087908568615</v>
       </c>
       <c r="C73">
-        <v>11283.99601250137</v>
+        <v>14375.44914247876</v>
       </c>
       <c r="D73">
-        <v>43987.35901250137</v>
+        <v>47078.81214247876</v>
       </c>
       <c r="E73">
         <v>30457.863</v>
@@ -7273,45 +7273,45 @@
         <v>5314.3</v>
       </c>
       <c r="M73">
-        <v>3399.952787478949</v>
+        <v>3017.438157478949</v>
       </c>
       <c r="N73">
-        <v>1914.347212521051</v>
+        <v>2296.861842521052</v>
       </c>
       <c r="O73">
-        <v>586.173116473946</v>
+        <v>703.2990961799461</v>
       </c>
       <c r="P73">
-        <v>1328.174096047105</v>
+        <v>1593.562746341106</v>
       </c>
       <c r="Q73">
-        <v>1757.874096047105</v>
+        <v>2023.262746341106</v>
       </c>
       <c r="R73">
         <v>2.448275862068965</v>
       </c>
       <c r="S73">
-        <v>0.1251131307850179</v>
+        <v>0.1250781134202931</v>
       </c>
       <c r="T73">
         <v>1.503876516507653</v>
       </c>
       <c r="U73">
-        <v>0.08888425489709895</v>
+        <v>0.07888425489709894</v>
       </c>
       <c r="V73">
         <v>0.3062</v>
       </c>
       <c r="W73">
-        <v>0.06166789604760724</v>
+        <v>0.05472989604760724</v>
       </c>
       <c r="X73" t="inlineStr">
         <is>
-          <t>B2/B</t>
+          <t>B1/B+</t>
         </is>
       </c>
       <c r="Y73">
-        <v>1.563051116348157</v>
+        <v>1.761195995625662</v>
       </c>
       <c r="Z73">
         <v>0</v>
@@ -7322,13 +7322,13 @@
         <v>0.72</v>
       </c>
       <c r="B74">
-        <v>0.08013569991318616</v>
+        <v>0.0770784150101006</v>
       </c>
       <c r="C74">
-        <v>10704.98599430726</v>
+        <v>12563.34033972872</v>
       </c>
       <c r="D74">
-        <v>43947.10199430725</v>
+        <v>45805.45633972871</v>
       </c>
       <c r="E74">
         <v>30996.61599999999</v>
@@ -7355,37 +7355,37 @@
         <v>5314.3</v>
       </c>
       <c r="M74">
-        <v>3447.839446457525</v>
+        <v>3211.219128857525</v>
       </c>
       <c r="N74">
-        <v>1866.460553542475</v>
+        <v>2103.080871142475</v>
       </c>
       <c r="O74">
-        <v>571.5102214947059</v>
+        <v>643.963362743826</v>
       </c>
       <c r="P74">
-        <v>1294.950332047769</v>
+        <v>1459.117508398649</v>
       </c>
       <c r="Q74">
-        <v>1724.650332047769</v>
+        <v>1888.817508398649</v>
       </c>
       <c r="R74">
         <v>2.571428571428571</v>
       </c>
       <c r="S74">
-        <v>0.1276243384246748</v>
+        <v>0.1275882123422264</v>
       </c>
       <c r="T74">
         <v>1.551492165517792</v>
       </c>
       <c r="U74">
-        <v>0.08888425489709895</v>
+        <v>0.08278425489709894</v>
       </c>
       <c r="V74">
         <v>0.3062</v>
       </c>
       <c r="W74">
-        <v>0.06166789604760724</v>
+        <v>0.05743571604760724</v>
       </c>
       <c r="X74" t="inlineStr">
         <is>
@@ -7393,7 +7393,7 @@
         </is>
       </c>
       <c r="Y74">
-        <v>1.541342073065544</v>
+        <v>1.654916649020679</v>
       </c>
       <c r="Z74">
         <v>0</v>
@@ -7404,13 +7404,13 @@
         <v>0.73</v>
       </c>
       <c r="B75">
-        <v>0.08020438570491598</v>
+        <v>0.07710481873451505</v>
       </c>
       <c r="C75">
-        <v>10126.04959479432</v>
+        <v>12007.79690351857</v>
       </c>
       <c r="D75">
-        <v>43906.91859479432</v>
+        <v>45788.66590351857</v>
       </c>
       <c r="E75">
         <v>31535.369</v>
@@ -7437,37 +7437,37 @@
         <v>5314.3</v>
       </c>
       <c r="M75">
-        <v>3495.726105436102</v>
+        <v>3255.819394536102</v>
       </c>
       <c r="N75">
-        <v>1818.573894563898</v>
+        <v>2058.480605463898</v>
       </c>
       <c r="O75">
-        <v>556.8473265154655</v>
+        <v>630.3067613930456</v>
       </c>
       <c r="P75">
-        <v>1261.726568048432</v>
+        <v>1428.173844070852</v>
       </c>
       <c r="Q75">
-        <v>1691.426568048432</v>
+        <v>1857.873844070852</v>
       </c>
       <c r="R75">
         <v>2.703703703703703</v>
       </c>
       <c r="S75">
-        <v>0.130321561445047</v>
+        <v>0.1302842445176362</v>
       </c>
       <c r="T75">
         <v>1.602634899639792</v>
       </c>
       <c r="U75">
-        <v>0.08888425489709895</v>
+        <v>0.08278425489709894</v>
       </c>
       <c r="V75">
         <v>0.3062</v>
       </c>
       <c r="W75">
-        <v>0.06166789604760724</v>
+        <v>0.05743571604760724</v>
       </c>
       <c r="X75" t="inlineStr">
         <is>
@@ -7475,7 +7475,7 @@
         </is>
       </c>
       <c r="Y75">
-        <v>1.520227798092043</v>
+        <v>1.632246557938204</v>
       </c>
       <c r="Z75">
         <v>0</v>
@@ -7486,13 +7486,13 @@
         <v>0.74</v>
       </c>
       <c r="B76">
-        <v>0.08864168709664579</v>
+        <v>0.0771312224589295</v>
       </c>
       <c r="C76">
-        <v>5153.694581703283</v>
+        <v>11452.26577219386</v>
       </c>
       <c r="D76">
-        <v>39473.31658170328</v>
+        <v>45771.88777219386</v>
       </c>
       <c r="E76">
         <v>32074.122</v>
@@ -7519,45 +7519,45 @@
         <v>5314.3</v>
       </c>
       <c r="M76">
-        <v>4193.456633014679</v>
+        <v>3300.419660214679</v>
       </c>
       <c r="N76">
-        <v>1120.843366985321</v>
+        <v>2013.880339785322</v>
       </c>
       <c r="O76">
-        <v>343.2022389709053</v>
+        <v>616.6501600422655</v>
       </c>
       <c r="P76">
-        <v>777.6411280144158</v>
+        <v>1397.230179743056</v>
       </c>
       <c r="Q76">
-        <v>1207.341128014416</v>
+        <v>1826.930179743056</v>
       </c>
       <c r="R76">
         <v>2.846153846153846</v>
       </c>
       <c r="S76">
-        <v>0.133226263159294</v>
+        <v>0.1331876637834621</v>
       </c>
       <c r="T76">
         <v>1.657711690232715</v>
       </c>
       <c r="U76">
-        <v>0.1051842548970989</v>
+        <v>0.08278425489709894</v>
       </c>
       <c r="V76">
         <v>0.3062</v>
       </c>
       <c r="W76">
-        <v>0.07297683604760724</v>
+        <v>0.05743571604760724</v>
       </c>
       <c r="X76" t="inlineStr">
         <is>
-          <t>B3/B-</t>
+          <t>B2/B</t>
         </is>
       </c>
       <c r="Y76">
-        <v>1.26728388178884</v>
+        <v>1.61018917202012</v>
       </c>
       <c r="Z76">
         <v>0</v>
@@ -7568,13 +7568,13 @@
         <v>0.75</v>
       </c>
       <c r="B77">
-        <v>0.08882346228837561</v>
+        <v>0.07715762618334396</v>
       </c>
       <c r="C77">
-        <v>4529.254640397034</v>
+        <v>10896.74693223304</v>
       </c>
       <c r="D77">
-        <v>39387.62964039703</v>
+        <v>45755.12193223304</v>
       </c>
       <c r="E77">
         <v>32612.875</v>
@@ -7601,45 +7601,45 @@
         <v>5314.3</v>
       </c>
       <c r="M77">
-        <v>4250.124965893256</v>
+        <v>3345.019925893256</v>
       </c>
       <c r="N77">
-        <v>1064.175034106745</v>
+        <v>1969.280074106744</v>
       </c>
       <c r="O77">
-        <v>325.8503954434852</v>
+        <v>602.9935586914852</v>
       </c>
       <c r="P77">
-        <v>738.3246386632593</v>
+        <v>1366.286515415259</v>
       </c>
       <c r="Q77">
-        <v>1168.024638663259</v>
+        <v>1795.986515415259</v>
       </c>
       <c r="R77">
         <v>3</v>
       </c>
       <c r="S77">
-        <v>0.1363633410106807</v>
+        <v>0.1363233565905541</v>
       </c>
       <c r="T77">
         <v>1.717194624073072</v>
       </c>
       <c r="U77">
-        <v>0.1051842548970989</v>
+        <v>0.08278425489709894</v>
       </c>
       <c r="V77">
         <v>0.3062</v>
       </c>
       <c r="W77">
-        <v>0.07297683604760724</v>
+        <v>0.05743571604760724</v>
       </c>
       <c r="X77" t="inlineStr">
         <is>
-          <t>B3/B-</t>
+          <t>B2/B</t>
         </is>
       </c>
       <c r="Y77">
-        <v>1.250386763364989</v>
+        <v>1.588719983059852</v>
       </c>
       <c r="Z77">
         <v>0</v>
@@ -7650,13 +7650,13 @@
         <v>0.76</v>
       </c>
       <c r="B78">
-        <v>0.1085325551045531</v>
+        <v>0.07718402990775841</v>
       </c>
       <c r="C78">
-        <v>-3513.749794620991</v>
+        <v>10341.24037013442</v>
       </c>
       <c r="D78">
-        <v>31883.37820537901</v>
+        <v>45738.36837013442</v>
       </c>
       <c r="E78">
         <v>33151.628</v>
@@ -7683,45 +7683,45 @@
         <v>5314.3</v>
       </c>
       <c r="M78">
-        <v>5645.702254371832</v>
+        <v>3389.620191571832</v>
       </c>
       <c r="N78">
-        <v>-331.402254371832</v>
+        <v>1924.679808428168</v>
       </c>
       <c r="O78">
-        <v>-101.475370288655</v>
+        <v>589.3369573407051</v>
       </c>
       <c r="P78">
-        <v>-229.926884083177</v>
+        <v>1335.342851087463</v>
       </c>
       <c r="Q78">
-        <v>199.773115916823</v>
+        <v>1765.042851087463</v>
       </c>
       <c r="R78">
         <v>3.166666666666667</v>
       </c>
       <c r="S78">
-        <v>0.1414346626726052</v>
+        <v>0.1397203571315705</v>
       </c>
       <c r="T78">
-        <v>1.813353248496778</v>
+        <v>1.781634469066793</v>
       </c>
       <c r="U78">
-        <v>0.1378842548970989</v>
+        <v>0.08278425489709894</v>
       </c>
       <c r="V78">
-        <v>0.288226085380242</v>
+        <v>0.3062</v>
       </c>
       <c r="W78">
-        <v>0.09814241587253665</v>
+        <v>0.05743571604760724</v>
       </c>
       <c r="X78" t="inlineStr">
         <is>
-          <t>Caa/CCC</t>
+          <t>B2/B</t>
         </is>
       </c>
       <c r="Y78">
-        <v>0.9413000828877921</v>
+        <v>1.567815772756433</v>
       </c>
       <c r="Z78">
         <v>0</v>
@@ -7732,13 +7732,13 @@
         <v>0.77</v>
       </c>
       <c r="B79">
-        <v>0.1094533976535241</v>
+        <v>0.07721043363217286</v>
       </c>
       <c r="C79">
-        <v>-4333.810618336218</v>
+        <v>9785.746072416056</v>
       </c>
       <c r="D79">
-        <v>31602.07038166378</v>
+        <v>45721.62707241606</v>
       </c>
       <c r="E79">
         <v>33690.381</v>
@@ -7765,45 +7765,45 @@
         <v>5314.3</v>
       </c>
       <c r="M79">
-        <v>5719.987810350409</v>
+        <v>3434.220457250409</v>
       </c>
       <c r="N79">
-        <v>-405.6878103504087</v>
+        <v>1880.079542749591</v>
       </c>
       <c r="O79">
-        <v>-124.2216075292951</v>
+        <v>575.6803559899248</v>
       </c>
       <c r="P79">
-        <v>-281.4662028211135</v>
+        <v>1304.399186759666</v>
       </c>
       <c r="Q79">
-        <v>148.2337971788865</v>
+        <v>1734.099186759666</v>
       </c>
       <c r="R79">
         <v>3.347826086956522</v>
       </c>
       <c r="S79">
-        <v>0.1455926914844576</v>
+        <v>0.1434127490239795</v>
       </c>
       <c r="T79">
-        <v>1.892194694083595</v>
+        <v>1.851677778842576</v>
       </c>
       <c r="U79">
-        <v>0.1378842548970989</v>
+        <v>0.08278425489709894</v>
       </c>
       <c r="V79">
-        <v>0.2844828894662128</v>
+        <v>0.3062</v>
       </c>
       <c r="W79">
-        <v>0.09865854365207642</v>
+        <v>0.05743571604760724</v>
       </c>
       <c r="X79" t="inlineStr">
         <is>
-          <t>Caa/CCC</t>
+          <t>B2/B</t>
         </is>
       </c>
       <c r="Y79">
-        <v>0.929075406486652</v>
+        <v>1.547454528954401</v>
       </c>
       <c r="Z79">
         <v>0</v>
@@ -7814,13 +7814,13 @@
         <v>0.78</v>
       </c>
       <c r="B80">
-        <v>0.1103742402024951</v>
+        <v>0.07723683735658732</v>
       </c>
       <c r="C80">
-        <v>-5148.950884666738</v>
+        <v>9230.264025615739</v>
       </c>
       <c r="D80">
-        <v>31325.68311533326</v>
+        <v>45704.89802561574</v>
       </c>
       <c r="E80">
         <v>34229.134</v>
@@ -7847,45 +7847,45 @@
         <v>5314.3</v>
       </c>
       <c r="M80">
-        <v>5794.273366328986</v>
+        <v>3478.820722928986</v>
       </c>
       <c r="N80">
-        <v>-479.9733663289853</v>
+        <v>1835.479277071014</v>
       </c>
       <c r="O80">
-        <v>-146.9678447699353</v>
+        <v>562.0237546391446</v>
       </c>
       <c r="P80">
-        <v>-333.00552155905</v>
+        <v>1273.45552243187</v>
       </c>
       <c r="Q80">
-        <v>96.69447844094998</v>
+        <v>1703.15552243187</v>
       </c>
       <c r="R80">
         <v>3.545454545454546</v>
       </c>
       <c r="S80">
-        <v>0.1501287229155693</v>
+        <v>0.1474408129066076</v>
       </c>
       <c r="T80">
-        <v>1.978203543814667</v>
+        <v>1.928088662234339</v>
       </c>
       <c r="U80">
-        <v>0.1378842548970989</v>
+        <v>0.08278425489709894</v>
       </c>
       <c r="V80">
-        <v>0.2808356729345948</v>
+        <v>0.3062</v>
       </c>
       <c r="W80">
-        <v>0.09916143738598696</v>
+        <v>0.05743571604760724</v>
       </c>
       <c r="X80" t="inlineStr">
         <is>
-          <t>Caa/CCC</t>
+          <t>B2/B</t>
         </is>
       </c>
       <c r="Y80">
-        <v>0.9171641833265667</v>
+        <v>1.527615368326781</v>
       </c>
       <c r="Z80">
         <v>0</v>
@@ -7896,13 +7896,13 @@
         <v>0.79</v>
       </c>
       <c r="B81">
-        <v>0.1112950827514661</v>
+        <v>0.07726324108100177</v>
       </c>
       <c r="C81">
-        <v>-5959.298577791058</v>
+        <v>8674.794216290938</v>
       </c>
       <c r="D81">
-        <v>31054.08842220894</v>
+        <v>45688.18121629094</v>
       </c>
       <c r="E81">
         <v>34767.887</v>
@@ -7929,45 +7929,45 @@
         <v>5314.3</v>
       </c>
       <c r="M81">
-        <v>5868.558922307563</v>
+        <v>3523.420988607563</v>
       </c>
       <c r="N81">
-        <v>-554.2589223075629</v>
+        <v>1790.879011392437</v>
       </c>
       <c r="O81">
-        <v>-169.7140820105758</v>
+        <v>548.3671532883644</v>
       </c>
       <c r="P81">
-        <v>-384.5448402969871</v>
+        <v>1242.511858104073</v>
       </c>
       <c r="Q81">
-        <v>45.15515970301288</v>
+        <v>1672.211858104073</v>
       </c>
       <c r="R81">
         <v>3.761904761904763</v>
       </c>
       <c r="S81">
-        <v>0.1550967573401202</v>
+        <v>0.1518525019209145</v>
       </c>
       <c r="T81">
-        <v>2.072403712567747</v>
+        <v>2.011776772615794</v>
       </c>
       <c r="U81">
-        <v>0.1378842548970989</v>
+        <v>0.08278425489709894</v>
       </c>
       <c r="V81">
-        <v>0.2772807909987138</v>
+        <v>0.3062</v>
       </c>
       <c r="W81">
-        <v>0.09965159963296306</v>
+        <v>0.05743571604760724</v>
       </c>
       <c r="X81" t="inlineStr">
         <is>
-          <t>Caa/CCC</t>
+          <t>B2/B</t>
         </is>
       </c>
       <c r="Y81">
-        <v>0.9055545101199012</v>
+        <v>1.508278464930239</v>
       </c>
       <c r="Z81">
         <v>0</v>
@@ -7978,13 +7978,13 @@
         <v>0.8</v>
       </c>
       <c r="B82">
-        <v>0.112215925300437</v>
+        <v>0.08517121280541622</v>
       </c>
       <c r="C82">
-        <v>-6764.977281530868</v>
+        <v>3625.281352365557</v>
       </c>
       <c r="D82">
-        <v>30787.16271846913</v>
+        <v>41177.42135236556</v>
       </c>
       <c r="E82">
         <v>35306.64</v>
@@ -8011,45 +8011,45 @@
         <v>5314.3</v>
       </c>
       <c r="M82">
-        <v>5942.844478286139</v>
+        <v>4180.044662286139</v>
       </c>
       <c r="N82">
-        <v>-628.5444782861387</v>
+        <v>1134.255337713861</v>
       </c>
       <c r="O82">
-        <v>-192.4603192512157</v>
+        <v>347.3089844079843</v>
       </c>
       <c r="P82">
-        <v>-436.084159034923</v>
+        <v>786.9463533058768</v>
       </c>
       <c r="Q82">
-        <v>-6.384159034923016</v>
+        <v>1216.646353305877</v>
       </c>
       <c r="R82">
         <v>4.000000000000001</v>
       </c>
       <c r="S82">
-        <v>0.1605615952071262</v>
+        <v>0.1567053598366522</v>
       </c>
       <c r="T82">
-        <v>2.176023898196134</v>
+        <v>2.103833694035394</v>
       </c>
       <c r="U82">
-        <v>0.1378842548970989</v>
+        <v>0.09698425489709894</v>
       </c>
       <c r="V82">
-        <v>0.2738147811112299</v>
+        <v>0.3062</v>
       </c>
       <c r="W82">
-        <v>0.1001295078237648</v>
+        <v>0.06728767604760724</v>
       </c>
       <c r="X82" t="inlineStr">
         <is>
-          <t>Caa/CCC</t>
+          <t>B3/B-</t>
         </is>
       </c>
       <c r="Y82">
-        <v>0.8942350787434025</v>
+        <v>1.271350052296694</v>
       </c>
       <c r="Z82">
         <v>0</v>
@@ -8060,13 +8060,13 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="B83">
-        <v>0.113136767849408</v>
+        <v>0.08529613612983067</v>
       </c>
       <c r="C83">
-        <v>-7566.106366856009</v>
+        <v>3022.406421118911</v>
       </c>
       <c r="D83">
-        <v>30524.78663314399</v>
+        <v>41113.29942111891</v>
       </c>
       <c r="E83">
         <v>35845.393</v>
@@ -8093,45 +8093,45 @@
         <v>5314.3</v>
       </c>
       <c r="M83">
-        <v>6017.130034264716</v>
+        <v>4232.295220564717</v>
       </c>
       <c r="N83">
-        <v>-702.8300342647162</v>
+        <v>1082.004779435283</v>
       </c>
       <c r="O83">
-        <v>-215.2065564918561</v>
+        <v>331.3098634630837</v>
       </c>
       <c r="P83">
-        <v>-487.6234777728601</v>
+        <v>750.6949159721994</v>
       </c>
       <c r="Q83">
-        <v>-57.92347777286011</v>
+        <v>1180.394915972199</v>
       </c>
       <c r="R83">
         <v>4.263157894736843</v>
       </c>
       <c r="S83">
-        <v>0.166601679165396</v>
+        <v>0.1620690449014148</v>
       </c>
       <c r="T83">
-        <v>2.290551471785404</v>
+        <v>2.20558081770969</v>
       </c>
       <c r="U83">
-        <v>0.1378842548970989</v>
+        <v>0.09698425489709894</v>
       </c>
       <c r="V83">
-        <v>0.2704343517147949</v>
+        <v>0.3062</v>
       </c>
       <c r="W83">
-        <v>0.1005956158123244</v>
+        <v>0.06728767604760724</v>
       </c>
       <c r="X83" t="inlineStr">
         <is>
-          <t>Caa/CCC</t>
+          <t>B3/B-</t>
         </is>
       </c>
       <c r="Y83">
-        <v>0.8831951394996567</v>
+        <v>1.25565437263871</v>
       </c>
       <c r="Z83">
         <v>0</v>
@@ -8142,13 +8142,13 @@
         <v>0.8200000000000001</v>
       </c>
       <c r="B84">
-        <v>0.114057610398379</v>
+        <v>0.1033312028104755</v>
       </c>
       <c r="C84">
-        <v>-8362.801169882427</v>
+        <v>-5062.648306489005</v>
       </c>
       <c r="D84">
-        <v>30266.84483011757</v>
+        <v>33566.997693511</v>
       </c>
       <c r="E84">
         <v>36384.146</v>
@@ -8175,37 +8175,37 @@
         <v>5314.3</v>
       </c>
       <c r="M84">
-        <v>6091.415590243293</v>
+        <v>5548.029314443294</v>
       </c>
       <c r="N84">
-        <v>-777.1155902432929</v>
+        <v>-233.7293144432933</v>
       </c>
       <c r="O84">
-        <v>-237.9527937324963</v>
+        <v>-71.56791608253643</v>
       </c>
       <c r="P84">
-        <v>-539.1627965107966</v>
+        <v>-162.1613983607569</v>
       </c>
       <c r="Q84">
-        <v>-109.4627965107966</v>
+        <v>267.5386016392431</v>
       </c>
       <c r="R84">
         <v>4.555555555555557</v>
       </c>
       <c r="S84">
-        <v>0.1733128835634736</v>
+        <v>0.1697550636306758</v>
       </c>
       <c r="T84">
-        <v>2.417804331329039</v>
+        <v>2.351381752844139</v>
       </c>
       <c r="U84">
-        <v>0.1378842548970989</v>
+        <v>0.125584254897099</v>
       </c>
       <c r="V84">
-        <v>0.267136371815834</v>
+        <v>0.2933002995791276</v>
       </c>
       <c r="W84">
-        <v>0.1010503553133583</v>
+        <v>0.08875035531335831</v>
       </c>
       <c r="X84" t="inlineStr">
         <is>
@@ -8213,7 +8213,7 @@
         </is>
       </c>
       <c r="Y84">
-        <v>0.872424467066734</v>
+        <v>0.9578716511401947</v>
       </c>
       <c r="Z84">
         <v>0</v>
@@ -8224,13 +8224,13 @@
         <v>0.8300000000000001</v>
       </c>
       <c r="B85">
-        <v>0.11497845294735</v>
+        <v>0.1041290453594464</v>
       </c>
       <c r="C85">
-        <v>-9155.173160921171</v>
+        <v>-5871.766999144464</v>
       </c>
       <c r="D85">
-        <v>30013.22583907883</v>
+        <v>33296.63200085554</v>
       </c>
       <c r="E85">
         <v>36922.899</v>
@@ -8257,37 +8257,37 @@
         <v>5314.3</v>
       </c>
       <c r="M85">
-        <v>6165.70114622187</v>
+        <v>5615.688208521871</v>
       </c>
       <c r="N85">
-        <v>-851.4011462218696</v>
+        <v>-301.3882085218711</v>
       </c>
       <c r="O85">
-        <v>-260.6990309731365</v>
+        <v>-92.28506944939694</v>
       </c>
       <c r="P85">
-        <v>-590.7021152487331</v>
+        <v>-209.1031390724742</v>
       </c>
       <c r="Q85">
-        <v>-161.0021152487331</v>
+        <v>220.5968609275258</v>
       </c>
       <c r="R85">
         <v>4.882352941176473</v>
       </c>
       <c r="S85">
-        <v>0.1808136414201485</v>
+        <v>0.1770465379618921</v>
       </c>
       <c r="T85">
-        <v>2.560028115524864</v>
+        <v>2.489698326540853</v>
       </c>
       <c r="U85">
-        <v>0.1378842548970989</v>
+        <v>0.125584254897099</v>
       </c>
       <c r="V85">
-        <v>0.2639178613120288</v>
+        <v>0.2897665610299815</v>
       </c>
       <c r="W85">
-        <v>0.101494137236054</v>
+        <v>0.08919413723605397</v>
       </c>
       <c r="X85" t="inlineStr">
         <is>
@@ -8295,7 +8295,7 @@
         </is>
       </c>
       <c r="Y85">
-        <v>0.8619133289093035</v>
+        <v>0.9463310288373007</v>
       </c>
       <c r="Z85">
         <v>0</v>
@@ -8306,13 +8306,13 @@
         <v>0.84</v>
       </c>
       <c r="B86">
-        <v>0.115899295496321</v>
+        <v>0.1049268879084174</v>
       </c>
       <c r="C86">
-        <v>-9943.330105098728</v>
+        <v>-6676.565165585671</v>
       </c>
       <c r="D86">
-        <v>29763.82189490126</v>
+        <v>33030.58683441432</v>
       </c>
       <c r="E86">
         <v>37461.65199999999</v>
@@ -8339,37 +8339,37 @@
         <v>5314.3</v>
       </c>
       <c r="M86">
-        <v>6239.986702200446</v>
+        <v>5683.347102600446</v>
       </c>
       <c r="N86">
-        <v>-925.6867022004453</v>
+        <v>-369.0471026004461</v>
       </c>
       <c r="O86">
-        <v>-283.4452682137764</v>
+        <v>-113.0022228162566</v>
       </c>
       <c r="P86">
-        <v>-642.2414339866689</v>
+        <v>-256.0448797841895</v>
       </c>
       <c r="Q86">
-        <v>-212.5414339866689</v>
+        <v>173.6551202158105</v>
       </c>
       <c r="R86">
         <v>5.249999999999999</v>
       </c>
       <c r="S86">
-        <v>0.1892519940089077</v>
+        <v>0.1852494465845103</v>
       </c>
       <c r="T86">
-        <v>2.720029872745167</v>
+        <v>2.645304471949655</v>
       </c>
       <c r="U86">
-        <v>0.1378842548970989</v>
+        <v>0.125584254897099</v>
       </c>
       <c r="V86">
-        <v>0.2607759820106951</v>
+        <v>0.286316959112958</v>
       </c>
       <c r="W86">
-        <v>0.101927352922495</v>
+        <v>0.08962735292249499</v>
       </c>
       <c r="X86" t="inlineStr">
         <is>
@@ -8377,7 +8377,7 @@
         </is>
       </c>
       <c r="Y86">
-        <v>0.8516524559460976</v>
+        <v>0.9350651832559045</v>
       </c>
       <c r="Z86">
         <v>0</v>
@@ -8388,13 +8388,13 @@
         <v>0.85</v>
       </c>
       <c r="B87">
-        <v>0.116820138045292</v>
+        <v>0.1057247304573884</v>
       </c>
       <c r="C87">
-        <v>-10727.37621503507</v>
+        <v>-7477.145549861671</v>
       </c>
       <c r="D87">
-        <v>29518.52878496493</v>
+        <v>32768.75945013833</v>
       </c>
       <c r="E87">
         <v>38000.405</v>
@@ -8421,37 +8421,37 @@
         <v>5314.3</v>
       </c>
       <c r="M87">
-        <v>6314.272258179023</v>
+        <v>5751.005996679024</v>
       </c>
       <c r="N87">
-        <v>-999.9722581790229</v>
+        <v>-436.7059966790239</v>
       </c>
       <c r="O87">
-        <v>-306.1915054544168</v>
+        <v>-133.7193761831171</v>
       </c>
       <c r="P87">
-        <v>-693.7807527246061</v>
+        <v>-302.9866204959068</v>
       </c>
       <c r="Q87">
-        <v>-264.0807527246062</v>
+        <v>126.7133795040932</v>
       </c>
       <c r="R87">
         <v>5.666666666666666</v>
       </c>
       <c r="S87">
-        <v>0.1988154602761683</v>
+        <v>0.1945460763568109</v>
       </c>
       <c r="T87">
-        <v>2.901365197594845</v>
+        <v>2.821658103412965</v>
       </c>
       <c r="U87">
-        <v>0.1378842548970989</v>
+        <v>0.125584254897099</v>
       </c>
       <c r="V87">
-        <v>0.2577080292811575</v>
+        <v>0.2829485242998643</v>
       </c>
       <c r="W87">
-        <v>0.1023503752986668</v>
+        <v>0.0900503752986668</v>
       </c>
       <c r="X87" t="inlineStr">
         <is>
@@ -8459,7 +8459,7 @@
         </is>
       </c>
       <c r="Y87">
-        <v>0.8416330152879081</v>
+        <v>0.9240644163940701</v>
       </c>
       <c r="Z87">
         <v>0</v>
@@ -8470,13 +8470,13 @@
         <v>0.86</v>
       </c>
       <c r="B88">
-        <v>0.117740980594263</v>
+        <v>0.1065225730063594</v>
       </c>
       <c r="C88">
-        <v>-11507.4122960337</v>
+        <v>-8273.607663909104</v>
       </c>
       <c r="D88">
-        <v>29277.24570396629</v>
+        <v>32511.05033609089</v>
       </c>
       <c r="E88">
         <v>38539.158</v>
@@ -8503,37 +8503,37 @@
         <v>5314.3</v>
       </c>
       <c r="M88">
-        <v>6388.557814157599</v>
+        <v>5818.6648907576</v>
       </c>
       <c r="N88">
-        <v>-1074.257814157599</v>
+        <v>-504.3648907575998</v>
       </c>
       <c r="O88">
-        <v>-328.9377426950567</v>
+        <v>-154.4365295499771</v>
       </c>
       <c r="P88">
-        <v>-745.3200714625419</v>
+        <v>-349.9283612076227</v>
       </c>
       <c r="Q88">
-        <v>-315.6200714625419</v>
+        <v>79.77163879237725</v>
       </c>
       <c r="R88">
         <v>6.142857142857142</v>
       </c>
       <c r="S88">
-        <v>0.2097451360101803</v>
+        <v>0.2051707960965831</v>
       </c>
       <c r="T88">
-        <v>3.108605568851619</v>
+        <v>3.023205110799606</v>
       </c>
       <c r="U88">
-        <v>0.1378842548970989</v>
+        <v>0.125584254897099</v>
       </c>
       <c r="V88">
-        <v>0.2547114242895162</v>
+        <v>0.2796584251800985</v>
       </c>
       <c r="W88">
-        <v>0.1027635599451602</v>
+        <v>0.0904635599451602</v>
       </c>
       <c r="X88" t="inlineStr">
         <is>
@@ -8541,7 +8541,7 @@
         </is>
       </c>
       <c r="Y88">
-        <v>0.8318465848775838</v>
+        <v>0.9133194813197206</v>
       </c>
       <c r="Z88">
         <v>0</v>
@@ -8552,13 +8552,13 @@
         <v>0.87</v>
       </c>
       <c r="B89">
-        <v>0.118661823143234</v>
+        <v>0.1073204155553304</v>
       </c>
       <c r="C89">
-        <v>-12283.5358842089</v>
+        <v>-9066.04791365494</v>
       </c>
       <c r="D89">
-        <v>29039.8751157911</v>
+        <v>32257.36308634506</v>
       </c>
       <c r="E89">
         <v>39077.911</v>
@@ -8585,37 +8585,37 @@
         <v>5314.3</v>
       </c>
       <c r="M89">
-        <v>6462.843370136176</v>
+        <v>5886.323784836178</v>
       </c>
       <c r="N89">
-        <v>-1148.543370136176</v>
+        <v>-572.0237848361776</v>
       </c>
       <c r="O89">
-        <v>-351.6839799356972</v>
+        <v>-175.1536829168376</v>
       </c>
       <c r="P89">
-        <v>-796.8593902004791</v>
+        <v>-396.87010191934</v>
       </c>
       <c r="Q89">
-        <v>-367.1593902004791</v>
+        <v>32.82989808066003</v>
       </c>
       <c r="R89">
         <v>6.692307692307692</v>
       </c>
       <c r="S89">
-        <v>0.2223563003186557</v>
+        <v>0.2174300881040126</v>
       </c>
       <c r="T89">
-        <v>3.347729074147898</v>
+        <v>3.255759350091883</v>
       </c>
       <c r="U89">
-        <v>0.1378842548970989</v>
+        <v>0.125584254897099</v>
       </c>
       <c r="V89">
-        <v>0.251783706768947</v>
+        <v>0.2764439605228559</v>
       </c>
       <c r="W89">
-        <v>0.103167246094033</v>
+        <v>0.09086724609403306</v>
       </c>
       <c r="X89" t="inlineStr">
         <is>
@@ -8623,7 +8623,7 @@
         </is>
       </c>
       <c r="Y89">
-        <v>0.8222851298789908</v>
+        <v>0.90282155624708</v>
       </c>
       <c r="Z89">
         <v>0</v>
@@ -8634,13 +8634,13 @@
         <v>0.88</v>
       </c>
       <c r="B90">
-        <v>0.119582665692205</v>
+        <v>0.1081182581043014</v>
       </c>
       <c r="C90">
-        <v>-13055.84137794756</v>
+        <v>-9854.559719260797</v>
       </c>
       <c r="D90">
-        <v>28806.32262205244</v>
+        <v>32007.6042807392</v>
       </c>
       <c r="E90">
         <v>39616.664</v>
@@ -8667,37 +8667,37 @@
         <v>5314.3</v>
       </c>
       <c r="M90">
-        <v>6537.128926114753</v>
+        <v>5953.982678914754</v>
       </c>
       <c r="N90">
-        <v>-1222.828926114753</v>
+        <v>-639.6826789147535</v>
       </c>
       <c r="O90">
-        <v>-374.4302171763374</v>
+        <v>-195.8708362836975</v>
       </c>
       <c r="P90">
-        <v>-848.3987089384156</v>
+        <v>-443.811842631056</v>
       </c>
       <c r="Q90">
-        <v>-418.6987089384156</v>
+        <v>-14.11184263105599</v>
       </c>
       <c r="R90">
         <v>7.333333333333334</v>
       </c>
       <c r="S90">
-        <v>0.2370693253452104</v>
+        <v>0.2317325954460137</v>
       </c>
       <c r="T90">
-        <v>3.626706496993557</v>
+        <v>3.527072629266207</v>
       </c>
       <c r="U90">
-        <v>0.1378842548970989</v>
+        <v>0.125584254897099</v>
       </c>
       <c r="V90">
-        <v>0.2489225282829362</v>
+        <v>0.2733025518805508</v>
       </c>
       <c r="W90">
-        <v>0.1035617575577042</v>
+        <v>0.09126175755770426</v>
       </c>
       <c r="X90" t="inlineStr">
         <is>
@@ -8705,7 +8705,7 @@
         </is>
       </c>
       <c r="Y90">
-        <v>0.8129409806758204</v>
+        <v>0.892562220380636</v>
       </c>
       <c r="Z90">
         <v>0</v>
@@ -8716,13 +8716,13 @@
         <v>0.89</v>
       </c>
       <c r="B91">
-        <v>0.120503508241176</v>
+        <v>0.1089161006532724</v>
       </c>
       <c r="C91">
-        <v>-13824.42016307807</v>
+        <v>-10639.23362982415</v>
       </c>
       <c r="D91">
-        <v>28576.49683692194</v>
+        <v>31761.68337017585</v>
       </c>
       <c r="E91">
         <v>40155.417</v>
@@ -8749,37 +8749,37 @@
         <v>5314.3</v>
       </c>
       <c r="M91">
-        <v>6611.41448209333</v>
+        <v>6021.641572993331</v>
       </c>
       <c r="N91">
-        <v>-1297.11448209333</v>
+        <v>-707.3415729933313</v>
       </c>
       <c r="O91">
-        <v>-397.1764544169775</v>
+        <v>-216.5879896505581</v>
       </c>
       <c r="P91">
-        <v>-899.938027676352</v>
+        <v>-490.7535833427733</v>
       </c>
       <c r="Q91">
-        <v>-470.238027676352</v>
+        <v>-61.05358334277327</v>
       </c>
       <c r="R91">
         <v>8.090909090909092</v>
       </c>
       <c r="S91">
-        <v>0.2544574458311386</v>
+        <v>0.2486355586683786</v>
       </c>
       <c r="T91">
-        <v>3.956407087629334</v>
+        <v>3.847715595563135</v>
       </c>
       <c r="U91">
-        <v>0.1378842548970989</v>
+        <v>0.125584254897099</v>
       </c>
       <c r="V91">
-        <v>0.2461256459426785</v>
+        <v>0.2702317366908816</v>
       </c>
       <c r="W91">
-        <v>0.1039474035952255</v>
+        <v>0.09164740359522555</v>
       </c>
       <c r="X91" t="inlineStr">
         <is>
@@ -8787,7 +8787,7 @@
         </is>
       </c>
       <c r="Y91">
-        <v>0.8038068123536202</v>
+        <v>0.882533431387595</v>
       </c>
       <c r="Z91">
         <v>0</v>
@@ -8798,13 +8798,13 @@
         <v>0.9</v>
       </c>
       <c r="B92">
-        <v>0.2002877850715729</v>
+        <v>0.1097139432022434</v>
       </c>
       <c r="C92">
-        <v>-26043.12061147188</v>
+        <v>-11420.15743283221</v>
       </c>
       <c r="D92">
-        <v>16896.54938852811</v>
+        <v>31519.51256716779</v>
       </c>
       <c r="E92">
         <v>40694.17</v>
@@ -8831,45 +8831,45 @@
         <v>5314.3</v>
       </c>
       <c r="M92">
-        <v>10802.31171107191</v>
+        <v>6089.300467071907</v>
       </c>
       <c r="N92">
-        <v>-5488.011711071907</v>
+        <v>-775.0004670719072</v>
       </c>
       <c r="O92">
-        <v>-1680.429185930218</v>
+        <v>-237.305143017418</v>
       </c>
       <c r="P92">
-        <v>-3807.582525141689</v>
+        <v>-537.6953240544892</v>
       </c>
       <c r="Q92">
-        <v>-3377.882525141689</v>
+        <v>-107.9953240544892</v>
       </c>
       <c r="R92">
         <v>9.000000000000002</v>
       </c>
       <c r="S92">
-        <v>0.2998575332285112</v>
+        <v>0.2689191145352164</v>
       </c>
       <c r="T92">
-        <v>4.817249732580136</v>
+        <v>4.232487155119449</v>
       </c>
       <c r="U92">
-        <v>0.222784254897099</v>
+        <v>0.125584254897099</v>
       </c>
       <c r="V92">
-        <v>0.1506380026353202</v>
+        <v>0.2672291618387607</v>
       </c>
       <c r="W92">
-        <v>0.1892244797208019</v>
+        <v>0.09202447972080191</v>
       </c>
       <c r="X92" t="inlineStr">
         <is>
-          <t>C2/C</t>
+          <t>Caa/CCC</t>
         </is>
       </c>
       <c r="Y92">
-        <v>0.4919595121989555</v>
+        <v>0.8727275043721774</v>
       </c>
       <c r="Z92">
         <v>0</v>
@@ -8880,13 +8880,13 @@
         <v>0.91</v>
       </c>
       <c r="B93">
-        <v>0.2020576276205439</v>
+        <v>0.1105117857512144</v>
       </c>
       <c r="C93">
-        <v>-26733.69304534289</v>
+        <v>-12197.41625864644</v>
       </c>
       <c r="D93">
-        <v>16744.7299546571</v>
+        <v>31281.00674135355</v>
       </c>
       <c r="E93">
         <v>41232.923</v>
@@ -8913,45 +8913,45 @@
         <v>5314.3</v>
       </c>
       <c r="M93">
-        <v>10922.33739675048</v>
+        <v>6156.959361150485</v>
       </c>
       <c r="N93">
-        <v>-5608.037396750485</v>
+        <v>-842.659361150485</v>
       </c>
       <c r="O93">
-        <v>-1717.181050884999</v>
+        <v>-258.0222963842785</v>
       </c>
       <c r="P93">
-        <v>-3890.856345865486</v>
+        <v>-584.6370647662064</v>
       </c>
       <c r="Q93">
-        <v>-3461.156345865486</v>
+        <v>-154.9370647662064</v>
       </c>
       <c r="R93">
         <v>10.11111111111111</v>
       </c>
       <c r="S93">
-        <v>0.3280861480316791</v>
+        <v>0.2937101272613517</v>
       </c>
       <c r="T93">
-        <v>5.352499702866819</v>
+        <v>4.702763505688278</v>
       </c>
       <c r="U93">
-        <v>0.222784254897099</v>
+        <v>0.125584254897099</v>
       </c>
       <c r="V93">
-        <v>0.148982639968998</v>
+        <v>0.2642925776427303</v>
       </c>
       <c r="W93">
-        <v>0.189593268459003</v>
+        <v>0.092393268459003</v>
       </c>
       <c r="X93" t="inlineStr">
         <is>
-          <t>C2/C</t>
+          <t>Caa/CCC</t>
         </is>
       </c>
       <c r="Y93">
-        <v>0.4865533637132526</v>
+        <v>0.8631370922362193</v>
       </c>
       <c r="Z93">
         <v>0</v>
@@ -8962,13 +8962,13 @@
         <v>0.92</v>
       </c>
       <c r="B94">
-        <v>0.2038274701695148</v>
+        <v>0.1113096283001853</v>
       </c>
       <c r="C94">
-        <v>-27421.56150902872</v>
+        <v>-12971.09268027894</v>
       </c>
       <c r="D94">
-        <v>16595.61449097128</v>
+        <v>31046.08331972106</v>
       </c>
       <c r="E94">
         <v>41771.676</v>
@@ -8995,45 +8995,45 @@
         <v>5314.3</v>
       </c>
       <c r="M94">
-        <v>11042.36308242906</v>
+        <v>6224.618255229061</v>
       </c>
       <c r="N94">
-        <v>-5728.063082429061</v>
+        <v>-910.3182552290609</v>
       </c>
       <c r="O94">
-        <v>-1753.932915839779</v>
+        <v>-278.7394497511385</v>
       </c>
       <c r="P94">
-        <v>-3974.130166589282</v>
+        <v>-631.5788054779225</v>
       </c>
       <c r="Q94">
-        <v>-3544.430166589283</v>
+        <v>-201.8788054779225</v>
       </c>
       <c r="R94">
         <v>11.50000000000001</v>
       </c>
       <c r="S94">
-        <v>0.3633719165356391</v>
+        <v>0.3246988931690206</v>
       </c>
       <c r="T94">
-        <v>6.021562165725173</v>
+        <v>5.290608943899312</v>
       </c>
       <c r="U94">
-        <v>0.222784254897099</v>
+        <v>0.125584254897099</v>
       </c>
       <c r="V94">
-        <v>0.1473632634475958</v>
+        <v>0.2614198322335703</v>
       </c>
       <c r="W94">
-        <v>0.1899540400507214</v>
+        <v>0.09275404005072141</v>
       </c>
       <c r="X94" t="inlineStr">
         <is>
-          <t>C2/C</t>
+          <t>Caa/CCC</t>
         </is>
       </c>
       <c r="Y94">
-        <v>0.4812647401946304</v>
+        <v>0.8537551673206083</v>
       </c>
       <c r="Z94">
         <v>0</v>
@@ -9044,13 +9044,13 @@
         <v>0.93</v>
       </c>
       <c r="B95">
-        <v>0.2055973127184858</v>
+        <v>0.1121074708491563</v>
       </c>
       <c r="C95">
-        <v>-28106.797603238</v>
+        <v>-13741.26680870631</v>
       </c>
       <c r="D95">
-        <v>16449.13139676199</v>
+        <v>30814.66219129368</v>
       </c>
       <c r="E95">
         <v>42310.429</v>
@@ -9077,45 +9077,45 @@
         <v>5314.3</v>
       </c>
       <c r="M95">
-        <v>11162.38876810764</v>
+        <v>6292.277149307638</v>
       </c>
       <c r="N95">
-        <v>-5848.088768107637</v>
+        <v>-977.9771493076378</v>
       </c>
       <c r="O95">
-        <v>-1790.684780794559</v>
+        <v>-299.4566031179987</v>
       </c>
       <c r="P95">
-        <v>-4057.403987313079</v>
+        <v>-678.520546189639</v>
       </c>
       <c r="Q95">
-        <v>-3627.703987313079</v>
+        <v>-248.8205461896391</v>
       </c>
       <c r="R95">
         <v>13.2857142857143</v>
       </c>
       <c r="S95">
-        <v>0.4087393331835876</v>
+        <v>0.3645415921931665</v>
       </c>
       <c r="T95">
-        <v>6.881785332257341</v>
+        <v>6.046410221599215</v>
       </c>
       <c r="U95">
-        <v>0.222784254897099</v>
+        <v>0.125584254897099</v>
       </c>
       <c r="V95">
-        <v>0.1457787122277292</v>
+        <v>0.2586088662955749</v>
       </c>
       <c r="W95">
-        <v>0.1903070531135857</v>
+        <v>0.09310705311358569</v>
       </c>
       <c r="X95" t="inlineStr">
         <is>
-          <t>C2/C</t>
+          <t>Caa/CCC</t>
         </is>
       </c>
       <c r="Y95">
-        <v>0.4760898505151182</v>
+        <v>0.8445750042311394</v>
       </c>
       <c r="Z95">
         <v>0</v>
@@ -9126,13 +9126,13 @@
         <v>0.9400000000000001</v>
       </c>
       <c r="B96">
-        <v>0.2073671552674568</v>
+        <v>0.1129053133981273</v>
       </c>
       <c r="C96">
-        <v>-28789.47042283014</v>
+        <v>-14508.01638395225</v>
       </c>
       <c r="D96">
-        <v>16305.21157716986</v>
+        <v>30586.66561604775</v>
       </c>
       <c r="E96">
         <v>42849.182</v>
@@ -9159,45 +9159,45 @@
         <v>5314.3</v>
       </c>
       <c r="M96">
-        <v>11282.41445378622</v>
+        <v>6359.936043386215</v>
       </c>
       <c r="N96">
-        <v>-5968.114453786216</v>
+        <v>-1045.636043386215</v>
       </c>
       <c r="O96">
-        <v>-1827.436645749339</v>
+        <v>-320.1737564848589</v>
       </c>
       <c r="P96">
-        <v>-4140.677808036877</v>
+        <v>-725.4622869013557</v>
       </c>
       <c r="Q96">
-        <v>-3710.977808036877</v>
+        <v>-295.7622869013557</v>
       </c>
       <c r="R96">
         <v>15.66666666666668</v>
       </c>
       <c r="S96">
-        <v>0.4692292220475189</v>
+        <v>0.4176651908920277</v>
       </c>
       <c r="T96">
-        <v>8.028749554300234</v>
+        <v>7.05414525853242</v>
       </c>
       <c r="U96">
-        <v>0.222784254897099</v>
+        <v>0.125584254897099</v>
       </c>
       <c r="V96">
-        <v>0.1442278748636044</v>
+        <v>0.2558577081434943</v>
       </c>
       <c r="W96">
-        <v>0.1906525552602188</v>
+        <v>0.09345255526021883</v>
       </c>
       <c r="X96" t="inlineStr">
         <is>
-          <t>C2/C</t>
+          <t>Caa/CCC</t>
         </is>
       </c>
       <c r="Y96">
-        <v>0.4710250648713403</v>
+        <v>0.8355901637605954</v>
       </c>
       <c r="Z96">
         <v>0</v>
@@ -9208,13 +9208,13 @@
         <v>0.9500000000000001</v>
       </c>
       <c r="B97">
-        <v>0.2091369978164278</v>
+        <v>0.1137031559470983</v>
       </c>
       <c r="C97">
-        <v>-29469.64666548757</v>
+        <v>-15271.41686215629</v>
       </c>
       <c r="D97">
-        <v>16163.78833451242</v>
+        <v>30362.0181378437</v>
       </c>
       <c r="E97">
         <v>43387.935</v>
@@ -9241,45 +9241,45 @@
         <v>5314.3</v>
       </c>
       <c r="M97">
-        <v>11402.44013946479</v>
+        <v>6427.594937464791</v>
       </c>
       <c r="N97">
-        <v>-6088.140139464792</v>
+        <v>-1113.294937464791</v>
       </c>
       <c r="O97">
-        <v>-1864.188510704119</v>
+        <v>-340.8909098517189</v>
       </c>
       <c r="P97">
-        <v>-4223.951628760673</v>
+        <v>-772.4040276130717</v>
       </c>
       <c r="Q97">
-        <v>-3794.251628760673</v>
+        <v>-342.7040276130717</v>
       </c>
       <c r="R97">
         <v>19.00000000000003</v>
       </c>
       <c r="S97">
-        <v>0.5539150664570229</v>
+        <v>0.4920382290704334</v>
       </c>
       <c r="T97">
-        <v>9.634499465160285</v>
+        <v>8.464974310238908</v>
       </c>
       <c r="U97">
-        <v>0.222784254897099</v>
+        <v>0.125584254897099</v>
       </c>
       <c r="V97">
-        <v>0.1427096867071454</v>
+        <v>0.253164469110405</v>
       </c>
       <c r="W97">
-        <v>0.1909907836774491</v>
+        <v>0.09379078367744913</v>
       </c>
       <c r="X97" t="inlineStr">
         <is>
-          <t>C2/C</t>
+          <t>Caa/CCC</t>
         </is>
       </c>
       <c r="Y97">
-        <v>0.4660669062937473</v>
+        <v>0.8267944778262735</v>
       </c>
       <c r="Z97">
         <v>0</v>
@@ -9290,13 +9290,13 @@
         <v>0.96</v>
       </c>
       <c r="B98">
-        <v>0.2109068403653988</v>
+        <v>0.1145009984960693</v>
       </c>
       <c r="C98">
-        <v>-30147.39073478154</v>
+        <v>-16031.5414988336</v>
       </c>
       <c r="D98">
-        <v>16024.79726521845</v>
+        <v>30140.64650116639</v>
       </c>
       <c r="E98">
         <v>43926.68799999999</v>
@@ -9323,45 +9323,45 @@
         <v>5314.3</v>
       </c>
       <c r="M98">
-        <v>11522.46582514337</v>
+        <v>6495.253831543368</v>
       </c>
       <c r="N98">
-        <v>-6208.165825143366</v>
+        <v>-1180.953831543367</v>
       </c>
       <c r="O98">
-        <v>-1900.940375658899</v>
+        <v>-361.6080632185792</v>
       </c>
       <c r="P98">
-        <v>-4307.225449484467</v>
+        <v>-819.3457683247882</v>
       </c>
       <c r="Q98">
-        <v>-3877.525449484468</v>
+        <v>-389.6457683247882</v>
       </c>
       <c r="R98">
         <v>23.99999999999998</v>
       </c>
       <c r="S98">
-        <v>0.6809438330712771</v>
+        <v>0.6035977863380405</v>
       </c>
       <c r="T98">
-        <v>12.04312433145033</v>
+        <v>10.58121788779861</v>
       </c>
       <c r="U98">
-        <v>0.222784254897099</v>
+        <v>0.125584254897099</v>
       </c>
       <c r="V98">
-        <v>0.1412231274706127</v>
+        <v>0.2505273392238382</v>
       </c>
       <c r="W98">
-        <v>0.1913219656693205</v>
+        <v>0.09412196566932048</v>
       </c>
       <c r="X98" t="inlineStr">
         <is>
-          <t>C2/C</t>
+          <t>Caa/CCC</t>
         </is>
       </c>
       <c r="Y98">
-        <v>0.4612120426865208</v>
+        <v>0.8181820353489164</v>
       </c>
       <c r="Z98">
         <v>0</v>
@@ -9372,13 +9372,13 @@
         <v>0.97</v>
       </c>
       <c r="B99">
-        <v>0.2126766829143698</v>
+        <v>0.1152988410450403</v>
       </c>
       <c r="C99">
-        <v>-30822.76483796544</v>
+        <v>-16788.4614285189</v>
       </c>
       <c r="D99">
-        <v>15888.17616203456</v>
+        <v>29922.4795714811</v>
       </c>
       <c r="E99">
         <v>44465.441</v>
@@ -9405,45 +9405,45 @@
         <v>5314.3</v>
       </c>
       <c r="M99">
-        <v>11642.49151082194</v>
+        <v>6562.912725621944</v>
       </c>
       <c r="N99">
-        <v>-6328.191510821945</v>
+        <v>-1248.612725621944</v>
       </c>
       <c r="O99">
-        <v>-1937.69224061368</v>
+        <v>-382.3252165854394</v>
       </c>
       <c r="P99">
-        <v>-4390.499270208265</v>
+        <v>-866.2875090365048</v>
       </c>
       <c r="Q99">
-        <v>-3960.799270208266</v>
+        <v>-436.5875090365049</v>
       </c>
       <c r="R99">
         <v>32.33333333333331</v>
       </c>
       <c r="S99">
-        <v>0.8926584440950365</v>
+        <v>0.7895303817840541</v>
       </c>
       <c r="T99">
-        <v>16.05749910860044</v>
+        <v>14.10829051706482</v>
       </c>
       <c r="U99">
-        <v>0.222784254897099</v>
+        <v>0.125584254897099</v>
       </c>
       <c r="V99">
-        <v>0.1397672189399878</v>
+        <v>0.2479445831493657</v>
       </c>
       <c r="W99">
-        <v>0.1916463191665141</v>
+        <v>0.09444631916651408</v>
       </c>
       <c r="X99" t="inlineStr">
         <is>
-          <t>C2/C</t>
+          <t>Caa/CCC</t>
         </is>
       </c>
       <c r="Y99">
-        <v>0.4564572793598557</v>
+        <v>0.8097471690051131</v>
       </c>
       <c r="Z99">
         <v>0</v>
@@ -9454,13 +9454,13 @@
         <v>0.98</v>
       </c>
       <c r="B100">
-        <v>0.2144465254633408</v>
+        <v>0.1160966835940113</v>
       </c>
       <c r="C100">
-        <v>-31495.82907880808</v>
+        <v>-17542.24574097615</v>
       </c>
       <c r="D100">
-        <v>15753.86492119191</v>
+        <v>29707.44825902385</v>
       </c>
       <c r="E100">
         <v>45004.194</v>
@@ -9487,45 +9487,45 @@
         <v>5314.3</v>
       </c>
       <c r="M100">
-        <v>11762.51719650052</v>
+        <v>6630.571619700521</v>
       </c>
       <c r="N100">
-        <v>-6448.217196500521</v>
+        <v>-1316.271619700521</v>
       </c>
       <c r="O100">
-        <v>-1974.44410556846</v>
+        <v>-403.0423699522996</v>
       </c>
       <c r="P100">
-        <v>-4473.773090932062</v>
+        <v>-913.2292497482215</v>
       </c>
       <c r="Q100">
-        <v>-4044.073090932062</v>
+        <v>-483.5292497482215</v>
       </c>
       <c r="R100">
         <v>48.99999999999996</v>
       </c>
       <c r="S100">
-        <v>1.316087666142554</v>
+        <v>1.161395572676081</v>
       </c>
       <c r="T100">
-        <v>24.08624866290066</v>
+        <v>21.16243577559722</v>
       </c>
       <c r="U100">
-        <v>0.222784254897099</v>
+        <v>0.125584254897099</v>
       </c>
       <c r="V100">
-        <v>0.1383410228283553</v>
+        <v>0.2454145363825354</v>
       </c>
       <c r="W100">
-        <v>0.1919640532045813</v>
+        <v>0.09476405320458127</v>
       </c>
       <c r="X100" t="inlineStr">
         <is>
-          <t>C2/C</t>
+          <t>Caa/CCC</t>
         </is>
       </c>
       <c r="Y100">
-        <v>0.451799552019449</v>
+        <v>0.8014844427907752</v>
       </c>
       <c r="Z100">
         <v>0</v>
@@ -9536,13 +9536,13 @@
         <v>0.99</v>
       </c>
       <c r="B101">
-        <v>0.2162163680123118</v>
+        <v>0.2010676310466908</v>
       </c>
       <c r="C101">
-        <v>-32166.64154575782</v>
+        <v>-30960.3233334473</v>
       </c>
       <c r="D101">
-        <v>15621.80545424218</v>
+        <v>16828.1236665527</v>
       </c>
       <c r="E101">
         <v>45542.947</v>
@@ -9569,37 +9569,37 @@
         <v>5314.3</v>
       </c>
       <c r="M101">
-        <v>11882.5428821791</v>
+        <v>11082.4946771791</v>
       </c>
       <c r="N101">
-        <v>-6568.242882179099</v>
+        <v>-5768.194677179098</v>
       </c>
       <c r="O101">
-        <v>-2011.19597052324</v>
+        <v>-1766.22121015224</v>
       </c>
       <c r="P101">
-        <v>-4557.046911655859</v>
+        <v>-4001.973467026858</v>
       </c>
       <c r="Q101">
-        <v>-4127.346911655859</v>
+        <v>-3572.273467026858</v>
       </c>
       <c r="R101">
         <v>98.99999999999991</v>
       </c>
       <c r="S101">
-        <v>2.586375332285109</v>
+        <v>2.556501635723011</v>
       </c>
       <c r="T101">
-        <v>48.17249732580132</v>
+        <v>47.6270822680133</v>
       </c>
       <c r="U101">
-        <v>0.222784254897099</v>
+        <v>0.207784254897099</v>
       </c>
       <c r="V101">
-        <v>0.136943638759382</v>
+        <v>0.1468296360521413</v>
       </c>
       <c r="W101">
-        <v>0.1922753683731926</v>
+        <v>0.1772753683731925</v>
       </c>
       <c r="X101" t="inlineStr">
         <is>
@@ -9607,7 +9607,7 @@
         </is>
       </c>
       <c r="Y101">
-        <v>0.4472359201808687</v>
+        <v>0.4795219988639493</v>
       </c>
       <c r="Z101">
         <v>0</v>

--- a/research/traditional_assets/database/data/japan/japan_tobacco.xlsx
+++ b/research/traditional_assets/database/data/japan/japan_tobacco.xlsx
@@ -1278,7 +1278,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:Z101"/>
+  <dimension ref="A1:Z100"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -1415,22 +1415,22 @@
     </row>
     <row r="2">
       <c r="A2">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="B2">
-        <v>0.07517734685226005</v>
+        <v>0.07502683157667452</v>
       </c>
       <c r="C2">
-        <v>52595.70626413845</v>
+        <v>52158.18359924489</v>
       </c>
       <c r="D2">
-        <v>47047.60626413846</v>
+        <v>47148.83659924489</v>
       </c>
       <c r="E2">
-        <v>-7793.6</v>
+        <v>-7254.847000000001</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>538.7529999999999</v>
       </c>
       <c r="G2">
         <v>5548.1</v>
@@ -1451,28 +1451,28 @@
         <v>5314.3</v>
       </c>
       <c r="M2">
-        <v>0</v>
+        <v>30.86206417857674</v>
       </c>
       <c r="N2">
-        <v>5314.3</v>
+        <v>5283.437935821424</v>
       </c>
       <c r="O2">
-        <v>1627.23866</v>
+        <v>1617.78869594852</v>
       </c>
       <c r="P2">
-        <v>3687.06134</v>
+        <v>3665.649239872903</v>
       </c>
       <c r="Q2">
-        <v>4116.76134</v>
+        <v>4095.349239872903</v>
       </c>
       <c r="R2">
-        <v>0</v>
+        <v>0.0101010101010101</v>
       </c>
       <c r="S2">
-        <v>0.07517734685226005</v>
+        <v>0.07538322567292771</v>
       </c>
       <c r="T2">
-        <v>0.5572774141861078</v>
+        <v>0.5611828593372423</v>
       </c>
       <c r="U2">
         <v>0.05728425489709894</v>
@@ -1489,7 +1489,7 @@
         </is>
       </c>
       <c r="Y2">
-        <v>10000000</v>
+        <v>172.1952222395086</v>
       </c>
       <c r="Z2">
         <v>0</v>
@@ -1497,22 +1497,22 @@
     </row>
     <row r="3">
       <c r="A3">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
       <c r="B3">
-        <v>0.07502683157667452</v>
+        <v>0.07487631630108894</v>
       </c>
       <c r="C3">
-        <v>52158.18359924489</v>
+        <v>51721.09749971099</v>
       </c>
       <c r="D3">
-        <v>47148.83659924489</v>
+        <v>47250.50349971099</v>
       </c>
       <c r="E3">
-        <v>-7254.847000000001</v>
+        <v>-6716.094000000001</v>
       </c>
       <c r="F3">
-        <v>538.7529999999999</v>
+        <v>1077.506</v>
       </c>
       <c r="G3">
         <v>5548.1</v>
@@ -1533,28 +1533,28 @@
         <v>5314.3</v>
       </c>
       <c r="M3">
-        <v>30.86206417857674</v>
+        <v>61.72412835715349</v>
       </c>
       <c r="N3">
-        <v>5283.437935821424</v>
+        <v>5252.575871642846</v>
       </c>
       <c r="O3">
-        <v>1617.78869594852</v>
+        <v>1608.33873189704</v>
       </c>
       <c r="P3">
-        <v>3665.649239872903</v>
+        <v>3644.237139745806</v>
       </c>
       <c r="Q3">
-        <v>4095.349239872903</v>
+        <v>4073.937139745806</v>
       </c>
       <c r="R3">
-        <v>0.0101010101010101</v>
+        <v>0.02040816326530612</v>
       </c>
       <c r="S3">
-        <v>0.07538322567292771</v>
+        <v>0.07559330610218042</v>
       </c>
       <c r="T3">
-        <v>0.5611828593372423</v>
+        <v>0.5651680074506449</v>
       </c>
       <c r="U3">
         <v>0.05728425489709894</v>
@@ -1571,7 +1571,7 @@
         </is>
       </c>
       <c r="Y3">
-        <v>172.1952222395086</v>
+        <v>86.09761111975429</v>
       </c>
       <c r="Z3">
         <v>0</v>
@@ -1579,22 +1579,22 @@
     </row>
     <row r="4">
       <c r="A4">
-        <v>0.02</v>
+        <v>0.03</v>
       </c>
       <c r="B4">
-        <v>0.07487631630108894</v>
+        <v>0.0747258010255034</v>
       </c>
       <c r="C4">
-        <v>51721.09749971099</v>
+        <v>51284.45079573335</v>
       </c>
       <c r="D4">
-        <v>47250.50349971099</v>
+        <v>47352.60979573335</v>
       </c>
       <c r="E4">
-        <v>-6716.094000000001</v>
+        <v>-6177.341</v>
       </c>
       <c r="F4">
-        <v>1077.506</v>
+        <v>1616.259</v>
       </c>
       <c r="G4">
         <v>5548.1</v>
@@ -1615,28 +1615,28 @@
         <v>5314.3</v>
       </c>
       <c r="M4">
-        <v>61.72412835715349</v>
+        <v>92.58619253573023</v>
       </c>
       <c r="N4">
-        <v>5252.575871642846</v>
+        <v>5221.71380746427</v>
       </c>
       <c r="O4">
-        <v>1608.33873189704</v>
+        <v>1598.88876784556</v>
       </c>
       <c r="P4">
-        <v>3644.237139745806</v>
+        <v>3622.82503961871</v>
       </c>
       <c r="Q4">
-        <v>4073.937139745806</v>
+        <v>4052.52503961871</v>
       </c>
       <c r="R4">
-        <v>0.02040816326530612</v>
+        <v>0.03092783505154639</v>
       </c>
       <c r="S4">
-        <v>0.07559330610218042</v>
+        <v>0.07580771808667545</v>
       </c>
       <c r="T4">
-        <v>0.5651680074506449</v>
+        <v>0.5692353235663858</v>
       </c>
       <c r="U4">
         <v>0.05728425489709894</v>
@@ -1653,7 +1653,7 @@
         </is>
       </c>
       <c r="Y4">
-        <v>86.09761111975429</v>
+        <v>57.39840741316954</v>
       </c>
       <c r="Z4">
         <v>0</v>
@@ -1661,22 +1661,22 @@
     </row>
     <row r="5">
       <c r="A5">
-        <v>0.03</v>
+        <v>0.04</v>
       </c>
       <c r="B5">
-        <v>0.0747258010255034</v>
+        <v>0.07457528574991786</v>
       </c>
       <c r="C5">
-        <v>51284.45079573335</v>
+        <v>50848.2463420253</v>
       </c>
       <c r="D5">
-        <v>47352.60979573335</v>
+        <v>47455.15834202531</v>
       </c>
       <c r="E5">
-        <v>-6177.341</v>
+        <v>-5638.588000000001</v>
       </c>
       <c r="F5">
-        <v>1616.259</v>
+        <v>2155.012</v>
       </c>
       <c r="G5">
         <v>5548.1</v>
@@ -1697,28 +1697,28 @@
         <v>5314.3</v>
       </c>
       <c r="M5">
-        <v>92.58619253573023</v>
+        <v>123.448256714307</v>
       </c>
       <c r="N5">
-        <v>5221.71380746427</v>
+        <v>5190.851743285693</v>
       </c>
       <c r="O5">
-        <v>1598.88876784556</v>
+        <v>1589.438803794079</v>
       </c>
       <c r="P5">
-        <v>3622.82503961871</v>
+        <v>3601.412939491614</v>
       </c>
       <c r="Q5">
-        <v>4052.52503961871</v>
+        <v>4031.112939491614</v>
       </c>
       <c r="R5">
-        <v>0.03092783505154639</v>
+        <v>0.04166666666666667</v>
       </c>
       <c r="S5">
-        <v>0.07580771808667545</v>
+        <v>0.07602659698751413</v>
       </c>
       <c r="T5">
-        <v>0.5692353235663858</v>
+        <v>0.5733873754345378</v>
       </c>
       <c r="U5">
         <v>0.05728425489709894</v>
@@ -1735,7 +1735,7 @@
         </is>
       </c>
       <c r="Y5">
-        <v>57.39840741316954</v>
+        <v>43.04880555987715</v>
       </c>
       <c r="Z5">
         <v>0</v>
@@ -1743,22 +1743,22 @@
     </row>
     <row r="6">
       <c r="A6">
-        <v>0.04</v>
+        <v>0.05</v>
       </c>
       <c r="B6">
-        <v>0.07457528574991786</v>
+        <v>0.0744247704743323</v>
       </c>
       <c r="C6">
-        <v>50848.2463420253</v>
+        <v>50412.48701808297</v>
       </c>
       <c r="D6">
-        <v>47455.15834202531</v>
+        <v>47558.15201808298</v>
       </c>
       <c r="E6">
-        <v>-5638.588000000001</v>
+        <v>-5099.835000000001</v>
       </c>
       <c r="F6">
-        <v>2155.012</v>
+        <v>2693.765</v>
       </c>
       <c r="G6">
         <v>5548.1</v>
@@ -1779,28 +1779,28 @@
         <v>5314.3</v>
       </c>
       <c r="M6">
-        <v>123.448256714307</v>
+        <v>154.3103208928837</v>
       </c>
       <c r="N6">
-        <v>5190.851743285693</v>
+        <v>5159.989679107117</v>
       </c>
       <c r="O6">
-        <v>1589.438803794079</v>
+        <v>1579.988839742599</v>
       </c>
       <c r="P6">
-        <v>3601.412939491614</v>
+        <v>3580.000839364518</v>
       </c>
       <c r="Q6">
-        <v>4031.112939491614</v>
+        <v>4009.700839364517</v>
       </c>
       <c r="R6">
-        <v>0.04166666666666667</v>
+        <v>0.05263157894736843</v>
       </c>
       <c r="S6">
-        <v>0.07602659698751413</v>
+        <v>0.07625008386521258</v>
       </c>
       <c r="T6">
-        <v>0.5733873754345378</v>
+        <v>0.5776268389209669</v>
       </c>
       <c r="U6">
         <v>0.05728425489709894</v>
@@ -1817,7 +1817,7 @@
         </is>
       </c>
       <c r="Y6">
-        <v>43.04880555987715</v>
+        <v>34.43904444790172</v>
       </c>
       <c r="Z6">
         <v>0</v>
@@ -1825,22 +1825,22 @@
     </row>
     <row r="7">
       <c r="A7">
-        <v>0.05</v>
+        <v>0.06</v>
       </c>
       <c r="B7">
-        <v>0.0744247704743323</v>
+        <v>0.07427425519874675</v>
       </c>
       <c r="C7">
-        <v>50412.48701808297</v>
+        <v>49977.17572845471</v>
       </c>
       <c r="D7">
-        <v>47558.15201808298</v>
+        <v>47661.5937284547</v>
       </c>
       <c r="E7">
-        <v>-5099.835000000001</v>
+        <v>-4561.082</v>
       </c>
       <c r="F7">
-        <v>2693.765</v>
+        <v>3232.518</v>
       </c>
       <c r="G7">
         <v>5548.1</v>
@@ -1861,28 +1861,28 @@
         <v>5314.3</v>
       </c>
       <c r="M7">
-        <v>154.3103208928837</v>
+        <v>185.1723850714605</v>
       </c>
       <c r="N7">
-        <v>5159.989679107117</v>
+        <v>5129.12761492854</v>
       </c>
       <c r="O7">
-        <v>1579.988839742599</v>
+        <v>1570.538875691119</v>
       </c>
       <c r="P7">
-        <v>3580.000839364518</v>
+        <v>3558.588739237421</v>
       </c>
       <c r="Q7">
-        <v>4009.700839364517</v>
+        <v>3988.28873923742</v>
       </c>
       <c r="R7">
-        <v>0.05263157894736843</v>
+        <v>0.06382978723404256</v>
       </c>
       <c r="S7">
-        <v>0.07625008386521258</v>
+        <v>0.07647832578286205</v>
       </c>
       <c r="T7">
-        <v>0.5776268389209669</v>
+        <v>0.5819565037581709</v>
       </c>
       <c r="U7">
         <v>0.05728425489709894</v>
@@ -1899,7 +1899,7 @@
         </is>
       </c>
       <c r="Y7">
-        <v>34.43904444790172</v>
+        <v>28.69920370658476</v>
       </c>
       <c r="Z7">
         <v>0</v>
@@ -1907,22 +1907,22 @@
     </row>
     <row r="8">
       <c r="A8">
-        <v>0.06</v>
+        <v>0.06999999999999999</v>
       </c>
       <c r="B8">
-        <v>0.07427425519874675</v>
+        <v>0.07412373992316122</v>
       </c>
       <c r="C8">
-        <v>49977.17572845471</v>
+        <v>49542.31540301417</v>
       </c>
       <c r="D8">
-        <v>47661.5937284547</v>
+        <v>47765.48640301418</v>
       </c>
       <c r="E8">
-        <v>-4561.082</v>
+        <v>-4022.329000000001</v>
       </c>
       <c r="F8">
-        <v>3232.518</v>
+        <v>3771.270999999999</v>
       </c>
       <c r="G8">
         <v>5548.1</v>
@@ -1943,28 +1943,28 @@
         <v>5314.3</v>
       </c>
       <c r="M8">
-        <v>185.1723850714605</v>
+        <v>216.0344492500372</v>
       </c>
       <c r="N8">
-        <v>5129.12761492854</v>
+        <v>5098.265550749963</v>
       </c>
       <c r="O8">
-        <v>1570.538875691119</v>
+        <v>1561.088911639639</v>
       </c>
       <c r="P8">
-        <v>3558.588739237421</v>
+        <v>3537.176639110324</v>
       </c>
       <c r="Q8">
-        <v>3988.28873923742</v>
+        <v>3966.876639110324</v>
       </c>
       <c r="R8">
-        <v>0.06382978723404255</v>
+        <v>0.07526881720430106</v>
       </c>
       <c r="S8">
-        <v>0.07647832578286205</v>
+        <v>0.07671147612884807</v>
       </c>
       <c r="T8">
-        <v>0.5819565037581709</v>
+        <v>0.5863792796671428</v>
       </c>
       <c r="U8">
         <v>0.05728425489709894</v>
@@ -1981,7 +1981,7 @@
         </is>
       </c>
       <c r="Y8">
-        <v>28.69920370658477</v>
+        <v>24.59931746278695</v>
       </c>
       <c r="Z8">
         <v>0</v>
@@ -1989,22 +1989,22 @@
     </row>
     <row r="9">
       <c r="A9">
-        <v>0.07000000000000001</v>
+        <v>0.08</v>
       </c>
       <c r="B9">
-        <v>0.07412373992316121</v>
+        <v>0.07397322464757566</v>
       </c>
       <c r="C9">
-        <v>49542.31540301419</v>
+        <v>49107.90899723707</v>
       </c>
       <c r="D9">
-        <v>47765.48640301419</v>
+        <v>47869.83299723707</v>
       </c>
       <c r="E9">
-        <v>-4022.329</v>
+        <v>-3483.576000000001</v>
       </c>
       <c r="F9">
-        <v>3771.271</v>
+        <v>4310.023999999999</v>
       </c>
       <c r="G9">
         <v>5548.1</v>
@@ -2025,28 +2025,28 @@
         <v>5314.3</v>
       </c>
       <c r="M9">
-        <v>216.0344492500372</v>
+        <v>246.896513428614</v>
       </c>
       <c r="N9">
-        <v>5098.265550749963</v>
+        <v>5067.403486571387</v>
       </c>
       <c r="O9">
-        <v>1561.088911639639</v>
+        <v>1551.638947588159</v>
       </c>
       <c r="P9">
-        <v>3537.176639110324</v>
+        <v>3515.764538983228</v>
       </c>
       <c r="Q9">
-        <v>3966.876639110324</v>
+        <v>3945.464538983228</v>
       </c>
       <c r="R9">
-        <v>0.07526881720430109</v>
+        <v>0.08695652173913043</v>
       </c>
       <c r="S9">
-        <v>0.07671147612884807</v>
+        <v>0.07694969496061639</v>
       </c>
       <c r="T9">
-        <v>0.5863792796671428</v>
+        <v>0.5908982028784835</v>
       </c>
       <c r="U9">
         <v>0.05728425489709894</v>
@@ -2063,7 +2063,7 @@
         </is>
       </c>
       <c r="Y9">
-        <v>24.59931746278694</v>
+        <v>21.52440277993858</v>
       </c>
       <c r="Z9">
         <v>0</v>
@@ -2071,22 +2071,22 @@
     </row>
     <row r="10">
       <c r="A10">
-        <v>0.08</v>
+        <v>0.09</v>
       </c>
       <c r="B10">
-        <v>0.07397322464757566</v>
+        <v>0.07382270937199012</v>
       </c>
       <c r="C10">
-        <v>49107.90899723707</v>
+        <v>48673.95949248118</v>
       </c>
       <c r="D10">
-        <v>47869.83299723707</v>
+        <v>47974.63649248119</v>
       </c>
       <c r="E10">
-        <v>-3483.576000000001</v>
+        <v>-2944.823000000001</v>
       </c>
       <c r="F10">
-        <v>4310.023999999999</v>
+        <v>4848.776999999999</v>
       </c>
       <c r="G10">
         <v>5548.1</v>
@@ -2107,28 +2107,28 @@
         <v>5314.3</v>
       </c>
       <c r="M10">
-        <v>246.896513428614</v>
+        <v>277.7585776071907</v>
       </c>
       <c r="N10">
-        <v>5067.403486571387</v>
+        <v>5036.541422392809</v>
       </c>
       <c r="O10">
-        <v>1551.638947588159</v>
+        <v>1542.188983536678</v>
       </c>
       <c r="P10">
-        <v>3515.764538983228</v>
+        <v>3494.352438856131</v>
       </c>
       <c r="Q10">
-        <v>3945.464538983228</v>
+        <v>3924.052438856131</v>
       </c>
       <c r="R10">
-        <v>0.08695652173913043</v>
+        <v>0.0989010989010989</v>
       </c>
       <c r="S10">
-        <v>0.07694969496061639</v>
+        <v>0.07719314937110491</v>
       </c>
       <c r="T10">
-        <v>0.5908982028784835</v>
+        <v>0.5955164430834802</v>
       </c>
       <c r="U10">
         <v>0.05728425489709894</v>
@@ -2145,7 +2145,7 @@
         </is>
       </c>
       <c r="Y10">
-        <v>21.52440277993858</v>
+        <v>19.13280247105651</v>
       </c>
       <c r="Z10">
         <v>0</v>
@@ -2153,22 +2153,22 @@
     </row>
     <row r="11">
       <c r="A11">
-        <v>0.09</v>
+        <v>0.09999999999999999</v>
       </c>
       <c r="B11">
-        <v>0.07382270937199012</v>
+        <v>0.07367219409640459</v>
       </c>
       <c r="C11">
-        <v>48673.95949248118</v>
+        <v>48240.46989627051</v>
       </c>
       <c r="D11">
-        <v>47974.63649248119</v>
+        <v>48079.89989627051</v>
       </c>
       <c r="E11">
-        <v>-2944.823000000001</v>
+        <v>-2406.070000000002</v>
       </c>
       <c r="F11">
-        <v>4848.776999999999</v>
+        <v>5387.529999999999</v>
       </c>
       <c r="G11">
         <v>5548.1</v>
@@ -2189,28 +2189,28 @@
         <v>5314.3</v>
       </c>
       <c r="M11">
-        <v>277.7585776071907</v>
+        <v>308.6206417857674</v>
       </c>
       <c r="N11">
-        <v>5036.541422392809</v>
+        <v>5005.679358214233</v>
       </c>
       <c r="O11">
-        <v>1542.188983536678</v>
+        <v>1532.739019485198</v>
       </c>
       <c r="P11">
-        <v>3494.352438856131</v>
+        <v>3472.940338729034</v>
       </c>
       <c r="Q11">
-        <v>3924.052438856131</v>
+        <v>3902.640338729034</v>
       </c>
       <c r="R11">
-        <v>0.0989010989010989</v>
+        <v>0.1111111111111111</v>
       </c>
       <c r="S11">
-        <v>0.07719314937110491</v>
+        <v>0.07744201387960428</v>
       </c>
       <c r="T11">
-        <v>0.5955164430834802</v>
+        <v>0.600237310848588</v>
       </c>
       <c r="U11">
         <v>0.05728425489709894</v>
@@ -2227,7 +2227,7 @@
         </is>
       </c>
       <c r="Y11">
-        <v>19.13280247105651</v>
+        <v>17.21952222395086</v>
       </c>
       <c r="Z11">
         <v>0</v>
@@ -2235,22 +2235,22 @@
     </row>
     <row r="12">
       <c r="A12">
-        <v>0.1</v>
+        <v>0.11</v>
       </c>
       <c r="B12">
-        <v>0.07367219409640459</v>
+        <v>0.07352167882081904</v>
       </c>
       <c r="C12">
-        <v>48240.46989627051</v>
+        <v>47807.4432425829</v>
       </c>
       <c r="D12">
-        <v>48079.89989627051</v>
+        <v>48185.6262425829</v>
       </c>
       <c r="E12">
-        <v>-2406.070000000001</v>
+        <v>-1867.317000000001</v>
       </c>
       <c r="F12">
-        <v>5387.53</v>
+        <v>5926.282999999999</v>
       </c>
       <c r="G12">
         <v>5548.1</v>
@@ -2271,28 +2271,28 @@
         <v>5314.3</v>
       </c>
       <c r="M12">
-        <v>308.6206417857675</v>
+        <v>339.4827059643442</v>
       </c>
       <c r="N12">
-        <v>5005.679358214233</v>
+        <v>4974.817294035656</v>
       </c>
       <c r="O12">
-        <v>1532.739019485198</v>
+        <v>1523.289055433718</v>
       </c>
       <c r="P12">
-        <v>3472.940338729034</v>
+        <v>3451.528238601938</v>
       </c>
       <c r="Q12">
-        <v>3902.640338729034</v>
+        <v>3881.228238601938</v>
       </c>
       <c r="R12">
-        <v>0.1111111111111111</v>
+        <v>0.1235955056179775</v>
       </c>
       <c r="S12">
-        <v>0.07744201387960428</v>
+        <v>0.0776964708489688</v>
       </c>
       <c r="T12">
-        <v>0.600237310848588</v>
+        <v>0.6050642655297654</v>
       </c>
       <c r="U12">
         <v>0.05728425489709894</v>
@@ -2309,7 +2309,7 @@
         </is>
       </c>
       <c r="Y12">
-        <v>17.21952222395086</v>
+        <v>15.6541111126826</v>
       </c>
       <c r="Z12">
         <v>0</v>
@@ -2317,22 +2317,22 @@
     </row>
     <row r="13">
       <c r="A13">
-        <v>0.11</v>
+        <v>0.12</v>
       </c>
       <c r="B13">
-        <v>0.07352167882081904</v>
+        <v>0.07337116354523347</v>
       </c>
       <c r="C13">
-        <v>47807.4432425829</v>
+        <v>47374.88259214153</v>
       </c>
       <c r="D13">
-        <v>48185.6262425829</v>
+        <v>48291.81859214154</v>
       </c>
       <c r="E13">
-        <v>-1867.317000000001</v>
+        <v>-1328.564000000001</v>
       </c>
       <c r="F13">
-        <v>5926.282999999999</v>
+        <v>6465.035999999999</v>
       </c>
       <c r="G13">
         <v>5548.1</v>
@@ -2353,28 +2353,28 @@
         <v>5314.3</v>
       </c>
       <c r="M13">
-        <v>339.4827059643442</v>
+        <v>370.3447701429209</v>
       </c>
       <c r="N13">
-        <v>4974.817294035656</v>
+        <v>4943.955229857079</v>
       </c>
       <c r="O13">
-        <v>1523.289055433718</v>
+        <v>1513.839091382238</v>
       </c>
       <c r="P13">
-        <v>3451.528238601938</v>
+        <v>3430.116138474841</v>
       </c>
       <c r="Q13">
-        <v>3881.228238601938</v>
+        <v>3859.816138474841</v>
       </c>
       <c r="R13">
-        <v>0.1235955056179775</v>
+        <v>0.1363636363636364</v>
       </c>
       <c r="S13">
-        <v>0.0776964708489688</v>
+        <v>0.07795671093127342</v>
       </c>
       <c r="T13">
-        <v>0.6050642655297654</v>
+        <v>0.6100009237264243</v>
       </c>
       <c r="U13">
         <v>0.05728425489709894</v>
@@ -2391,7 +2391,7 @@
         </is>
       </c>
       <c r="Y13">
-        <v>15.6541111126826</v>
+        <v>14.34960185329238</v>
       </c>
       <c r="Z13">
         <v>0</v>
@@ -2399,22 +2399,22 @@
     </row>
     <row r="14">
       <c r="A14">
-        <v>0.12</v>
+        <v>0.13</v>
       </c>
       <c r="B14">
-        <v>0.07337116354523347</v>
+        <v>0.07322064826964793</v>
       </c>
       <c r="C14">
-        <v>47374.88259214153</v>
+        <v>46942.79103271024</v>
       </c>
       <c r="D14">
-        <v>48291.81859214154</v>
+        <v>48398.48003271024</v>
       </c>
       <c r="E14">
-        <v>-1328.564000000001</v>
+        <v>-789.8110000000006</v>
       </c>
       <c r="F14">
-        <v>6465.035999999999</v>
+        <v>7003.789</v>
       </c>
       <c r="G14">
         <v>5548.1</v>
@@ -2435,28 +2435,28 @@
         <v>5314.3</v>
       </c>
       <c r="M14">
-        <v>370.3447701429209</v>
+        <v>401.2068343214977</v>
       </c>
       <c r="N14">
-        <v>4943.955229857079</v>
+        <v>4913.093165678502</v>
       </c>
       <c r="O14">
-        <v>1513.839091382238</v>
+        <v>1504.389127330758</v>
       </c>
       <c r="P14">
-        <v>3430.116138474841</v>
+        <v>3408.704038347745</v>
       </c>
       <c r="Q14">
-        <v>3859.816138474841</v>
+        <v>3838.404038347745</v>
       </c>
       <c r="R14">
-        <v>0.1363636363636364</v>
+        <v>0.1494252873563219</v>
       </c>
       <c r="S14">
-        <v>0.07795671093127342</v>
+        <v>0.07822293354420573</v>
       </c>
       <c r="T14">
-        <v>0.6100009237264243</v>
+        <v>0.6150510683184087</v>
       </c>
       <c r="U14">
         <v>0.05728425489709894</v>
@@ -2473,7 +2473,7 @@
         </is>
       </c>
       <c r="Y14">
-        <v>14.34960185329238</v>
+        <v>13.24578632611605</v>
       </c>
       <c r="Z14">
         <v>0</v>
@@ -2481,22 +2481,22 @@
     </row>
     <row r="15">
       <c r="A15">
-        <v>0.13</v>
+        <v>0.14</v>
       </c>
       <c r="B15">
-        <v>0.07322064826964793</v>
+        <v>0.07307013299406238</v>
       </c>
       <c r="C15">
-        <v>46942.79103271024</v>
+        <v>46511.17167939289</v>
       </c>
       <c r="D15">
-        <v>48398.48003271024</v>
+        <v>48505.61367939289</v>
       </c>
       <c r="E15">
-        <v>-789.8110000000006</v>
+        <v>-251.058</v>
       </c>
       <c r="F15">
-        <v>7003.789</v>
+        <v>7542.542</v>
       </c>
       <c r="G15">
         <v>5548.1</v>
@@ -2517,28 +2517,28 @@
         <v>5314.3</v>
       </c>
       <c r="M15">
-        <v>401.2068343214977</v>
+        <v>432.0688985000745</v>
       </c>
       <c r="N15">
-        <v>4913.093165678502</v>
+        <v>4882.231101499926</v>
       </c>
       <c r="O15">
-        <v>1504.389127330758</v>
+        <v>1494.939163279277</v>
       </c>
       <c r="P15">
-        <v>3408.704038347745</v>
+        <v>3387.291938220648</v>
       </c>
       <c r="Q15">
-        <v>3838.404038347745</v>
+        <v>3816.991938220648</v>
       </c>
       <c r="R15">
-        <v>0.1494252873563219</v>
+        <v>0.1627906976744186</v>
       </c>
       <c r="S15">
-        <v>0.07822293354420573</v>
+        <v>0.07849534738069461</v>
       </c>
       <c r="T15">
-        <v>0.6150510683184087</v>
+        <v>0.6202186581334624</v>
       </c>
       <c r="U15">
         <v>0.05728425489709894</v>
@@ -2555,7 +2555,7 @@
         </is>
       </c>
       <c r="Y15">
-        <v>13.24578632611605</v>
+        <v>12.29965873139347</v>
       </c>
       <c r="Z15">
         <v>0</v>
@@ -2563,22 +2563,22 @@
     </row>
     <row r="16">
       <c r="A16">
-        <v>0.14</v>
+        <v>0.15</v>
       </c>
       <c r="B16">
-        <v>0.07307013299406238</v>
+        <v>0.07291961771847683</v>
       </c>
       <c r="C16">
-        <v>46511.17167939289</v>
+        <v>46080.0276749366</v>
       </c>
       <c r="D16">
-        <v>48505.61367939289</v>
+        <v>48613.2226749366</v>
       </c>
       <c r="E16">
-        <v>-251.058</v>
+        <v>287.6950000000006</v>
       </c>
       <c r="F16">
-        <v>7542.542</v>
+        <v>8081.295000000001</v>
       </c>
       <c r="G16">
         <v>5548.1</v>
@@ -2599,28 +2599,28 @@
         <v>5314.3</v>
       </c>
       <c r="M16">
-        <v>432.0688985000745</v>
+        <v>462.9309626786513</v>
       </c>
       <c r="N16">
-        <v>4882.231101499926</v>
+        <v>4851.369037321349</v>
       </c>
       <c r="O16">
-        <v>1494.939163279277</v>
+        <v>1485.489199227797</v>
       </c>
       <c r="P16">
-        <v>3387.291938220648</v>
+        <v>3365.879838093551</v>
       </c>
       <c r="Q16">
-        <v>3816.991938220648</v>
+        <v>3795.579838093551</v>
       </c>
       <c r="R16">
-        <v>0.1627906976744186</v>
+        <v>0.1764705882352942</v>
       </c>
       <c r="S16">
-        <v>0.07849534738069461</v>
+        <v>0.07877417095451264</v>
       </c>
       <c r="T16">
-        <v>0.6202186581334624</v>
+        <v>0.6255078382971057</v>
       </c>
       <c r="U16">
         <v>0.05728425489709894</v>
@@ -2637,7 +2637,7 @@
         </is>
       </c>
       <c r="Y16">
-        <v>12.29965873139347</v>
+        <v>11.4796814826339</v>
       </c>
       <c r="Z16">
         <v>0</v>
@@ -2645,22 +2645,22 @@
     </row>
     <row r="17">
       <c r="A17">
-        <v>0.15</v>
+        <v>0.16</v>
       </c>
       <c r="B17">
-        <v>0.07291961771847683</v>
+        <v>0.07276910244289128</v>
       </c>
       <c r="C17">
-        <v>46080.0276749366</v>
+        <v>45649.36219003901</v>
       </c>
       <c r="D17">
-        <v>48613.2226749366</v>
+        <v>48721.31019003901</v>
       </c>
       <c r="E17">
-        <v>287.6949999999988</v>
+        <v>826.4479999999985</v>
       </c>
       <c r="F17">
-        <v>8081.294999999999</v>
+        <v>8620.047999999999</v>
       </c>
       <c r="G17">
         <v>5548.1</v>
@@ -2681,28 +2681,28 @@
         <v>5314.3</v>
       </c>
       <c r="M17">
-        <v>462.9309626786512</v>
+        <v>493.7930268572279</v>
       </c>
       <c r="N17">
-        <v>4851.369037321349</v>
+        <v>4820.506973142772</v>
       </c>
       <c r="O17">
-        <v>1485.489199227797</v>
+        <v>1476.039235176317</v>
       </c>
       <c r="P17">
-        <v>3365.879838093552</v>
+        <v>3344.467737966455</v>
       </c>
       <c r="Q17">
-        <v>3795.579838093552</v>
+        <v>3774.167737966455</v>
       </c>
       <c r="R17">
-        <v>0.1764705882352941</v>
+        <v>0.1904761904761905</v>
       </c>
       <c r="S17">
-        <v>0.07877417095451264</v>
+        <v>0.07905963318485015</v>
       </c>
       <c r="T17">
-        <v>0.6255078382971057</v>
+        <v>0.6309229513217881</v>
       </c>
       <c r="U17">
         <v>0.05728425489709894</v>
@@ -2719,7 +2719,7 @@
         </is>
       </c>
       <c r="Y17">
-        <v>11.47968148263391</v>
+        <v>10.76220138996929</v>
       </c>
       <c r="Z17">
         <v>0</v>
@@ -2727,22 +2727,22 @@
     </row>
     <row r="18">
       <c r="A18">
-        <v>0.16</v>
+        <v>0.17</v>
       </c>
       <c r="B18">
-        <v>0.07276910244289128</v>
+        <v>0.07261858716730574</v>
       </c>
       <c r="C18">
-        <v>45649.36219003901</v>
+        <v>45219.17842365977</v>
       </c>
       <c r="D18">
-        <v>48721.31019003901</v>
+        <v>48829.87942365978</v>
       </c>
       <c r="E18">
-        <v>826.4479999999985</v>
+        <v>1365.200999999999</v>
       </c>
       <c r="F18">
-        <v>8620.047999999999</v>
+        <v>9158.800999999999</v>
       </c>
       <c r="G18">
         <v>5548.1</v>
@@ -2763,28 +2763,28 @@
         <v>5314.3</v>
       </c>
       <c r="M18">
-        <v>493.7930268572279</v>
+        <v>524.6550910358046</v>
       </c>
       <c r="N18">
-        <v>4820.506973142772</v>
+        <v>4789.644908964196</v>
       </c>
       <c r="O18">
-        <v>1476.039235176317</v>
+        <v>1466.589271124837</v>
       </c>
       <c r="P18">
-        <v>3344.467737966455</v>
+        <v>3323.055637839358</v>
       </c>
       <c r="Q18">
-        <v>3774.167737966455</v>
+        <v>3752.755637839358</v>
       </c>
       <c r="R18">
-        <v>0.1904761904761905</v>
+        <v>0.2048192771084338</v>
       </c>
       <c r="S18">
-        <v>0.07905963318485015</v>
+        <v>0.07935197402314759</v>
       </c>
       <c r="T18">
-        <v>0.6309229513217881</v>
+        <v>0.6364685489976676</v>
       </c>
       <c r="U18">
         <v>0.05728425489709894</v>
@@ -2801,7 +2801,7 @@
         </is>
       </c>
       <c r="Y18">
-        <v>10.76220138996929</v>
+        <v>10.1291307199711</v>
       </c>
       <c r="Z18">
         <v>0</v>
@@ -2809,22 +2809,22 @@
     </row>
     <row r="19">
       <c r="A19">
-        <v>0.17</v>
+        <v>0.18</v>
       </c>
       <c r="B19">
-        <v>0.07261858716730574</v>
+        <v>0.07246807189172018</v>
       </c>
       <c r="C19">
-        <v>45219.17842365977</v>
+        <v>44789.47960333613</v>
       </c>
       <c r="D19">
-        <v>48829.87942365978</v>
+        <v>48938.93360333614</v>
       </c>
       <c r="E19">
-        <v>1365.200999999999</v>
+        <v>1903.954</v>
       </c>
       <c r="F19">
-        <v>9158.800999999999</v>
+        <v>9697.554</v>
       </c>
       <c r="G19">
         <v>5548.1</v>
@@ -2845,28 +2845,28 @@
         <v>5314.3</v>
       </c>
       <c r="M19">
-        <v>524.6550910358046</v>
+        <v>555.5171552143814</v>
       </c>
       <c r="N19">
-        <v>4789.644908964196</v>
+        <v>4758.782844785619</v>
       </c>
       <c r="O19">
-        <v>1466.589271124837</v>
+        <v>1457.139307073357</v>
       </c>
       <c r="P19">
-        <v>3323.055637839358</v>
+        <v>3301.643537712263</v>
       </c>
       <c r="Q19">
-        <v>3752.755637839358</v>
+        <v>3731.343537712262</v>
       </c>
       <c r="R19">
-        <v>0.2048192771084338</v>
+        <v>0.2195121951219512</v>
       </c>
       <c r="S19">
-        <v>0.07935197402314759</v>
+        <v>0.07965144512579377</v>
       </c>
       <c r="T19">
-        <v>0.6364685489976676</v>
+        <v>0.6421494051534468</v>
       </c>
       <c r="U19">
         <v>0.05728425489709894</v>
@@ -2883,7 +2883,7 @@
         </is>
       </c>
       <c r="Y19">
-        <v>10.1291307199711</v>
+        <v>9.566401235528255</v>
       </c>
       <c r="Z19">
         <v>0</v>
@@ -2891,22 +2891,22 @@
     </row>
     <row r="20">
       <c r="A20">
-        <v>0.18</v>
+        <v>0.19</v>
       </c>
       <c r="B20">
-        <v>0.07246807189172018</v>
+        <v>0.07231755661613465</v>
       </c>
       <c r="C20">
-        <v>44789.47960333614</v>
+        <v>44360.26898550271</v>
       </c>
       <c r="D20">
-        <v>48938.93360333614</v>
+        <v>49048.47598550272</v>
       </c>
       <c r="E20">
-        <v>1903.953999999998</v>
+        <v>2442.706999999999</v>
       </c>
       <c r="F20">
-        <v>9697.553999999998</v>
+        <v>10236.307</v>
       </c>
       <c r="G20">
         <v>5548.1</v>
@@ -2927,28 +2927,28 @@
         <v>5314.3</v>
       </c>
       <c r="M20">
-        <v>555.5171552143813</v>
+        <v>586.3792193929581</v>
       </c>
       <c r="N20">
-        <v>4758.782844785619</v>
+        <v>4727.920780607042</v>
       </c>
       <c r="O20">
-        <v>1457.139307073357</v>
+        <v>1447.689343021876</v>
       </c>
       <c r="P20">
-        <v>3301.643537712263</v>
+        <v>3280.231437585166</v>
       </c>
       <c r="Q20">
-        <v>3731.343537712262</v>
+        <v>3709.931437585165</v>
       </c>
       <c r="R20">
-        <v>0.2195121951219512</v>
+        <v>0.2345679012345679</v>
       </c>
       <c r="S20">
-        <v>0.07965144512579375</v>
+        <v>0.07995831057665341</v>
       </c>
       <c r="T20">
-        <v>0.6421494051534465</v>
+        <v>0.6479705293624547</v>
       </c>
       <c r="U20">
         <v>0.05728425489709894</v>
@@ -2965,7 +2965,7 @@
         </is>
       </c>
       <c r="Y20">
-        <v>9.566401235528257</v>
+        <v>9.062906433658346</v>
       </c>
       <c r="Z20">
         <v>0</v>
@@ -2973,22 +2973,22 @@
     </row>
     <row r="21">
       <c r="A21">
-        <v>0.19</v>
+        <v>0.2</v>
       </c>
       <c r="B21">
-        <v>0.07231755661613465</v>
+        <v>0.0723751813405491</v>
       </c>
       <c r="C21">
-        <v>44360.26898550271</v>
+        <v>43779.51983622946</v>
       </c>
       <c r="D21">
-        <v>49048.47598550272</v>
+        <v>49006.47983622946</v>
       </c>
       <c r="E21">
-        <v>2442.706999999999</v>
+        <v>2981.459999999999</v>
       </c>
       <c r="F21">
-        <v>10236.307</v>
+        <v>10775.06</v>
       </c>
       <c r="G21">
         <v>5548.1</v>
@@ -3009,45 +3009,45 @@
         <v>5314.3</v>
       </c>
       <c r="M21">
-        <v>586.3792193929581</v>
+        <v>633.4038735715349</v>
       </c>
       <c r="N21">
-        <v>4727.920780607042</v>
+        <v>4680.896126428465</v>
       </c>
       <c r="O21">
-        <v>1447.689343021876</v>
+        <v>1433.290393912396</v>
       </c>
       <c r="P21">
-        <v>3280.231437585166</v>
+        <v>3247.605732516069</v>
       </c>
       <c r="Q21">
-        <v>3709.931437585165</v>
+        <v>3677.305732516069</v>
       </c>
       <c r="R21">
-        <v>0.2345679012345679</v>
+        <v>0.25</v>
       </c>
       <c r="S21">
-        <v>0.07995831057665341</v>
+        <v>0.08027284766378456</v>
       </c>
       <c r="T21">
-        <v>0.6479705293624547</v>
+        <v>0.6539371816766881</v>
       </c>
       <c r="U21">
-        <v>0.05728425489709894</v>
+        <v>0.05878425489709894</v>
       </c>
       <c r="V21">
         <v>0.3062</v>
       </c>
       <c r="W21">
-        <v>0.03974381604760725</v>
+        <v>0.04078451604760724</v>
       </c>
       <c r="X21" t="inlineStr">
         <is>
-          <t>Aaa/AAA</t>
+          <t>Aa2/AA</t>
         </is>
       </c>
       <c r="Y21">
-        <v>9.062906433658346</v>
+        <v>8.390065520178442</v>
       </c>
       <c r="Z21">
         <v>0</v>
@@ -3055,22 +3055,22 @@
     </row>
     <row r="22">
       <c r="A22">
-        <v>0.2</v>
+        <v>0.21</v>
       </c>
       <c r="B22">
-        <v>0.0723751813405491</v>
+        <v>0.07223507306496355</v>
       </c>
       <c r="C22">
-        <v>43779.51983622946</v>
+        <v>43343.0013283704</v>
       </c>
       <c r="D22">
-        <v>49006.47983622946</v>
+        <v>49108.7143283704</v>
       </c>
       <c r="E22">
-        <v>2981.459999999999</v>
+        <v>3520.213</v>
       </c>
       <c r="F22">
-        <v>10775.06</v>
+        <v>11313.813</v>
       </c>
       <c r="G22">
         <v>5548.1</v>
@@ -3091,28 +3091,28 @@
         <v>5314.3</v>
       </c>
       <c r="M22">
-        <v>633.4038735715349</v>
+        <v>665.0740672501116</v>
       </c>
       <c r="N22">
-        <v>4680.896126428465</v>
+        <v>4649.225932749889</v>
       </c>
       <c r="O22">
-        <v>1433.290393912396</v>
+        <v>1423.592980608016</v>
       </c>
       <c r="P22">
-        <v>3247.605732516069</v>
+        <v>3225.632952141873</v>
       </c>
       <c r="Q22">
-        <v>3677.305732516069</v>
+        <v>3655.332952141873</v>
       </c>
       <c r="R22">
-        <v>0.25</v>
+        <v>0.2658227848101266</v>
       </c>
       <c r="S22">
-        <v>0.08027284766378456</v>
+        <v>0.08059534771514687</v>
       </c>
       <c r="T22">
-        <v>0.6539371816766881</v>
+        <v>0.6600548884798895</v>
       </c>
       <c r="U22">
         <v>0.05878425489709894</v>
@@ -3129,7 +3129,7 @@
         </is>
       </c>
       <c r="Y22">
-        <v>8.390065520178442</v>
+        <v>7.990538590646135</v>
       </c>
       <c r="Z22">
         <v>0</v>
@@ -3137,22 +3137,22 @@
     </row>
     <row r="23">
       <c r="A23">
-        <v>0.21</v>
+        <v>0.22</v>
       </c>
       <c r="B23">
-        <v>0.07223507306496355</v>
+        <v>0.072094964789378</v>
       </c>
       <c r="C23">
-        <v>43343.0013283704</v>
+        <v>42906.91026362224</v>
       </c>
       <c r="D23">
-        <v>49108.7143283704</v>
+        <v>49211.37626362224</v>
       </c>
       <c r="E23">
-        <v>3520.212999999998</v>
+        <v>4058.965999999999</v>
       </c>
       <c r="F23">
-        <v>11313.813</v>
+        <v>11852.566</v>
       </c>
       <c r="G23">
         <v>5548.1</v>
@@ -3173,28 +3173,28 @@
         <v>5314.3</v>
       </c>
       <c r="M23">
-        <v>665.0740672501115</v>
+        <v>696.7442609286883</v>
       </c>
       <c r="N23">
-        <v>4649.225932749889</v>
+        <v>4617.555739071312</v>
       </c>
       <c r="O23">
-        <v>1423.592980608016</v>
+        <v>1413.895567303636</v>
       </c>
       <c r="P23">
-        <v>3225.632952141873</v>
+        <v>3203.660171767676</v>
       </c>
       <c r="Q23">
-        <v>3655.332952141873</v>
+        <v>3633.360171767676</v>
       </c>
       <c r="R23">
-        <v>0.2658227848101266</v>
+        <v>0.282051282051282</v>
       </c>
       <c r="S23">
-        <v>0.08059534771514687</v>
+        <v>0.08092611699859539</v>
       </c>
       <c r="T23">
-        <v>0.6600548884798895</v>
+        <v>0.6663294595600959</v>
       </c>
       <c r="U23">
         <v>0.05878425489709894</v>
@@ -3211,7 +3211,7 @@
         </is>
       </c>
       <c r="Y23">
-        <v>7.990538590646137</v>
+        <v>7.627332291071313</v>
       </c>
       <c r="Z23">
         <v>0</v>
@@ -3219,22 +3219,22 @@
     </row>
     <row r="24">
       <c r="A24">
-        <v>0.22</v>
+        <v>0.23</v>
       </c>
       <c r="B24">
-        <v>0.072094964789378</v>
+        <v>0.07195485651379245</v>
       </c>
       <c r="C24">
-        <v>42906.91026362224</v>
+        <v>42471.24932831462</v>
       </c>
       <c r="D24">
-        <v>49211.37626362224</v>
+        <v>49314.46832831462</v>
       </c>
       <c r="E24">
-        <v>4058.965999999999</v>
+        <v>4597.718999999999</v>
       </c>
       <c r="F24">
-        <v>11852.566</v>
+        <v>12391.319</v>
       </c>
       <c r="G24">
         <v>5548.1</v>
@@ -3255,28 +3255,28 @@
         <v>5314.3</v>
       </c>
       <c r="M24">
-        <v>696.7442609286883</v>
+        <v>728.414454607265</v>
       </c>
       <c r="N24">
-        <v>4617.555739071312</v>
+        <v>4585.885545392735</v>
       </c>
       <c r="O24">
-        <v>1413.895567303636</v>
+        <v>1404.198153999256</v>
       </c>
       <c r="P24">
-        <v>3203.660171767676</v>
+        <v>3181.68739139348</v>
       </c>
       <c r="Q24">
-        <v>3633.360171767676</v>
+        <v>3611.387391393479</v>
       </c>
       <c r="R24">
-        <v>0.282051282051282</v>
+        <v>0.2987012987012987</v>
       </c>
       <c r="S24">
-        <v>0.08092611699859539</v>
+        <v>0.08126547769200362</v>
       </c>
       <c r="T24">
-        <v>0.6663294595600959</v>
+        <v>0.6727670065125155</v>
       </c>
       <c r="U24">
         <v>0.05878425489709894</v>
@@ -3293,7 +3293,7 @@
         </is>
       </c>
       <c r="Y24">
-        <v>7.627332291071313</v>
+        <v>7.295709147981255</v>
       </c>
       <c r="Z24">
         <v>0</v>
@@ -3301,22 +3301,22 @@
     </row>
     <row r="25">
       <c r="A25">
-        <v>0.23</v>
+        <v>0.24</v>
       </c>
       <c r="B25">
-        <v>0.07195485651379245</v>
+        <v>0.0718147482382069</v>
       </c>
       <c r="C25">
-        <v>42471.24932831462</v>
+        <v>42036.02123133464</v>
       </c>
       <c r="D25">
-        <v>49314.46832831462</v>
+        <v>49417.99323133464</v>
       </c>
       <c r="E25">
-        <v>4597.718999999999</v>
+        <v>5136.472</v>
       </c>
       <c r="F25">
-        <v>12391.319</v>
+        <v>12930.072</v>
       </c>
       <c r="G25">
         <v>5548.1</v>
@@ -3337,28 +3337,28 @@
         <v>5314.3</v>
       </c>
       <c r="M25">
-        <v>728.414454607265</v>
+        <v>760.0846482858418</v>
       </c>
       <c r="N25">
-        <v>4585.885545392735</v>
+        <v>4554.215351714159</v>
       </c>
       <c r="O25">
-        <v>1404.198153999256</v>
+        <v>1394.500740694876</v>
       </c>
       <c r="P25">
-        <v>3181.68739139348</v>
+        <v>3159.714611019283</v>
       </c>
       <c r="Q25">
-        <v>3611.387391393479</v>
+        <v>3589.414611019283</v>
       </c>
       <c r="R25">
-        <v>0.2987012987012987</v>
+        <v>0.3157894736842106</v>
       </c>
       <c r="S25">
-        <v>0.08126547769200362</v>
+        <v>0.08161376892997521</v>
       </c>
       <c r="T25">
-        <v>0.6727670065125155</v>
+        <v>0.6793739625952619</v>
       </c>
       <c r="U25">
         <v>0.05878425489709894</v>
@@ -3375,7 +3375,7 @@
         </is>
       </c>
       <c r="Y25">
-        <v>7.295709147981255</v>
+        <v>6.99172126681537</v>
       </c>
       <c r="Z25">
         <v>0</v>
@@ -3383,22 +3383,22 @@
     </row>
     <row r="26">
       <c r="A26">
-        <v>0.24</v>
+        <v>0.25</v>
       </c>
       <c r="B26">
-        <v>0.0718147482382069</v>
+        <v>0.07167463996262136</v>
       </c>
       <c r="C26">
-        <v>42036.02123133464</v>
+        <v>41601.22870436406</v>
       </c>
       <c r="D26">
-        <v>49417.99323133464</v>
+        <v>49521.95370436406</v>
       </c>
       <c r="E26">
-        <v>5136.471999999998</v>
+        <v>5675.224999999999</v>
       </c>
       <c r="F26">
-        <v>12930.072</v>
+        <v>13468.825</v>
       </c>
       <c r="G26">
         <v>5548.1</v>
@@ -3419,28 +3419,28 @@
         <v>5314.3</v>
       </c>
       <c r="M26">
-        <v>760.0846482858418</v>
+        <v>791.7548419644186</v>
       </c>
       <c r="N26">
-        <v>4554.215351714159</v>
+        <v>4522.545158035582</v>
       </c>
       <c r="O26">
-        <v>1394.500740694876</v>
+        <v>1384.803327390495</v>
       </c>
       <c r="P26">
-        <v>3159.714611019283</v>
+        <v>3137.741830645087</v>
       </c>
       <c r="Q26">
-        <v>3589.414611019283</v>
+        <v>3567.441830645087</v>
       </c>
       <c r="R26">
-        <v>0.3157894736842105</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="S26">
-        <v>0.08161376892997521</v>
+        <v>0.08197134793429273</v>
       </c>
       <c r="T26">
-        <v>0.6793739625952619</v>
+        <v>0.6861571041735484</v>
       </c>
       <c r="U26">
         <v>0.05878425489709894</v>
@@ -3457,7 +3457,7 @@
         </is>
       </c>
       <c r="Y26">
-        <v>6.99172126681537</v>
+        <v>6.712052416142755</v>
       </c>
       <c r="Z26">
         <v>0</v>
@@ -3465,22 +3465,22 @@
     </row>
     <row r="27">
       <c r="A27">
-        <v>0.25</v>
+        <v>0.26</v>
       </c>
       <c r="B27">
-        <v>0.07167463996262136</v>
+        <v>0.0718411912870358</v>
       </c>
       <c r="C27">
-        <v>41601.22870436406</v>
+        <v>40938.94340800585</v>
       </c>
       <c r="D27">
-        <v>49521.95370436406</v>
+        <v>49398.42140800585</v>
       </c>
       <c r="E27">
-        <v>5675.224999999999</v>
+        <v>6213.977999999999</v>
       </c>
       <c r="F27">
-        <v>13468.825</v>
+        <v>14007.578</v>
       </c>
       <c r="G27">
         <v>5548.1</v>
@@ -3501,45 +3501,45 @@
         <v>5314.3</v>
       </c>
       <c r="M27">
-        <v>791.7548419644186</v>
+        <v>847.2379182429953</v>
       </c>
       <c r="N27">
-        <v>4522.545158035582</v>
+        <v>4467.062081757005</v>
       </c>
       <c r="O27">
-        <v>1384.803327390495</v>
+        <v>1367.814409433995</v>
       </c>
       <c r="P27">
-        <v>3137.741830645087</v>
+        <v>3099.24767232301</v>
       </c>
       <c r="Q27">
-        <v>3567.441830645087</v>
+        <v>3528.94767232301</v>
       </c>
       <c r="R27">
-        <v>0.3333333333333333</v>
+        <v>0.3513513513513514</v>
       </c>
       <c r="S27">
-        <v>0.08197134793429273</v>
+        <v>0.08233859123602422</v>
       </c>
       <c r="T27">
-        <v>0.6861571041735484</v>
+        <v>0.6931235739025992</v>
       </c>
       <c r="U27">
-        <v>0.05878425489709894</v>
+        <v>0.06048425489709894</v>
       </c>
       <c r="V27">
         <v>0.3062</v>
       </c>
       <c r="W27">
-        <v>0.04078451604760724</v>
+        <v>0.04196397604760724</v>
       </c>
       <c r="X27" t="inlineStr">
         <is>
-          <t>Aa2/AA</t>
+          <t>A1/A+</t>
         </is>
       </c>
       <c r="Y27">
-        <v>6.712052416142755</v>
+        <v>6.272500186276853</v>
       </c>
       <c r="Z27">
         <v>0</v>
@@ -3547,22 +3547,22 @@
     </row>
     <row r="28">
       <c r="A28">
-        <v>0.26</v>
+        <v>0.27</v>
       </c>
       <c r="B28">
-        <v>0.0718411912870358</v>
+        <v>0.07171287761145026</v>
       </c>
       <c r="C28">
-        <v>40938.94340800585</v>
+        <v>40495.30696023503</v>
       </c>
       <c r="D28">
-        <v>49398.42140800585</v>
+        <v>49493.53796023503</v>
       </c>
       <c r="E28">
-        <v>6213.977999999999</v>
+        <v>6752.731</v>
       </c>
       <c r="F28">
-        <v>14007.578</v>
+        <v>14546.331</v>
       </c>
       <c r="G28">
         <v>5548.1</v>
@@ -3583,28 +3583,28 @@
         <v>5314.3</v>
       </c>
       <c r="M28">
-        <v>847.2379182429953</v>
+        <v>879.8239920215721</v>
       </c>
       <c r="N28">
-        <v>4467.062081757005</v>
+        <v>4434.476007978428</v>
       </c>
       <c r="O28">
-        <v>1367.814409433995</v>
+        <v>1357.836553642995</v>
       </c>
       <c r="P28">
-        <v>3099.24767232301</v>
+        <v>3076.639454335434</v>
       </c>
       <c r="Q28">
-        <v>3528.94767232301</v>
+        <v>3506.339454335433</v>
       </c>
       <c r="R28">
-        <v>0.3513513513513514</v>
+        <v>0.3698630136986302</v>
       </c>
       <c r="S28">
-        <v>0.08233859123602422</v>
+        <v>0.08271589599807713</v>
       </c>
       <c r="T28">
-        <v>0.6931235739025992</v>
+        <v>0.7002809058160075</v>
       </c>
       <c r="U28">
         <v>0.06048425489709894</v>
@@ -3621,7 +3621,7 @@
         </is>
       </c>
       <c r="Y28">
-        <v>6.272500186276853</v>
+        <v>6.040185364562895</v>
       </c>
       <c r="Z28">
         <v>0</v>
@@ -3629,22 +3629,22 @@
     </row>
     <row r="29">
       <c r="A29">
-        <v>0.27</v>
+        <v>0.28</v>
       </c>
       <c r="B29">
-        <v>0.07171287761145026</v>
+        <v>0.07158456393586472</v>
       </c>
       <c r="C29">
-        <v>40495.30696023503</v>
+        <v>40052.03751254803</v>
       </c>
       <c r="D29">
-        <v>49493.53796023503</v>
+        <v>49589.02151254803</v>
       </c>
       <c r="E29">
-        <v>6752.731</v>
+        <v>7291.484</v>
       </c>
       <c r="F29">
-        <v>14546.331</v>
+        <v>15085.084</v>
       </c>
       <c r="G29">
         <v>5548.1</v>
@@ -3665,28 +3665,28 @@
         <v>5314.3</v>
       </c>
       <c r="M29">
-        <v>879.8239920215721</v>
+        <v>912.4100658001489</v>
       </c>
       <c r="N29">
-        <v>4434.476007978428</v>
+        <v>4401.889934199851</v>
       </c>
       <c r="O29">
-        <v>1357.836553642995</v>
+        <v>1347.858697851995</v>
       </c>
       <c r="P29">
-        <v>3076.639454335434</v>
+        <v>3054.031236347857</v>
       </c>
       <c r="Q29">
-        <v>3506.339454335433</v>
+        <v>3483.731236347857</v>
       </c>
       <c r="R29">
-        <v>0.3698630136986302</v>
+        <v>0.388888888888889</v>
       </c>
       <c r="S29">
-        <v>0.08271589599807713</v>
+        <v>0.08310368144796484</v>
       </c>
       <c r="T29">
-        <v>0.7002809058160075</v>
+        <v>0.7076370525047885</v>
       </c>
       <c r="U29">
         <v>0.06048425489709894</v>
@@ -3703,7 +3703,7 @@
         </is>
       </c>
       <c r="Y29">
-        <v>6.040185364562895</v>
+        <v>5.824464458685648</v>
       </c>
       <c r="Z29">
         <v>0</v>
@@ -3711,22 +3711,22 @@
     </row>
     <row r="30">
       <c r="A30">
-        <v>0.28</v>
+        <v>0.29</v>
       </c>
       <c r="B30">
-        <v>0.07158456393586472</v>
+        <v>0.07145625026027916</v>
       </c>
       <c r="C30">
-        <v>40052.03751254803</v>
+        <v>39609.13719311406</v>
       </c>
       <c r="D30">
-        <v>49589.02151254803</v>
+        <v>49684.87419311406</v>
       </c>
       <c r="E30">
-        <v>7291.484</v>
+        <v>7830.237000000001</v>
       </c>
       <c r="F30">
-        <v>15085.084</v>
+        <v>15623.837</v>
       </c>
       <c r="G30">
         <v>5548.1</v>
@@ -3747,28 +3747,28 @@
         <v>5314.3</v>
       </c>
       <c r="M30">
-        <v>912.4100658001489</v>
+        <v>944.9961395787257</v>
       </c>
       <c r="N30">
-        <v>4401.889934199851</v>
+        <v>4369.303860421274</v>
       </c>
       <c r="O30">
-        <v>1347.858697851995</v>
+        <v>1337.880842060994</v>
       </c>
       <c r="P30">
-        <v>3054.031236347857</v>
+        <v>3031.42301836028</v>
       </c>
       <c r="Q30">
-        <v>3483.731236347857</v>
+        <v>3461.12301836028</v>
       </c>
       <c r="R30">
-        <v>0.388888888888889</v>
+        <v>0.4084507042253522</v>
       </c>
       <c r="S30">
-        <v>0.08310368144796484</v>
+        <v>0.0835023904316522</v>
       </c>
       <c r="T30">
-        <v>0.7076370525047885</v>
+        <v>0.7152004145932532</v>
       </c>
       <c r="U30">
         <v>0.06048425489709894</v>
@@ -3785,7 +3785,7 @@
         </is>
       </c>
       <c r="Y30">
-        <v>5.824464458685648</v>
+        <v>5.623620856662004</v>
       </c>
       <c r="Z30">
         <v>0</v>
@@ -3793,22 +3793,22 @@
     </row>
     <row r="31">
       <c r="A31">
-        <v>0.29</v>
+        <v>0.3</v>
       </c>
       <c r="B31">
-        <v>0.07145625026027916</v>
+        <v>0.0714944485846936</v>
       </c>
       <c r="C31">
-        <v>39609.13719311406</v>
+        <v>39041.81062655097</v>
       </c>
       <c r="D31">
-        <v>49684.87419311406</v>
+        <v>49656.30062655097</v>
       </c>
       <c r="E31">
-        <v>7830.236999999997</v>
+        <v>8368.989999999998</v>
       </c>
       <c r="F31">
-        <v>15623.837</v>
+        <v>16162.59</v>
       </c>
       <c r="G31">
         <v>5548.1</v>
@@ -3829,45 +3829,45 @@
         <v>5314.3</v>
       </c>
       <c r="M31">
-        <v>944.9961395787254</v>
+        <v>990.5122853573023</v>
       </c>
       <c r="N31">
-        <v>4369.303860421274</v>
+        <v>4323.787714642698</v>
       </c>
       <c r="O31">
-        <v>1337.880842060994</v>
+        <v>1323.943798223594</v>
       </c>
       <c r="P31">
-        <v>3031.42301836028</v>
+        <v>2999.843916419104</v>
       </c>
       <c r="Q31">
-        <v>3461.12301836028</v>
+        <v>3429.543916419104</v>
       </c>
       <c r="R31">
-        <v>0.4084507042253521</v>
+        <v>0.4285714285714286</v>
       </c>
       <c r="S31">
-        <v>0.0835023904316522</v>
+        <v>0.08391249110058777</v>
       </c>
       <c r="T31">
-        <v>0.7152004145932532</v>
+        <v>0.7229798727413884</v>
       </c>
       <c r="U31">
-        <v>0.06048425489709894</v>
+        <v>0.06128425489709894</v>
       </c>
       <c r="V31">
         <v>0.3062</v>
       </c>
       <c r="W31">
-        <v>0.04196397604760724</v>
+        <v>0.04251901604760724</v>
       </c>
       <c r="X31" t="inlineStr">
         <is>
-          <t>A1/A+</t>
+          <t>A2/A</t>
         </is>
       </c>
       <c r="Y31">
-        <v>5.623620856662005</v>
+        <v>5.365203519997737</v>
       </c>
       <c r="Z31">
         <v>0</v>
@@ -3875,22 +3875,22 @@
     </row>
     <row r="32">
       <c r="A32">
-        <v>0.3</v>
+        <v>0.31</v>
       </c>
       <c r="B32">
-        <v>0.0714944485846936</v>
+        <v>0.07137168530910806</v>
       </c>
       <c r="C32">
-        <v>39041.81062655097</v>
+        <v>38595.00561001849</v>
       </c>
       <c r="D32">
-        <v>49656.30062655097</v>
+        <v>49748.24861001848</v>
       </c>
       <c r="E32">
-        <v>8368.989999999998</v>
+        <v>8907.742999999997</v>
       </c>
       <c r="F32">
-        <v>16162.59</v>
+        <v>16701.343</v>
       </c>
       <c r="G32">
         <v>5548.1</v>
@@ -3911,28 +3911,28 @@
         <v>5314.3</v>
       </c>
       <c r="M32">
-        <v>990.5122853573023</v>
+        <v>1023.529361535879</v>
       </c>
       <c r="N32">
-        <v>4323.787714642698</v>
+        <v>4290.770638464121</v>
       </c>
       <c r="O32">
-        <v>1323.943798223594</v>
+        <v>1313.833969497714</v>
       </c>
       <c r="P32">
-        <v>2999.843916419104</v>
+        <v>2976.936668966408</v>
       </c>
       <c r="Q32">
-        <v>3429.543916419104</v>
+        <v>3406.636668966407</v>
       </c>
       <c r="R32">
-        <v>0.4285714285714286</v>
+        <v>0.4492753623188406</v>
       </c>
       <c r="S32">
-        <v>0.08391249110058777</v>
+        <v>0.08433447874543452</v>
       </c>
       <c r="T32">
-        <v>0.7229798727413884</v>
+        <v>0.7309848224300494</v>
       </c>
       <c r="U32">
         <v>0.06128425489709894</v>
@@ -3949,7 +3949,7 @@
         </is>
       </c>
       <c r="Y32">
-        <v>5.365203519997737</v>
+        <v>5.192132438707487</v>
       </c>
       <c r="Z32">
         <v>0</v>
@@ -3957,22 +3957,22 @@
     </row>
     <row r="33">
       <c r="A33">
-        <v>0.31</v>
+        <v>0.32</v>
       </c>
       <c r="B33">
-        <v>0.07137168530910806</v>
+        <v>0.07124892203352251</v>
       </c>
       <c r="C33">
-        <v>38595.00561001849</v>
+        <v>38148.54174317174</v>
       </c>
       <c r="D33">
-        <v>49748.24861001848</v>
+        <v>49840.53774317174</v>
       </c>
       <c r="E33">
-        <v>8907.742999999997</v>
+        <v>9446.495999999997</v>
       </c>
       <c r="F33">
-        <v>16701.343</v>
+        <v>17240.096</v>
       </c>
       <c r="G33">
         <v>5548.1</v>
@@ -3993,28 +3993,28 @@
         <v>5314.3</v>
       </c>
       <c r="M33">
-        <v>1023.529361535879</v>
+        <v>1056.546437714456</v>
       </c>
       <c r="N33">
-        <v>4290.770638464121</v>
+        <v>4257.753562285545</v>
       </c>
       <c r="O33">
-        <v>1313.833969497714</v>
+        <v>1303.724140771834</v>
       </c>
       <c r="P33">
-        <v>2976.936668966408</v>
+        <v>2954.029421513711</v>
       </c>
       <c r="Q33">
-        <v>3406.636668966407</v>
+        <v>3383.729421513711</v>
       </c>
       <c r="R33">
-        <v>0.4492753623188406</v>
+        <v>0.4705882352941177</v>
       </c>
       <c r="S33">
-        <v>0.08433447874543452</v>
+        <v>0.08476887779160029</v>
       </c>
       <c r="T33">
-        <v>0.7309848224300494</v>
+        <v>0.7392252118154355</v>
       </c>
       <c r="U33">
         <v>0.06128425489709894</v>
@@ -4031,7 +4031,7 @@
         </is>
       </c>
       <c r="Y33">
-        <v>5.192132438707487</v>
+        <v>5.029878299997878</v>
       </c>
       <c r="Z33">
         <v>0</v>
@@ -4039,22 +4039,22 @@
     </row>
     <row r="34">
       <c r="A34">
-        <v>0.32</v>
+        <v>0.33</v>
       </c>
       <c r="B34">
-        <v>0.07124892203352251</v>
+        <v>0.07112615875793697</v>
       </c>
       <c r="C34">
-        <v>38148.54174317174</v>
+        <v>37702.4209281636</v>
       </c>
       <c r="D34">
-        <v>49840.53774317174</v>
+        <v>49933.1699281636</v>
       </c>
       <c r="E34">
-        <v>9446.495999999997</v>
+        <v>9985.248999999998</v>
       </c>
       <c r="F34">
-        <v>17240.096</v>
+        <v>17778.849</v>
       </c>
       <c r="G34">
         <v>5548.1</v>
@@ -4075,28 +4075,28 @@
         <v>5314.3</v>
       </c>
       <c r="M34">
-        <v>1056.546437714456</v>
+        <v>1089.563513893032</v>
       </c>
       <c r="N34">
-        <v>4257.753562285545</v>
+        <v>4224.736486106967</v>
       </c>
       <c r="O34">
-        <v>1303.724140771834</v>
+        <v>1293.614312045954</v>
       </c>
       <c r="P34">
-        <v>2954.029421513711</v>
+        <v>2931.122174061014</v>
       </c>
       <c r="Q34">
-        <v>3383.729421513711</v>
+        <v>3360.822174061013</v>
       </c>
       <c r="R34">
-        <v>0.4705882352941177</v>
+        <v>0.4925373134328359</v>
       </c>
       <c r="S34">
-        <v>0.08476887779160029</v>
+        <v>0.08521624397347251</v>
       </c>
       <c r="T34">
-        <v>0.7392252118154355</v>
+        <v>0.7477115829735199</v>
       </c>
       <c r="U34">
         <v>0.06128425489709894</v>
@@ -4113,7 +4113,7 @@
         </is>
       </c>
       <c r="Y34">
-        <v>5.029878299997878</v>
+        <v>4.877457745452487</v>
       </c>
       <c r="Z34">
         <v>0</v>
@@ -4121,22 +4121,22 @@
     </row>
     <row r="35">
       <c r="A35">
-        <v>0.33</v>
+        <v>0.34</v>
       </c>
       <c r="B35">
-        <v>0.07112615875793697</v>
+        <v>0.07100339548235142</v>
       </c>
       <c r="C35">
-        <v>37702.4209281636</v>
+        <v>37256.64508131442</v>
       </c>
       <c r="D35">
-        <v>49933.1699281636</v>
+        <v>50026.14708131442</v>
       </c>
       <c r="E35">
-        <v>9985.248999999998</v>
+        <v>10524.002</v>
       </c>
       <c r="F35">
-        <v>17778.849</v>
+        <v>18317.602</v>
       </c>
       <c r="G35">
         <v>5548.1</v>
@@ -4157,28 +4157,28 @@
         <v>5314.3</v>
       </c>
       <c r="M35">
-        <v>1089.563513893032</v>
+        <v>1122.580590071609</v>
       </c>
       <c r="N35">
-        <v>4224.736486106967</v>
+        <v>4191.719409928391</v>
       </c>
       <c r="O35">
-        <v>1293.614312045954</v>
+        <v>1283.504483320073</v>
       </c>
       <c r="P35">
-        <v>2931.122174061014</v>
+        <v>2908.214926608317</v>
       </c>
       <c r="Q35">
-        <v>3360.822174061013</v>
+        <v>3337.914926608317</v>
       </c>
       <c r="R35">
-        <v>0.4925373134328359</v>
+        <v>0.5151515151515152</v>
       </c>
       <c r="S35">
-        <v>0.08521624397347251</v>
+        <v>0.08567716670631055</v>
       </c>
       <c r="T35">
-        <v>0.7477115829735199</v>
+        <v>0.7564551168939705</v>
       </c>
       <c r="U35">
         <v>0.06128425489709894</v>
@@ -4195,7 +4195,7 @@
         </is>
       </c>
       <c r="Y35">
-        <v>4.877457745452487</v>
+        <v>4.734003105880355</v>
       </c>
       <c r="Z35">
         <v>0</v>
@@ -4203,22 +4203,22 @@
     </row>
     <row r="36">
       <c r="A36">
-        <v>0.34</v>
+        <v>0.35</v>
       </c>
       <c r="B36">
-        <v>0.07100339548235142</v>
+        <v>0.07088063220676587</v>
       </c>
       <c r="C36">
-        <v>37256.64508131442</v>
+        <v>36811.21613324419</v>
       </c>
       <c r="D36">
-        <v>50026.14708131442</v>
+        <v>50119.47113324419</v>
       </c>
       <c r="E36">
-        <v>10524.002</v>
+        <v>11062.755</v>
       </c>
       <c r="F36">
-        <v>18317.602</v>
+        <v>18856.355</v>
       </c>
       <c r="G36">
         <v>5548.1</v>
@@ -4239,28 +4239,28 @@
         <v>5314.3</v>
       </c>
       <c r="M36">
-        <v>1122.580590071609</v>
+        <v>1155.597666250186</v>
       </c>
       <c r="N36">
-        <v>4191.719409928391</v>
+        <v>4158.702333749814</v>
       </c>
       <c r="O36">
-        <v>1283.504483320073</v>
+        <v>1273.394654594193</v>
       </c>
       <c r="P36">
-        <v>2908.214926608317</v>
+        <v>2885.307679155621</v>
       </c>
       <c r="Q36">
-        <v>3337.914926608317</v>
+        <v>3315.007679155621</v>
       </c>
       <c r="R36">
-        <v>0.5151515151515152</v>
+        <v>0.5384615384615385</v>
       </c>
       <c r="S36">
-        <v>0.08567716670631055</v>
+        <v>0.08615227167708206</v>
       </c>
       <c r="T36">
-        <v>0.7564551168939705</v>
+        <v>0.7654676826273579</v>
       </c>
       <c r="U36">
         <v>0.06128425489709894</v>
@@ -4277,7 +4277,7 @@
         </is>
       </c>
       <c r="Y36">
-        <v>4.734003105880355</v>
+        <v>4.598745874283773</v>
       </c>
       <c r="Z36">
         <v>0</v>
@@ -4285,22 +4285,22 @@
     </row>
     <row r="37">
       <c r="A37">
-        <v>0.35</v>
+        <v>0.36</v>
       </c>
       <c r="B37">
-        <v>0.07088063220676587</v>
+        <v>0.07075786893118033</v>
       </c>
       <c r="C37">
-        <v>36811.21613324419</v>
+        <v>36366.13602900613</v>
       </c>
       <c r="D37">
-        <v>50119.47113324419</v>
+        <v>50213.14402900614</v>
       </c>
       <c r="E37">
-        <v>11062.755</v>
+        <v>11601.508</v>
       </c>
       <c r="F37">
-        <v>18856.355</v>
+        <v>19395.108</v>
       </c>
       <c r="G37">
         <v>5548.1</v>
@@ -4321,28 +4321,28 @@
         <v>5314.3</v>
       </c>
       <c r="M37">
-        <v>1155.597666250186</v>
+        <v>1188.614742428763</v>
       </c>
       <c r="N37">
-        <v>4158.702333749814</v>
+        <v>4125.685257571237</v>
       </c>
       <c r="O37">
-        <v>1273.394654594193</v>
+        <v>1263.284825868313</v>
       </c>
       <c r="P37">
-        <v>2885.307679155621</v>
+        <v>2862.400431702924</v>
       </c>
       <c r="Q37">
-        <v>3315.007679155621</v>
+        <v>3292.100431702924</v>
       </c>
       <c r="R37">
-        <v>0.5384615384615385</v>
+        <v>0.5625000000000001</v>
       </c>
       <c r="S37">
-        <v>0.08615227167708206</v>
+        <v>0.08664222367819019</v>
       </c>
       <c r="T37">
-        <v>0.7654676826273579</v>
+        <v>0.7747618910399137</v>
       </c>
       <c r="U37">
         <v>0.06128425489709894</v>
@@ -4359,7 +4359,7 @@
         </is>
       </c>
       <c r="Y37">
-        <v>4.598745874283773</v>
+        <v>4.471002933331446</v>
       </c>
       <c r="Z37">
         <v>0</v>
@@ -4367,22 +4367,22 @@
     </row>
     <row r="38">
       <c r="A38">
-        <v>0.36</v>
+        <v>0.37</v>
       </c>
       <c r="B38">
-        <v>0.07075786893118033</v>
+        <v>0.07063510565559478</v>
       </c>
       <c r="C38">
-        <v>36366.13602900614</v>
+        <v>35921.4067282219</v>
       </c>
       <c r="D38">
-        <v>50213.14402900614</v>
+        <v>50307.1677282219</v>
       </c>
       <c r="E38">
-        <v>11601.508</v>
+        <v>12140.261</v>
       </c>
       <c r="F38">
-        <v>19395.108</v>
+        <v>19933.861</v>
       </c>
       <c r="G38">
         <v>5548.1</v>
@@ -4403,28 +4403,28 @@
         <v>5314.3</v>
       </c>
       <c r="M38">
-        <v>1188.614742428763</v>
+        <v>1221.631818607339</v>
       </c>
       <c r="N38">
-        <v>4125.685257571237</v>
+        <v>4092.668181392661</v>
       </c>
       <c r="O38">
-        <v>1263.284825868313</v>
+        <v>1253.174997142433</v>
       </c>
       <c r="P38">
-        <v>2862.400431702924</v>
+        <v>2839.493184250228</v>
       </c>
       <c r="Q38">
-        <v>3292.100431702924</v>
+        <v>3269.193184250228</v>
       </c>
       <c r="R38">
-        <v>0.5625</v>
+        <v>0.5873015873015873</v>
       </c>
       <c r="S38">
-        <v>0.08664222367819019</v>
+        <v>0.08714772971107952</v>
       </c>
       <c r="T38">
-        <v>0.7747618910399137</v>
+        <v>0.7843511536877886</v>
       </c>
       <c r="U38">
         <v>0.06128425489709894</v>
@@ -4441,7 +4441,7 @@
         </is>
       </c>
       <c r="Y38">
-        <v>4.471002933331447</v>
+        <v>4.350165016214381</v>
       </c>
       <c r="Z38">
         <v>0</v>
@@ -4449,22 +4449,22 @@
     </row>
     <row r="39">
       <c r="A39">
-        <v>0.37</v>
+        <v>0.38</v>
       </c>
       <c r="B39">
-        <v>0.07063510565559478</v>
+        <v>0.07077598638000923</v>
       </c>
       <c r="C39">
-        <v>35921.4067282219</v>
+        <v>35274.78373071074</v>
       </c>
       <c r="D39">
-        <v>50307.1677282219</v>
+        <v>50199.29773071074</v>
       </c>
       <c r="E39">
-        <v>12140.261</v>
+        <v>12679.014</v>
       </c>
       <c r="F39">
-        <v>19933.861</v>
+        <v>20472.614</v>
       </c>
       <c r="G39">
         <v>5548.1</v>
@@ -4485,45 +4485,45 @@
         <v>5314.3</v>
       </c>
       <c r="M39">
-        <v>1221.631818607339</v>
+        <v>1275.121508785916</v>
       </c>
       <c r="N39">
-        <v>4092.668181392661</v>
+        <v>4039.178491214084</v>
       </c>
       <c r="O39">
-        <v>1253.174997142433</v>
+        <v>1236.796454009753</v>
       </c>
       <c r="P39">
-        <v>2839.493184250228</v>
+        <v>2802.382037204331</v>
       </c>
       <c r="Q39">
-        <v>3269.193184250228</v>
+        <v>3232.082037204331</v>
       </c>
       <c r="R39">
-        <v>0.5873015873015873</v>
+        <v>0.6129032258064516</v>
       </c>
       <c r="S39">
-        <v>0.08714772971107952</v>
+        <v>0.08766954239019109</v>
       </c>
       <c r="T39">
-        <v>0.7843511536877886</v>
+        <v>0.794249747388821</v>
       </c>
       <c r="U39">
-        <v>0.06128425489709894</v>
+        <v>0.06228425489709894</v>
       </c>
       <c r="V39">
         <v>0.3062</v>
       </c>
       <c r="W39">
-        <v>0.04251901604760724</v>
+        <v>0.04321281604760725</v>
       </c>
       <c r="X39" t="inlineStr">
         <is>
-          <t>A2/A</t>
+          <t>A3/A-</t>
         </is>
       </c>
       <c r="Y39">
-        <v>4.350165016214381</v>
+        <v>4.167681247146332</v>
       </c>
       <c r="Z39">
         <v>0</v>
@@ -4531,22 +4531,22 @@
     </row>
     <row r="40">
       <c r="A40">
-        <v>0.38</v>
+        <v>0.39</v>
       </c>
       <c r="B40">
-        <v>0.07077598638000923</v>
+        <v>0.07066016110442369</v>
       </c>
       <c r="C40">
-        <v>35274.78373071074</v>
+        <v>34824.68231337438</v>
       </c>
       <c r="D40">
-        <v>50199.29773071074</v>
+        <v>50287.94931337438</v>
       </c>
       <c r="E40">
-        <v>12679.014</v>
+        <v>13217.767</v>
       </c>
       <c r="F40">
-        <v>20472.614</v>
+        <v>21011.367</v>
       </c>
       <c r="G40">
         <v>5548.1</v>
@@ -4567,28 +4567,28 @@
         <v>5314.3</v>
       </c>
       <c r="M40">
-        <v>1275.121508785916</v>
+        <v>1308.677337964493</v>
       </c>
       <c r="N40">
-        <v>4039.178491214084</v>
+        <v>4005.622662035507</v>
       </c>
       <c r="O40">
-        <v>1236.796454009753</v>
+        <v>1226.521659115273</v>
       </c>
       <c r="P40">
-        <v>2802.382037204331</v>
+        <v>2779.101002920235</v>
       </c>
       <c r="Q40">
-        <v>3232.082037204331</v>
+        <v>3208.801002920235</v>
       </c>
       <c r="R40">
-        <v>0.6129032258064516</v>
+        <v>0.639344262295082</v>
       </c>
       <c r="S40">
-        <v>0.08766954239019109</v>
+        <v>0.08820846368173256</v>
       </c>
       <c r="T40">
-        <v>0.794249747388821</v>
+        <v>0.8044728851456249</v>
       </c>
       <c r="U40">
         <v>0.06228425489709894</v>
@@ -4605,7 +4605,7 @@
         </is>
       </c>
       <c r="Y40">
-        <v>4.167681247146332</v>
+        <v>4.060817625424631</v>
       </c>
       <c r="Z40">
         <v>0</v>
@@ -4613,22 +4613,22 @@
     </row>
     <row r="41">
       <c r="A41">
-        <v>0.39</v>
+        <v>0.4</v>
       </c>
       <c r="B41">
-        <v>0.07066016110442369</v>
+        <v>0.07054433582883814</v>
       </c>
       <c r="C41">
-        <v>34824.68231337438</v>
+        <v>34374.89456603485</v>
       </c>
       <c r="D41">
-        <v>50287.94931337438</v>
+        <v>50376.91456603485</v>
       </c>
       <c r="E41">
-        <v>13217.767</v>
+        <v>13756.52</v>
       </c>
       <c r="F41">
-        <v>21011.367</v>
+        <v>21550.12</v>
       </c>
       <c r="G41">
         <v>5548.1</v>
@@ -4649,28 +4649,28 @@
         <v>5314.3</v>
       </c>
       <c r="M41">
-        <v>1308.677337964493</v>
+        <v>1342.23316714307</v>
       </c>
       <c r="N41">
-        <v>4005.622662035507</v>
+        <v>3972.06683285693</v>
       </c>
       <c r="O41">
-        <v>1226.521659115273</v>
+        <v>1216.246864220792</v>
       </c>
       <c r="P41">
-        <v>2779.101002920235</v>
+        <v>2755.819968636138</v>
       </c>
       <c r="Q41">
-        <v>3208.801002920235</v>
+        <v>3185.519968636138</v>
       </c>
       <c r="R41">
-        <v>0.639344262295082</v>
+        <v>0.6666666666666667</v>
       </c>
       <c r="S41">
-        <v>0.08820846368173256</v>
+        <v>0.08876534901632541</v>
       </c>
       <c r="T41">
-        <v>0.8044728851456249</v>
+        <v>0.8150367941609888</v>
       </c>
       <c r="U41">
         <v>0.06228425489709894</v>
@@ -4687,7 +4687,7 @@
         </is>
       </c>
       <c r="Y41">
-        <v>4.060817625424631</v>
+        <v>3.959297184789015</v>
       </c>
       <c r="Z41">
         <v>0</v>
@@ -4695,22 +4695,22 @@
     </row>
     <row r="42">
       <c r="A42">
-        <v>0.4</v>
+        <v>0.41</v>
       </c>
       <c r="B42">
-        <v>0.07054433582883814</v>
+        <v>0.0704285105532526</v>
       </c>
       <c r="C42">
-        <v>34374.89456603485</v>
+        <v>33925.422156399</v>
       </c>
       <c r="D42">
-        <v>50376.91456603485</v>
+        <v>50466.195156399</v>
       </c>
       <c r="E42">
-        <v>13756.52</v>
+        <v>14295.273</v>
       </c>
       <c r="F42">
-        <v>21550.12</v>
+        <v>22088.873</v>
       </c>
       <c r="G42">
         <v>5548.1</v>
@@ -4731,28 +4731,28 @@
         <v>5314.3</v>
       </c>
       <c r="M42">
-        <v>1342.23316714307</v>
+        <v>1375.788996321646</v>
       </c>
       <c r="N42">
-        <v>3972.06683285693</v>
+        <v>3938.511003678354</v>
       </c>
       <c r="O42">
-        <v>1216.246864220792</v>
+        <v>1205.972069326312</v>
       </c>
       <c r="P42">
-        <v>2755.819968636138</v>
+        <v>2732.538934352041</v>
       </c>
       <c r="Q42">
-        <v>3185.519968636138</v>
+        <v>3162.238934352041</v>
       </c>
       <c r="R42">
-        <v>0.6666666666666667</v>
+        <v>0.6949152542372882</v>
       </c>
       <c r="S42">
-        <v>0.08876534901632541</v>
+        <v>0.08934111181988749</v>
       </c>
       <c r="T42">
-        <v>0.8150367941609888</v>
+        <v>0.8259588017870431</v>
       </c>
       <c r="U42">
         <v>0.06228425489709894</v>
@@ -4769,7 +4769,7 @@
         </is>
       </c>
       <c r="Y42">
-        <v>3.959297184789015</v>
+        <v>3.862728960769771</v>
       </c>
       <c r="Z42">
         <v>0</v>
@@ -4777,22 +4777,22 @@
     </row>
     <row r="43">
       <c r="A43">
-        <v>0.41</v>
+        <v>0.42</v>
       </c>
       <c r="B43">
-        <v>0.0704285105532526</v>
+        <v>0.07031268527766704</v>
       </c>
       <c r="C43">
-        <v>33925.422156399</v>
+        <v>33476.26676401714</v>
       </c>
       <c r="D43">
-        <v>50466.195156399</v>
+        <v>50555.79276401715</v>
       </c>
       <c r="E43">
-        <v>14295.273</v>
+        <v>14834.026</v>
       </c>
       <c r="F43">
-        <v>22088.873</v>
+        <v>22627.626</v>
       </c>
       <c r="G43">
         <v>5548.1</v>
@@ -4813,28 +4813,28 @@
         <v>5314.3</v>
       </c>
       <c r="M43">
-        <v>1375.788996321646</v>
+        <v>1409.344825500223</v>
       </c>
       <c r="N43">
-        <v>3938.511003678354</v>
+        <v>3904.955174499777</v>
       </c>
       <c r="O43">
-        <v>1205.972069326312</v>
+        <v>1195.697274431832</v>
       </c>
       <c r="P43">
-        <v>2732.538934352041</v>
+        <v>2709.257900067945</v>
       </c>
       <c r="Q43">
-        <v>3162.238934352041</v>
+        <v>3138.957900067945</v>
       </c>
       <c r="R43">
-        <v>0.6949152542372882</v>
+        <v>0.7241379310344829</v>
       </c>
       <c r="S43">
-        <v>0.08934111181988749</v>
+        <v>0.08993672851322758</v>
       </c>
       <c r="T43">
-        <v>0.8259588017870431</v>
+        <v>0.8372574303657199</v>
       </c>
       <c r="U43">
         <v>0.06228425489709894</v>
@@ -4851,7 +4851,7 @@
         </is>
       </c>
       <c r="Y43">
-        <v>3.862728960769771</v>
+        <v>3.770759223608586</v>
       </c>
       <c r="Z43">
         <v>0</v>
@@ -4859,22 +4859,22 @@
     </row>
     <row r="44">
       <c r="A44">
-        <v>0.42</v>
+        <v>0.43</v>
       </c>
       <c r="B44">
-        <v>0.07031268527766704</v>
+        <v>0.0701968600020815</v>
       </c>
       <c r="C44">
-        <v>33476.26676401715</v>
+        <v>33027.43008038821</v>
       </c>
       <c r="D44">
-        <v>50555.79276401715</v>
+        <v>50645.70908038821</v>
       </c>
       <c r="E44">
-        <v>14834.026</v>
+        <v>15372.779</v>
       </c>
       <c r="F44">
-        <v>22627.626</v>
+        <v>23166.379</v>
       </c>
       <c r="G44">
         <v>5548.1</v>
@@ -4895,28 +4895,28 @@
         <v>5314.3</v>
       </c>
       <c r="M44">
-        <v>1409.344825500223</v>
+        <v>1442.9006546788</v>
       </c>
       <c r="N44">
-        <v>3904.955174499777</v>
+        <v>3871.399345321201</v>
       </c>
       <c r="O44">
-        <v>1195.697274431832</v>
+        <v>1185.422479537352</v>
       </c>
       <c r="P44">
-        <v>2709.257900067945</v>
+        <v>2685.976865783849</v>
       </c>
       <c r="Q44">
-        <v>3138.957900067945</v>
+        <v>3115.676865783848</v>
       </c>
       <c r="R44">
-        <v>0.7241379310344827</v>
+        <v>0.7543859649122806</v>
       </c>
       <c r="S44">
-        <v>0.08993672851322758</v>
+        <v>0.09055324403791294</v>
       </c>
       <c r="T44">
-        <v>0.8372574303657199</v>
+        <v>0.8489525020524205</v>
       </c>
       <c r="U44">
         <v>0.06228425489709894</v>
@@ -4933,7 +4933,7 @@
         </is>
       </c>
       <c r="Y44">
-        <v>3.770759223608587</v>
+        <v>3.683067148640945</v>
       </c>
       <c r="Z44">
         <v>0</v>
@@ -4941,22 +4941,22 @@
     </row>
     <row r="45">
       <c r="A45">
-        <v>0.43</v>
+        <v>0.44</v>
       </c>
       <c r="B45">
-        <v>0.0701968600020815</v>
+        <v>0.07008103472649595</v>
       </c>
       <c r="C45">
-        <v>33027.43008038821</v>
+        <v>32578.91380906632</v>
       </c>
       <c r="D45">
-        <v>50645.70908038821</v>
+        <v>50735.94580906632</v>
       </c>
       <c r="E45">
-        <v>15372.779</v>
+        <v>15911.532</v>
       </c>
       <c r="F45">
-        <v>23166.379</v>
+        <v>23705.132</v>
       </c>
       <c r="G45">
         <v>5548.1</v>
@@ -4977,28 +4977,28 @@
         <v>5314.3</v>
       </c>
       <c r="M45">
-        <v>1442.9006546788</v>
+        <v>1476.456483857377</v>
       </c>
       <c r="N45">
-        <v>3871.399345321201</v>
+        <v>3837.843516142623</v>
       </c>
       <c r="O45">
-        <v>1185.422479537352</v>
+        <v>1175.147684642871</v>
       </c>
       <c r="P45">
-        <v>2685.976865783849</v>
+        <v>2662.695831499752</v>
       </c>
       <c r="Q45">
-        <v>3115.676865783848</v>
+        <v>3092.395831499752</v>
       </c>
       <c r="R45">
-        <v>0.7543859649122806</v>
+        <v>0.7857142857142857</v>
       </c>
       <c r="S45">
-        <v>0.09055324403791294</v>
+        <v>0.09119177797419421</v>
       </c>
       <c r="T45">
-        <v>0.8489525020524205</v>
+        <v>0.861065254870789</v>
       </c>
       <c r="U45">
         <v>0.06228425489709894</v>
@@ -5015,7 +5015,7 @@
         </is>
       </c>
       <c r="Y45">
-        <v>3.683067148640945</v>
+        <v>3.599361077080923</v>
       </c>
       <c r="Z45">
         <v>0</v>
@@ -5023,22 +5023,22 @@
     </row>
     <row r="46">
       <c r="A46">
-        <v>0.44</v>
+        <v>0.45</v>
       </c>
       <c r="B46">
-        <v>0.07008103472649595</v>
+        <v>0.06996520945091041</v>
       </c>
       <c r="C46">
-        <v>32578.91380906632</v>
+        <v>32130.71966576831</v>
       </c>
       <c r="D46">
-        <v>50735.94580906632</v>
+        <v>50826.50466576831</v>
       </c>
       <c r="E46">
-        <v>15911.532</v>
+        <v>16450.285</v>
       </c>
       <c r="F46">
-        <v>23705.132</v>
+        <v>24243.885</v>
       </c>
       <c r="G46">
         <v>5548.1</v>
@@ -5059,28 +5059,28 @@
         <v>5314.3</v>
       </c>
       <c r="M46">
-        <v>1476.456483857377</v>
+        <v>1510.012313035953</v>
       </c>
       <c r="N46">
-        <v>3837.843516142623</v>
+        <v>3804.287686964047</v>
       </c>
       <c r="O46">
-        <v>1175.147684642871</v>
+        <v>1164.872889748391</v>
       </c>
       <c r="P46">
-        <v>2662.695831499752</v>
+        <v>2639.414797215656</v>
       </c>
       <c r="Q46">
-        <v>3092.395831499752</v>
+        <v>3069.114797215655</v>
       </c>
       <c r="R46">
-        <v>0.7857142857142857</v>
+        <v>0.8181818181818181</v>
       </c>
       <c r="S46">
-        <v>0.09119177797419421</v>
+        <v>0.09185353132634025</v>
       </c>
       <c r="T46">
-        <v>0.861065254870789</v>
+        <v>0.8736184714280072</v>
       </c>
       <c r="U46">
         <v>0.06228425489709894</v>
@@ -5097,7 +5097,7 @@
         </is>
       </c>
       <c r="Y46">
-        <v>3.599361077080923</v>
+        <v>3.519375275368014</v>
       </c>
       <c r="Z46">
         <v>0</v>
@@ -5105,22 +5105,22 @@
     </row>
     <row r="47">
       <c r="A47">
-        <v>0.45</v>
+        <v>0.46</v>
       </c>
       <c r="B47">
-        <v>0.06996520945091041</v>
+        <v>0.06984938417532485</v>
       </c>
       <c r="C47">
-        <v>32130.71966576831</v>
+        <v>31682.84937848249</v>
       </c>
       <c r="D47">
-        <v>50826.50466576831</v>
+        <v>50917.38737848249</v>
       </c>
       <c r="E47">
-        <v>16450.285</v>
+        <v>16989.038</v>
       </c>
       <c r="F47">
-        <v>24243.885</v>
+        <v>24782.638</v>
       </c>
       <c r="G47">
         <v>5548.1</v>
@@ -5141,28 +5141,28 @@
         <v>5314.3</v>
       </c>
       <c r="M47">
-        <v>1510.012313035953</v>
+        <v>1543.56814221453</v>
       </c>
       <c r="N47">
-        <v>3804.287686964047</v>
+        <v>3770.73185778547</v>
       </c>
       <c r="O47">
-        <v>1164.872889748391</v>
+        <v>1154.598094853911</v>
       </c>
       <c r="P47">
-        <v>2639.414797215656</v>
+        <v>2616.133762931559</v>
       </c>
       <c r="Q47">
-        <v>3069.114797215655</v>
+        <v>3045.833762931559</v>
       </c>
       <c r="R47">
-        <v>0.8181818181818181</v>
+        <v>0.8518518518518519</v>
       </c>
       <c r="S47">
-        <v>0.09185353132634025</v>
+        <v>0.09253979406189911</v>
       </c>
       <c r="T47">
-        <v>0.8736184714280072</v>
+        <v>0.886636621931789</v>
       </c>
       <c r="U47">
         <v>0.06228425489709894</v>
@@ -5179,7 +5179,7 @@
         </is>
       </c>
       <c r="Y47">
-        <v>3.519375275368014</v>
+        <v>3.442867117207839</v>
       </c>
       <c r="Z47">
         <v>0</v>
@@ -5187,22 +5187,22 @@
     </row>
     <row r="48">
       <c r="A48">
-        <v>0.46</v>
+        <v>0.47</v>
       </c>
       <c r="B48">
-        <v>0.06984938417532485</v>
+        <v>0.06973355889973931</v>
       </c>
       <c r="C48">
-        <v>31682.84937848249</v>
+        <v>31235.30468757856</v>
       </c>
       <c r="D48">
-        <v>50917.38737848249</v>
+        <v>51008.59568757856</v>
       </c>
       <c r="E48">
-        <v>16989.038</v>
+        <v>17527.791</v>
       </c>
       <c r="F48">
-        <v>24782.638</v>
+        <v>25321.391</v>
       </c>
       <c r="G48">
         <v>5548.1</v>
@@ -5223,28 +5223,28 @@
         <v>5314.3</v>
       </c>
       <c r="M48">
-        <v>1543.56814221453</v>
+        <v>1577.123971393107</v>
       </c>
       <c r="N48">
-        <v>3770.73185778547</v>
+        <v>3737.176028606893</v>
       </c>
       <c r="O48">
-        <v>1154.598094853911</v>
+        <v>1144.323299959431</v>
       </c>
       <c r="P48">
-        <v>2616.133762931559</v>
+        <v>2592.852728647462</v>
       </c>
       <c r="Q48">
-        <v>3045.833762931559</v>
+        <v>3022.552728647462</v>
       </c>
       <c r="R48">
-        <v>0.8518518518518519</v>
+        <v>0.8867924528301887</v>
       </c>
       <c r="S48">
-        <v>0.09253979406189911</v>
+        <v>0.09325195350446019</v>
       </c>
       <c r="T48">
-        <v>0.886636621931789</v>
+        <v>0.9001460233979779</v>
       </c>
       <c r="U48">
         <v>0.06228425489709894</v>
@@ -5261,7 +5261,7 @@
         </is>
       </c>
       <c r="Y48">
-        <v>3.442867117207839</v>
+        <v>3.369614625352353</v>
       </c>
       <c r="Z48">
         <v>0</v>
@@ -5269,22 +5269,22 @@
     </row>
     <row r="49">
       <c r="A49">
-        <v>0.47</v>
+        <v>0.48</v>
       </c>
       <c r="B49">
-        <v>0.06973355889973931</v>
+        <v>0.06961773362415376</v>
       </c>
       <c r="C49">
-        <v>31235.30468757856</v>
+        <v>30788.08734591868</v>
       </c>
       <c r="D49">
-        <v>51008.59568757856</v>
+        <v>51100.13134591868</v>
       </c>
       <c r="E49">
-        <v>17527.791</v>
+        <v>18066.544</v>
       </c>
       <c r="F49">
-        <v>25321.391</v>
+        <v>25860.144</v>
       </c>
       <c r="G49">
         <v>5548.1</v>
@@ -5305,28 +5305,28 @@
         <v>5314.3</v>
       </c>
       <c r="M49">
-        <v>1577.123971393107</v>
+        <v>1610.679800571684</v>
       </c>
       <c r="N49">
-        <v>3737.176028606893</v>
+        <v>3703.620199428316</v>
       </c>
       <c r="O49">
-        <v>1144.323299959431</v>
+        <v>1134.048505064951</v>
       </c>
       <c r="P49">
-        <v>2592.852728647462</v>
+        <v>2569.571694363366</v>
       </c>
       <c r="Q49">
-        <v>3022.552728647462</v>
+        <v>2999.271694363366</v>
       </c>
       <c r="R49">
-        <v>0.8867924528301887</v>
+        <v>0.9230769230769231</v>
       </c>
       <c r="S49">
-        <v>0.09325195350446019</v>
+        <v>0.09399150369481207</v>
       </c>
       <c r="T49">
-        <v>0.9001460233979779</v>
+        <v>0.9141750172282507</v>
       </c>
       <c r="U49">
         <v>0.06228425489709894</v>
@@ -5343,7 +5343,7 @@
         </is>
       </c>
       <c r="Y49">
-        <v>3.369614625352353</v>
+        <v>3.299414320657513</v>
       </c>
       <c r="Z49">
         <v>0</v>
@@ -5351,22 +5351,22 @@
     </row>
     <row r="50">
       <c r="A50">
-        <v>0.48</v>
+        <v>0.49</v>
       </c>
       <c r="B50">
-        <v>0.06961773362415376</v>
+        <v>0.0695019083485682</v>
       </c>
       <c r="C50">
-        <v>30788.08734591868</v>
+        <v>30341.19911896979</v>
       </c>
       <c r="D50">
-        <v>51100.13134591868</v>
+        <v>51191.99611896979</v>
       </c>
       <c r="E50">
-        <v>18066.54399999999</v>
+        <v>18605.297</v>
       </c>
       <c r="F50">
-        <v>25860.144</v>
+        <v>26398.897</v>
       </c>
       <c r="G50">
         <v>5548.1</v>
@@ -5387,28 +5387,28 @@
         <v>5314.3</v>
       </c>
       <c r="M50">
-        <v>1610.679800571683</v>
+        <v>1644.23562975026</v>
       </c>
       <c r="N50">
-        <v>3703.620199428316</v>
+        <v>3670.06437024974</v>
       </c>
       <c r="O50">
-        <v>1134.048505064951</v>
+        <v>1123.77371017047</v>
       </c>
       <c r="P50">
-        <v>2569.571694363366</v>
+        <v>2546.290660079269</v>
       </c>
       <c r="Q50">
-        <v>2999.271694363366</v>
+        <v>2975.990660079269</v>
       </c>
       <c r="R50">
-        <v>0.923076923076923</v>
+        <v>0.9607843137254901</v>
       </c>
       <c r="S50">
-        <v>0.09399150369481207</v>
+        <v>0.09476005585341304</v>
       </c>
       <c r="T50">
-        <v>0.9141750172282507</v>
+        <v>0.9287541676793187</v>
       </c>
       <c r="U50">
         <v>0.06228425489709894</v>
@@ -5425,7 +5425,7 @@
         </is>
       </c>
       <c r="Y50">
-        <v>3.299414320657513</v>
+        <v>3.232079334521646</v>
       </c>
       <c r="Z50">
         <v>0</v>
@@ -5433,22 +5433,22 @@
     </row>
     <row r="51">
       <c r="A51">
-        <v>0.49</v>
+        <v>0.5</v>
       </c>
       <c r="B51">
-        <v>0.0695019083485682</v>
+        <v>0.06938608307298266</v>
       </c>
       <c r="C51">
-        <v>30341.19911896979</v>
+        <v>29894.64178491706</v>
       </c>
       <c r="D51">
-        <v>51191.99611896979</v>
+        <v>51284.19178491706</v>
       </c>
       <c r="E51">
-        <v>18605.297</v>
+        <v>19144.05</v>
       </c>
       <c r="F51">
-        <v>26398.897</v>
+        <v>26937.65</v>
       </c>
       <c r="G51">
         <v>5548.1</v>
@@ -5469,28 +5469,28 @@
         <v>5314.3</v>
       </c>
       <c r="M51">
-        <v>1644.23562975026</v>
+        <v>1677.791458928837</v>
       </c>
       <c r="N51">
-        <v>3670.06437024974</v>
+        <v>3636.508541071163</v>
       </c>
       <c r="O51">
-        <v>1123.77371017047</v>
+        <v>1113.49891527599</v>
       </c>
       <c r="P51">
-        <v>2546.290660079269</v>
+        <v>2523.009625795173</v>
       </c>
       <c r="Q51">
-        <v>2975.990660079269</v>
+        <v>2952.709625795173</v>
       </c>
       <c r="R51">
-        <v>0.9607843137254901</v>
+        <v>1</v>
       </c>
       <c r="S51">
-        <v>0.09476005585341304</v>
+        <v>0.09555935009835807</v>
       </c>
       <c r="T51">
-        <v>0.9287541676793187</v>
+        <v>0.9439164841484293</v>
       </c>
       <c r="U51">
         <v>0.06228425489709894</v>
@@ -5507,7 +5507,7 @@
         </is>
       </c>
       <c r="Y51">
-        <v>3.232079334521646</v>
+        <v>3.167437747831213</v>
       </c>
       <c r="Z51">
         <v>0</v>
@@ -5515,22 +5515,22 @@
     </row>
     <row r="52">
       <c r="A52">
-        <v>0.5</v>
+        <v>0.51</v>
       </c>
       <c r="B52">
-        <v>0.06938608307298266</v>
+        <v>0.06927025779739711</v>
       </c>
       <c r="C52">
-        <v>29894.64178491706</v>
+        <v>29448.41713477872</v>
       </c>
       <c r="D52">
-        <v>51284.19178491706</v>
+        <v>51376.72013477872</v>
       </c>
       <c r="E52">
-        <v>19144.05</v>
+        <v>19682.803</v>
       </c>
       <c r="F52">
-        <v>26937.65</v>
+        <v>27476.403</v>
       </c>
       <c r="G52">
         <v>5548.1</v>
@@ -5551,28 +5551,28 @@
         <v>5314.3</v>
       </c>
       <c r="M52">
-        <v>1677.791458928837</v>
+        <v>1711.347288107414</v>
       </c>
       <c r="N52">
-        <v>3636.508541071163</v>
+        <v>3602.952711892586</v>
       </c>
       <c r="O52">
-        <v>1113.49891527599</v>
+        <v>1103.22412038151</v>
       </c>
       <c r="P52">
-        <v>2523.009625795173</v>
+        <v>2499.728591511076</v>
       </c>
       <c r="Q52">
-        <v>2952.709625795173</v>
+        <v>2929.428591511076</v>
       </c>
       <c r="R52">
-        <v>1</v>
+        <v>1.040816326530612</v>
       </c>
       <c r="S52">
-        <v>0.09555935009835807</v>
+        <v>0.0963912685981988</v>
       </c>
       <c r="T52">
-        <v>0.9439164841484293</v>
+        <v>0.9596976706775037</v>
       </c>
       <c r="U52">
         <v>0.06228425489709894</v>
@@ -5589,7 +5589,7 @@
         </is>
       </c>
       <c r="Y52">
-        <v>3.167437747831213</v>
+        <v>3.105331125324718</v>
       </c>
       <c r="Z52">
         <v>0</v>
@@ -5597,22 +5597,22 @@
     </row>
     <row r="53">
       <c r="A53">
-        <v>0.51</v>
+        <v>0.52</v>
       </c>
       <c r="B53">
-        <v>0.06927025779739711</v>
+        <v>0.06915443252181155</v>
       </c>
       <c r="C53">
-        <v>29448.41713477872</v>
+        <v>29002.52697252197</v>
       </c>
       <c r="D53">
-        <v>51376.72013477872</v>
+        <v>51469.58297252197</v>
       </c>
       <c r="E53">
-        <v>19682.803</v>
+        <v>20221.556</v>
       </c>
       <c r="F53">
-        <v>27476.403</v>
+        <v>28015.156</v>
       </c>
       <c r="G53">
         <v>5548.1</v>
@@ -5633,28 +5633,28 @@
         <v>5314.3</v>
       </c>
       <c r="M53">
-        <v>1711.347288107414</v>
+        <v>1744.903117285991</v>
       </c>
       <c r="N53">
-        <v>3602.952711892586</v>
+        <v>3569.39688271401</v>
       </c>
       <c r="O53">
-        <v>1103.22412038151</v>
+        <v>1092.94932548703</v>
       </c>
       <c r="P53">
-        <v>2499.728591511076</v>
+        <v>2476.44755722698</v>
       </c>
       <c r="Q53">
-        <v>2929.428591511076</v>
+        <v>2906.14755722698</v>
       </c>
       <c r="R53">
-        <v>1.040816326530612</v>
+        <v>1.083333333333333</v>
       </c>
       <c r="S53">
-        <v>0.0963912685981988</v>
+        <v>0.09725785036886624</v>
       </c>
       <c r="T53">
-        <v>0.9596976706775037</v>
+        <v>0.9761364066452894</v>
       </c>
       <c r="U53">
         <v>0.06228425489709894</v>
@@ -5671,7 +5671,7 @@
         </is>
       </c>
       <c r="Y53">
-        <v>3.105331125324718</v>
+        <v>3.045613219068473</v>
       </c>
       <c r="Z53">
         <v>0</v>
@@ -5679,22 +5679,22 @@
     </row>
     <row r="54">
       <c r="A54">
-        <v>0.52</v>
+        <v>0.53</v>
       </c>
       <c r="B54">
-        <v>0.06915443252181155</v>
+        <v>0.06995789224622601</v>
       </c>
       <c r="C54">
-        <v>29002.52697252197</v>
+        <v>27826.42753468717</v>
       </c>
       <c r="D54">
-        <v>51469.58297252197</v>
+        <v>50832.23653468717</v>
       </c>
       <c r="E54">
-        <v>20221.556</v>
+        <v>20760.309</v>
       </c>
       <c r="F54">
-        <v>28015.156</v>
+        <v>28553.909</v>
       </c>
       <c r="G54">
         <v>5548.1</v>
@@ -5715,45 +5715,45 @@
         <v>5314.3</v>
       </c>
       <c r="M54">
-        <v>1744.903117285991</v>
+        <v>1849.843718964567</v>
       </c>
       <c r="N54">
-        <v>3569.39688271401</v>
+        <v>3464.456281035433</v>
       </c>
       <c r="O54">
-        <v>1092.94932548703</v>
+        <v>1060.81651325305</v>
       </c>
       <c r="P54">
-        <v>2476.44755722698</v>
+        <v>2403.639767782383</v>
       </c>
       <c r="Q54">
-        <v>2906.14755722698</v>
+        <v>2833.339767782383</v>
       </c>
       <c r="R54">
-        <v>1.083333333333333</v>
+        <v>1.127659574468085</v>
       </c>
       <c r="S54">
-        <v>0.09725785036886624</v>
+        <v>0.09816130795956207</v>
       </c>
       <c r="T54">
-        <v>0.9761364066452894</v>
+        <v>0.9932746632925555</v>
       </c>
       <c r="U54">
-        <v>0.06228425489709894</v>
+        <v>0.06478425489709894</v>
       </c>
       <c r="V54">
         <v>0.3062</v>
       </c>
       <c r="W54">
-        <v>0.04321281604760725</v>
+        <v>0.04494731604760724</v>
       </c>
       <c r="X54" t="inlineStr">
         <is>
-          <t>A3/A-</t>
+          <t>Baa2/BBB</t>
         </is>
       </c>
       <c r="Y54">
-        <v>3.045613219068473</v>
+        <v>2.872837281072927</v>
       </c>
       <c r="Z54">
         <v>0</v>
@@ -5761,22 +5761,22 @@
     </row>
     <row r="55">
       <c r="A55">
-        <v>0.53</v>
+        <v>0.54</v>
       </c>
       <c r="B55">
-        <v>0.06995789224622601</v>
+        <v>0.06985941197064047</v>
       </c>
       <c r="C55">
-        <v>27826.42753468717</v>
+        <v>27364.94418408018</v>
       </c>
       <c r="D55">
-        <v>50832.23653468717</v>
+        <v>50909.50618408018</v>
       </c>
       <c r="E55">
-        <v>20760.309</v>
+        <v>21299.062</v>
       </c>
       <c r="F55">
-        <v>28553.909</v>
+        <v>29092.662</v>
       </c>
       <c r="G55">
         <v>5548.1</v>
@@ -5797,28 +5797,28 @@
         <v>5314.3</v>
       </c>
       <c r="M55">
-        <v>1849.843718964567</v>
+        <v>1884.746430643144</v>
       </c>
       <c r="N55">
-        <v>3464.456281035433</v>
+        <v>3429.553569356856</v>
       </c>
       <c r="O55">
-        <v>1060.81651325305</v>
+        <v>1050.129302937069</v>
       </c>
       <c r="P55">
-        <v>2403.639767782383</v>
+        <v>2379.424266419787</v>
       </c>
       <c r="Q55">
-        <v>2833.339767782383</v>
+        <v>2809.124266419787</v>
       </c>
       <c r="R55">
-        <v>1.127659574468085</v>
+        <v>1.173913043478261</v>
       </c>
       <c r="S55">
-        <v>0.09816130795956207</v>
+        <v>0.09910404631507078</v>
       </c>
       <c r="T55">
-        <v>0.9932746632925555</v>
+        <v>1.011158061533181</v>
       </c>
       <c r="U55">
         <v>0.06478425489709894</v>
@@ -5835,7 +5835,7 @@
         </is>
       </c>
       <c r="Y55">
-        <v>2.872837281072927</v>
+        <v>2.819636590682688</v>
       </c>
       <c r="Z55">
         <v>0</v>
@@ -5843,22 +5843,22 @@
     </row>
     <row r="56">
       <c r="A56">
-        <v>0.54</v>
+        <v>0.55</v>
       </c>
       <c r="B56">
-        <v>0.06985941197064047</v>
+        <v>0.06976093169505493</v>
       </c>
       <c r="C56">
-        <v>27364.94418408018</v>
+        <v>26903.69610497797</v>
       </c>
       <c r="D56">
-        <v>50909.50618408018</v>
+        <v>50987.01110497797</v>
       </c>
       <c r="E56">
-        <v>21299.062</v>
+        <v>21837.815</v>
       </c>
       <c r="F56">
-        <v>29092.662</v>
+        <v>29631.415</v>
       </c>
       <c r="G56">
         <v>5548.1</v>
@@ -5879,28 +5879,28 @@
         <v>5314.3</v>
       </c>
       <c r="M56">
-        <v>1884.746430643144</v>
+        <v>1919.649142321721</v>
       </c>
       <c r="N56">
-        <v>3429.553569356856</v>
+        <v>3394.650857678279</v>
       </c>
       <c r="O56">
-        <v>1050.129302937069</v>
+        <v>1039.442092621089</v>
       </c>
       <c r="P56">
-        <v>2379.424266419787</v>
+        <v>2355.20876505719</v>
       </c>
       <c r="Q56">
-        <v>2809.124266419787</v>
+        <v>2784.90876505719</v>
       </c>
       <c r="R56">
-        <v>1.173913043478261</v>
+        <v>1.222222222222223</v>
       </c>
       <c r="S56">
-        <v>0.09910404631507078</v>
+        <v>0.1000886841530465</v>
       </c>
       <c r="T56">
-        <v>1.011158061533181</v>
+        <v>1.02983627747339</v>
       </c>
       <c r="U56">
         <v>0.06478425489709894</v>
@@ -5917,7 +5917,7 @@
         </is>
       </c>
       <c r="Y56">
-        <v>2.819636590682688</v>
+        <v>2.768370470852093</v>
       </c>
       <c r="Z56">
         <v>0</v>
@@ -5925,22 +5925,22 @@
     </row>
     <row r="57">
       <c r="A57">
-        <v>0.55</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="B57">
-        <v>0.06976093169505493</v>
+        <v>0.06966245141946936</v>
       </c>
       <c r="C57">
-        <v>26903.69610497797</v>
+        <v>26442.68437355496</v>
       </c>
       <c r="D57">
-        <v>50987.01110497797</v>
+        <v>51064.75237355496</v>
       </c>
       <c r="E57">
-        <v>21837.815</v>
+        <v>22376.568</v>
       </c>
       <c r="F57">
-        <v>29631.415</v>
+        <v>30170.168</v>
       </c>
       <c r="G57">
         <v>5548.1</v>
@@ -5961,28 +5961,28 @@
         <v>5314.3</v>
       </c>
       <c r="M57">
-        <v>1919.649142321721</v>
+        <v>1954.551854000298</v>
       </c>
       <c r="N57">
-        <v>3394.650857678279</v>
+        <v>3359.748145999703</v>
       </c>
       <c r="O57">
-        <v>1039.442092621089</v>
+        <v>1028.754882305109</v>
       </c>
       <c r="P57">
-        <v>2355.20876505719</v>
+        <v>2330.993263694593</v>
       </c>
       <c r="Q57">
-        <v>2784.90876505719</v>
+        <v>2760.693263694593</v>
       </c>
       <c r="R57">
-        <v>1.222222222222223</v>
+        <v>1.272727272727273</v>
       </c>
       <c r="S57">
-        <v>0.1000886841530465</v>
+        <v>0.1011180782563848</v>
       </c>
       <c r="T57">
-        <v>1.02983627747339</v>
+        <v>1.049363503229062</v>
       </c>
       <c r="U57">
         <v>0.06478425489709894</v>
@@ -5999,7 +5999,7 @@
         </is>
       </c>
       <c r="Y57">
-        <v>2.768370470852093</v>
+        <v>2.718935283872592</v>
       </c>
       <c r="Z57">
         <v>0</v>
@@ -6007,22 +6007,22 @@
     </row>
     <row r="58">
       <c r="A58">
-        <v>0.5600000000000001</v>
+        <v>0.5700000000000001</v>
       </c>
       <c r="B58">
-        <v>0.06966245141946936</v>
+        <v>0.06956397114388382</v>
       </c>
       <c r="C58">
-        <v>26442.68437355496</v>
+        <v>25981.91007255903</v>
       </c>
       <c r="D58">
-        <v>51064.75237355496</v>
+        <v>51142.73107255904</v>
       </c>
       <c r="E58">
-        <v>22376.568</v>
+        <v>22915.321</v>
       </c>
       <c r="F58">
-        <v>30170.168</v>
+        <v>30708.921</v>
       </c>
       <c r="G58">
         <v>5548.1</v>
@@ -6043,28 +6043,28 @@
         <v>5314.3</v>
       </c>
       <c r="M58">
-        <v>1954.551854000298</v>
+        <v>1989.454565678875</v>
       </c>
       <c r="N58">
-        <v>3359.748145999703</v>
+        <v>3324.845434321126</v>
       </c>
       <c r="O58">
-        <v>1028.754882305109</v>
+        <v>1018.067671989129</v>
       </c>
       <c r="P58">
-        <v>2330.993263694593</v>
+        <v>2306.777762331997</v>
       </c>
       <c r="Q58">
-        <v>2760.693263694593</v>
+        <v>2736.477762331997</v>
       </c>
       <c r="R58">
-        <v>1.272727272727273</v>
+        <v>1.325581395348838</v>
       </c>
       <c r="S58">
-        <v>0.1011180782563848</v>
+        <v>0.1021953511552272</v>
       </c>
       <c r="T58">
-        <v>1.049363503229062</v>
+        <v>1.069798972043139</v>
       </c>
       <c r="U58">
         <v>0.06478425489709894</v>
@@ -6081,7 +6081,7 @@
         </is>
       </c>
       <c r="Y58">
-        <v>2.718935283872592</v>
+        <v>2.671234664857283</v>
       </c>
       <c r="Z58">
         <v>0</v>
@@ -6089,22 +6089,22 @@
     </row>
     <row r="59">
       <c r="A59">
-        <v>0.5700000000000001</v>
+        <v>0.5800000000000001</v>
       </c>
       <c r="B59">
-        <v>0.06956397114388382</v>
+        <v>0.06946549086829827</v>
       </c>
       <c r="C59">
-        <v>25981.91007255903</v>
+        <v>25521.37429136187</v>
       </c>
       <c r="D59">
-        <v>51142.73107255904</v>
+        <v>51220.94829136188</v>
       </c>
       <c r="E59">
-        <v>22915.321</v>
+        <v>23454.074</v>
       </c>
       <c r="F59">
-        <v>30708.921</v>
+        <v>31247.674</v>
       </c>
       <c r="G59">
         <v>5548.1</v>
@@ -6125,28 +6125,28 @@
         <v>5314.3</v>
       </c>
       <c r="M59">
-        <v>1989.454565678875</v>
+        <v>2024.357277357451</v>
       </c>
       <c r="N59">
-        <v>3324.845434321126</v>
+        <v>3289.942722642549</v>
       </c>
       <c r="O59">
-        <v>1018.067671989129</v>
+        <v>1007.380461673148</v>
       </c>
       <c r="P59">
-        <v>2306.777762331997</v>
+        <v>2282.5622609694</v>
       </c>
       <c r="Q59">
-        <v>2736.477762331997</v>
+        <v>2712.2622609694</v>
       </c>
       <c r="R59">
-        <v>1.325581395348838</v>
+        <v>1.380952380952381</v>
       </c>
       <c r="S59">
-        <v>0.1021953511552272</v>
+        <v>0.1033239227635383</v>
       </c>
       <c r="T59">
-        <v>1.069798972043139</v>
+        <v>1.09120755841979</v>
       </c>
       <c r="U59">
         <v>0.06478425489709894</v>
@@ -6163,7 +6163,7 @@
         </is>
       </c>
       <c r="Y59">
-        <v>2.671234664857283</v>
+        <v>2.625178894773537</v>
       </c>
       <c r="Z59">
         <v>0</v>
@@ -6171,22 +6171,22 @@
     </row>
     <row r="60">
       <c r="A60">
-        <v>0.58</v>
+        <v>0.59</v>
       </c>
       <c r="B60">
-        <v>0.06946549086829829</v>
+        <v>0.06936701059271272</v>
       </c>
       <c r="C60">
-        <v>25521.37429136187</v>
+        <v>25061.07812600968</v>
       </c>
       <c r="D60">
-        <v>51220.94829136187</v>
+        <v>51299.40512600967</v>
       </c>
       <c r="E60">
-        <v>23454.07399999999</v>
+        <v>23992.827</v>
       </c>
       <c r="F60">
-        <v>31247.674</v>
+        <v>31786.427</v>
       </c>
       <c r="G60">
         <v>5548.1</v>
@@ -6207,28 +6207,28 @@
         <v>5314.3</v>
       </c>
       <c r="M60">
-        <v>2024.357277357451</v>
+        <v>2059.259989036027</v>
       </c>
       <c r="N60">
-        <v>3289.94272264255</v>
+        <v>3255.040010963973</v>
       </c>
       <c r="O60">
-        <v>1007.380461673149</v>
+        <v>996.6932513571685</v>
       </c>
       <c r="P60">
-        <v>2282.562260969401</v>
+        <v>2258.346759606804</v>
       </c>
       <c r="Q60">
-        <v>2712.262260969401</v>
+        <v>2688.046759606804</v>
       </c>
       <c r="R60">
-        <v>1.380952380952381</v>
+        <v>1.439024390243902</v>
       </c>
       <c r="S60">
-        <v>0.1033239227635383</v>
+        <v>0.1045075466454255</v>
       </c>
       <c r="T60">
-        <v>1.09120755841979</v>
+        <v>1.113660466083107</v>
       </c>
       <c r="U60">
         <v>0.06478425489709894</v>
@@ -6245,7 +6245,7 @@
         </is>
       </c>
       <c r="Y60">
-        <v>2.625178894773537</v>
+        <v>2.580684337235003</v>
       </c>
       <c r="Z60">
         <v>0</v>
@@ -6253,22 +6253,22 @@
     </row>
     <row r="61">
       <c r="A61">
-        <v>0.59</v>
+        <v>0.6</v>
       </c>
       <c r="B61">
-        <v>0.06936701059271272</v>
+        <v>0.06926853031712718</v>
       </c>
       <c r="C61">
-        <v>25061.07812600968</v>
+        <v>24601.02267927432</v>
       </c>
       <c r="D61">
-        <v>51299.40512600967</v>
+        <v>51378.10267927432</v>
       </c>
       <c r="E61">
-        <v>23992.827</v>
+        <v>24531.57999999999</v>
       </c>
       <c r="F61">
-        <v>31786.427</v>
+        <v>32325.18</v>
       </c>
       <c r="G61">
         <v>5548.1</v>
@@ -6289,28 +6289,28 @@
         <v>5314.3</v>
       </c>
       <c r="M61">
-        <v>2059.259989036027</v>
+        <v>2094.162700714604</v>
       </c>
       <c r="N61">
-        <v>3255.040010963973</v>
+        <v>3220.137299285396</v>
       </c>
       <c r="O61">
-        <v>996.6932513571685</v>
+        <v>986.0060410411883</v>
       </c>
       <c r="P61">
-        <v>2258.346759606804</v>
+        <v>2234.131258244207</v>
       </c>
       <c r="Q61">
-        <v>2688.046759606804</v>
+        <v>2663.831258244207</v>
       </c>
       <c r="R61">
-        <v>1.439024390243902</v>
+        <v>1.5</v>
       </c>
       <c r="S61">
-        <v>0.1045075466454255</v>
+        <v>0.1057503517214071</v>
       </c>
       <c r="T61">
-        <v>1.113660466083107</v>
+        <v>1.13723601912959</v>
       </c>
       <c r="U61">
         <v>0.06478425489709894</v>
@@ -6327,7 +6327,7 @@
         </is>
       </c>
       <c r="Y61">
-        <v>2.580684337235003</v>
+        <v>2.53767293161442</v>
       </c>
       <c r="Z61">
         <v>0</v>
@@ -6335,22 +6335,22 @@
     </row>
     <row r="62">
       <c r="A62">
-        <v>0.6</v>
+        <v>0.61</v>
       </c>
       <c r="B62">
-        <v>0.06926853031712718</v>
+        <v>0.07065131304154162</v>
       </c>
       <c r="C62">
-        <v>24601.02267927432</v>
+        <v>22978.9014130053</v>
       </c>
       <c r="D62">
-        <v>51378.10267927432</v>
+        <v>50294.7344130053</v>
       </c>
       <c r="E62">
-        <v>24531.57999999999</v>
+        <v>25070.333</v>
       </c>
       <c r="F62">
-        <v>32325.18</v>
+        <v>32863.933</v>
       </c>
       <c r="G62">
         <v>5548.1</v>
@@ -6371,45 +6371,45 @@
         <v>5314.3</v>
       </c>
       <c r="M62">
-        <v>2094.162700714604</v>
+        <v>2244.089177893181</v>
       </c>
       <c r="N62">
-        <v>3220.137299285396</v>
+        <v>3070.210822106819</v>
       </c>
       <c r="O62">
-        <v>986.0060410411883</v>
+        <v>940.0985537291079</v>
       </c>
       <c r="P62">
-        <v>2234.131258244207</v>
+        <v>2130.112268377711</v>
       </c>
       <c r="Q62">
-        <v>2663.831258244207</v>
+        <v>2559.812268377711</v>
       </c>
       <c r="R62">
-        <v>1.5</v>
+        <v>1.564102564102564</v>
       </c>
       <c r="S62">
-        <v>0.1057503517214071</v>
+        <v>0.1070568903910288</v>
       </c>
       <c r="T62">
-        <v>1.13723601912959</v>
+        <v>1.162020574896406</v>
       </c>
       <c r="U62">
-        <v>0.06478425489709894</v>
+        <v>0.06828425489709894</v>
       </c>
       <c r="V62">
         <v>0.3062</v>
       </c>
       <c r="W62">
-        <v>0.04494731604760724</v>
+        <v>0.04737561604760724</v>
       </c>
       <c r="X62" t="inlineStr">
         <is>
-          <t>Baa2/BBB</t>
+          <t>Ba1/BB+</t>
         </is>
       </c>
       <c r="Y62">
-        <v>2.53767293161442</v>
+        <v>2.368132270478317</v>
       </c>
       <c r="Z62">
         <v>0</v>
@@ -6417,22 +6417,22 @@
     </row>
     <row r="63">
       <c r="A63">
-        <v>0.61</v>
+        <v>0.62</v>
       </c>
       <c r="B63">
-        <v>0.07065131304154162</v>
+        <v>0.07057711576595607</v>
       </c>
       <c r="C63">
-        <v>22978.9014130053</v>
+        <v>22497.11841540599</v>
       </c>
       <c r="D63">
-        <v>50294.7344130053</v>
+        <v>50351.70441540598</v>
       </c>
       <c r="E63">
-        <v>25070.333</v>
+        <v>25609.086</v>
       </c>
       <c r="F63">
-        <v>32863.933</v>
+        <v>33402.68599999999</v>
       </c>
       <c r="G63">
         <v>5548.1</v>
@@ -6453,28 +6453,28 @@
         <v>5314.3</v>
       </c>
       <c r="M63">
-        <v>2244.089177893181</v>
+        <v>2280.877525071758</v>
       </c>
       <c r="N63">
-        <v>3070.210822106819</v>
+        <v>3033.422474928243</v>
       </c>
       <c r="O63">
-        <v>940.0985537291079</v>
+        <v>928.8339618230279</v>
       </c>
       <c r="P63">
-        <v>2130.112268377711</v>
+        <v>2104.588513105215</v>
       </c>
       <c r="Q63">
-        <v>2559.812268377711</v>
+        <v>2534.288513105214</v>
       </c>
       <c r="R63">
-        <v>1.564102564102564</v>
+        <v>1.631578947368421</v>
       </c>
       <c r="S63">
-        <v>0.1070568903910288</v>
+        <v>0.1084321942537884</v>
       </c>
       <c r="T63">
-        <v>1.162020574896406</v>
+        <v>1.188109580966738</v>
       </c>
       <c r="U63">
         <v>0.06828425489709894</v>
@@ -6491,7 +6491,7 @@
         </is>
       </c>
       <c r="Y63">
-        <v>2.368132270478317</v>
+        <v>2.329936588696409</v>
       </c>
       <c r="Z63">
         <v>0</v>
@@ -6499,22 +6499,22 @@
     </row>
     <row r="64">
       <c r="A64">
-        <v>0.62</v>
+        <v>0.63</v>
       </c>
       <c r="B64">
-        <v>0.07057711576595607</v>
+        <v>0.07050291849037053</v>
       </c>
       <c r="C64">
-        <v>22497.11841540599</v>
+        <v>22015.46462662842</v>
       </c>
       <c r="D64">
-        <v>50351.70441540598</v>
+        <v>50408.80362662842</v>
       </c>
       <c r="E64">
-        <v>25609.086</v>
+        <v>26147.839</v>
       </c>
       <c r="F64">
-        <v>33402.68599999999</v>
+        <v>33941.439</v>
       </c>
       <c r="G64">
         <v>5548.1</v>
@@ -6535,28 +6535,28 @@
         <v>5314.3</v>
       </c>
       <c r="M64">
-        <v>2280.877525071758</v>
+        <v>2317.665872250335</v>
       </c>
       <c r="N64">
-        <v>3033.422474928243</v>
+        <v>2996.634127749665</v>
       </c>
       <c r="O64">
-        <v>928.8339618230279</v>
+        <v>917.5693699169476</v>
       </c>
       <c r="P64">
-        <v>2104.588513105215</v>
+        <v>2079.064757832718</v>
       </c>
       <c r="Q64">
-        <v>2534.288513105214</v>
+        <v>2508.764757832718</v>
       </c>
       <c r="R64">
-        <v>1.631578947368421</v>
+        <v>1.702702702702703</v>
       </c>
       <c r="S64">
-        <v>0.1084321942537884</v>
+        <v>0.1098818388658864</v>
       </c>
       <c r="T64">
-        <v>1.188109580966738</v>
+        <v>1.215608803581412</v>
       </c>
       <c r="U64">
         <v>0.06828425489709894</v>
@@ -6573,7 +6573,7 @@
         </is>
       </c>
       <c r="Y64">
-        <v>2.329936588696409</v>
+        <v>2.292953468240911</v>
       </c>
       <c r="Z64">
         <v>0</v>
@@ -6581,22 +6581,22 @@
     </row>
     <row r="65">
       <c r="A65">
-        <v>0.63</v>
+        <v>0.64</v>
       </c>
       <c r="B65">
-        <v>0.07050291849037053</v>
+        <v>0.070428721214785</v>
       </c>
       <c r="C65">
-        <v>22015.46462662842</v>
+        <v>21533.94048674298</v>
       </c>
       <c r="D65">
-        <v>50408.80362662842</v>
+        <v>50466.03248674297</v>
       </c>
       <c r="E65">
-        <v>26147.839</v>
+        <v>26686.592</v>
       </c>
       <c r="F65">
-        <v>33941.439</v>
+        <v>34480.192</v>
       </c>
       <c r="G65">
         <v>5548.1</v>
@@ -6617,28 +6617,28 @@
         <v>5314.3</v>
       </c>
       <c r="M65">
-        <v>2317.665872250335</v>
+        <v>2354.454219428912</v>
       </c>
       <c r="N65">
-        <v>2996.634127749665</v>
+        <v>2959.845780571089</v>
       </c>
       <c r="O65">
-        <v>917.5693699169476</v>
+        <v>906.3047780108674</v>
       </c>
       <c r="P65">
-        <v>2079.064757832718</v>
+        <v>2053.541002560221</v>
       </c>
       <c r="Q65">
-        <v>2508.764757832718</v>
+        <v>2483.241002560221</v>
       </c>
       <c r="R65">
-        <v>1.702702702702703</v>
+        <v>1.777777777777778</v>
       </c>
       <c r="S65">
-        <v>0.1098818388658864</v>
+        <v>0.1114120192897677</v>
       </c>
       <c r="T65">
-        <v>1.215608803581412</v>
+        <v>1.244635760785791</v>
       </c>
       <c r="U65">
         <v>0.06828425489709894</v>
@@ -6655,7 +6655,7 @@
         </is>
       </c>
       <c r="Y65">
-        <v>2.292953468240911</v>
+        <v>2.257126070299647</v>
       </c>
       <c r="Z65">
         <v>0</v>
@@ -6663,22 +6663,22 @@
     </row>
     <row r="66">
       <c r="A66">
-        <v>0.64</v>
+        <v>0.65</v>
       </c>
       <c r="B66">
-        <v>0.070428721214785</v>
+        <v>0.07161723993919944</v>
       </c>
       <c r="C66">
-        <v>21533.94048674298</v>
+        <v>20093.8259901945</v>
       </c>
       <c r="D66">
-        <v>50466.03248674297</v>
+        <v>49564.6709901945</v>
       </c>
       <c r="E66">
-        <v>26686.592</v>
+        <v>27225.345</v>
       </c>
       <c r="F66">
-        <v>34480.192</v>
+        <v>35018.945</v>
       </c>
       <c r="G66">
         <v>5548.1</v>
@@ -6699,45 +6699,45 @@
         <v>5314.3</v>
       </c>
       <c r="M66">
-        <v>2354.454219428912</v>
+        <v>2489.295612607488</v>
       </c>
       <c r="N66">
-        <v>2959.845780571089</v>
+        <v>2825.004387392512</v>
       </c>
       <c r="O66">
-        <v>906.3047780108674</v>
+        <v>865.0163434195872</v>
       </c>
       <c r="P66">
-        <v>2053.541002560221</v>
+        <v>1959.988043972925</v>
       </c>
       <c r="Q66">
-        <v>2483.241002560221</v>
+        <v>2389.688043972925</v>
       </c>
       <c r="R66">
-        <v>1.777777777777778</v>
+        <v>1.857142857142857</v>
       </c>
       <c r="S66">
-        <v>0.1114120192897677</v>
+        <v>0.1130296385950135</v>
       </c>
       <c r="T66">
-        <v>1.244635760785791</v>
+        <v>1.275321401258991</v>
       </c>
       <c r="U66">
-        <v>0.06828425489709894</v>
+        <v>0.07108425489709894</v>
       </c>
       <c r="V66">
         <v>0.3062</v>
       </c>
       <c r="W66">
-        <v>0.04737561604760724</v>
+        <v>0.04931825604760724</v>
       </c>
       <c r="X66" t="inlineStr">
         <is>
-          <t>Ba1/BB+</t>
+          <t>Ba2/BB</t>
         </is>
       </c>
       <c r="Y66">
-        <v>2.257126070299647</v>
+        <v>2.134860951461436</v>
       </c>
       <c r="Z66">
         <v>0</v>
@@ -6745,22 +6745,22 @@
     </row>
     <row r="67">
       <c r="A67">
-        <v>0.65</v>
+        <v>0.66</v>
       </c>
       <c r="B67">
-        <v>0.07161723993919944</v>
+        <v>0.07156246906361388</v>
       </c>
       <c r="C67">
-        <v>20093.8259901945</v>
+        <v>19595.90242143654</v>
       </c>
       <c r="D67">
-        <v>49564.6709901945</v>
+        <v>49605.50042143654</v>
       </c>
       <c r="E67">
-        <v>27225.345</v>
+        <v>27764.098</v>
       </c>
       <c r="F67">
-        <v>35018.945</v>
+        <v>35557.698</v>
       </c>
       <c r="G67">
         <v>5548.1</v>
@@ -6781,28 +6781,28 @@
         <v>5314.3</v>
       </c>
       <c r="M67">
-        <v>2489.295612607488</v>
+        <v>2527.592468186065</v>
       </c>
       <c r="N67">
-        <v>2825.004387392512</v>
+        <v>2786.707531813935</v>
       </c>
       <c r="O67">
-        <v>865.0163434195872</v>
+        <v>853.2898462414271</v>
       </c>
       <c r="P67">
-        <v>1959.988043972925</v>
+        <v>1933.417685572508</v>
       </c>
       <c r="Q67">
-        <v>2389.688043972925</v>
+        <v>2363.117685572508</v>
       </c>
       <c r="R67">
-        <v>1.857142857142857</v>
+        <v>1.941176470588236</v>
       </c>
       <c r="S67">
-        <v>0.1130296385950135</v>
+        <v>0.1147424119770385</v>
       </c>
       <c r="T67">
-        <v>1.275321401258991</v>
+        <v>1.307812079407085</v>
       </c>
       <c r="U67">
         <v>0.07108425489709894</v>
@@ -6819,7 +6819,7 @@
         </is>
       </c>
       <c r="Y67">
-        <v>2.134860951461436</v>
+        <v>2.10251457340899</v>
       </c>
       <c r="Z67">
         <v>0</v>
@@ -6827,22 +6827,22 @@
     </row>
     <row r="68">
       <c r="A68">
-        <v>0.66</v>
+        <v>0.67</v>
       </c>
       <c r="B68">
-        <v>0.07156246906361388</v>
+        <v>0.07150769818802835</v>
       </c>
       <c r="C68">
-        <v>19595.90242143654</v>
+        <v>19098.04617550341</v>
       </c>
       <c r="D68">
-        <v>49605.50042143654</v>
+        <v>49646.39717550341</v>
       </c>
       <c r="E68">
-        <v>27764.098</v>
+        <v>28302.851</v>
       </c>
       <c r="F68">
-        <v>35557.698</v>
+        <v>36096.451</v>
       </c>
       <c r="G68">
         <v>5548.1</v>
@@ -6863,28 +6863,28 @@
         <v>5314.3</v>
       </c>
       <c r="M68">
-        <v>2527.592468186065</v>
+        <v>2565.889323764642</v>
       </c>
       <c r="N68">
-        <v>2786.707531813935</v>
+        <v>2748.410676235358</v>
       </c>
       <c r="O68">
-        <v>853.2898462414271</v>
+        <v>841.5633490632667</v>
       </c>
       <c r="P68">
-        <v>1933.417685572508</v>
+        <v>1906.847327172091</v>
       </c>
       <c r="Q68">
-        <v>2363.117685572508</v>
+        <v>2336.547327172091</v>
       </c>
       <c r="R68">
-        <v>1.941176470588236</v>
+        <v>2.030303030303031</v>
       </c>
       <c r="S68">
-        <v>0.1147424119770385</v>
+        <v>0.1165589898064591</v>
       </c>
       <c r="T68">
-        <v>1.307812079407085</v>
+        <v>1.342271889564155</v>
       </c>
       <c r="U68">
         <v>0.07108425489709894</v>
@@ -6901,7 +6901,7 @@
         </is>
       </c>
       <c r="Y68">
-        <v>2.10251457340899</v>
+        <v>2.071133758880497</v>
       </c>
       <c r="Z68">
         <v>0</v>
@@ -6909,22 +6909,22 @@
     </row>
     <row r="69">
       <c r="A69">
-        <v>0.67</v>
+        <v>0.68</v>
       </c>
       <c r="B69">
-        <v>0.07150769818802835</v>
+        <v>0.07145292731244279</v>
       </c>
       <c r="C69">
-        <v>19098.04617550341</v>
+        <v>18600.25741904341</v>
       </c>
       <c r="D69">
-        <v>49646.39717550341</v>
+        <v>49687.36141904341</v>
       </c>
       <c r="E69">
-        <v>28302.851</v>
+        <v>28841.604</v>
       </c>
       <c r="F69">
-        <v>36096.451</v>
+        <v>36635.204</v>
       </c>
       <c r="G69">
         <v>5548.1</v>
@@ -6945,28 +6945,28 @@
         <v>5314.3</v>
       </c>
       <c r="M69">
-        <v>2565.889323764642</v>
+        <v>2604.186179343219</v>
       </c>
       <c r="N69">
-        <v>2748.410676235358</v>
+        <v>2710.113820656782</v>
       </c>
       <c r="O69">
-        <v>841.5633490632667</v>
+        <v>829.8368518851066</v>
       </c>
       <c r="P69">
-        <v>1906.847327172091</v>
+        <v>1880.276968771675</v>
       </c>
       <c r="Q69">
-        <v>2336.547327172091</v>
+        <v>2309.976968771675</v>
       </c>
       <c r="R69">
-        <v>2.030303030303031</v>
+        <v>2.125</v>
       </c>
       <c r="S69">
-        <v>0.1165589898064591</v>
+        <v>0.1184891037502184</v>
       </c>
       <c r="T69">
-        <v>1.342271889564155</v>
+        <v>1.378885437856041</v>
       </c>
       <c r="U69">
         <v>0.07108425489709894</v>
@@ -6983,7 +6983,7 @@
         </is>
       </c>
       <c r="Y69">
-        <v>2.071133758880497</v>
+        <v>2.040675909485196</v>
       </c>
       <c r="Z69">
         <v>0</v>
@@ -6991,22 +6991,22 @@
     </row>
     <row r="70">
       <c r="A70">
-        <v>0.68</v>
+        <v>0.6900000000000001</v>
       </c>
       <c r="B70">
-        <v>0.07145292731244279</v>
+        <v>0.07139815643685725</v>
       </c>
       <c r="C70">
-        <v>18600.25741904341</v>
+        <v>18102.53631925525</v>
       </c>
       <c r="D70">
-        <v>49687.36141904341</v>
+        <v>49728.39331925525</v>
       </c>
       <c r="E70">
-        <v>28841.604</v>
+        <v>29380.357</v>
       </c>
       <c r="F70">
-        <v>36635.204</v>
+        <v>37173.957</v>
       </c>
       <c r="G70">
         <v>5548.1</v>
@@ -7027,28 +7027,28 @@
         <v>5314.3</v>
       </c>
       <c r="M70">
-        <v>2604.186179343219</v>
+        <v>2642.483034921795</v>
       </c>
       <c r="N70">
-        <v>2710.113820656782</v>
+        <v>2671.816965078205</v>
       </c>
       <c r="O70">
-        <v>829.8368518851066</v>
+        <v>818.1103547069464</v>
       </c>
       <c r="P70">
-        <v>1880.276968771675</v>
+        <v>1853.706610371258</v>
       </c>
       <c r="Q70">
-        <v>2309.976968771675</v>
+        <v>2283.406610371258</v>
       </c>
       <c r="R70">
-        <v>2.125</v>
+        <v>2.225806451612904</v>
       </c>
       <c r="S70">
-        <v>0.1184891037502184</v>
+        <v>0.1205437411742202</v>
       </c>
       <c r="T70">
-        <v>1.378885437856041</v>
+        <v>1.417861150553856</v>
       </c>
       <c r="U70">
         <v>0.07108425489709894</v>
@@ -7065,7 +7065,7 @@
         </is>
       </c>
       <c r="Y70">
-        <v>2.040675909485196</v>
+        <v>2.011100896304251</v>
       </c>
       <c r="Z70">
         <v>0</v>
@@ -7073,22 +7073,22 @@
     </row>
     <row r="71">
       <c r="A71">
-        <v>0.6900000000000001</v>
+        <v>0.7000000000000001</v>
       </c>
       <c r="B71">
-        <v>0.07139815643685725</v>
+        <v>0.0751315335612717</v>
       </c>
       <c r="C71">
-        <v>18102.53631925525</v>
+        <v>14913.76233564843</v>
       </c>
       <c r="D71">
-        <v>49728.39331925525</v>
+        <v>47078.37233564843</v>
       </c>
       <c r="E71">
-        <v>29380.357</v>
+        <v>29919.11</v>
       </c>
       <c r="F71">
-        <v>37173.957</v>
+        <v>37712.71</v>
       </c>
       <c r="G71">
         <v>5548.1</v>
@@ -7109,45 +7109,45 @@
         <v>5314.3</v>
       </c>
       <c r="M71">
-        <v>2642.483034921795</v>
+        <v>2974.939028500372</v>
       </c>
       <c r="N71">
-        <v>2671.816965078205</v>
+        <v>2339.360971499628</v>
       </c>
       <c r="O71">
-        <v>818.1103547069464</v>
+        <v>716.3123294731862</v>
       </c>
       <c r="P71">
-        <v>1853.706610371258</v>
+        <v>1623.048642026442</v>
       </c>
       <c r="Q71">
-        <v>2283.406610371258</v>
+        <v>2052.748642026442</v>
       </c>
       <c r="R71">
-        <v>2.225806451612904</v>
+        <v>2.333333333333334</v>
       </c>
       <c r="S71">
-        <v>0.1205437411742202</v>
+        <v>0.1227353544264888</v>
       </c>
       <c r="T71">
-        <v>1.417861150553856</v>
+        <v>1.459435244098192</v>
       </c>
       <c r="U71">
-        <v>0.07108425489709894</v>
+        <v>0.07888425489709894</v>
       </c>
       <c r="V71">
         <v>0.3062</v>
       </c>
       <c r="W71">
-        <v>0.04931825604760724</v>
+        <v>0.05472989604760724</v>
       </c>
       <c r="X71" t="inlineStr">
         <is>
-          <t>Ba2/BB</t>
+          <t>B1/B+</t>
         </is>
       </c>
       <c r="Y71">
-        <v>2.011100896304251</v>
+        <v>1.786355938420314</v>
       </c>
       <c r="Z71">
         <v>0</v>
@@ -7155,22 +7155,22 @@
     </row>
     <row r="72">
       <c r="A72">
-        <v>0.7000000000000001</v>
+        <v>0.7100000000000001</v>
       </c>
       <c r="B72">
-        <v>0.0751315335612717</v>
+        <v>0.07513087908568615</v>
       </c>
       <c r="C72">
-        <v>14913.76233564843</v>
+        <v>14375.44914247876</v>
       </c>
       <c r="D72">
-        <v>47078.37233564843</v>
+        <v>47078.81214247876</v>
       </c>
       <c r="E72">
-        <v>29919.11</v>
+        <v>30457.863</v>
       </c>
       <c r="F72">
-        <v>37712.71</v>
+        <v>38251.463</v>
       </c>
       <c r="G72">
         <v>5548.1</v>
@@ -7191,28 +7191,28 @@
         <v>5314.3</v>
       </c>
       <c r="M72">
-        <v>2974.939028500372</v>
+        <v>3017.438157478949</v>
       </c>
       <c r="N72">
-        <v>2339.360971499628</v>
+        <v>2296.861842521051</v>
       </c>
       <c r="O72">
-        <v>716.3123294731862</v>
+        <v>703.2990961799459</v>
       </c>
       <c r="P72">
-        <v>1623.048642026442</v>
+        <v>1593.562746341105</v>
       </c>
       <c r="Q72">
-        <v>2052.748642026442</v>
+        <v>2023.262746341105</v>
       </c>
       <c r="R72">
-        <v>2.333333333333334</v>
+        <v>2.448275862068967</v>
       </c>
       <c r="S72">
-        <v>0.1227353544264888</v>
+        <v>0.1250781134202932</v>
       </c>
       <c r="T72">
-        <v>1.459435244098192</v>
+        <v>1.503876516507654</v>
       </c>
       <c r="U72">
         <v>0.07888425489709894</v>
@@ -7229,7 +7229,7 @@
         </is>
       </c>
       <c r="Y72">
-        <v>1.786355938420314</v>
+        <v>1.761195995625662</v>
       </c>
       <c r="Z72">
         <v>0</v>
@@ -7237,22 +7237,22 @@
     </row>
     <row r="73">
       <c r="A73">
-        <v>0.71</v>
+        <v>0.72</v>
       </c>
       <c r="B73">
-        <v>0.07513087908568615</v>
+        <v>0.0770784150101006</v>
       </c>
       <c r="C73">
-        <v>14375.44914247876</v>
+        <v>12563.34033972872</v>
       </c>
       <c r="D73">
-        <v>47078.81214247876</v>
+        <v>45805.45633972871</v>
       </c>
       <c r="E73">
-        <v>30457.863</v>
+        <v>30996.61599999999</v>
       </c>
       <c r="F73">
-        <v>38251.463</v>
+        <v>38790.21599999999</v>
       </c>
       <c r="G73">
         <v>5548.1</v>
@@ -7273,45 +7273,45 @@
         <v>5314.3</v>
       </c>
       <c r="M73">
-        <v>3017.438157478949</v>
+        <v>3211.219128857525</v>
       </c>
       <c r="N73">
-        <v>2296.861842521052</v>
+        <v>2103.080871142475</v>
       </c>
       <c r="O73">
-        <v>703.2990961799461</v>
+        <v>643.963362743826</v>
       </c>
       <c r="P73">
-        <v>1593.562746341106</v>
+        <v>1459.117508398649</v>
       </c>
       <c r="Q73">
-        <v>2023.262746341106</v>
+        <v>1888.817508398649</v>
       </c>
       <c r="R73">
-        <v>2.448275862068965</v>
+        <v>2.571428571428571</v>
       </c>
       <c r="S73">
-        <v>0.1250781134202931</v>
+        <v>0.1275882123422264</v>
       </c>
       <c r="T73">
-        <v>1.503876516507653</v>
+        <v>1.551492165517792</v>
       </c>
       <c r="U73">
-        <v>0.07888425489709894</v>
+        <v>0.08278425489709894</v>
       </c>
       <c r="V73">
         <v>0.3062</v>
       </c>
       <c r="W73">
-        <v>0.05472989604760724</v>
+        <v>0.05743571604760724</v>
       </c>
       <c r="X73" t="inlineStr">
         <is>
-          <t>B1/B+</t>
+          <t>B2/B</t>
         </is>
       </c>
       <c r="Y73">
-        <v>1.761195995625662</v>
+        <v>1.654916649020679</v>
       </c>
       <c r="Z73">
         <v>0</v>
@@ -7319,22 +7319,22 @@
     </row>
     <row r="74">
       <c r="A74">
-        <v>0.72</v>
+        <v>0.73</v>
       </c>
       <c r="B74">
-        <v>0.0770784150101006</v>
+        <v>0.07710481873451505</v>
       </c>
       <c r="C74">
-        <v>12563.34033972872</v>
+        <v>12007.79690351857</v>
       </c>
       <c r="D74">
-        <v>45805.45633972871</v>
+        <v>45788.66590351857</v>
       </c>
       <c r="E74">
-        <v>30996.61599999999</v>
+        <v>31535.369</v>
       </c>
       <c r="F74">
-        <v>38790.21599999999</v>
+        <v>39328.969</v>
       </c>
       <c r="G74">
         <v>5548.1</v>
@@ -7355,28 +7355,28 @@
         <v>5314.3</v>
       </c>
       <c r="M74">
-        <v>3211.219128857525</v>
+        <v>3255.819394536102</v>
       </c>
       <c r="N74">
-        <v>2103.080871142475</v>
+        <v>2058.480605463898</v>
       </c>
       <c r="O74">
-        <v>643.963362743826</v>
+        <v>630.3067613930456</v>
       </c>
       <c r="P74">
-        <v>1459.117508398649</v>
+        <v>1428.173844070852</v>
       </c>
       <c r="Q74">
-        <v>1888.817508398649</v>
+        <v>1857.873844070852</v>
       </c>
       <c r="R74">
-        <v>2.571428571428571</v>
+        <v>2.703703703703703</v>
       </c>
       <c r="S74">
-        <v>0.1275882123422264</v>
+        <v>0.1302842445176362</v>
       </c>
       <c r="T74">
-        <v>1.551492165517792</v>
+        <v>1.602634899639792</v>
       </c>
       <c r="U74">
         <v>0.08278425489709894</v>
@@ -7393,7 +7393,7 @@
         </is>
       </c>
       <c r="Y74">
-        <v>1.654916649020679</v>
+        <v>1.632246557938204</v>
       </c>
       <c r="Z74">
         <v>0</v>
@@ -7401,22 +7401,22 @@
     </row>
     <row r="75">
       <c r="A75">
-        <v>0.73</v>
+        <v>0.74</v>
       </c>
       <c r="B75">
-        <v>0.07710481873451505</v>
+        <v>0.0771312224589295</v>
       </c>
       <c r="C75">
-        <v>12007.79690351857</v>
+        <v>11452.26577219386</v>
       </c>
       <c r="D75">
-        <v>45788.66590351857</v>
+        <v>45771.88777219386</v>
       </c>
       <c r="E75">
-        <v>31535.369</v>
+        <v>32074.122</v>
       </c>
       <c r="F75">
-        <v>39328.969</v>
+        <v>39867.72199999999</v>
       </c>
       <c r="G75">
         <v>5548.1</v>
@@ -7437,28 +7437,28 @@
         <v>5314.3</v>
       </c>
       <c r="M75">
-        <v>3255.819394536102</v>
+        <v>3300.419660214679</v>
       </c>
       <c r="N75">
-        <v>2058.480605463898</v>
+        <v>2013.880339785322</v>
       </c>
       <c r="O75">
-        <v>630.3067613930456</v>
+        <v>616.6501600422655</v>
       </c>
       <c r="P75">
-        <v>1428.173844070852</v>
+        <v>1397.230179743056</v>
       </c>
       <c r="Q75">
-        <v>1857.873844070852</v>
+        <v>1826.930179743056</v>
       </c>
       <c r="R75">
-        <v>2.703703703703703</v>
+        <v>2.846153846153846</v>
       </c>
       <c r="S75">
-        <v>0.1302842445176362</v>
+        <v>0.1331876637834621</v>
       </c>
       <c r="T75">
-        <v>1.602634899639792</v>
+        <v>1.657711690232715</v>
       </c>
       <c r="U75">
         <v>0.08278425489709894</v>
@@ -7475,7 +7475,7 @@
         </is>
       </c>
       <c r="Y75">
-        <v>1.632246557938204</v>
+        <v>1.61018917202012</v>
       </c>
       <c r="Z75">
         <v>0</v>
@@ -7483,22 +7483,22 @@
     </row>
     <row r="76">
       <c r="A76">
-        <v>0.74</v>
+        <v>0.75</v>
       </c>
       <c r="B76">
-        <v>0.0771312224589295</v>
+        <v>0.07715762618334396</v>
       </c>
       <c r="C76">
-        <v>11452.26577219386</v>
+        <v>10896.74693223304</v>
       </c>
       <c r="D76">
-        <v>45771.88777219386</v>
+        <v>45755.12193223304</v>
       </c>
       <c r="E76">
-        <v>32074.122</v>
+        <v>32612.875</v>
       </c>
       <c r="F76">
-        <v>39867.72199999999</v>
+        <v>40406.475</v>
       </c>
       <c r="G76">
         <v>5548.1</v>
@@ -7519,28 +7519,28 @@
         <v>5314.3</v>
       </c>
       <c r="M76">
-        <v>3300.419660214679</v>
+        <v>3345.019925893256</v>
       </c>
       <c r="N76">
-        <v>2013.880339785322</v>
+        <v>1969.280074106744</v>
       </c>
       <c r="O76">
-        <v>616.6501600422655</v>
+        <v>602.9935586914852</v>
       </c>
       <c r="P76">
-        <v>1397.230179743056</v>
+        <v>1366.286515415259</v>
       </c>
       <c r="Q76">
-        <v>1826.930179743056</v>
+        <v>1795.986515415259</v>
       </c>
       <c r="R76">
-        <v>2.846153846153846</v>
+        <v>3</v>
       </c>
       <c r="S76">
-        <v>0.1331876637834621</v>
+        <v>0.1363233565905541</v>
       </c>
       <c r="T76">
-        <v>1.657711690232715</v>
+        <v>1.717194624073072</v>
       </c>
       <c r="U76">
         <v>0.08278425489709894</v>
@@ -7557,7 +7557,7 @@
         </is>
       </c>
       <c r="Y76">
-        <v>1.61018917202012</v>
+        <v>1.588719983059852</v>
       </c>
       <c r="Z76">
         <v>0</v>
@@ -7565,22 +7565,22 @@
     </row>
     <row r="77">
       <c r="A77">
-        <v>0.75</v>
+        <v>0.76</v>
       </c>
       <c r="B77">
-        <v>0.07715762618334396</v>
+        <v>0.07718402990775841</v>
       </c>
       <c r="C77">
-        <v>10896.74693223304</v>
+        <v>10341.24037013442</v>
       </c>
       <c r="D77">
-        <v>45755.12193223304</v>
+        <v>45738.36837013442</v>
       </c>
       <c r="E77">
-        <v>32612.875</v>
+        <v>33151.628</v>
       </c>
       <c r="F77">
-        <v>40406.475</v>
+        <v>40945.228</v>
       </c>
       <c r="G77">
         <v>5548.1</v>
@@ -7601,28 +7601,28 @@
         <v>5314.3</v>
       </c>
       <c r="M77">
-        <v>3345.019925893256</v>
+        <v>3389.620191571832</v>
       </c>
       <c r="N77">
-        <v>1969.280074106744</v>
+        <v>1924.679808428168</v>
       </c>
       <c r="O77">
-        <v>602.9935586914852</v>
+        <v>589.3369573407051</v>
       </c>
       <c r="P77">
-        <v>1366.286515415259</v>
+        <v>1335.342851087463</v>
       </c>
       <c r="Q77">
-        <v>1795.986515415259</v>
+        <v>1765.042851087463</v>
       </c>
       <c r="R77">
-        <v>3</v>
+        <v>3.166666666666667</v>
       </c>
       <c r="S77">
-        <v>0.1363233565905541</v>
+        <v>0.1397203571315705</v>
       </c>
       <c r="T77">
-        <v>1.717194624073072</v>
+        <v>1.781634469066793</v>
       </c>
       <c r="U77">
         <v>0.08278425489709894</v>
@@ -7639,7 +7639,7 @@
         </is>
       </c>
       <c r="Y77">
-        <v>1.588719983059852</v>
+        <v>1.567815772756433</v>
       </c>
       <c r="Z77">
         <v>0</v>
@@ -7647,22 +7647,22 @@
     </row>
     <row r="78">
       <c r="A78">
-        <v>0.76</v>
+        <v>0.77</v>
       </c>
       <c r="B78">
-        <v>0.07718402990775841</v>
+        <v>0.07721043363217286</v>
       </c>
       <c r="C78">
-        <v>10341.24037013442</v>
+        <v>9785.746072416056</v>
       </c>
       <c r="D78">
-        <v>45738.36837013442</v>
+        <v>45721.62707241606</v>
       </c>
       <c r="E78">
-        <v>33151.628</v>
+        <v>33690.381</v>
       </c>
       <c r="F78">
-        <v>40945.228</v>
+        <v>41483.981</v>
       </c>
       <c r="G78">
         <v>5548.1</v>
@@ -7683,28 +7683,28 @@
         <v>5314.3</v>
       </c>
       <c r="M78">
-        <v>3389.620191571832</v>
+        <v>3434.220457250409</v>
       </c>
       <c r="N78">
-        <v>1924.679808428168</v>
+        <v>1880.079542749591</v>
       </c>
       <c r="O78">
-        <v>589.3369573407051</v>
+        <v>575.6803559899248</v>
       </c>
       <c r="P78">
-        <v>1335.342851087463</v>
+        <v>1304.399186759666</v>
       </c>
       <c r="Q78">
-        <v>1765.042851087463</v>
+        <v>1734.099186759666</v>
       </c>
       <c r="R78">
-        <v>3.166666666666667</v>
+        <v>3.347826086956522</v>
       </c>
       <c r="S78">
-        <v>0.1397203571315705</v>
+        <v>0.1434127490239795</v>
       </c>
       <c r="T78">
-        <v>1.781634469066793</v>
+        <v>1.851677778842576</v>
       </c>
       <c r="U78">
         <v>0.08278425489709894</v>
@@ -7721,7 +7721,7 @@
         </is>
       </c>
       <c r="Y78">
-        <v>1.567815772756433</v>
+        <v>1.547454528954401</v>
       </c>
       <c r="Z78">
         <v>0</v>
@@ -7729,22 +7729,22 @@
     </row>
     <row r="79">
       <c r="A79">
-        <v>0.77</v>
+        <v>0.78</v>
       </c>
       <c r="B79">
-        <v>0.07721043363217286</v>
+        <v>0.07723683735658732</v>
       </c>
       <c r="C79">
-        <v>9785.746072416056</v>
+        <v>9230.264025615739</v>
       </c>
       <c r="D79">
-        <v>45721.62707241606</v>
+        <v>45704.89802561574</v>
       </c>
       <c r="E79">
-        <v>33690.381</v>
+        <v>34229.134</v>
       </c>
       <c r="F79">
-        <v>41483.981</v>
+        <v>42022.734</v>
       </c>
       <c r="G79">
         <v>5548.1</v>
@@ -7765,28 +7765,28 @@
         <v>5314.3</v>
       </c>
       <c r="M79">
-        <v>3434.220457250409</v>
+        <v>3478.820722928986</v>
       </c>
       <c r="N79">
-        <v>1880.079542749591</v>
+        <v>1835.479277071014</v>
       </c>
       <c r="O79">
-        <v>575.6803559899248</v>
+        <v>562.0237546391446</v>
       </c>
       <c r="P79">
-        <v>1304.399186759666</v>
+        <v>1273.45552243187</v>
       </c>
       <c r="Q79">
-        <v>1734.099186759666</v>
+        <v>1703.15552243187</v>
       </c>
       <c r="R79">
-        <v>3.347826086956522</v>
+        <v>3.545454545454546</v>
       </c>
       <c r="S79">
-        <v>0.1434127490239795</v>
+        <v>0.1474408129066076</v>
       </c>
       <c r="T79">
-        <v>1.851677778842576</v>
+        <v>1.928088662234339</v>
       </c>
       <c r="U79">
         <v>0.08278425489709894</v>
@@ -7803,7 +7803,7 @@
         </is>
       </c>
       <c r="Y79">
-        <v>1.547454528954401</v>
+        <v>1.527615368326781</v>
       </c>
       <c r="Z79">
         <v>0</v>
@@ -7811,22 +7811,22 @@
     </row>
     <row r="80">
       <c r="A80">
-        <v>0.78</v>
+        <v>0.79</v>
       </c>
       <c r="B80">
-        <v>0.07723683735658732</v>
+        <v>0.07726324108100177</v>
       </c>
       <c r="C80">
-        <v>9230.264025615739</v>
+        <v>8674.794216290938</v>
       </c>
       <c r="D80">
-        <v>45704.89802561574</v>
+        <v>45688.18121629094</v>
       </c>
       <c r="E80">
-        <v>34229.134</v>
+        <v>34767.887</v>
       </c>
       <c r="F80">
-        <v>42022.734</v>
+        <v>42561.487</v>
       </c>
       <c r="G80">
         <v>5548.1</v>
@@ -7847,28 +7847,28 @@
         <v>5314.3</v>
       </c>
       <c r="M80">
-        <v>3478.820722928986</v>
+        <v>3523.420988607563</v>
       </c>
       <c r="N80">
-        <v>1835.479277071014</v>
+        <v>1790.879011392437</v>
       </c>
       <c r="O80">
-        <v>562.0237546391446</v>
+        <v>548.3671532883644</v>
       </c>
       <c r="P80">
-        <v>1273.45552243187</v>
+        <v>1242.511858104073</v>
       </c>
       <c r="Q80">
-        <v>1703.15552243187</v>
+        <v>1672.211858104073</v>
       </c>
       <c r="R80">
-        <v>3.545454545454546</v>
+        <v>3.761904761904763</v>
       </c>
       <c r="S80">
-        <v>0.1474408129066076</v>
+        <v>0.1518525019209145</v>
       </c>
       <c r="T80">
-        <v>1.928088662234339</v>
+        <v>2.011776772615794</v>
       </c>
       <c r="U80">
         <v>0.08278425489709894</v>
@@ -7885,7 +7885,7 @@
         </is>
       </c>
       <c r="Y80">
-        <v>1.527615368326781</v>
+        <v>1.508278464930239</v>
       </c>
       <c r="Z80">
         <v>0</v>
@@ -7893,22 +7893,22 @@
     </row>
     <row r="81">
       <c r="A81">
-        <v>0.79</v>
+        <v>0.8</v>
       </c>
       <c r="B81">
-        <v>0.07726324108100177</v>
+        <v>0.08517121280541622</v>
       </c>
       <c r="C81">
-        <v>8674.794216290938</v>
+        <v>3625.281352365557</v>
       </c>
       <c r="D81">
-        <v>45688.18121629094</v>
+        <v>41177.42135236556</v>
       </c>
       <c r="E81">
-        <v>34767.887</v>
+        <v>35306.64</v>
       </c>
       <c r="F81">
-        <v>42561.487</v>
+        <v>43100.24</v>
       </c>
       <c r="G81">
         <v>5548.1</v>
@@ -7929,45 +7929,45 @@
         <v>5314.3</v>
       </c>
       <c r="M81">
-        <v>3523.420988607563</v>
+        <v>4180.044662286139</v>
       </c>
       <c r="N81">
-        <v>1790.879011392437</v>
+        <v>1134.255337713861</v>
       </c>
       <c r="O81">
-        <v>548.3671532883644</v>
+        <v>347.3089844079843</v>
       </c>
       <c r="P81">
-        <v>1242.511858104073</v>
+        <v>786.9463533058768</v>
       </c>
       <c r="Q81">
-        <v>1672.211858104073</v>
+        <v>1216.646353305877</v>
       </c>
       <c r="R81">
-        <v>3.761904761904763</v>
+        <v>4.000000000000001</v>
       </c>
       <c r="S81">
-        <v>0.1518525019209145</v>
+        <v>0.1567053598366522</v>
       </c>
       <c r="T81">
-        <v>2.011776772615794</v>
+        <v>2.103833694035394</v>
       </c>
       <c r="U81">
-        <v>0.08278425489709894</v>
+        <v>0.09698425489709894</v>
       </c>
       <c r="V81">
         <v>0.3062</v>
       </c>
       <c r="W81">
-        <v>0.05743571604760724</v>
+        <v>0.06728767604760724</v>
       </c>
       <c r="X81" t="inlineStr">
         <is>
-          <t>B2/B</t>
+          <t>B3/B-</t>
         </is>
       </c>
       <c r="Y81">
-        <v>1.508278464930239</v>
+        <v>1.271350052296694</v>
       </c>
       <c r="Z81">
         <v>0</v>
@@ -7975,22 +7975,22 @@
     </row>
     <row r="82">
       <c r="A82">
-        <v>0.8</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="B82">
-        <v>0.08517121280541622</v>
+        <v>0.08529613612983067</v>
       </c>
       <c r="C82">
-        <v>3625.281352365557</v>
+        <v>3022.406421118911</v>
       </c>
       <c r="D82">
-        <v>41177.42135236556</v>
+        <v>41113.29942111891</v>
       </c>
       <c r="E82">
-        <v>35306.64</v>
+        <v>35845.393</v>
       </c>
       <c r="F82">
-        <v>43100.24</v>
+        <v>43638.993</v>
       </c>
       <c r="G82">
         <v>5548.1</v>
@@ -8011,28 +8011,28 @@
         <v>5314.3</v>
       </c>
       <c r="M82">
-        <v>4180.044662286139</v>
+        <v>4232.295220564717</v>
       </c>
       <c r="N82">
-        <v>1134.255337713861</v>
+        <v>1082.004779435283</v>
       </c>
       <c r="O82">
-        <v>347.3089844079843</v>
+        <v>331.3098634630837</v>
       </c>
       <c r="P82">
-        <v>786.9463533058768</v>
+        <v>750.6949159721994</v>
       </c>
       <c r="Q82">
-        <v>1216.646353305877</v>
+        <v>1180.394915972199</v>
       </c>
       <c r="R82">
-        <v>4.000000000000001</v>
+        <v>4.263157894736843</v>
       </c>
       <c r="S82">
-        <v>0.1567053598366522</v>
+        <v>0.1620690449014148</v>
       </c>
       <c r="T82">
-        <v>2.103833694035394</v>
+        <v>2.20558081770969</v>
       </c>
       <c r="U82">
         <v>0.09698425489709894</v>
@@ -8049,7 +8049,7 @@
         </is>
       </c>
       <c r="Y82">
-        <v>1.271350052296694</v>
+        <v>1.25565437263871</v>
       </c>
       <c r="Z82">
         <v>0</v>
@@ -8057,22 +8057,22 @@
     </row>
     <row r="83">
       <c r="A83">
-        <v>0.8100000000000001</v>
+        <v>0.8200000000000001</v>
       </c>
       <c r="B83">
-        <v>0.08529613612983067</v>
+        <v>0.1033312028104755</v>
       </c>
       <c r="C83">
-        <v>3022.406421118911</v>
+        <v>-5062.648306489005</v>
       </c>
       <c r="D83">
-        <v>41113.29942111891</v>
+        <v>33566.997693511</v>
       </c>
       <c r="E83">
-        <v>35845.393</v>
+        <v>36384.146</v>
       </c>
       <c r="F83">
-        <v>43638.993</v>
+        <v>44177.746</v>
       </c>
       <c r="G83">
         <v>5548.1</v>
@@ -8093,45 +8093,45 @@
         <v>5314.3</v>
       </c>
       <c r="M83">
-        <v>4232.295220564717</v>
+        <v>5548.029314443294</v>
       </c>
       <c r="N83">
-        <v>1082.004779435283</v>
+        <v>-233.7293144432933</v>
       </c>
       <c r="O83">
-        <v>331.3098634630837</v>
+        <v>-71.56791608253643</v>
       </c>
       <c r="P83">
-        <v>750.6949159721994</v>
+        <v>-162.1613983607569</v>
       </c>
       <c r="Q83">
-        <v>1180.394915972199</v>
+        <v>267.5386016392431</v>
       </c>
       <c r="R83">
-        <v>4.263157894736843</v>
+        <v>4.555555555555557</v>
       </c>
       <c r="S83">
-        <v>0.1620690449014148</v>
+        <v>0.1697550636306758</v>
       </c>
       <c r="T83">
-        <v>2.20558081770969</v>
+        <v>2.351381752844139</v>
       </c>
       <c r="U83">
-        <v>0.09698425489709894</v>
+        <v>0.125584254897099</v>
       </c>
       <c r="V83">
-        <v>0.3062</v>
+        <v>0.2933002995791276</v>
       </c>
       <c r="W83">
-        <v>0.06728767604760724</v>
+        <v>0.08875035531335831</v>
       </c>
       <c r="X83" t="inlineStr">
         <is>
-          <t>B3/B-</t>
+          <t>Caa/CCC</t>
         </is>
       </c>
       <c r="Y83">
-        <v>1.25565437263871</v>
+        <v>0.9578716511401947</v>
       </c>
       <c r="Z83">
         <v>0</v>
@@ -8139,22 +8139,22 @@
     </row>
     <row r="84">
       <c r="A84">
-        <v>0.8200000000000001</v>
+        <v>0.8300000000000001</v>
       </c>
       <c r="B84">
-        <v>0.1033312028104755</v>
+        <v>0.1041290453594464</v>
       </c>
       <c r="C84">
-        <v>-5062.648306489005</v>
+        <v>-5871.766999144464</v>
       </c>
       <c r="D84">
-        <v>33566.997693511</v>
+        <v>33296.63200085554</v>
       </c>
       <c r="E84">
-        <v>36384.146</v>
+        <v>36922.899</v>
       </c>
       <c r="F84">
-        <v>44177.746</v>
+        <v>44716.499</v>
       </c>
       <c r="G84">
         <v>5548.1</v>
@@ -8175,37 +8175,37 @@
         <v>5314.3</v>
       </c>
       <c r="M84">
-        <v>5548.029314443294</v>
+        <v>5615.688208521871</v>
       </c>
       <c r="N84">
-        <v>-233.7293144432933</v>
+        <v>-301.3882085218711</v>
       </c>
       <c r="O84">
-        <v>-71.56791608253643</v>
+        <v>-92.28506944939694</v>
       </c>
       <c r="P84">
-        <v>-162.1613983607569</v>
+        <v>-209.1031390724742</v>
       </c>
       <c r="Q84">
-        <v>267.5386016392431</v>
+        <v>220.5968609275258</v>
       </c>
       <c r="R84">
-        <v>4.555555555555557</v>
+        <v>4.882352941176473</v>
       </c>
       <c r="S84">
-        <v>0.1697550636306758</v>
+        <v>0.1770465379618921</v>
       </c>
       <c r="T84">
-        <v>2.351381752844139</v>
+        <v>2.489698326540853</v>
       </c>
       <c r="U84">
         <v>0.125584254897099</v>
       </c>
       <c r="V84">
-        <v>0.2933002995791276</v>
+        <v>0.2897665610299815</v>
       </c>
       <c r="W84">
-        <v>0.08875035531335831</v>
+        <v>0.08919413723605397</v>
       </c>
       <c r="X84" t="inlineStr">
         <is>
@@ -8213,7 +8213,7 @@
         </is>
       </c>
       <c r="Y84">
-        <v>0.9578716511401947</v>
+        <v>0.9463310288373007</v>
       </c>
       <c r="Z84">
         <v>0</v>
@@ -8221,22 +8221,22 @@
     </row>
     <row r="85">
       <c r="A85">
-        <v>0.8300000000000001</v>
+        <v>0.8400000000000001</v>
       </c>
       <c r="B85">
-        <v>0.1041290453594464</v>
+        <v>0.1049268879084174</v>
       </c>
       <c r="C85">
-        <v>-5871.766999144464</v>
+        <v>-6676.565165585678</v>
       </c>
       <c r="D85">
-        <v>33296.63200085554</v>
+        <v>33030.58683441432</v>
       </c>
       <c r="E85">
-        <v>36922.899</v>
+        <v>37461.652</v>
       </c>
       <c r="F85">
-        <v>44716.499</v>
+        <v>45255.252</v>
       </c>
       <c r="G85">
         <v>5548.1</v>
@@ -8257,37 +8257,37 @@
         <v>5314.3</v>
       </c>
       <c r="M85">
-        <v>5615.688208521871</v>
+        <v>5683.347102600447</v>
       </c>
       <c r="N85">
-        <v>-301.3882085218711</v>
+        <v>-369.047102600447</v>
       </c>
       <c r="O85">
-        <v>-92.28506944939694</v>
+        <v>-113.0022228162569</v>
       </c>
       <c r="P85">
-        <v>-209.1031390724742</v>
+        <v>-256.0448797841901</v>
       </c>
       <c r="Q85">
-        <v>220.5968609275258</v>
+        <v>173.6551202158099</v>
       </c>
       <c r="R85">
-        <v>4.882352941176473</v>
+        <v>5.250000000000004</v>
       </c>
       <c r="S85">
-        <v>0.1770465379618921</v>
+        <v>0.1852494465845103</v>
       </c>
       <c r="T85">
-        <v>2.489698326540853</v>
+        <v>2.645304471949657</v>
       </c>
       <c r="U85">
         <v>0.125584254897099</v>
       </c>
       <c r="V85">
-        <v>0.2897665610299815</v>
+        <v>0.286316959112958</v>
       </c>
       <c r="W85">
-        <v>0.08919413723605397</v>
+        <v>0.08962735292249499</v>
       </c>
       <c r="X85" t="inlineStr">
         <is>
@@ -8295,7 +8295,7 @@
         </is>
       </c>
       <c r="Y85">
-        <v>0.9463310288373007</v>
+        <v>0.9350651832559044</v>
       </c>
       <c r="Z85">
         <v>0</v>
@@ -8303,22 +8303,22 @@
     </row>
     <row r="86">
       <c r="A86">
-        <v>0.84</v>
+        <v>0.85</v>
       </c>
       <c r="B86">
-        <v>0.1049268879084174</v>
+        <v>0.1057247304573884</v>
       </c>
       <c r="C86">
-        <v>-6676.565165585671</v>
+        <v>-7477.145549861671</v>
       </c>
       <c r="D86">
-        <v>33030.58683441432</v>
+        <v>32768.75945013833</v>
       </c>
       <c r="E86">
-        <v>37461.65199999999</v>
+        <v>38000.405</v>
       </c>
       <c r="F86">
-        <v>45255.25199999999</v>
+        <v>45794.005</v>
       </c>
       <c r="G86">
         <v>5548.1</v>
@@ -8339,37 +8339,37 @@
         <v>5314.3</v>
       </c>
       <c r="M86">
-        <v>5683.347102600446</v>
+        <v>5751.005996679024</v>
       </c>
       <c r="N86">
-        <v>-369.0471026004461</v>
+        <v>-436.7059966790239</v>
       </c>
       <c r="O86">
-        <v>-113.0022228162566</v>
+        <v>-133.7193761831171</v>
       </c>
       <c r="P86">
-        <v>-256.0448797841895</v>
+        <v>-302.9866204959068</v>
       </c>
       <c r="Q86">
-        <v>173.6551202158105</v>
+        <v>126.7133795040932</v>
       </c>
       <c r="R86">
-        <v>5.249999999999999</v>
+        <v>5.666666666666666</v>
       </c>
       <c r="S86">
-        <v>0.1852494465845103</v>
+        <v>0.1945460763568109</v>
       </c>
       <c r="T86">
-        <v>2.645304471949655</v>
+        <v>2.821658103412965</v>
       </c>
       <c r="U86">
         <v>0.125584254897099</v>
       </c>
       <c r="V86">
-        <v>0.286316959112958</v>
+        <v>0.2829485242998643</v>
       </c>
       <c r="W86">
-        <v>0.08962735292249499</v>
+        <v>0.0900503752986668</v>
       </c>
       <c r="X86" t="inlineStr">
         <is>
@@ -8377,7 +8377,7 @@
         </is>
       </c>
       <c r="Y86">
-        <v>0.9350651832559045</v>
+        <v>0.9240644163940701</v>
       </c>
       <c r="Z86">
         <v>0</v>
@@ -8385,22 +8385,22 @@
     </row>
     <row r="87">
       <c r="A87">
-        <v>0.85</v>
+        <v>0.86</v>
       </c>
       <c r="B87">
-        <v>0.1057247304573884</v>
+        <v>0.1065225730063594</v>
       </c>
       <c r="C87">
-        <v>-7477.145549861671</v>
+        <v>-8273.607663909104</v>
       </c>
       <c r="D87">
-        <v>32768.75945013833</v>
+        <v>32511.05033609089</v>
       </c>
       <c r="E87">
-        <v>38000.405</v>
+        <v>38539.158</v>
       </c>
       <c r="F87">
-        <v>45794.005</v>
+        <v>46332.75799999999</v>
       </c>
       <c r="G87">
         <v>5548.1</v>
@@ -8421,37 +8421,37 @@
         <v>5314.3</v>
       </c>
       <c r="M87">
-        <v>5751.005996679024</v>
+        <v>5818.6648907576</v>
       </c>
       <c r="N87">
-        <v>-436.7059966790239</v>
+        <v>-504.3648907575998</v>
       </c>
       <c r="O87">
-        <v>-133.7193761831171</v>
+        <v>-154.4365295499771</v>
       </c>
       <c r="P87">
-        <v>-302.9866204959068</v>
+        <v>-349.9283612076227</v>
       </c>
       <c r="Q87">
-        <v>126.7133795040932</v>
+        <v>79.77163879237725</v>
       </c>
       <c r="R87">
-        <v>5.666666666666666</v>
+        <v>6.142857142857142</v>
       </c>
       <c r="S87">
-        <v>0.1945460763568109</v>
+        <v>0.2051707960965831</v>
       </c>
       <c r="T87">
-        <v>2.821658103412965</v>
+        <v>3.023205110799606</v>
       </c>
       <c r="U87">
         <v>0.125584254897099</v>
       </c>
       <c r="V87">
-        <v>0.2829485242998643</v>
+        <v>0.2796584251800985</v>
       </c>
       <c r="W87">
-        <v>0.0900503752986668</v>
+        <v>0.0904635599451602</v>
       </c>
       <c r="X87" t="inlineStr">
         <is>
@@ -8459,7 +8459,7 @@
         </is>
       </c>
       <c r="Y87">
-        <v>0.9240644163940701</v>
+        <v>0.9133194813197206</v>
       </c>
       <c r="Z87">
         <v>0</v>
@@ -8467,22 +8467,22 @@
     </row>
     <row r="88">
       <c r="A88">
-        <v>0.86</v>
+        <v>0.87</v>
       </c>
       <c r="B88">
-        <v>0.1065225730063594</v>
+        <v>0.1073204155553304</v>
       </c>
       <c r="C88">
-        <v>-8273.607663909104</v>
+        <v>-9066.04791365494</v>
       </c>
       <c r="D88">
-        <v>32511.05033609089</v>
+        <v>32257.36308634506</v>
       </c>
       <c r="E88">
-        <v>38539.158</v>
+        <v>39077.911</v>
       </c>
       <c r="F88">
-        <v>46332.75799999999</v>
+        <v>46871.511</v>
       </c>
       <c r="G88">
         <v>5548.1</v>
@@ -8503,37 +8503,37 @@
         <v>5314.3</v>
       </c>
       <c r="M88">
-        <v>5818.6648907576</v>
+        <v>5886.323784836178</v>
       </c>
       <c r="N88">
-        <v>-504.3648907575998</v>
+        <v>-572.0237848361776</v>
       </c>
       <c r="O88">
-        <v>-154.4365295499771</v>
+        <v>-175.1536829168376</v>
       </c>
       <c r="P88">
-        <v>-349.9283612076227</v>
+        <v>-396.87010191934</v>
       </c>
       <c r="Q88">
-        <v>79.77163879237725</v>
+        <v>32.82989808066003</v>
       </c>
       <c r="R88">
-        <v>6.142857142857142</v>
+        <v>6.692307692307692</v>
       </c>
       <c r="S88">
-        <v>0.2051707960965831</v>
+        <v>0.2174300881040126</v>
       </c>
       <c r="T88">
-        <v>3.023205110799606</v>
+        <v>3.255759350091883</v>
       </c>
       <c r="U88">
         <v>0.125584254897099</v>
       </c>
       <c r="V88">
-        <v>0.2796584251800985</v>
+        <v>0.2764439605228559</v>
       </c>
       <c r="W88">
-        <v>0.0904635599451602</v>
+        <v>0.09086724609403306</v>
       </c>
       <c r="X88" t="inlineStr">
         <is>
@@ -8541,7 +8541,7 @@
         </is>
       </c>
       <c r="Y88">
-        <v>0.9133194813197206</v>
+        <v>0.90282155624708</v>
       </c>
       <c r="Z88">
         <v>0</v>
@@ -8549,22 +8549,22 @@
     </row>
     <row r="89">
       <c r="A89">
-        <v>0.87</v>
+        <v>0.88</v>
       </c>
       <c r="B89">
-        <v>0.1073204155553304</v>
+        <v>0.1081182581043014</v>
       </c>
       <c r="C89">
-        <v>-9066.04791365494</v>
+        <v>-9854.559719260797</v>
       </c>
       <c r="D89">
-        <v>32257.36308634506</v>
+        <v>32007.6042807392</v>
       </c>
       <c r="E89">
-        <v>39077.911</v>
+        <v>39616.664</v>
       </c>
       <c r="F89">
-        <v>46871.511</v>
+        <v>47410.264</v>
       </c>
       <c r="G89">
         <v>5548.1</v>
@@ -8585,37 +8585,37 @@
         <v>5314.3</v>
       </c>
       <c r="M89">
-        <v>5886.323784836178</v>
+        <v>5953.982678914754</v>
       </c>
       <c r="N89">
-        <v>-572.0237848361776</v>
+        <v>-639.6826789147535</v>
       </c>
       <c r="O89">
-        <v>-175.1536829168376</v>
+        <v>-195.8708362836975</v>
       </c>
       <c r="P89">
-        <v>-396.87010191934</v>
+        <v>-443.811842631056</v>
       </c>
       <c r="Q89">
-        <v>32.82989808066003</v>
+        <v>-14.11184263105599</v>
       </c>
       <c r="R89">
-        <v>6.692307692307692</v>
+        <v>7.333333333333334</v>
       </c>
       <c r="S89">
-        <v>0.2174300881040126</v>
+        <v>0.2317325954460137</v>
       </c>
       <c r="T89">
-        <v>3.255759350091883</v>
+        <v>3.527072629266207</v>
       </c>
       <c r="U89">
         <v>0.125584254897099</v>
       </c>
       <c r="V89">
-        <v>0.2764439605228559</v>
+        <v>0.2733025518805508</v>
       </c>
       <c r="W89">
-        <v>0.09086724609403306</v>
+        <v>0.09126175755770426</v>
       </c>
       <c r="X89" t="inlineStr">
         <is>
@@ -8623,7 +8623,7 @@
         </is>
       </c>
       <c r="Y89">
-        <v>0.90282155624708</v>
+        <v>0.892562220380636</v>
       </c>
       <c r="Z89">
         <v>0</v>
@@ -8631,22 +8631,22 @@
     </row>
     <row r="90">
       <c r="A90">
-        <v>0.88</v>
+        <v>0.89</v>
       </c>
       <c r="B90">
-        <v>0.1081182581043014</v>
+        <v>0.1089161006532724</v>
       </c>
       <c r="C90">
-        <v>-9854.559719260797</v>
+        <v>-10639.23362982415</v>
       </c>
       <c r="D90">
-        <v>32007.6042807392</v>
+        <v>31761.68337017585</v>
       </c>
       <c r="E90">
-        <v>39616.664</v>
+        <v>40155.417</v>
       </c>
       <c r="F90">
-        <v>47410.264</v>
+        <v>47949.017</v>
       </c>
       <c r="G90">
         <v>5548.1</v>
@@ -8667,37 +8667,37 @@
         <v>5314.3</v>
       </c>
       <c r="M90">
-        <v>5953.982678914754</v>
+        <v>6021.641572993331</v>
       </c>
       <c r="N90">
-        <v>-639.6826789147535</v>
+        <v>-707.3415729933313</v>
       </c>
       <c r="O90">
-        <v>-195.8708362836975</v>
+        <v>-216.5879896505581</v>
       </c>
       <c r="P90">
-        <v>-443.811842631056</v>
+        <v>-490.7535833427733</v>
       </c>
       <c r="Q90">
-        <v>-14.11184263105599</v>
+        <v>-61.05358334277327</v>
       </c>
       <c r="R90">
-        <v>7.333333333333334</v>
+        <v>8.090909090909092</v>
       </c>
       <c r="S90">
-        <v>0.2317325954460137</v>
+        <v>0.2486355586683786</v>
       </c>
       <c r="T90">
-        <v>3.527072629266207</v>
+        <v>3.847715595563135</v>
       </c>
       <c r="U90">
         <v>0.125584254897099</v>
       </c>
       <c r="V90">
-        <v>0.2733025518805508</v>
+        <v>0.2702317366908816</v>
       </c>
       <c r="W90">
-        <v>0.09126175755770426</v>
+        <v>0.09164740359522555</v>
       </c>
       <c r="X90" t="inlineStr">
         <is>
@@ -8705,7 +8705,7 @@
         </is>
       </c>
       <c r="Y90">
-        <v>0.892562220380636</v>
+        <v>0.882533431387595</v>
       </c>
       <c r="Z90">
         <v>0</v>
@@ -8713,22 +8713,22 @@
     </row>
     <row r="91">
       <c r="A91">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="B91">
-        <v>0.1089161006532724</v>
+        <v>0.1097139432022434</v>
       </c>
       <c r="C91">
-        <v>-10639.23362982415</v>
+        <v>-11420.15743283221</v>
       </c>
       <c r="D91">
-        <v>31761.68337017585</v>
+        <v>31519.51256716779</v>
       </c>
       <c r="E91">
-        <v>40155.417</v>
+        <v>40694.17</v>
       </c>
       <c r="F91">
-        <v>47949.017</v>
+        <v>48487.77</v>
       </c>
       <c r="G91">
         <v>5548.1</v>
@@ -8749,37 +8749,37 @@
         <v>5314.3</v>
       </c>
       <c r="M91">
-        <v>6021.641572993331</v>
+        <v>6089.300467071907</v>
       </c>
       <c r="N91">
-        <v>-707.3415729933313</v>
+        <v>-775.0004670719072</v>
       </c>
       <c r="O91">
-        <v>-216.5879896505581</v>
+        <v>-237.305143017418</v>
       </c>
       <c r="P91">
-        <v>-490.7535833427733</v>
+        <v>-537.6953240544892</v>
       </c>
       <c r="Q91">
-        <v>-61.05358334277327</v>
+        <v>-107.9953240544892</v>
       </c>
       <c r="R91">
-        <v>8.090909090909092</v>
+        <v>9.000000000000002</v>
       </c>
       <c r="S91">
-        <v>0.2486355586683786</v>
+        <v>0.2689191145352164</v>
       </c>
       <c r="T91">
-        <v>3.847715595563135</v>
+        <v>4.232487155119449</v>
       </c>
       <c r="U91">
         <v>0.125584254897099</v>
       </c>
       <c r="V91">
-        <v>0.2702317366908816</v>
+        <v>0.2672291618387607</v>
       </c>
       <c r="W91">
-        <v>0.09164740359522555</v>
+        <v>0.09202447972080191</v>
       </c>
       <c r="X91" t="inlineStr">
         <is>
@@ -8787,7 +8787,7 @@
         </is>
       </c>
       <c r="Y91">
-        <v>0.882533431387595</v>
+        <v>0.8727275043721774</v>
       </c>
       <c r="Z91">
         <v>0</v>
@@ -8795,22 +8795,22 @@
     </row>
     <row r="92">
       <c r="A92">
-        <v>0.9</v>
+        <v>0.91</v>
       </c>
       <c r="B92">
-        <v>0.1097139432022434</v>
+        <v>0.1105117857512144</v>
       </c>
       <c r="C92">
-        <v>-11420.15743283221</v>
+        <v>-12197.41625864644</v>
       </c>
       <c r="D92">
-        <v>31519.51256716779</v>
+        <v>31281.00674135355</v>
       </c>
       <c r="E92">
-        <v>40694.17</v>
+        <v>41232.923</v>
       </c>
       <c r="F92">
-        <v>48487.77</v>
+        <v>49026.523</v>
       </c>
       <c r="G92">
         <v>5548.1</v>
@@ -8831,37 +8831,37 @@
         <v>5314.3</v>
       </c>
       <c r="M92">
-        <v>6089.300467071907</v>
+        <v>6156.959361150485</v>
       </c>
       <c r="N92">
-        <v>-775.0004670719072</v>
+        <v>-842.659361150485</v>
       </c>
       <c r="O92">
-        <v>-237.305143017418</v>
+        <v>-258.0222963842785</v>
       </c>
       <c r="P92">
-        <v>-537.6953240544892</v>
+        <v>-584.6370647662064</v>
       </c>
       <c r="Q92">
-        <v>-107.9953240544892</v>
+        <v>-154.9370647662064</v>
       </c>
       <c r="R92">
-        <v>9.000000000000002</v>
+        <v>10.11111111111111</v>
       </c>
       <c r="S92">
-        <v>0.2689191145352164</v>
+        <v>0.2937101272613517</v>
       </c>
       <c r="T92">
-        <v>4.232487155119449</v>
+        <v>4.702763505688278</v>
       </c>
       <c r="U92">
         <v>0.125584254897099</v>
       </c>
       <c r="V92">
-        <v>0.2672291618387607</v>
+        <v>0.2642925776427303</v>
       </c>
       <c r="W92">
-        <v>0.09202447972080191</v>
+        <v>0.092393268459003</v>
       </c>
       <c r="X92" t="inlineStr">
         <is>
@@ -8869,7 +8869,7 @@
         </is>
       </c>
       <c r="Y92">
-        <v>0.8727275043721774</v>
+        <v>0.8631370922362193</v>
       </c>
       <c r="Z92">
         <v>0</v>
@@ -8877,22 +8877,22 @@
     </row>
     <row r="93">
       <c r="A93">
-        <v>0.91</v>
+        <v>0.92</v>
       </c>
       <c r="B93">
-        <v>0.1105117857512144</v>
+        <v>0.1113096283001853</v>
       </c>
       <c r="C93">
-        <v>-12197.41625864644</v>
+        <v>-12971.09268027894</v>
       </c>
       <c r="D93">
-        <v>31281.00674135355</v>
+        <v>31046.08331972106</v>
       </c>
       <c r="E93">
-        <v>41232.923</v>
+        <v>41771.676</v>
       </c>
       <c r="F93">
-        <v>49026.523</v>
+        <v>49565.276</v>
       </c>
       <c r="G93">
         <v>5548.1</v>
@@ -8913,37 +8913,37 @@
         <v>5314.3</v>
       </c>
       <c r="M93">
-        <v>6156.959361150485</v>
+        <v>6224.618255229061</v>
       </c>
       <c r="N93">
-        <v>-842.659361150485</v>
+        <v>-910.3182552290609</v>
       </c>
       <c r="O93">
-        <v>-258.0222963842785</v>
+        <v>-278.7394497511385</v>
       </c>
       <c r="P93">
-        <v>-584.6370647662064</v>
+        <v>-631.5788054779225</v>
       </c>
       <c r="Q93">
-        <v>-154.9370647662064</v>
+        <v>-201.8788054779225</v>
       </c>
       <c r="R93">
-        <v>10.11111111111111</v>
+        <v>11.50000000000001</v>
       </c>
       <c r="S93">
-        <v>0.2937101272613517</v>
+        <v>0.3246988931690206</v>
       </c>
       <c r="T93">
-        <v>4.702763505688278</v>
+        <v>5.290608943899312</v>
       </c>
       <c r="U93">
         <v>0.125584254897099</v>
       </c>
       <c r="V93">
-        <v>0.2642925776427303</v>
+        <v>0.2614198322335703</v>
       </c>
       <c r="W93">
-        <v>0.092393268459003</v>
+        <v>0.09275404005072141</v>
       </c>
       <c r="X93" t="inlineStr">
         <is>
@@ -8951,7 +8951,7 @@
         </is>
       </c>
       <c r="Y93">
-        <v>0.8631370922362193</v>
+        <v>0.8537551673206083</v>
       </c>
       <c r="Z93">
         <v>0</v>
@@ -8959,22 +8959,22 @@
     </row>
     <row r="94">
       <c r="A94">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="B94">
-        <v>0.1113096283001853</v>
+        <v>0.1121074708491563</v>
       </c>
       <c r="C94">
-        <v>-12971.09268027894</v>
+        <v>-13741.26680870631</v>
       </c>
       <c r="D94">
-        <v>31046.08331972106</v>
+        <v>30814.66219129368</v>
       </c>
       <c r="E94">
-        <v>41771.676</v>
+        <v>42310.429</v>
       </c>
       <c r="F94">
-        <v>49565.276</v>
+        <v>50104.02899999999</v>
       </c>
       <c r="G94">
         <v>5548.1</v>
@@ -8995,37 +8995,37 @@
         <v>5314.3</v>
       </c>
       <c r="M94">
-        <v>6224.618255229061</v>
+        <v>6292.277149307638</v>
       </c>
       <c r="N94">
-        <v>-910.3182552290609</v>
+        <v>-977.9771493076378</v>
       </c>
       <c r="O94">
-        <v>-278.7394497511385</v>
+        <v>-299.4566031179987</v>
       </c>
       <c r="P94">
-        <v>-631.5788054779225</v>
+        <v>-678.520546189639</v>
       </c>
       <c r="Q94">
-        <v>-201.8788054779225</v>
+        <v>-248.8205461896391</v>
       </c>
       <c r="R94">
-        <v>11.50000000000001</v>
+        <v>13.2857142857143</v>
       </c>
       <c r="S94">
-        <v>0.3246988931690206</v>
+        <v>0.3645415921931665</v>
       </c>
       <c r="T94">
-        <v>5.290608943899312</v>
+        <v>6.046410221599215</v>
       </c>
       <c r="U94">
         <v>0.125584254897099</v>
       </c>
       <c r="V94">
-        <v>0.2614198322335703</v>
+        <v>0.2586088662955749</v>
       </c>
       <c r="W94">
-        <v>0.09275404005072141</v>
+        <v>0.09310705311358569</v>
       </c>
       <c r="X94" t="inlineStr">
         <is>
@@ -9033,7 +9033,7 @@
         </is>
       </c>
       <c r="Y94">
-        <v>0.8537551673206083</v>
+        <v>0.8445750042311394</v>
       </c>
       <c r="Z94">
         <v>0</v>
@@ -9041,22 +9041,22 @@
     </row>
     <row r="95">
       <c r="A95">
-        <v>0.93</v>
+        <v>0.9400000000000001</v>
       </c>
       <c r="B95">
-        <v>0.1121074708491563</v>
+        <v>0.1129053133981273</v>
       </c>
       <c r="C95">
-        <v>-13741.26680870631</v>
+        <v>-14508.01638395225</v>
       </c>
       <c r="D95">
-        <v>30814.66219129368</v>
+        <v>30586.66561604775</v>
       </c>
       <c r="E95">
-        <v>42310.429</v>
+        <v>42849.182</v>
       </c>
       <c r="F95">
-        <v>50104.02899999999</v>
+        <v>50642.782</v>
       </c>
       <c r="G95">
         <v>5548.1</v>
@@ -9077,37 +9077,37 @@
         <v>5314.3</v>
       </c>
       <c r="M95">
-        <v>6292.277149307638</v>
+        <v>6359.936043386215</v>
       </c>
       <c r="N95">
-        <v>-977.9771493076378</v>
+        <v>-1045.636043386215</v>
       </c>
       <c r="O95">
-        <v>-299.4566031179987</v>
+        <v>-320.1737564848589</v>
       </c>
       <c r="P95">
-        <v>-678.520546189639</v>
+        <v>-725.4622869013557</v>
       </c>
       <c r="Q95">
-        <v>-248.8205461896391</v>
+        <v>-295.7622869013557</v>
       </c>
       <c r="R95">
-        <v>13.2857142857143</v>
+        <v>15.66666666666668</v>
       </c>
       <c r="S95">
-        <v>0.3645415921931665</v>
+        <v>0.4176651908920277</v>
       </c>
       <c r="T95">
-        <v>6.046410221599215</v>
+        <v>7.05414525853242</v>
       </c>
       <c r="U95">
         <v>0.125584254897099</v>
       </c>
       <c r="V95">
-        <v>0.2586088662955749</v>
+        <v>0.2558577081434943</v>
       </c>
       <c r="W95">
-        <v>0.09310705311358569</v>
+        <v>0.09345255526021883</v>
       </c>
       <c r="X95" t="inlineStr">
         <is>
@@ -9115,7 +9115,7 @@
         </is>
       </c>
       <c r="Y95">
-        <v>0.8445750042311394</v>
+        <v>0.8355901637605954</v>
       </c>
       <c r="Z95">
         <v>0</v>
@@ -9123,22 +9123,22 @@
     </row>
     <row r="96">
       <c r="A96">
-        <v>0.9400000000000001</v>
+        <v>0.9500000000000001</v>
       </c>
       <c r="B96">
-        <v>0.1129053133981273</v>
+        <v>0.1137031559470983</v>
       </c>
       <c r="C96">
-        <v>-14508.01638395225</v>
+        <v>-15271.41686215629</v>
       </c>
       <c r="D96">
-        <v>30586.66561604775</v>
+        <v>30362.0181378437</v>
       </c>
       <c r="E96">
-        <v>42849.182</v>
+        <v>43387.935</v>
       </c>
       <c r="F96">
-        <v>50642.782</v>
+        <v>51181.535</v>
       </c>
       <c r="G96">
         <v>5548.1</v>
@@ -9159,37 +9159,37 @@
         <v>5314.3</v>
       </c>
       <c r="M96">
-        <v>6359.936043386215</v>
+        <v>6427.594937464791</v>
       </c>
       <c r="N96">
-        <v>-1045.636043386215</v>
+        <v>-1113.294937464791</v>
       </c>
       <c r="O96">
-        <v>-320.1737564848589</v>
+        <v>-340.8909098517189</v>
       </c>
       <c r="P96">
-        <v>-725.4622869013557</v>
+        <v>-772.4040276130717</v>
       </c>
       <c r="Q96">
-        <v>-295.7622869013557</v>
+        <v>-342.7040276130717</v>
       </c>
       <c r="R96">
-        <v>15.66666666666668</v>
+        <v>19.00000000000003</v>
       </c>
       <c r="S96">
-        <v>0.4176651908920277</v>
+        <v>0.4920382290704334</v>
       </c>
       <c r="T96">
-        <v>7.05414525853242</v>
+        <v>8.464974310238908</v>
       </c>
       <c r="U96">
         <v>0.125584254897099</v>
       </c>
       <c r="V96">
-        <v>0.2558577081434943</v>
+        <v>0.253164469110405</v>
       </c>
       <c r="W96">
-        <v>0.09345255526021883</v>
+        <v>0.09379078367744913</v>
       </c>
       <c r="X96" t="inlineStr">
         <is>
@@ -9197,7 +9197,7 @@
         </is>
       </c>
       <c r="Y96">
-        <v>0.8355901637605954</v>
+        <v>0.8267944778262735</v>
       </c>
       <c r="Z96">
         <v>0</v>
@@ -9205,22 +9205,22 @@
     </row>
     <row r="97">
       <c r="A97">
-        <v>0.9500000000000001</v>
+        <v>0.9600000000000001</v>
       </c>
       <c r="B97">
-        <v>0.1137031559470983</v>
+        <v>0.1145009984960693</v>
       </c>
       <c r="C97">
-        <v>-15271.41686215629</v>
+        <v>-16031.54149883362</v>
       </c>
       <c r="D97">
-        <v>30362.0181378437</v>
+        <v>30140.64650116638</v>
       </c>
       <c r="E97">
-        <v>43387.935</v>
+        <v>43926.688</v>
       </c>
       <c r="F97">
-        <v>51181.535</v>
+        <v>51720.288</v>
       </c>
       <c r="G97">
         <v>5548.1</v>
@@ -9241,37 +9241,37 @@
         <v>5314.3</v>
       </c>
       <c r="M97">
-        <v>6427.594937464791</v>
+        <v>6495.253831543369</v>
       </c>
       <c r="N97">
-        <v>-1113.294937464791</v>
+        <v>-1180.953831543368</v>
       </c>
       <c r="O97">
-        <v>-340.8909098517189</v>
+        <v>-361.6080632185794</v>
       </c>
       <c r="P97">
-        <v>-772.4040276130717</v>
+        <v>-819.3457683247889</v>
       </c>
       <c r="Q97">
-        <v>-342.7040276130717</v>
+        <v>-389.6457683247889</v>
       </c>
       <c r="R97">
-        <v>19.00000000000003</v>
+        <v>24.00000000000005</v>
       </c>
       <c r="S97">
-        <v>0.4920382290704334</v>
+        <v>0.603597786338042</v>
       </c>
       <c r="T97">
-        <v>8.464974310238908</v>
+        <v>10.58121788779864</v>
       </c>
       <c r="U97">
         <v>0.125584254897099</v>
       </c>
       <c r="V97">
-        <v>0.253164469110405</v>
+        <v>0.2505273392238382</v>
       </c>
       <c r="W97">
-        <v>0.09379078367744913</v>
+        <v>0.09412196566932049</v>
       </c>
       <c r="X97" t="inlineStr">
         <is>
@@ -9279,7 +9279,7 @@
         </is>
       </c>
       <c r="Y97">
-        <v>0.8267944778262735</v>
+        <v>0.8181820353489162</v>
       </c>
       <c r="Z97">
         <v>0</v>
@@ -9287,22 +9287,22 @@
     </row>
     <row r="98">
       <c r="A98">
-        <v>0.96</v>
+        <v>0.97</v>
       </c>
       <c r="B98">
-        <v>0.1145009984960693</v>
+        <v>0.1152988410450403</v>
       </c>
       <c r="C98">
-        <v>-16031.5414988336</v>
+        <v>-16788.4614285189</v>
       </c>
       <c r="D98">
-        <v>30140.64650116639</v>
+        <v>29922.4795714811</v>
       </c>
       <c r="E98">
-        <v>43926.68799999999</v>
+        <v>44465.441</v>
       </c>
       <c r="F98">
-        <v>51720.28799999999</v>
+        <v>52259.041</v>
       </c>
       <c r="G98">
         <v>5548.1</v>
@@ -9323,37 +9323,37 @@
         <v>5314.3</v>
       </c>
       <c r="M98">
-        <v>6495.253831543368</v>
+        <v>6562.912725621944</v>
       </c>
       <c r="N98">
-        <v>-1180.953831543367</v>
+        <v>-1248.612725621944</v>
       </c>
       <c r="O98">
-        <v>-361.6080632185792</v>
+        <v>-382.3252165854394</v>
       </c>
       <c r="P98">
-        <v>-819.3457683247882</v>
+        <v>-866.2875090365048</v>
       </c>
       <c r="Q98">
-        <v>-389.6457683247882</v>
+        <v>-436.5875090365049</v>
       </c>
       <c r="R98">
-        <v>23.99999999999998</v>
+        <v>32.33333333333331</v>
       </c>
       <c r="S98">
-        <v>0.6035977863380405</v>
+        <v>0.7895303817840541</v>
       </c>
       <c r="T98">
-        <v>10.58121788779861</v>
+        <v>14.10829051706482</v>
       </c>
       <c r="U98">
         <v>0.125584254897099</v>
       </c>
       <c r="V98">
-        <v>0.2505273392238382</v>
+        <v>0.2479445831493657</v>
       </c>
       <c r="W98">
-        <v>0.09412196566932048</v>
+        <v>0.09444631916651408</v>
       </c>
       <c r="X98" t="inlineStr">
         <is>
@@ -9361,7 +9361,7 @@
         </is>
       </c>
       <c r="Y98">
-        <v>0.8181820353489164</v>
+        <v>0.8097471690051131</v>
       </c>
       <c r="Z98">
         <v>0</v>
@@ -9369,22 +9369,22 @@
     </row>
     <row r="99">
       <c r="A99">
-        <v>0.97</v>
+        <v>0.98</v>
       </c>
       <c r="B99">
-        <v>0.1152988410450403</v>
+        <v>0.1160966835940113</v>
       </c>
       <c r="C99">
-        <v>-16788.4614285189</v>
+        <v>-17542.24574097615</v>
       </c>
       <c r="D99">
-        <v>29922.4795714811</v>
+        <v>29707.44825902385</v>
       </c>
       <c r="E99">
-        <v>44465.441</v>
+        <v>45004.194</v>
       </c>
       <c r="F99">
-        <v>52259.041</v>
+        <v>52797.79399999999</v>
       </c>
       <c r="G99">
         <v>5548.1</v>
@@ -9405,37 +9405,37 @@
         <v>5314.3</v>
       </c>
       <c r="M99">
-        <v>6562.912725621944</v>
+        <v>6630.571619700521</v>
       </c>
       <c r="N99">
-        <v>-1248.612725621944</v>
+        <v>-1316.271619700521</v>
       </c>
       <c r="O99">
-        <v>-382.3252165854394</v>
+        <v>-403.0423699522996</v>
       </c>
       <c r="P99">
-        <v>-866.2875090365048</v>
+        <v>-913.2292497482215</v>
       </c>
       <c r="Q99">
-        <v>-436.5875090365049</v>
+        <v>-483.5292497482215</v>
       </c>
       <c r="R99">
-        <v>32.33333333333331</v>
+        <v>48.99999999999996</v>
       </c>
       <c r="S99">
-        <v>0.7895303817840541</v>
+        <v>1.161395572676081</v>
       </c>
       <c r="T99">
-        <v>14.10829051706482</v>
+        <v>21.16243577559722</v>
       </c>
       <c r="U99">
         <v>0.125584254897099</v>
       </c>
       <c r="V99">
-        <v>0.2479445831493657</v>
+        <v>0.2454145363825354</v>
       </c>
       <c r="W99">
-        <v>0.09444631916651408</v>
+        <v>0.09476405320458127</v>
       </c>
       <c r="X99" t="inlineStr">
         <is>
@@ -9443,7 +9443,7 @@
         </is>
       </c>
       <c r="Y99">
-        <v>0.8097471690051131</v>
+        <v>0.8014844427907752</v>
       </c>
       <c r="Z99">
         <v>0</v>
@@ -9451,22 +9451,22 @@
     </row>
     <row r="100">
       <c r="A100">
-        <v>0.98</v>
+        <v>0.99</v>
       </c>
       <c r="B100">
-        <v>0.1160966835940113</v>
+        <v>0.2010676310466908</v>
       </c>
       <c r="C100">
-        <v>-17542.24574097615</v>
+        <v>-30960.3233334473</v>
       </c>
       <c r="D100">
-        <v>29707.44825902385</v>
+        <v>16828.1236665527</v>
       </c>
       <c r="E100">
-        <v>45004.194</v>
+        <v>45542.947</v>
       </c>
       <c r="F100">
-        <v>52797.79399999999</v>
+        <v>53336.547</v>
       </c>
       <c r="G100">
         <v>5548.1</v>
@@ -9487,129 +9487,47 @@
         <v>5314.3</v>
       </c>
       <c r="M100">
-        <v>6630.571619700521</v>
+        <v>11082.4946771791</v>
       </c>
       <c r="N100">
-        <v>-1316.271619700521</v>
+        <v>-5768.194677179098</v>
       </c>
       <c r="O100">
-        <v>-403.0423699522996</v>
+        <v>-1766.22121015224</v>
       </c>
       <c r="P100">
-        <v>-913.2292497482215</v>
+        <v>-4001.973467026858</v>
       </c>
       <c r="Q100">
-        <v>-483.5292497482215</v>
+        <v>-3572.273467026858</v>
       </c>
       <c r="R100">
-        <v>48.99999999999996</v>
+        <v>98.99999999999991</v>
       </c>
       <c r="S100">
-        <v>1.161395572676081</v>
+        <v>2.556501635723011</v>
       </c>
       <c r="T100">
-        <v>21.16243577559722</v>
+        <v>47.6270822680133</v>
       </c>
       <c r="U100">
-        <v>0.125584254897099</v>
+        <v>0.207784254897099</v>
       </c>
       <c r="V100">
-        <v>0.2454145363825354</v>
+        <v>0.1468296360521413</v>
       </c>
       <c r="W100">
-        <v>0.09476405320458127</v>
+        <v>0.1772753683731925</v>
       </c>
       <c r="X100" t="inlineStr">
         <is>
-          <t>Caa/CCC</t>
+          <t>C2/C</t>
         </is>
       </c>
       <c r="Y100">
-        <v>0.8014844427907752</v>
+        <v>0.4795219988639493</v>
       </c>
       <c r="Z100">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101">
-        <v>0.99</v>
-      </c>
-      <c r="B101">
-        <v>0.2010676310466908</v>
-      </c>
-      <c r="C101">
-        <v>-30960.3233334473</v>
-      </c>
-      <c r="D101">
-        <v>16828.1236665527</v>
-      </c>
-      <c r="E101">
-        <v>45542.947</v>
-      </c>
-      <c r="F101">
-        <v>53336.547</v>
-      </c>
-      <c r="G101">
-        <v>5548.1</v>
-      </c>
-      <c r="H101">
-        <v>46081.7</v>
-      </c>
-      <c r="I101">
-        <v>0</v>
-      </c>
-      <c r="J101">
-        <v>5744</v>
-      </c>
-      <c r="K101">
-        <v>429.7</v>
-      </c>
-      <c r="L101">
-        <v>5314.3</v>
-      </c>
-      <c r="M101">
-        <v>11082.4946771791</v>
-      </c>
-      <c r="N101">
-        <v>-5768.194677179098</v>
-      </c>
-      <c r="O101">
-        <v>-1766.22121015224</v>
-      </c>
-      <c r="P101">
-        <v>-4001.973467026858</v>
-      </c>
-      <c r="Q101">
-        <v>-3572.273467026858</v>
-      </c>
-      <c r="R101">
-        <v>98.99999999999991</v>
-      </c>
-      <c r="S101">
-        <v>2.556501635723011</v>
-      </c>
-      <c r="T101">
-        <v>47.6270822680133</v>
-      </c>
-      <c r="U101">
-        <v>0.207784254897099</v>
-      </c>
-      <c r="V101">
-        <v>0.1468296360521413</v>
-      </c>
-      <c r="W101">
-        <v>0.1772753683731925</v>
-      </c>
-      <c r="X101" t="inlineStr">
-        <is>
-          <t>C2/C</t>
-        </is>
-      </c>
-      <c r="Y101">
-        <v>0.4795219988639493</v>
-      </c>
-      <c r="Z101">
         <v>0</v>
       </c>
     </row>
